--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB9AA3B-B164-4E25-96CA-88E38CBBE3E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020DE1C6-C5A5-422C-A5AC-08B08A2519F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -376,7 +376,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -431,15 +431,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -459,18 +456,23 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -542,7 +544,7 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaEventosV4" displayName="TablaEventosV4" ref="A1:J16">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Área Solicitante"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="N° OT"/>
@@ -706,10 +708,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J460"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="20.125" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -753,10 +755,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="15">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -785,10 +787,10 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="15">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -817,10 +819,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -849,10 +851,10 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -881,10 +883,10 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="15">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -911,10 +913,10 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="15">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -939,10 +941,10 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="15">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -971,10 +973,10 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="15">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1003,10 +1005,10 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="15">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -1035,10 +1037,10 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="143.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1067,10 +1069,10 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="228.75">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -1099,10 +1101,10 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="200.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -1131,10 +1133,10 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="129">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>64</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1163,86 +1165,1418 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="270.75">
-      <c r="A15" s="11">
+      <c r="A15" s="13">
         <v>46177</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="270.75">
-      <c r="A16" s="11">
+      <c r="A16" s="13">
         <v>46178</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="I16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="J16" s="7" t="s">
         <v>23</v>
       </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="14"/>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="14"/>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="14"/>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="14"/>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="14"/>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="14"/>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="14"/>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="14"/>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="14"/>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="14"/>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="14"/>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="14"/>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="14"/>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="14"/>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="14"/>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="14"/>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="14"/>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="14"/>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="14"/>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="14"/>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="14"/>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="14"/>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="14"/>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="14"/>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="14"/>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="14"/>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="14"/>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="14"/>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="14"/>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="14"/>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="14"/>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="14"/>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="14"/>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="14"/>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="14"/>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="14"/>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="14"/>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="14"/>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="14"/>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="14"/>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="14"/>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="14"/>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="14"/>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="14"/>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="14"/>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="14"/>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="14"/>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="14"/>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="14"/>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="14"/>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="14"/>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="14"/>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="14"/>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="14"/>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="14"/>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="14"/>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="14"/>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="14"/>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="14"/>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="14"/>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="14"/>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="14"/>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="14"/>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="14"/>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="14"/>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="14"/>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="14"/>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="14"/>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="14"/>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="14"/>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="14"/>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="14"/>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="14"/>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="14"/>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="14"/>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="14"/>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="14"/>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="14"/>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="14"/>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="14"/>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="14"/>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="14"/>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="14"/>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="14"/>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="14"/>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="14"/>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="14"/>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="14"/>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="14"/>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="14"/>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="14"/>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="14"/>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="14"/>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="14"/>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="14"/>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="14"/>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="14"/>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="14"/>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="14"/>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="14"/>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="14"/>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="14"/>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="14"/>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="14"/>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="14"/>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="14"/>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="14"/>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="14"/>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="14"/>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="14"/>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="14"/>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="14"/>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="14"/>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="14"/>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="14"/>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="14"/>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="14"/>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="14"/>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="14"/>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="14"/>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="14"/>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="14"/>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="14"/>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="14"/>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="14"/>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="14"/>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="14"/>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="14"/>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="14"/>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="14"/>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="14"/>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="14"/>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="14"/>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="14"/>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="14"/>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="14"/>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="14"/>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="14"/>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="14"/>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="14"/>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="14"/>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="14"/>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="14"/>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="14"/>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="12"/>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="12"/>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="12"/>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="12"/>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="12"/>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="12"/>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="12"/>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="12"/>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="12"/>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="12"/>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="12"/>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" s="12"/>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="12"/>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="12"/>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" s="12"/>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="12"/>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="12"/>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="12"/>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="12"/>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="12"/>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="12"/>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="12"/>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" s="12"/>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="12"/>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" s="12"/>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" s="12"/>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" s="12"/>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" s="12"/>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" s="12"/>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" s="12"/>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" s="12"/>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="12"/>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" s="12"/>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" s="12"/>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" s="12"/>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" s="12"/>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" s="12"/>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" s="12"/>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" s="12"/>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" s="12"/>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" s="12"/>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" s="12"/>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" s="12"/>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" s="12"/>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" s="12"/>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" s="12"/>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" s="12"/>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" s="12"/>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" s="12"/>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" s="12"/>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="12"/>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" s="12"/>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" s="12"/>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="12"/>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" s="12"/>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" s="12"/>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" s="12"/>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" s="12"/>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" s="12"/>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" s="12"/>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="12"/>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" s="12"/>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" s="12"/>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="12"/>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="12"/>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" s="12"/>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" s="12"/>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="12"/>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="12"/>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" s="12"/>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" s="12"/>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="12"/>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" s="12"/>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="12"/>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" s="12"/>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="12"/>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" s="12"/>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" s="12"/>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" s="12"/>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" s="12"/>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" s="12"/>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" s="12"/>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" s="12"/>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" s="12"/>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" s="12"/>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="12"/>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="12"/>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" s="12"/>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" s="12"/>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" s="12"/>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" s="12"/>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252" s="12"/>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" s="12"/>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" s="12"/>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" s="12"/>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" s="12"/>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" s="12"/>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" s="12"/>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" s="12"/>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260" s="12"/>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" s="12"/>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262" s="12"/>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263" s="12"/>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264" s="12"/>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265" s="12"/>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266" s="12"/>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" s="12"/>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268" s="12"/>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269" s="12"/>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" s="12"/>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" s="12"/>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" s="12"/>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273" s="12"/>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274" s="12"/>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275" s="12"/>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276" s="12"/>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277" s="12"/>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278" s="12"/>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279" s="12"/>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280" s="12"/>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281" s="12"/>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282" s="12"/>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283" s="12"/>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284" s="12"/>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285" s="12"/>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286" s="12"/>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287" s="12"/>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288" s="12"/>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289" s="12"/>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290" s="12"/>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291" s="12"/>
+    </row>
+    <row r="292" spans="1:1">
+      <c r="A292" s="12"/>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293" s="12"/>
+    </row>
+    <row r="294" spans="1:1">
+      <c r="A294" s="12"/>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295" s="12"/>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296" s="12"/>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297" s="12"/>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298" s="12"/>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299" s="12"/>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300" s="12"/>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301" s="12"/>
+    </row>
+    <row r="302" spans="1:1">
+      <c r="A302" s="12"/>
+    </row>
+    <row r="303" spans="1:1">
+      <c r="A303" s="12"/>
+    </row>
+    <row r="304" spans="1:1">
+      <c r="A304" s="12"/>
+    </row>
+    <row r="305" spans="1:1">
+      <c r="A305" s="12"/>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306" s="12"/>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307" s="12"/>
+    </row>
+    <row r="308" spans="1:1">
+      <c r="A308" s="12"/>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309" s="12"/>
+    </row>
+    <row r="310" spans="1:1">
+      <c r="A310" s="12"/>
+    </row>
+    <row r="311" spans="1:1">
+      <c r="A311" s="12"/>
+    </row>
+    <row r="312" spans="1:1">
+      <c r="A312" s="12"/>
+    </row>
+    <row r="313" spans="1:1">
+      <c r="A313" s="12"/>
+    </row>
+    <row r="314" spans="1:1">
+      <c r="A314" s="12"/>
+    </row>
+    <row r="315" spans="1:1">
+      <c r="A315" s="12"/>
+    </row>
+    <row r="316" spans="1:1">
+      <c r="A316" s="12"/>
+    </row>
+    <row r="317" spans="1:1">
+      <c r="A317" s="12"/>
+    </row>
+    <row r="318" spans="1:1">
+      <c r="A318" s="12"/>
+    </row>
+    <row r="319" spans="1:1">
+      <c r="A319" s="12"/>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320" s="12"/>
+    </row>
+    <row r="321" spans="1:1">
+      <c r="A321" s="12"/>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322" s="12"/>
+    </row>
+    <row r="323" spans="1:1">
+      <c r="A323" s="12"/>
+    </row>
+    <row r="324" spans="1:1">
+      <c r="A324" s="12"/>
+    </row>
+    <row r="325" spans="1:1">
+      <c r="A325" s="12"/>
+    </row>
+    <row r="326" spans="1:1">
+      <c r="A326" s="12"/>
+    </row>
+    <row r="327" spans="1:1">
+      <c r="A327" s="12"/>
+    </row>
+    <row r="328" spans="1:1">
+      <c r="A328" s="12"/>
+    </row>
+    <row r="329" spans="1:1">
+      <c r="A329" s="12"/>
+    </row>
+    <row r="330" spans="1:1">
+      <c r="A330" s="12"/>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331" s="12"/>
+    </row>
+    <row r="332" spans="1:1">
+      <c r="A332" s="12"/>
+    </row>
+    <row r="333" spans="1:1">
+      <c r="A333" s="12"/>
+    </row>
+    <row r="334" spans="1:1">
+      <c r="A334" s="12"/>
+    </row>
+    <row r="335" spans="1:1">
+      <c r="A335" s="12"/>
+    </row>
+    <row r="336" spans="1:1">
+      <c r="A336" s="12"/>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337" s="12"/>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338" s="12"/>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339" s="12"/>
+    </row>
+    <row r="340" spans="1:1">
+      <c r="A340" s="12"/>
+    </row>
+    <row r="341" spans="1:1">
+      <c r="A341" s="12"/>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342" s="12"/>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343" s="12"/>
+    </row>
+    <row r="344" spans="1:1">
+      <c r="A344" s="12"/>
+    </row>
+    <row r="345" spans="1:1">
+      <c r="A345" s="12"/>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346" s="12"/>
+    </row>
+    <row r="347" spans="1:1">
+      <c r="A347" s="12"/>
+    </row>
+    <row r="348" spans="1:1">
+      <c r="A348" s="12"/>
+    </row>
+    <row r="349" spans="1:1">
+      <c r="A349" s="12"/>
+    </row>
+    <row r="350" spans="1:1">
+      <c r="A350" s="12"/>
+    </row>
+    <row r="351" spans="1:1">
+      <c r="A351" s="12"/>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352" s="12"/>
+    </row>
+    <row r="353" spans="1:1">
+      <c r="A353" s="12"/>
+    </row>
+    <row r="354" spans="1:1">
+      <c r="A354" s="12"/>
+    </row>
+    <row r="355" spans="1:1">
+      <c r="A355" s="12"/>
+    </row>
+    <row r="356" spans="1:1">
+      <c r="A356" s="12"/>
+    </row>
+    <row r="357" spans="1:1">
+      <c r="A357" s="12"/>
+    </row>
+    <row r="358" spans="1:1">
+      <c r="A358" s="12"/>
+    </row>
+    <row r="359" spans="1:1">
+      <c r="A359" s="12"/>
+    </row>
+    <row r="360" spans="1:1">
+      <c r="A360" s="12"/>
+    </row>
+    <row r="361" spans="1:1">
+      <c r="A361" s="12"/>
+    </row>
+    <row r="362" spans="1:1">
+      <c r="A362" s="12"/>
+    </row>
+    <row r="363" spans="1:1">
+      <c r="A363" s="12"/>
+    </row>
+    <row r="364" spans="1:1">
+      <c r="A364" s="12"/>
+    </row>
+    <row r="365" spans="1:1">
+      <c r="A365" s="12"/>
+    </row>
+    <row r="366" spans="1:1">
+      <c r="A366" s="12"/>
+    </row>
+    <row r="367" spans="1:1">
+      <c r="A367" s="12"/>
+    </row>
+    <row r="368" spans="1:1">
+      <c r="A368" s="12"/>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369" s="12"/>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370" s="12"/>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371" s="12"/>
+    </row>
+    <row r="372" spans="1:1">
+      <c r="A372" s="12"/>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373" s="12"/>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374" s="12"/>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375" s="12"/>
+    </row>
+    <row r="376" spans="1:1">
+      <c r="A376" s="12"/>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377" s="12"/>
+    </row>
+    <row r="378" spans="1:1">
+      <c r="A378" s="12"/>
+    </row>
+    <row r="379" spans="1:1">
+      <c r="A379" s="12"/>
+    </row>
+    <row r="380" spans="1:1">
+      <c r="A380" s="12"/>
+    </row>
+    <row r="381" spans="1:1">
+      <c r="A381" s="12"/>
+    </row>
+    <row r="382" spans="1:1">
+      <c r="A382" s="12"/>
+    </row>
+    <row r="383" spans="1:1">
+      <c r="A383" s="12"/>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384" s="12"/>
+    </row>
+    <row r="385" spans="1:1">
+      <c r="A385" s="12"/>
+    </row>
+    <row r="386" spans="1:1">
+      <c r="A386" s="12"/>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387" s="12"/>
+    </row>
+    <row r="388" spans="1:1">
+      <c r="A388" s="12"/>
+    </row>
+    <row r="389" spans="1:1">
+      <c r="A389" s="12"/>
+    </row>
+    <row r="390" spans="1:1">
+      <c r="A390" s="12"/>
+    </row>
+    <row r="391" spans="1:1">
+      <c r="A391" s="12"/>
+    </row>
+    <row r="392" spans="1:1">
+      <c r="A392" s="12"/>
+    </row>
+    <row r="393" spans="1:1">
+      <c r="A393" s="12"/>
+    </row>
+    <row r="394" spans="1:1">
+      <c r="A394" s="12"/>
+    </row>
+    <row r="395" spans="1:1">
+      <c r="A395" s="12"/>
+    </row>
+    <row r="396" spans="1:1">
+      <c r="A396" s="12"/>
+    </row>
+    <row r="397" spans="1:1">
+      <c r="A397" s="12"/>
+    </row>
+    <row r="398" spans="1:1">
+      <c r="A398" s="12"/>
+    </row>
+    <row r="399" spans="1:1">
+      <c r="A399" s="12"/>
+    </row>
+    <row r="400" spans="1:1">
+      <c r="A400" s="12"/>
+    </row>
+    <row r="401" spans="1:1">
+      <c r="A401" s="12"/>
+    </row>
+    <row r="402" spans="1:1">
+      <c r="A402" s="12"/>
+    </row>
+    <row r="403" spans="1:1">
+      <c r="A403" s="12"/>
+    </row>
+    <row r="404" spans="1:1">
+      <c r="A404" s="12"/>
+    </row>
+    <row r="405" spans="1:1">
+      <c r="A405" s="12"/>
+    </row>
+    <row r="406" spans="1:1">
+      <c r="A406" s="12"/>
+    </row>
+    <row r="407" spans="1:1">
+      <c r="A407" s="12"/>
+    </row>
+    <row r="408" spans="1:1">
+      <c r="A408" s="12"/>
+    </row>
+    <row r="409" spans="1:1">
+      <c r="A409" s="12"/>
+    </row>
+    <row r="410" spans="1:1">
+      <c r="A410" s="12"/>
+    </row>
+    <row r="411" spans="1:1">
+      <c r="A411" s="12"/>
+    </row>
+    <row r="412" spans="1:1">
+      <c r="A412" s="12"/>
+    </row>
+    <row r="413" spans="1:1">
+      <c r="A413" s="12"/>
+    </row>
+    <row r="414" spans="1:1">
+      <c r="A414" s="12"/>
+    </row>
+    <row r="415" spans="1:1">
+      <c r="A415" s="12"/>
+    </row>
+    <row r="416" spans="1:1">
+      <c r="A416" s="12"/>
+    </row>
+    <row r="417" spans="1:1">
+      <c r="A417" s="12"/>
+    </row>
+    <row r="418" spans="1:1">
+      <c r="A418" s="12"/>
+    </row>
+    <row r="419" spans="1:1">
+      <c r="A419" s="12"/>
+    </row>
+    <row r="420" spans="1:1">
+      <c r="A420" s="12"/>
+    </row>
+    <row r="421" spans="1:1">
+      <c r="A421" s="12"/>
+    </row>
+    <row r="422" spans="1:1">
+      <c r="A422" s="12"/>
+    </row>
+    <row r="423" spans="1:1">
+      <c r="A423" s="12"/>
+    </row>
+    <row r="424" spans="1:1">
+      <c r="A424" s="12"/>
+    </row>
+    <row r="425" spans="1:1">
+      <c r="A425" s="12"/>
+    </row>
+    <row r="426" spans="1:1">
+      <c r="A426" s="12"/>
+    </row>
+    <row r="427" spans="1:1">
+      <c r="A427" s="12"/>
+    </row>
+    <row r="428" spans="1:1">
+      <c r="A428" s="12"/>
+    </row>
+    <row r="429" spans="1:1">
+      <c r="A429" s="12"/>
+    </row>
+    <row r="430" spans="1:1">
+      <c r="A430" s="12"/>
+    </row>
+    <row r="431" spans="1:1">
+      <c r="A431" s="12"/>
+    </row>
+    <row r="432" spans="1:1">
+      <c r="A432" s="12"/>
+    </row>
+    <row r="433" spans="1:1">
+      <c r="A433" s="12"/>
+    </row>
+    <row r="434" spans="1:1">
+      <c r="A434" s="12"/>
+    </row>
+    <row r="435" spans="1:1">
+      <c r="A435" s="12"/>
+    </row>
+    <row r="436" spans="1:1">
+      <c r="A436" s="12"/>
+    </row>
+    <row r="437" spans="1:1">
+      <c r="A437" s="12"/>
+    </row>
+    <row r="438" spans="1:1">
+      <c r="A438" s="12"/>
+    </row>
+    <row r="439" spans="1:1">
+      <c r="A439" s="12"/>
+    </row>
+    <row r="440" spans="1:1">
+      <c r="A440" s="12"/>
+    </row>
+    <row r="441" spans="1:1">
+      <c r="A441" s="12"/>
+    </row>
+    <row r="442" spans="1:1">
+      <c r="A442" s="12"/>
+    </row>
+    <row r="443" spans="1:1">
+      <c r="A443" s="12"/>
+    </row>
+    <row r="444" spans="1:1">
+      <c r="A444" s="12"/>
+    </row>
+    <row r="445" spans="1:1">
+      <c r="A445" s="12"/>
+    </row>
+    <row r="446" spans="1:1">
+      <c r="A446" s="12"/>
+    </row>
+    <row r="447" spans="1:1">
+      <c r="A447" s="12"/>
+    </row>
+    <row r="448" spans="1:1">
+      <c r="A448" s="12"/>
+    </row>
+    <row r="449" spans="1:1">
+      <c r="A449" s="12"/>
+    </row>
+    <row r="450" spans="1:1">
+      <c r="A450" s="12"/>
+    </row>
+    <row r="451" spans="1:1">
+      <c r="A451" s="12"/>
+    </row>
+    <row r="452" spans="1:1">
+      <c r="A452" s="12"/>
+    </row>
+    <row r="453" spans="1:1">
+      <c r="A453" s="12"/>
+    </row>
+    <row r="454" spans="1:1">
+      <c r="A454" s="12"/>
+    </row>
+    <row r="455" spans="1:1">
+      <c r="A455" s="12"/>
+    </row>
+    <row r="456" spans="1:1">
+      <c r="A456" s="12"/>
+    </row>
+    <row r="457" spans="1:1">
+      <c r="A457" s="12"/>
+    </row>
+    <row r="458" spans="1:1">
+      <c r="A458" s="12"/>
+    </row>
+    <row r="459" spans="1:1">
+      <c r="A459" s="12"/>
+    </row>
+    <row r="460" spans="1:1">
+      <c r="A460" s="12"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H64">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>H2="Alta"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>H2="Media"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>H2="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J64">
-    <cfRule type="expression" dxfId="1" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>J2="Ejecutado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>J2="Pendiente"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1286,13 +2620,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1361,25 +2695,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="3" spans="1:6" ht="15">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>77</v>
       </c>
       <c r="B4">
@@ -1388,7 +2722,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="15">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>78</v>
       </c>
       <c r="B5">
@@ -1397,7 +2731,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="15">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>79</v>
       </c>
       <c r="B6">
@@ -1406,7 +2740,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="15">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>80</v>
       </c>
       <c r="B7">
@@ -1415,7 +2749,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="15">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>81</v>
       </c>
       <c r="B8">

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020DE1C6-C5A5-422C-A5AC-08B08A2519F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7274A1-A26D-492E-94E0-DBD9A1513892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVENTOS" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="103">
   <si>
     <t>Fecha</t>
   </si>
@@ -238,19 +238,6 @@
   </si>
   <si>
     <t>Ciclo de Conferencias: “Zero Waste: Ecodiseño y Negocios Sostenibles”</t>
-  </si>
-  <si>
-    <t>Requerimiento:
-40 sillas
-Televisor con parante
-Podio
-Equipo de sonido con 2 micrófonos inalámbricos con pilas nuevas
-Extensión eléctrica
-Layout:
-Las sillas se colocarán en formato auditorio orientadas hacia el televisor.
-Se requiere retirar los muebles del hall.
-La exhibición de EKOVA será reubicada temporalmente.
-Se requiere apoyo para el brandeo del espacio en coordinación con @Maria Luisa Leveau Besarez.</t>
   </si>
   <si>
     <t>22/06/2026</t>
@@ -370,13 +357,47 @@
   <si>
     <t xml:space="preserve">Pabellon N </t>
   </si>
+  <si>
+    <t>Requerimiento:
+ 40 sillas
+Televisor con parante
+Podio
+Equipo de sonido con 2 micrófonos inalámbricos con pilas nuevas
+Extensión eléctrica
+Layout:
+Las sillas se colocarán en formato auditorio orientadas hacia el televisor.
+Se requiere retirar los muebles del hall.
+La exhibición de EKOVA será reubicada temporalmente.
+Se requiere apoyo para el brandeo del espacio en coordinación con @Maria Luisa Leveau Besarez.</t>
+  </si>
+  <si>
+    <t>LOTE 28</t>
+  </si>
+  <si>
+    <t>VILLA 2</t>
+  </si>
+  <si>
+    <t>Instalacion de sogas                       estacas para evento</t>
+  </si>
+  <si>
+    <t>Simulacion</t>
+  </si>
+  <si>
+    <t>BLS</t>
+  </si>
+  <si>
+    <t>Pballeon L</t>
+  </si>
+  <si>
+    <t>instalacion de mesas</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -431,7 +452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -456,23 +477,21 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
-    <dxf>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -528,6 +547,9 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -542,9 +564,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaEventosV4" displayName="TablaEventosV4" ref="A1:J16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaEventosV4" displayName="TablaEventosV4" ref="A1:J18">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Área Solicitante"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="N° OT"/>
@@ -727,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -755,7 +777,7 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="15">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="11" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -771,7 +793,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>14</v>
@@ -787,7 +809,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="15">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="11" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -803,7 +825,7 @@
         <v>21</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>22</v>
@@ -819,7 +841,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="11" t="s">
         <v>18</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -835,7 +857,7 @@
         <v>21</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>26</v>
@@ -851,7 +873,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -867,7 +889,7 @@
         <v>29</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>30</v>
@@ -883,7 +905,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="15">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="11" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -913,7 +935,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="15">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -927,7 +949,7 @@
         <v>37</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
@@ -941,7 +963,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="15">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="11" t="s">
         <v>39</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -957,7 +979,7 @@
         <v>41</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>42</v>
@@ -973,7 +995,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="15">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="11" t="s">
         <v>44</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -989,7 +1011,7 @@
         <v>46</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>47</v>
@@ -1005,7 +1027,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="15">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="11" t="s">
         <v>44</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -1021,7 +1043,7 @@
         <v>48</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>47</v>
@@ -1037,7 +1059,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="143.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="11" t="s">
         <v>49</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -1069,7 +1091,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="228.75">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="11" t="s">
         <v>55</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -1101,7 +1123,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="200.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="11" t="s">
         <v>55</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -1120,7 +1142,7 @@
         <v>53</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>15</v>
@@ -1133,26 +1155,26 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="129">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>15</v>
@@ -1165,26 +1187,26 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="270.75">
-      <c r="A15" s="13">
+      <c r="A15" s="11">
         <v>46177</v>
       </c>
       <c r="B15" s="9">
         <v>0.33333333333333331</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="8" t="s">
         <v>84</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>85</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>15</v>
@@ -1197,26 +1219,26 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="270.75">
-      <c r="A16" s="13">
+      <c r="A16" s="11">
         <v>46178</v>
       </c>
       <c r="B16" s="9">
         <v>0.33333333333333331</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="F16" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="8" t="s">
         <v>84</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>85</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>15</v>
@@ -1228,1355 +1250,1413 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="14"/>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="14"/>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="14"/>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="14"/>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="14"/>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="14"/>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="14"/>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="14"/>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="14"/>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="14"/>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="14"/>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="14"/>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="14"/>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="14"/>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="14"/>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="14"/>
+    <row r="17" spans="1:10">
+      <c r="A17" s="12">
+        <v>46179</v>
+      </c>
+      <c r="B17" s="15">
+        <v>0.375</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" t="s">
+        <v>97</v>
+      </c>
+      <c r="G17" t="s">
+        <v>98</v>
+      </c>
+      <c r="H17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="12">
+        <v>46179</v>
+      </c>
+      <c r="B18" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G18" t="s">
+        <v>102</v>
+      </c>
+      <c r="H18" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="12"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="12"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="12"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="12"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="12"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="12"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="12"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="12"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="12"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="12"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="12"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="12"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="12"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="12"/>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="14"/>
+      <c r="A33" s="12"/>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="14"/>
+      <c r="A34" s="12"/>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="14"/>
+      <c r="A35" s="12"/>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="14"/>
+      <c r="A36" s="12"/>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="14"/>
+      <c r="A37" s="12"/>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="14"/>
+      <c r="A38" s="12"/>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="14"/>
+      <c r="A39" s="12"/>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="14"/>
+      <c r="A40" s="12"/>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="14"/>
+      <c r="A41" s="12"/>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="14"/>
+      <c r="A42" s="12"/>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="14"/>
+      <c r="A43" s="12"/>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="14"/>
+      <c r="A44" s="12"/>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="14"/>
+      <c r="A45" s="12"/>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="14"/>
+      <c r="A46" s="12"/>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="14"/>
+      <c r="A47" s="12"/>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="14"/>
+      <c r="A48" s="12"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="14"/>
+      <c r="A49" s="12"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="14"/>
+      <c r="A50" s="12"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="14"/>
+      <c r="A51" s="12"/>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="14"/>
+      <c r="A52" s="12"/>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="14"/>
+      <c r="A53" s="12"/>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="14"/>
+      <c r="A54" s="12"/>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="14"/>
+      <c r="A55" s="12"/>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="14"/>
+      <c r="A56" s="12"/>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="14"/>
+      <c r="A57" s="12"/>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="14"/>
+      <c r="A58" s="12"/>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="14"/>
+      <c r="A59" s="12"/>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="14"/>
+      <c r="A60" s="12"/>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="14"/>
+      <c r="A61" s="12"/>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="14"/>
+      <c r="A62" s="12"/>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="14"/>
+      <c r="A63" s="12"/>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="14"/>
+      <c r="A64" s="12"/>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="14"/>
+      <c r="A65" s="12"/>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="14"/>
+      <c r="A66" s="12"/>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="14"/>
+      <c r="A67" s="12"/>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="14"/>
+      <c r="A68" s="12"/>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="14"/>
+      <c r="A69" s="12"/>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="14"/>
+      <c r="A70" s="12"/>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="14"/>
+      <c r="A71" s="12"/>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="14"/>
+      <c r="A72" s="12"/>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="14"/>
+      <c r="A73" s="12"/>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="14"/>
+      <c r="A74" s="12"/>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="14"/>
+      <c r="A75" s="12"/>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="14"/>
+      <c r="A76" s="12"/>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="14"/>
+      <c r="A77" s="12"/>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="14"/>
+      <c r="A78" s="12"/>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="14"/>
+      <c r="A79" s="12"/>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="14"/>
+      <c r="A80" s="12"/>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="14"/>
+      <c r="A81" s="12"/>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="14"/>
+      <c r="A82" s="12"/>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="14"/>
+      <c r="A83" s="12"/>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="14"/>
+      <c r="A84" s="12"/>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="14"/>
+      <c r="A85" s="12"/>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="14"/>
+      <c r="A86" s="12"/>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="14"/>
+      <c r="A87" s="12"/>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="14"/>
+      <c r="A88" s="12"/>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="14"/>
+      <c r="A89" s="12"/>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="14"/>
+      <c r="A90" s="12"/>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="14"/>
+      <c r="A91" s="12"/>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="14"/>
+      <c r="A92" s="12"/>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="14"/>
+      <c r="A93" s="12"/>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="14"/>
+      <c r="A94" s="12"/>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="14"/>
+      <c r="A95" s="12"/>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="14"/>
+      <c r="A96" s="12"/>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="14"/>
+      <c r="A97" s="12"/>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="14"/>
+      <c r="A98" s="12"/>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="14"/>
+      <c r="A99" s="12"/>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="14"/>
+      <c r="A100" s="12"/>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="14"/>
+      <c r="A101" s="12"/>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="14"/>
+      <c r="A102" s="12"/>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="14"/>
+      <c r="A103" s="12"/>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="14"/>
+      <c r="A104" s="12"/>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="14"/>
+      <c r="A105" s="12"/>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="14"/>
+      <c r="A106" s="12"/>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="14"/>
+      <c r="A107" s="12"/>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" s="14"/>
+      <c r="A108" s="12"/>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="14"/>
+      <c r="A109" s="12"/>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="14"/>
+      <c r="A110" s="12"/>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="14"/>
+      <c r="A111" s="12"/>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="14"/>
+      <c r="A112" s="12"/>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="14"/>
+      <c r="A113" s="12"/>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="14"/>
+      <c r="A114" s="12"/>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="14"/>
+      <c r="A115" s="12"/>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="14"/>
+      <c r="A116" s="12"/>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" s="14"/>
+      <c r="A117" s="12"/>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="14"/>
+      <c r="A118" s="12"/>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="14"/>
+      <c r="A119" s="12"/>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="14"/>
+      <c r="A120" s="12"/>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" s="14"/>
+      <c r="A121" s="12"/>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" s="14"/>
+      <c r="A122" s="12"/>
     </row>
     <row r="123" spans="1:1">
-      <c r="A123" s="14"/>
+      <c r="A123" s="12"/>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" s="14"/>
+      <c r="A124" s="12"/>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="14"/>
+      <c r="A125" s="12"/>
     </row>
     <row r="126" spans="1:1">
-      <c r="A126" s="14"/>
+      <c r="A126" s="12"/>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="14"/>
+      <c r="A127" s="12"/>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" s="14"/>
+      <c r="A128" s="12"/>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="14"/>
+      <c r="A129" s="12"/>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" s="14"/>
+      <c r="A130" s="12"/>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="14"/>
+      <c r="A131" s="12"/>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" s="14"/>
+      <c r="A132" s="12"/>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" s="14"/>
+      <c r="A133" s="12"/>
     </row>
     <row r="134" spans="1:1">
-      <c r="A134" s="14"/>
+      <c r="A134" s="12"/>
     </row>
     <row r="135" spans="1:1">
-      <c r="A135" s="14"/>
+      <c r="A135" s="12"/>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" s="14"/>
+      <c r="A136" s="12"/>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="14"/>
+      <c r="A137" s="12"/>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" s="14"/>
+      <c r="A138" s="12"/>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="14"/>
+      <c r="A139" s="12"/>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="14"/>
+      <c r="A140" s="12"/>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="14"/>
+      <c r="A141" s="12"/>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" s="14"/>
+      <c r="A142" s="12"/>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="14"/>
+      <c r="A143" s="12"/>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="14"/>
+      <c r="A144" s="12"/>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="14"/>
+      <c r="A145" s="12"/>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="14"/>
+      <c r="A146" s="12"/>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="14"/>
+      <c r="A147" s="12"/>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" s="14"/>
+      <c r="A148" s="12"/>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="14"/>
+      <c r="A149" s="12"/>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" s="14"/>
+      <c r="A150" s="12"/>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="14"/>
+      <c r="A151" s="12"/>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" s="14"/>
+      <c r="A152" s="12"/>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="14"/>
+      <c r="A153" s="12"/>
     </row>
     <row r="154" spans="1:1">
-      <c r="A154" s="14"/>
+      <c r="A154" s="12"/>
     </row>
     <row r="155" spans="1:1">
-      <c r="A155" s="14"/>
+      <c r="A155" s="12"/>
     </row>
     <row r="156" spans="1:1">
-      <c r="A156" s="14"/>
+      <c r="A156" s="12"/>
     </row>
     <row r="157" spans="1:1">
-      <c r="A157" s="14"/>
+      <c r="A157" s="12"/>
     </row>
     <row r="158" spans="1:1">
-      <c r="A158" s="14"/>
+      <c r="A158" s="12"/>
     </row>
     <row r="159" spans="1:1">
-      <c r="A159" s="14"/>
+      <c r="A159" s="12"/>
     </row>
     <row r="160" spans="1:1">
-      <c r="A160" s="14"/>
+      <c r="A160" s="12"/>
     </row>
     <row r="161" spans="1:1">
-      <c r="A161" s="12"/>
+      <c r="A161" s="10"/>
     </row>
     <row r="162" spans="1:1">
-      <c r="A162" s="12"/>
+      <c r="A162" s="10"/>
     </row>
     <row r="163" spans="1:1">
-      <c r="A163" s="12"/>
+      <c r="A163" s="10"/>
     </row>
     <row r="164" spans="1:1">
-      <c r="A164" s="12"/>
+      <c r="A164" s="10"/>
     </row>
     <row r="165" spans="1:1">
-      <c r="A165" s="12"/>
+      <c r="A165" s="10"/>
     </row>
     <row r="166" spans="1:1">
-      <c r="A166" s="12"/>
+      <c r="A166" s="10"/>
     </row>
     <row r="167" spans="1:1">
-      <c r="A167" s="12"/>
+      <c r="A167" s="10"/>
     </row>
     <row r="168" spans="1:1">
-      <c r="A168" s="12"/>
+      <c r="A168" s="10"/>
     </row>
     <row r="169" spans="1:1">
-      <c r="A169" s="12"/>
+      <c r="A169" s="10"/>
     </row>
     <row r="170" spans="1:1">
-      <c r="A170" s="12"/>
+      <c r="A170" s="10"/>
     </row>
     <row r="171" spans="1:1">
-      <c r="A171" s="12"/>
+      <c r="A171" s="10"/>
     </row>
     <row r="172" spans="1:1">
-      <c r="A172" s="12"/>
+      <c r="A172" s="10"/>
     </row>
     <row r="173" spans="1:1">
-      <c r="A173" s="12"/>
+      <c r="A173" s="10"/>
     </row>
     <row r="174" spans="1:1">
-      <c r="A174" s="12"/>
+      <c r="A174" s="10"/>
     </row>
     <row r="175" spans="1:1">
-      <c r="A175" s="12"/>
+      <c r="A175" s="10"/>
     </row>
     <row r="176" spans="1:1">
-      <c r="A176" s="12"/>
+      <c r="A176" s="10"/>
     </row>
     <row r="177" spans="1:1">
-      <c r="A177" s="12"/>
+      <c r="A177" s="10"/>
     </row>
     <row r="178" spans="1:1">
-      <c r="A178" s="12"/>
+      <c r="A178" s="10"/>
     </row>
     <row r="179" spans="1:1">
-      <c r="A179" s="12"/>
+      <c r="A179" s="10"/>
     </row>
     <row r="180" spans="1:1">
-      <c r="A180" s="12"/>
+      <c r="A180" s="10"/>
     </row>
     <row r="181" spans="1:1">
-      <c r="A181" s="12"/>
+      <c r="A181" s="10"/>
     </row>
     <row r="182" spans="1:1">
-      <c r="A182" s="12"/>
+      <c r="A182" s="10"/>
     </row>
     <row r="183" spans="1:1">
-      <c r="A183" s="12"/>
+      <c r="A183" s="10"/>
     </row>
     <row r="184" spans="1:1">
-      <c r="A184" s="12"/>
+      <c r="A184" s="10"/>
     </row>
     <row r="185" spans="1:1">
-      <c r="A185" s="12"/>
+      <c r="A185" s="10"/>
     </row>
     <row r="186" spans="1:1">
-      <c r="A186" s="12"/>
+      <c r="A186" s="10"/>
     </row>
     <row r="187" spans="1:1">
-      <c r="A187" s="12"/>
+      <c r="A187" s="10"/>
     </row>
     <row r="188" spans="1:1">
-      <c r="A188" s="12"/>
+      <c r="A188" s="10"/>
     </row>
     <row r="189" spans="1:1">
-      <c r="A189" s="12"/>
+      <c r="A189" s="10"/>
     </row>
     <row r="190" spans="1:1">
-      <c r="A190" s="12"/>
+      <c r="A190" s="10"/>
     </row>
     <row r="191" spans="1:1">
-      <c r="A191" s="12"/>
+      <c r="A191" s="10"/>
     </row>
     <row r="192" spans="1:1">
-      <c r="A192" s="12"/>
+      <c r="A192" s="10"/>
     </row>
     <row r="193" spans="1:1">
-      <c r="A193" s="12"/>
+      <c r="A193" s="10"/>
     </row>
     <row r="194" spans="1:1">
-      <c r="A194" s="12"/>
+      <c r="A194" s="10"/>
     </row>
     <row r="195" spans="1:1">
-      <c r="A195" s="12"/>
+      <c r="A195" s="10"/>
     </row>
     <row r="196" spans="1:1">
-      <c r="A196" s="12"/>
+      <c r="A196" s="10"/>
     </row>
     <row r="197" spans="1:1">
-      <c r="A197" s="12"/>
+      <c r="A197" s="10"/>
     </row>
     <row r="198" spans="1:1">
-      <c r="A198" s="12"/>
+      <c r="A198" s="10"/>
     </row>
     <row r="199" spans="1:1">
-      <c r="A199" s="12"/>
+      <c r="A199" s="10"/>
     </row>
     <row r="200" spans="1:1">
-      <c r="A200" s="12"/>
+      <c r="A200" s="10"/>
     </row>
     <row r="201" spans="1:1">
-      <c r="A201" s="12"/>
+      <c r="A201" s="10"/>
     </row>
     <row r="202" spans="1:1">
-      <c r="A202" s="12"/>
+      <c r="A202" s="10"/>
     </row>
     <row r="203" spans="1:1">
-      <c r="A203" s="12"/>
+      <c r="A203" s="10"/>
     </row>
     <row r="204" spans="1:1">
-      <c r="A204" s="12"/>
+      <c r="A204" s="10"/>
     </row>
     <row r="205" spans="1:1">
-      <c r="A205" s="12"/>
+      <c r="A205" s="10"/>
     </row>
     <row r="206" spans="1:1">
-      <c r="A206" s="12"/>
+      <c r="A206" s="10"/>
     </row>
     <row r="207" spans="1:1">
-      <c r="A207" s="12"/>
+      <c r="A207" s="10"/>
     </row>
     <row r="208" spans="1:1">
-      <c r="A208" s="12"/>
+      <c r="A208" s="10"/>
     </row>
     <row r="209" spans="1:1">
-      <c r="A209" s="12"/>
+      <c r="A209" s="10"/>
     </row>
     <row r="210" spans="1:1">
-      <c r="A210" s="12"/>
+      <c r="A210" s="10"/>
     </row>
     <row r="211" spans="1:1">
-      <c r="A211" s="12"/>
+      <c r="A211" s="10"/>
     </row>
     <row r="212" spans="1:1">
-      <c r="A212" s="12"/>
+      <c r="A212" s="10"/>
     </row>
     <row r="213" spans="1:1">
-      <c r="A213" s="12"/>
+      <c r="A213" s="10"/>
     </row>
     <row r="214" spans="1:1">
-      <c r="A214" s="12"/>
+      <c r="A214" s="10"/>
     </row>
     <row r="215" spans="1:1">
-      <c r="A215" s="12"/>
+      <c r="A215" s="10"/>
     </row>
     <row r="216" spans="1:1">
-      <c r="A216" s="12"/>
+      <c r="A216" s="10"/>
     </row>
     <row r="217" spans="1:1">
-      <c r="A217" s="12"/>
+      <c r="A217" s="10"/>
     </row>
     <row r="218" spans="1:1">
-      <c r="A218" s="12"/>
+      <c r="A218" s="10"/>
     </row>
     <row r="219" spans="1:1">
-      <c r="A219" s="12"/>
+      <c r="A219" s="10"/>
     </row>
     <row r="220" spans="1:1">
-      <c r="A220" s="12"/>
+      <c r="A220" s="10"/>
     </row>
     <row r="221" spans="1:1">
-      <c r="A221" s="12"/>
+      <c r="A221" s="10"/>
     </row>
     <row r="222" spans="1:1">
-      <c r="A222" s="12"/>
+      <c r="A222" s="10"/>
     </row>
     <row r="223" spans="1:1">
-      <c r="A223" s="12"/>
+      <c r="A223" s="10"/>
     </row>
     <row r="224" spans="1:1">
-      <c r="A224" s="12"/>
+      <c r="A224" s="10"/>
     </row>
     <row r="225" spans="1:1">
-      <c r="A225" s="12"/>
+      <c r="A225" s="10"/>
     </row>
     <row r="226" spans="1:1">
-      <c r="A226" s="12"/>
+      <c r="A226" s="10"/>
     </row>
     <row r="227" spans="1:1">
-      <c r="A227" s="12"/>
+      <c r="A227" s="10"/>
     </row>
     <row r="228" spans="1:1">
-      <c r="A228" s="12"/>
+      <c r="A228" s="10"/>
     </row>
     <row r="229" spans="1:1">
-      <c r="A229" s="12"/>
+      <c r="A229" s="10"/>
     </row>
     <row r="230" spans="1:1">
-      <c r="A230" s="12"/>
+      <c r="A230" s="10"/>
     </row>
     <row r="231" spans="1:1">
-      <c r="A231" s="12"/>
+      <c r="A231" s="10"/>
     </row>
     <row r="232" spans="1:1">
-      <c r="A232" s="12"/>
+      <c r="A232" s="10"/>
     </row>
     <row r="233" spans="1:1">
-      <c r="A233" s="12"/>
+      <c r="A233" s="10"/>
     </row>
     <row r="234" spans="1:1">
-      <c r="A234" s="12"/>
+      <c r="A234" s="10"/>
     </row>
     <row r="235" spans="1:1">
-      <c r="A235" s="12"/>
+      <c r="A235" s="10"/>
     </row>
     <row r="236" spans="1:1">
-      <c r="A236" s="12"/>
+      <c r="A236" s="10"/>
     </row>
     <row r="237" spans="1:1">
-      <c r="A237" s="12"/>
+      <c r="A237" s="10"/>
     </row>
     <row r="238" spans="1:1">
-      <c r="A238" s="12"/>
+      <c r="A238" s="10"/>
     </row>
     <row r="239" spans="1:1">
-      <c r="A239" s="12"/>
+      <c r="A239" s="10"/>
     </row>
     <row r="240" spans="1:1">
-      <c r="A240" s="12"/>
+      <c r="A240" s="10"/>
     </row>
     <row r="241" spans="1:1">
-      <c r="A241" s="12"/>
+      <c r="A241" s="10"/>
     </row>
     <row r="242" spans="1:1">
-      <c r="A242" s="12"/>
+      <c r="A242" s="10"/>
     </row>
     <row r="243" spans="1:1">
-      <c r="A243" s="12"/>
+      <c r="A243" s="10"/>
     </row>
     <row r="244" spans="1:1">
-      <c r="A244" s="12"/>
+      <c r="A244" s="10"/>
     </row>
     <row r="245" spans="1:1">
-      <c r="A245" s="12"/>
+      <c r="A245" s="10"/>
     </row>
     <row r="246" spans="1:1">
-      <c r="A246" s="12"/>
+      <c r="A246" s="10"/>
     </row>
     <row r="247" spans="1:1">
-      <c r="A247" s="12"/>
+      <c r="A247" s="10"/>
     </row>
     <row r="248" spans="1:1">
-      <c r="A248" s="12"/>
+      <c r="A248" s="10"/>
     </row>
     <row r="249" spans="1:1">
-      <c r="A249" s="12"/>
+      <c r="A249" s="10"/>
     </row>
     <row r="250" spans="1:1">
-      <c r="A250" s="12"/>
+      <c r="A250" s="10"/>
     </row>
     <row r="251" spans="1:1">
-      <c r="A251" s="12"/>
+      <c r="A251" s="10"/>
     </row>
     <row r="252" spans="1:1">
-      <c r="A252" s="12"/>
+      <c r="A252" s="10"/>
     </row>
     <row r="253" spans="1:1">
-      <c r="A253" s="12"/>
+      <c r="A253" s="10"/>
     </row>
     <row r="254" spans="1:1">
-      <c r="A254" s="12"/>
+      <c r="A254" s="10"/>
     </row>
     <row r="255" spans="1:1">
-      <c r="A255" s="12"/>
+      <c r="A255" s="10"/>
     </row>
     <row r="256" spans="1:1">
-      <c r="A256" s="12"/>
+      <c r="A256" s="10"/>
     </row>
     <row r="257" spans="1:1">
-      <c r="A257" s="12"/>
+      <c r="A257" s="10"/>
     </row>
     <row r="258" spans="1:1">
-      <c r="A258" s="12"/>
+      <c r="A258" s="10"/>
     </row>
     <row r="259" spans="1:1">
-      <c r="A259" s="12"/>
+      <c r="A259" s="10"/>
     </row>
     <row r="260" spans="1:1">
-      <c r="A260" s="12"/>
+      <c r="A260" s="10"/>
     </row>
     <row r="261" spans="1:1">
-      <c r="A261" s="12"/>
+      <c r="A261" s="10"/>
     </row>
     <row r="262" spans="1:1">
-      <c r="A262" s="12"/>
+      <c r="A262" s="10"/>
     </row>
     <row r="263" spans="1:1">
-      <c r="A263" s="12"/>
+      <c r="A263" s="10"/>
     </row>
     <row r="264" spans="1:1">
-      <c r="A264" s="12"/>
+      <c r="A264" s="10"/>
     </row>
     <row r="265" spans="1:1">
-      <c r="A265" s="12"/>
+      <c r="A265" s="10"/>
     </row>
     <row r="266" spans="1:1">
-      <c r="A266" s="12"/>
+      <c r="A266" s="10"/>
     </row>
     <row r="267" spans="1:1">
-      <c r="A267" s="12"/>
+      <c r="A267" s="10"/>
     </row>
     <row r="268" spans="1:1">
-      <c r="A268" s="12"/>
+      <c r="A268" s="10"/>
     </row>
     <row r="269" spans="1:1">
-      <c r="A269" s="12"/>
+      <c r="A269" s="10"/>
     </row>
     <row r="270" spans="1:1">
-      <c r="A270" s="12"/>
+      <c r="A270" s="10"/>
     </row>
     <row r="271" spans="1:1">
-      <c r="A271" s="12"/>
+      <c r="A271" s="10"/>
     </row>
     <row r="272" spans="1:1">
-      <c r="A272" s="12"/>
+      <c r="A272" s="10"/>
     </row>
     <row r="273" spans="1:1">
-      <c r="A273" s="12"/>
+      <c r="A273" s="10"/>
     </row>
     <row r="274" spans="1:1">
-      <c r="A274" s="12"/>
+      <c r="A274" s="10"/>
     </row>
     <row r="275" spans="1:1">
-      <c r="A275" s="12"/>
+      <c r="A275" s="10"/>
     </row>
     <row r="276" spans="1:1">
-      <c r="A276" s="12"/>
+      <c r="A276" s="10"/>
     </row>
     <row r="277" spans="1:1">
-      <c r="A277" s="12"/>
+      <c r="A277" s="10"/>
     </row>
     <row r="278" spans="1:1">
-      <c r="A278" s="12"/>
+      <c r="A278" s="10"/>
     </row>
     <row r="279" spans="1:1">
-      <c r="A279" s="12"/>
+      <c r="A279" s="10"/>
     </row>
     <row r="280" spans="1:1">
-      <c r="A280" s="12"/>
+      <c r="A280" s="10"/>
     </row>
     <row r="281" spans="1:1">
-      <c r="A281" s="12"/>
+      <c r="A281" s="10"/>
     </row>
     <row r="282" spans="1:1">
-      <c r="A282" s="12"/>
+      <c r="A282" s="10"/>
     </row>
     <row r="283" spans="1:1">
-      <c r="A283" s="12"/>
+      <c r="A283" s="10"/>
     </row>
     <row r="284" spans="1:1">
-      <c r="A284" s="12"/>
+      <c r="A284" s="10"/>
     </row>
     <row r="285" spans="1:1">
-      <c r="A285" s="12"/>
+      <c r="A285" s="10"/>
     </row>
     <row r="286" spans="1:1">
-      <c r="A286" s="12"/>
+      <c r="A286" s="10"/>
     </row>
     <row r="287" spans="1:1">
-      <c r="A287" s="12"/>
+      <c r="A287" s="10"/>
     </row>
     <row r="288" spans="1:1">
-      <c r="A288" s="12"/>
+      <c r="A288" s="10"/>
     </row>
     <row r="289" spans="1:1">
-      <c r="A289" s="12"/>
+      <c r="A289" s="10"/>
     </row>
     <row r="290" spans="1:1">
-      <c r="A290" s="12"/>
+      <c r="A290" s="10"/>
     </row>
     <row r="291" spans="1:1">
-      <c r="A291" s="12"/>
+      <c r="A291" s="10"/>
     </row>
     <row r="292" spans="1:1">
-      <c r="A292" s="12"/>
+      <c r="A292" s="10"/>
     </row>
     <row r="293" spans="1:1">
-      <c r="A293" s="12"/>
+      <c r="A293" s="10"/>
     </row>
     <row r="294" spans="1:1">
-      <c r="A294" s="12"/>
+      <c r="A294" s="10"/>
     </row>
     <row r="295" spans="1:1">
-      <c r="A295" s="12"/>
+      <c r="A295" s="10"/>
     </row>
     <row r="296" spans="1:1">
-      <c r="A296" s="12"/>
+      <c r="A296" s="10"/>
     </row>
     <row r="297" spans="1:1">
-      <c r="A297" s="12"/>
+      <c r="A297" s="10"/>
     </row>
     <row r="298" spans="1:1">
-      <c r="A298" s="12"/>
+      <c r="A298" s="10"/>
     </row>
     <row r="299" spans="1:1">
-      <c r="A299" s="12"/>
+      <c r="A299" s="10"/>
     </row>
     <row r="300" spans="1:1">
-      <c r="A300" s="12"/>
+      <c r="A300" s="10"/>
     </row>
     <row r="301" spans="1:1">
-      <c r="A301" s="12"/>
+      <c r="A301" s="10"/>
     </row>
     <row r="302" spans="1:1">
-      <c r="A302" s="12"/>
+      <c r="A302" s="10"/>
     </row>
     <row r="303" spans="1:1">
-      <c r="A303" s="12"/>
+      <c r="A303" s="10"/>
     </row>
     <row r="304" spans="1:1">
-      <c r="A304" s="12"/>
+      <c r="A304" s="10"/>
     </row>
     <row r="305" spans="1:1">
-      <c r="A305" s="12"/>
+      <c r="A305" s="10"/>
     </row>
     <row r="306" spans="1:1">
-      <c r="A306" s="12"/>
+      <c r="A306" s="10"/>
     </row>
     <row r="307" spans="1:1">
-      <c r="A307" s="12"/>
+      <c r="A307" s="10"/>
     </row>
     <row r="308" spans="1:1">
-      <c r="A308" s="12"/>
+      <c r="A308" s="10"/>
     </row>
     <row r="309" spans="1:1">
-      <c r="A309" s="12"/>
+      <c r="A309" s="10"/>
     </row>
     <row r="310" spans="1:1">
-      <c r="A310" s="12"/>
+      <c r="A310" s="10"/>
     </row>
     <row r="311" spans="1:1">
-      <c r="A311" s="12"/>
+      <c r="A311" s="10"/>
     </row>
     <row r="312" spans="1:1">
-      <c r="A312" s="12"/>
+      <c r="A312" s="10"/>
     </row>
     <row r="313" spans="1:1">
-      <c r="A313" s="12"/>
+      <c r="A313" s="10"/>
     </row>
     <row r="314" spans="1:1">
-      <c r="A314" s="12"/>
+      <c r="A314" s="10"/>
     </row>
     <row r="315" spans="1:1">
-      <c r="A315" s="12"/>
+      <c r="A315" s="10"/>
     </row>
     <row r="316" spans="1:1">
-      <c r="A316" s="12"/>
+      <c r="A316" s="10"/>
     </row>
     <row r="317" spans="1:1">
-      <c r="A317" s="12"/>
+      <c r="A317" s="10"/>
     </row>
     <row r="318" spans="1:1">
-      <c r="A318" s="12"/>
+      <c r="A318" s="10"/>
     </row>
     <row r="319" spans="1:1">
-      <c r="A319" s="12"/>
+      <c r="A319" s="10"/>
     </row>
     <row r="320" spans="1:1">
-      <c r="A320" s="12"/>
+      <c r="A320" s="10"/>
     </row>
     <row r="321" spans="1:1">
-      <c r="A321" s="12"/>
+      <c r="A321" s="10"/>
     </row>
     <row r="322" spans="1:1">
-      <c r="A322" s="12"/>
+      <c r="A322" s="10"/>
     </row>
     <row r="323" spans="1:1">
-      <c r="A323" s="12"/>
+      <c r="A323" s="10"/>
     </row>
     <row r="324" spans="1:1">
-      <c r="A324" s="12"/>
+      <c r="A324" s="10"/>
     </row>
     <row r="325" spans="1:1">
-      <c r="A325" s="12"/>
+      <c r="A325" s="10"/>
     </row>
     <row r="326" spans="1:1">
-      <c r="A326" s="12"/>
+      <c r="A326" s="10"/>
     </row>
     <row r="327" spans="1:1">
-      <c r="A327" s="12"/>
+      <c r="A327" s="10"/>
     </row>
     <row r="328" spans="1:1">
-      <c r="A328" s="12"/>
+      <c r="A328" s="10"/>
     </row>
     <row r="329" spans="1:1">
-      <c r="A329" s="12"/>
+      <c r="A329" s="10"/>
     </row>
     <row r="330" spans="1:1">
-      <c r="A330" s="12"/>
+      <c r="A330" s="10"/>
     </row>
     <row r="331" spans="1:1">
-      <c r="A331" s="12"/>
+      <c r="A331" s="10"/>
     </row>
     <row r="332" spans="1:1">
-      <c r="A332" s="12"/>
+      <c r="A332" s="10"/>
     </row>
     <row r="333" spans="1:1">
-      <c r="A333" s="12"/>
+      <c r="A333" s="10"/>
     </row>
     <row r="334" spans="1:1">
-      <c r="A334" s="12"/>
+      <c r="A334" s="10"/>
     </row>
     <row r="335" spans="1:1">
-      <c r="A335" s="12"/>
+      <c r="A335" s="10"/>
     </row>
     <row r="336" spans="1:1">
-      <c r="A336" s="12"/>
+      <c r="A336" s="10"/>
     </row>
     <row r="337" spans="1:1">
-      <c r="A337" s="12"/>
+      <c r="A337" s="10"/>
     </row>
     <row r="338" spans="1:1">
-      <c r="A338" s="12"/>
+      <c r="A338" s="10"/>
     </row>
     <row r="339" spans="1:1">
-      <c r="A339" s="12"/>
+      <c r="A339" s="10"/>
     </row>
     <row r="340" spans="1:1">
-      <c r="A340" s="12"/>
+      <c r="A340" s="10"/>
     </row>
     <row r="341" spans="1:1">
-      <c r="A341" s="12"/>
+      <c r="A341" s="10"/>
     </row>
     <row r="342" spans="1:1">
-      <c r="A342" s="12"/>
+      <c r="A342" s="10"/>
     </row>
     <row r="343" spans="1:1">
-      <c r="A343" s="12"/>
+      <c r="A343" s="10"/>
     </row>
     <row r="344" spans="1:1">
-      <c r="A344" s="12"/>
+      <c r="A344" s="10"/>
     </row>
     <row r="345" spans="1:1">
-      <c r="A345" s="12"/>
+      <c r="A345" s="10"/>
     </row>
     <row r="346" spans="1:1">
-      <c r="A346" s="12"/>
+      <c r="A346" s="10"/>
     </row>
     <row r="347" spans="1:1">
-      <c r="A347" s="12"/>
+      <c r="A347" s="10"/>
     </row>
     <row r="348" spans="1:1">
-      <c r="A348" s="12"/>
+      <c r="A348" s="10"/>
     </row>
     <row r="349" spans="1:1">
-      <c r="A349" s="12"/>
+      <c r="A349" s="10"/>
     </row>
     <row r="350" spans="1:1">
-      <c r="A350" s="12"/>
+      <c r="A350" s="10"/>
     </row>
     <row r="351" spans="1:1">
-      <c r="A351" s="12"/>
+      <c r="A351" s="10"/>
     </row>
     <row r="352" spans="1:1">
-      <c r="A352" s="12"/>
+      <c r="A352" s="10"/>
     </row>
     <row r="353" spans="1:1">
-      <c r="A353" s="12"/>
+      <c r="A353" s="10"/>
     </row>
     <row r="354" spans="1:1">
-      <c r="A354" s="12"/>
+      <c r="A354" s="10"/>
     </row>
     <row r="355" spans="1:1">
-      <c r="A355" s="12"/>
+      <c r="A355" s="10"/>
     </row>
     <row r="356" spans="1:1">
-      <c r="A356" s="12"/>
+      <c r="A356" s="10"/>
     </row>
     <row r="357" spans="1:1">
-      <c r="A357" s="12"/>
+      <c r="A357" s="10"/>
     </row>
     <row r="358" spans="1:1">
-      <c r="A358" s="12"/>
+      <c r="A358" s="10"/>
     </row>
     <row r="359" spans="1:1">
-      <c r="A359" s="12"/>
+      <c r="A359" s="10"/>
     </row>
     <row r="360" spans="1:1">
-      <c r="A360" s="12"/>
+      <c r="A360" s="10"/>
     </row>
     <row r="361" spans="1:1">
-      <c r="A361" s="12"/>
+      <c r="A361" s="10"/>
     </row>
     <row r="362" spans="1:1">
-      <c r="A362" s="12"/>
+      <c r="A362" s="10"/>
     </row>
     <row r="363" spans="1:1">
-      <c r="A363" s="12"/>
+      <c r="A363" s="10"/>
     </row>
     <row r="364" spans="1:1">
-      <c r="A364" s="12"/>
+      <c r="A364" s="10"/>
     </row>
     <row r="365" spans="1:1">
-      <c r="A365" s="12"/>
+      <c r="A365" s="10"/>
     </row>
     <row r="366" spans="1:1">
-      <c r="A366" s="12"/>
+      <c r="A366" s="10"/>
     </row>
     <row r="367" spans="1:1">
-      <c r="A367" s="12"/>
+      <c r="A367" s="10"/>
     </row>
     <row r="368" spans="1:1">
-      <c r="A368" s="12"/>
+      <c r="A368" s="10"/>
     </row>
     <row r="369" spans="1:1">
-      <c r="A369" s="12"/>
+      <c r="A369" s="10"/>
     </row>
     <row r="370" spans="1:1">
-      <c r="A370" s="12"/>
+      <c r="A370" s="10"/>
     </row>
     <row r="371" spans="1:1">
-      <c r="A371" s="12"/>
+      <c r="A371" s="10"/>
     </row>
     <row r="372" spans="1:1">
-      <c r="A372" s="12"/>
+      <c r="A372" s="10"/>
     </row>
     <row r="373" spans="1:1">
-      <c r="A373" s="12"/>
+      <c r="A373" s="10"/>
     </row>
     <row r="374" spans="1:1">
-      <c r="A374" s="12"/>
+      <c r="A374" s="10"/>
     </row>
     <row r="375" spans="1:1">
-      <c r="A375" s="12"/>
+      <c r="A375" s="10"/>
     </row>
     <row r="376" spans="1:1">
-      <c r="A376" s="12"/>
+      <c r="A376" s="10"/>
     </row>
     <row r="377" spans="1:1">
-      <c r="A377" s="12"/>
+      <c r="A377" s="10"/>
     </row>
     <row r="378" spans="1:1">
-      <c r="A378" s="12"/>
+      <c r="A378" s="10"/>
     </row>
     <row r="379" spans="1:1">
-      <c r="A379" s="12"/>
+      <c r="A379" s="10"/>
     </row>
     <row r="380" spans="1:1">
-      <c r="A380" s="12"/>
+      <c r="A380" s="10"/>
     </row>
     <row r="381" spans="1:1">
-      <c r="A381" s="12"/>
+      <c r="A381" s="10"/>
     </row>
     <row r="382" spans="1:1">
-      <c r="A382" s="12"/>
+      <c r="A382" s="10"/>
     </row>
     <row r="383" spans="1:1">
-      <c r="A383" s="12"/>
+      <c r="A383" s="10"/>
     </row>
     <row r="384" spans="1:1">
-      <c r="A384" s="12"/>
+      <c r="A384" s="10"/>
     </row>
     <row r="385" spans="1:1">
-      <c r="A385" s="12"/>
+      <c r="A385" s="10"/>
     </row>
     <row r="386" spans="1:1">
-      <c r="A386" s="12"/>
+      <c r="A386" s="10"/>
     </row>
     <row r="387" spans="1:1">
-      <c r="A387" s="12"/>
+      <c r="A387" s="10"/>
     </row>
     <row r="388" spans="1:1">
-      <c r="A388" s="12"/>
+      <c r="A388" s="10"/>
     </row>
     <row r="389" spans="1:1">
-      <c r="A389" s="12"/>
+      <c r="A389" s="10"/>
     </row>
     <row r="390" spans="1:1">
-      <c r="A390" s="12"/>
+      <c r="A390" s="10"/>
     </row>
     <row r="391" spans="1:1">
-      <c r="A391" s="12"/>
+      <c r="A391" s="10"/>
     </row>
     <row r="392" spans="1:1">
-      <c r="A392" s="12"/>
+      <c r="A392" s="10"/>
     </row>
     <row r="393" spans="1:1">
-      <c r="A393" s="12"/>
+      <c r="A393" s="10"/>
     </row>
     <row r="394" spans="1:1">
-      <c r="A394" s="12"/>
+      <c r="A394" s="10"/>
     </row>
     <row r="395" spans="1:1">
-      <c r="A395" s="12"/>
+      <c r="A395" s="10"/>
     </row>
     <row r="396" spans="1:1">
-      <c r="A396" s="12"/>
+      <c r="A396" s="10"/>
     </row>
     <row r="397" spans="1:1">
-      <c r="A397" s="12"/>
+      <c r="A397" s="10"/>
     </row>
     <row r="398" spans="1:1">
-      <c r="A398" s="12"/>
+      <c r="A398" s="10"/>
     </row>
     <row r="399" spans="1:1">
-      <c r="A399" s="12"/>
+      <c r="A399" s="10"/>
     </row>
     <row r="400" spans="1:1">
-      <c r="A400" s="12"/>
+      <c r="A400" s="10"/>
     </row>
     <row r="401" spans="1:1">
-      <c r="A401" s="12"/>
+      <c r="A401" s="10"/>
     </row>
     <row r="402" spans="1:1">
-      <c r="A402" s="12"/>
+      <c r="A402" s="10"/>
     </row>
     <row r="403" spans="1:1">
-      <c r="A403" s="12"/>
+      <c r="A403" s="10"/>
     </row>
     <row r="404" spans="1:1">
-      <c r="A404" s="12"/>
+      <c r="A404" s="10"/>
     </row>
     <row r="405" spans="1:1">
-      <c r="A405" s="12"/>
+      <c r="A405" s="10"/>
     </row>
     <row r="406" spans="1:1">
-      <c r="A406" s="12"/>
+      <c r="A406" s="10"/>
     </row>
     <row r="407" spans="1:1">
-      <c r="A407" s="12"/>
+      <c r="A407" s="10"/>
     </row>
     <row r="408" spans="1:1">
-      <c r="A408" s="12"/>
+      <c r="A408" s="10"/>
     </row>
     <row r="409" spans="1:1">
-      <c r="A409" s="12"/>
+      <c r="A409" s="10"/>
     </row>
     <row r="410" spans="1:1">
-      <c r="A410" s="12"/>
+      <c r="A410" s="10"/>
     </row>
     <row r="411" spans="1:1">
-      <c r="A411" s="12"/>
+      <c r="A411" s="10"/>
     </row>
     <row r="412" spans="1:1">
-      <c r="A412" s="12"/>
+      <c r="A412" s="10"/>
     </row>
     <row r="413" spans="1:1">
-      <c r="A413" s="12"/>
+      <c r="A413" s="10"/>
     </row>
     <row r="414" spans="1:1">
-      <c r="A414" s="12"/>
+      <c r="A414" s="10"/>
     </row>
     <row r="415" spans="1:1">
-      <c r="A415" s="12"/>
+      <c r="A415" s="10"/>
     </row>
     <row r="416" spans="1:1">
-      <c r="A416" s="12"/>
+      <c r="A416" s="10"/>
     </row>
     <row r="417" spans="1:1">
-      <c r="A417" s="12"/>
+      <c r="A417" s="10"/>
     </row>
     <row r="418" spans="1:1">
-      <c r="A418" s="12"/>
+      <c r="A418" s="10"/>
     </row>
     <row r="419" spans="1:1">
-      <c r="A419" s="12"/>
+      <c r="A419" s="10"/>
     </row>
     <row r="420" spans="1:1">
-      <c r="A420" s="12"/>
+      <c r="A420" s="10"/>
     </row>
     <row r="421" spans="1:1">
-      <c r="A421" s="12"/>
+      <c r="A421" s="10"/>
     </row>
     <row r="422" spans="1:1">
-      <c r="A422" s="12"/>
+      <c r="A422" s="10"/>
     </row>
     <row r="423" spans="1:1">
-      <c r="A423" s="12"/>
+      <c r="A423" s="10"/>
     </row>
     <row r="424" spans="1:1">
-      <c r="A424" s="12"/>
+      <c r="A424" s="10"/>
     </row>
     <row r="425" spans="1:1">
-      <c r="A425" s="12"/>
+      <c r="A425" s="10"/>
     </row>
     <row r="426" spans="1:1">
-      <c r="A426" s="12"/>
+      <c r="A426" s="10"/>
     </row>
     <row r="427" spans="1:1">
-      <c r="A427" s="12"/>
+      <c r="A427" s="10"/>
     </row>
     <row r="428" spans="1:1">
-      <c r="A428" s="12"/>
+      <c r="A428" s="10"/>
     </row>
     <row r="429" spans="1:1">
-      <c r="A429" s="12"/>
+      <c r="A429" s="10"/>
     </row>
     <row r="430" spans="1:1">
-      <c r="A430" s="12"/>
+      <c r="A430" s="10"/>
     </row>
     <row r="431" spans="1:1">
-      <c r="A431" s="12"/>
+      <c r="A431" s="10"/>
     </row>
     <row r="432" spans="1:1">
-      <c r="A432" s="12"/>
+      <c r="A432" s="10"/>
     </row>
     <row r="433" spans="1:1">
-      <c r="A433" s="12"/>
+      <c r="A433" s="10"/>
     </row>
     <row r="434" spans="1:1">
-      <c r="A434" s="12"/>
+      <c r="A434" s="10"/>
     </row>
     <row r="435" spans="1:1">
-      <c r="A435" s="12"/>
+      <c r="A435" s="10"/>
     </row>
     <row r="436" spans="1:1">
-      <c r="A436" s="12"/>
+      <c r="A436" s="10"/>
     </row>
     <row r="437" spans="1:1">
-      <c r="A437" s="12"/>
+      <c r="A437" s="10"/>
     </row>
     <row r="438" spans="1:1">
-      <c r="A438" s="12"/>
+      <c r="A438" s="10"/>
     </row>
     <row r="439" spans="1:1">
-      <c r="A439" s="12"/>
+      <c r="A439" s="10"/>
     </row>
     <row r="440" spans="1:1">
-      <c r="A440" s="12"/>
+      <c r="A440" s="10"/>
     </row>
     <row r="441" spans="1:1">
-      <c r="A441" s="12"/>
+      <c r="A441" s="10"/>
     </row>
     <row r="442" spans="1:1">
-      <c r="A442" s="12"/>
+      <c r="A442" s="10"/>
     </row>
     <row r="443" spans="1:1">
-      <c r="A443" s="12"/>
+      <c r="A443" s="10"/>
     </row>
     <row r="444" spans="1:1">
-      <c r="A444" s="12"/>
+      <c r="A444" s="10"/>
     </row>
     <row r="445" spans="1:1">
-      <c r="A445" s="12"/>
+      <c r="A445" s="10"/>
     </row>
     <row r="446" spans="1:1">
-      <c r="A446" s="12"/>
+      <c r="A446" s="10"/>
     </row>
     <row r="447" spans="1:1">
-      <c r="A447" s="12"/>
+      <c r="A447" s="10"/>
     </row>
     <row r="448" spans="1:1">
-      <c r="A448" s="12"/>
+      <c r="A448" s="10"/>
     </row>
     <row r="449" spans="1:1">
-      <c r="A449" s="12"/>
+      <c r="A449" s="10"/>
     </row>
     <row r="450" spans="1:1">
-      <c r="A450" s="12"/>
+      <c r="A450" s="10"/>
     </row>
     <row r="451" spans="1:1">
-      <c r="A451" s="12"/>
+      <c r="A451" s="10"/>
     </row>
     <row r="452" spans="1:1">
-      <c r="A452" s="12"/>
+      <c r="A452" s="10"/>
     </row>
     <row r="453" spans="1:1">
-      <c r="A453" s="12"/>
+      <c r="A453" s="10"/>
     </row>
     <row r="454" spans="1:1">
-      <c r="A454" s="12"/>
+      <c r="A454" s="10"/>
     </row>
     <row r="455" spans="1:1">
-      <c r="A455" s="12"/>
+      <c r="A455" s="10"/>
     </row>
     <row r="456" spans="1:1">
-      <c r="A456" s="12"/>
+      <c r="A456" s="10"/>
     </row>
     <row r="457" spans="1:1">
-      <c r="A457" s="12"/>
+      <c r="A457" s="10"/>
     </row>
     <row r="458" spans="1:1">
-      <c r="A458" s="12"/>
+      <c r="A458" s="10"/>
     </row>
     <row r="459" spans="1:1">
-      <c r="A459" s="12"/>
+      <c r="A459" s="10"/>
     </row>
     <row r="460" spans="1:1">
-      <c r="A460" s="12"/>
+      <c r="A460" s="10"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H64">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>H2="Alta"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>H2="Media"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>H2="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J64">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>J2="Ejecutado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>J2="Pendiente"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2635,7 +2715,7 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
@@ -2649,26 +2729,26 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="B5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" t="s">
         <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2695,66 +2775,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="A1" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="A3" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15">
       <c r="A4" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B4">
-        <f>COUNTA(EVENTOS!E2:E16)</f>
-        <v>15</v>
+        <f>COUNTA(EVENTOS!E2:E18)</f>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15">
       <c r="A5" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B5">
-        <f>COUNTIF(EVENTOS!J2:J16,"Ejecutado")</f>
+        <f>COUNTIF(EVENTOS!J2:J18,"Ejecutado")</f>
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15">
       <c r="A6" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B6">
-        <f>COUNTIF(EVENTOS!J2:J16,"Pendiente")</f>
+        <f>COUNTIF(EVENTOS!J2:J18,"Pendiente")</f>
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15">
       <c r="A7" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B7">
-        <f>COUNTIF(EVENTOS!H2:H16,"Alta")</f>
-        <v>12</v>
+        <f>COUNTIF(EVENTOS!H2:H18,"Alta")</f>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15">
       <c r="A8" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B8">
-        <f>COUNTA(EVENTOS!F2:F16)</f>
-        <v>15</v>
+        <f>COUNTA(EVENTOS!F2:F18)</f>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7274A1-A26D-492E-94E0-DBD9A1513892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6894530D-CB91-4970-9D83-50FC8758795F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVENTOS" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="108">
   <si>
     <t>Fecha</t>
   </si>
@@ -391,6 +391,21 @@
   <si>
     <t>instalacion de mesas</t>
   </si>
+  <si>
+    <t xml:space="preserve">Medicina </t>
+  </si>
+  <si>
+    <t>OT 811187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONFERENCIA </t>
+  </si>
+  <si>
+    <t>AUDITORIO PABELLON O</t>
+  </si>
+  <si>
+    <t>2 mesas afuera con mantel                                                     4 sillas  dentro con una mesa de centro</t>
+  </si>
 </sst>
 </file>
 
@@ -399,7 +414,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -418,6 +433,11 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
@@ -486,7 +506,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -564,7 +584,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaEventosV4" displayName="TablaEventosV4" ref="A1:J18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaEventosV4" displayName="TablaEventosV4" ref="A1:J19">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora"/>
@@ -1251,10 +1271,10 @@
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="12">
+      <c r="A17" s="11">
         <v>46179</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="9">
         <v>0.375</v>
       </c>
       <c r="C17" t="s">
@@ -1283,10 +1303,10 @@
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="12">
+      <c r="A18" s="11">
         <v>46179</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="9">
         <v>0.41666666666666669</v>
       </c>
       <c r="C18" t="s">
@@ -1314,8 +1334,28 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="12"/>
+    <row r="19" spans="1:10" ht="28.5">
+      <c r="A19" s="12">
+        <v>46181</v>
+      </c>
+      <c r="B19" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" t="s">
+        <v>106</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="12"/>
@@ -1325,6 +1365,7 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="12"/>
+      <c r="D22" s="15"/>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="12"/>
@@ -2797,8 +2838,8 @@
         <v>76</v>
       </c>
       <c r="B4">
-        <f>COUNTA(EVENTOS!E2:E18)</f>
-        <v>17</v>
+        <f>COUNTA(EVENTOS!E2:E19)</f>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15">
@@ -2806,7 +2847,7 @@
         <v>77</v>
       </c>
       <c r="B5">
-        <f>COUNTIF(EVENTOS!J2:J18,"Ejecutado")</f>
+        <f>COUNTIF(EVENTOS!J2:J19,"Ejecutado")</f>
         <v>2</v>
       </c>
     </row>
@@ -2815,7 +2856,7 @@
         <v>78</v>
       </c>
       <c r="B6">
-        <f>COUNTIF(EVENTOS!J2:J18,"Pendiente")</f>
+        <f>COUNTIF(EVENTOS!J2:J19,"Pendiente")</f>
         <v>13</v>
       </c>
     </row>
@@ -2824,7 +2865,7 @@
         <v>79</v>
       </c>
       <c r="B7">
-        <f>COUNTIF(EVENTOS!H2:H18,"Alta")</f>
+        <f>COUNTIF(EVENTOS!H2:H19,"Alta")</f>
         <v>14</v>
       </c>
     </row>
@@ -2833,8 +2874,8 @@
         <v>80</v>
       </c>
       <c r="B8">
-        <f>COUNTA(EVENTOS!F2:F18)</f>
-        <v>17</v>
+        <f>COUNTA(EVENTOS!F2:F19)</f>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC37A300-22B0-4B40-B6DD-B9B6E12E4E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A653DD-0324-43DE-9B6E-2CDDE8F6C02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="176">
   <si>
     <t>Fecha</t>
   </si>
@@ -532,6 +532,84 @@
   <si>
     <t>Ubicaciones registradas</t>
   </si>
+  <si>
+    <t>Sede Villa - Martes de la Semana de Ingeniería</t>
+  </si>
+  <si>
+    <t>Requerimientos :</t>
+  </si>
+  <si>
+    <t>• 3 toldos con 3 puntos de luz.</t>
+  </si>
+  <si>
+    <t>• 3 mesas con mantel.</t>
+  </si>
+  <si>
+    <t>• 6 sillas (2 por toldo).</t>
+  </si>
+  <si>
+    <t>• 1 televisor.</t>
+  </si>
+  <si>
+    <t>Sede Villa - Feria Empresarial</t>
+  </si>
+  <si>
+    <t>Sede Villa – Jardin Lote 28</t>
+  </si>
+  <si>
+    <t>• 8 toldos.</t>
+  </si>
+  <si>
+    <t>• 8 mesas con mantel.</t>
+  </si>
+  <si>
+    <t>• 16 sillas (2 por mesa).</t>
+  </si>
+  <si>
+    <t>MEDICINA HUMANA</t>
+  </si>
+  <si>
+    <t>Campaña Donacion de Sangre</t>
+  </si>
+  <si>
+    <t>Clínica de Simulación</t>
+  </si>
+  <si>
+    <t>• 5 mesas</t>
+  </si>
+  <si>
+    <t>• 25 sillas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no especifica </t>
+  </si>
+  <si>
+    <t>Hall del Pabellón N</t>
+  </si>
+  <si>
+    <t>Por favor retirar muebles del hall y colocar: 9:30 am a 12:00 pm</t>
+  </si>
+  <si>
+    <t>- 60 sillas en formato auditorio.</t>
+  </si>
+  <si>
+    <t>-  TV en rack al fondo  - la del pabellón L.</t>
+  </si>
+  <si>
+    <t>- Bandera de Científica y del Perú</t>
+  </si>
+  <si>
+    <t>- Podio de Científica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaña Certijoven </t>
+  </si>
+  <si>
+    <t>Pabellon I</t>
+  </si>
+  <si>
+    <t>solicitamos su apoyo para habilitar una mesa con mantel + dos sillas en el hall de pasillo del pabellón I. Para la socialización del aplicativo ApliJoven de MINEDU que se realizará el lunes16 de junio de 8:30 am a 2:00</t>
+  </si>
 </sst>
 </file>
 
@@ -540,7 +618,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -567,8 +645,19 @@
       <color theme="1"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF991B1B"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -597,8 +686,26 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E6F5"/>
+        <bgColor rgb="FFC0E6F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEE2E2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61CBF3"/>
+        <bgColor rgb="FFC0E6F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -643,11 +750,159 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF44B3E1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF44B3E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF44B3E1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF44B3E1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF44B3E1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF44B3E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF44B3E1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF44B3E1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF44B3E1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF44B3E1"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -678,10 +933,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -696,6 +947,118 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -937,7 +1300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1458,2726 +1821,3235 @@
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C17" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="14" t="s">
+      <c r="C17" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="G17" s="16" t="s">
+      <c r="G17" s="14" t="s">
         <v>85</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
       </c>
-      <c r="I17" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="15" t="s">
+      <c r="I17" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C18" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="14" t="s">
+      <c r="C18" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="14" t="s">
         <v>85</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
       </c>
-      <c r="I18" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" s="15" t="s">
+      <c r="I18" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C19" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="14" t="s">
+      <c r="C19" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="G19" s="14" t="s">
         <v>85</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
       </c>
-      <c r="I19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" s="15" t="s">
+      <c r="I19" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="14" t="s">
+      <c r="C20" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="14" t="s">
         <v>85</v>
       </c>
       <c r="H20" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" s="15" t="s">
+      <c r="I20" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="14" t="s">
+      <c r="C21" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G21" s="16" t="s">
+      <c r="G21" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" s="15" t="s">
+      <c r="I21" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E22" s="14" t="s">
+      <c r="C22" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
       </c>
-      <c r="I22" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="15" t="s">
+      <c r="I22" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="14" t="s">
+      <c r="C23" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G23" s="16" t="s">
+      <c r="G23" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
       </c>
-      <c r="I23" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23" s="15" t="s">
+      <c r="I23" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E24" s="14" t="s">
+      <c r="C24" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
       </c>
-      <c r="I24" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" s="15" t="s">
+      <c r="I24" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" s="14" t="s">
+      <c r="C25" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G25" s="16" t="s">
+      <c r="G25" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
       </c>
-      <c r="I25" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J25" s="15" t="s">
+      <c r="I25" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J25" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C26" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="14" t="s">
+      <c r="C26" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
       </c>
-      <c r="I26" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J26" s="15" t="s">
+      <c r="I26" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C27" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E27" s="14" t="s">
+      <c r="C27" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G27" s="16" t="s">
+      <c r="G27" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H27" t="s">
         <v>17</v>
       </c>
-      <c r="I27" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" s="15" t="s">
+      <c r="I27" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C28" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="14" t="s">
+      <c r="C28" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G28" s="16" t="s">
+      <c r="G28" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
       </c>
-      <c r="I28" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J28" s="15" t="s">
+      <c r="I28" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E29" s="14" t="s">
+      <c r="C29" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G29" s="16" t="s">
+      <c r="G29" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H29" t="s">
         <v>17</v>
       </c>
-      <c r="I29" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J29" s="15" t="s">
+      <c r="I29" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C30" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E30" s="14" t="s">
+      <c r="C30" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G30" s="16" t="s">
+      <c r="G30" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
       </c>
-      <c r="I30" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J30" s="15" t="s">
+      <c r="I30" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J30" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C31" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E31" s="14" t="s">
+      <c r="C31" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="G31" s="16" t="s">
+      <c r="G31" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
       </c>
-      <c r="I31" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J31" s="15" t="s">
+      <c r="I31" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J31" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C32" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E32" s="14" t="s">
+      <c r="C32" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="G32" s="16" t="s">
+      <c r="G32" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H32" t="s">
         <v>17</v>
       </c>
-      <c r="I32" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J32" s="15" t="s">
+      <c r="I32" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C33" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E33" s="14" t="s">
+      <c r="C33" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="G33" s="16" t="s">
+      <c r="G33" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H33" t="s">
         <v>17</v>
       </c>
-      <c r="I33" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J33" s="15" t="s">
+      <c r="I33" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C34" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E34" s="14" t="s">
+      <c r="C34" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="G34" s="16" t="s">
+      <c r="G34" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
       </c>
-      <c r="I34" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J34" s="15" t="s">
+      <c r="I34" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C35" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E35" s="14" t="s">
+      <c r="C35" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="G35" s="16" t="s">
+      <c r="G35" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H35" t="s">
         <v>17</v>
       </c>
-      <c r="I35" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J35" s="15" t="s">
+      <c r="I35" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C36" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E36" s="14" t="s">
+      <c r="C36" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F36" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G36" s="16" t="s">
+      <c r="G36" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
       </c>
-      <c r="I36" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J36" s="15" t="s">
+      <c r="I36" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="18" t="s">
+      <c r="A37" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C37" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E37" s="14" t="s">
+      <c r="C37" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E37" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G37" s="16" t="s">
+      <c r="G37" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H37" t="s">
         <v>17</v>
       </c>
-      <c r="I37" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J37" s="15" t="s">
+      <c r="I37" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C38" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E38" s="14" t="s">
+      <c r="C38" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E38" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G38" s="16" t="s">
+      <c r="G38" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
       </c>
-      <c r="I38" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J38" s="15" t="s">
+      <c r="I38" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C39" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E39" s="14" t="s">
+      <c r="C39" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="F39" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G39" s="16" t="s">
+      <c r="G39" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
       </c>
-      <c r="I39" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J39" s="15" t="s">
+      <c r="I39" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="18" t="s">
+      <c r="A40" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C40" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E40" s="14" t="s">
+      <c r="C40" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E40" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="F40" s="14" t="s">
+      <c r="F40" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="G40" s="16" t="s">
+      <c r="G40" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
       </c>
-      <c r="I40" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J40" s="15" t="s">
+      <c r="I40" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="18" t="s">
+      <c r="A41" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C41" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E41" s="14" t="s">
+      <c r="C41" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F41" s="14" t="s">
+      <c r="F41" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G41" s="16" t="s">
+      <c r="G41" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H41" t="s">
         <v>17</v>
       </c>
-      <c r="I41" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J41" s="15" t="s">
+      <c r="I41" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="18" t="s">
+      <c r="A42" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C42" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E42" s="14" t="s">
+      <c r="C42" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F42" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G42" s="16" t="s">
+      <c r="G42" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
       </c>
-      <c r="I42" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J42" s="15" t="s">
+      <c r="I42" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="18" t="s">
+      <c r="A43" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C43" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E43" s="14" t="s">
+      <c r="C43" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F43" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G43" s="16" t="s">
+      <c r="G43" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
       </c>
-      <c r="I43" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J43" s="15" t="s">
+      <c r="I43" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J43" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="18" t="s">
+      <c r="A44" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C44" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E44" s="14" t="s">
+      <c r="C44" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E44" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F44" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G44" s="16" t="s">
+      <c r="G44" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
       </c>
-      <c r="I44" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J44" s="15" t="s">
+      <c r="I44" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J44" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="18" t="s">
+      <c r="A45" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="17" t="s">
+      <c r="B45" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C45" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E45" s="14" t="s">
+      <c r="C45" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E45" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G45" s="16" t="s">
+      <c r="G45" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H45" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J45" s="15" t="s">
+      <c r="I45" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="18" t="s">
+      <c r="A46" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B46" s="17" t="s">
+      <c r="B46" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C46" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E46" s="14" t="s">
+      <c r="C46" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E46" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F46" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G46" s="16" t="s">
+      <c r="G46" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
       </c>
-      <c r="I46" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J46" s="15" t="s">
+      <c r="I46" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="18" t="s">
+      <c r="A47" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C47" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E47" s="14" t="s">
+      <c r="C47" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E47" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F47" s="14" t="s">
+      <c r="F47" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G47" s="16" t="s">
+      <c r="G47" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
       </c>
-      <c r="I47" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J47" s="15" t="s">
+      <c r="I47" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="18" t="s">
+      <c r="A48" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B48" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C48" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E48" s="14" t="s">
+      <c r="C48" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E48" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F48" s="14" t="s">
+      <c r="F48" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G48" s="16" t="s">
+      <c r="G48" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H48" t="s">
         <v>17</v>
       </c>
-      <c r="I48" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J48" s="15" t="s">
+      <c r="I48" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="18" t="s">
+      <c r="A49" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="B49" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C49" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E49" s="14" t="s">
+      <c r="C49" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E49" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F49" s="14" t="s">
+      <c r="F49" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G49" s="16" t="s">
+      <c r="G49" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
       </c>
-      <c r="I49" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J49" s="15" t="s">
+      <c r="I49" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J49" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="18" t="s">
+      <c r="A50" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B50" s="17" t="s">
+      <c r="B50" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C50" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E50" s="14" t="s">
+      <c r="C50" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E50" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F50" s="14" t="s">
+      <c r="F50" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G50" s="16" t="s">
+      <c r="G50" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H50" t="s">
         <v>17</v>
       </c>
-      <c r="I50" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J50" s="15" t="s">
+      <c r="I50" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="18" t="s">
+      <c r="A51" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B51" s="17" t="s">
+      <c r="B51" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C51" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E51" s="14" t="s">
+      <c r="C51" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E51" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="F51" s="14" t="s">
+      <c r="F51" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="G51" s="16" t="s">
+      <c r="G51" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H51" t="s">
         <v>17</v>
       </c>
-      <c r="I51" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J51" s="15" t="s">
+      <c r="I51" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J51" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="18" t="s">
+      <c r="A52" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="B52" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C52" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E52" s="14" t="s">
+      <c r="C52" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E52" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="F52" s="14" t="s">
+      <c r="F52" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="G52" s="16" t="s">
+      <c r="G52" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
       </c>
-      <c r="I52" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J52" s="15" t="s">
+      <c r="I52" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J52" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="18" t="s">
+      <c r="A53" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B53" s="17" t="s">
+      <c r="B53" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C53" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E53" s="14" t="s">
+      <c r="C53" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E53" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="F53" s="14" t="s">
+      <c r="F53" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="G53" s="16" t="s">
+      <c r="G53" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H53" t="s">
         <v>17</v>
       </c>
-      <c r="I53" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J53" s="15" t="s">
+      <c r="I53" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J53" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="18" t="s">
+      <c r="A54" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="17" t="s">
+      <c r="B54" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C54" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E54" s="14" t="s">
+      <c r="C54" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E54" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="F54" s="14" t="s">
+      <c r="F54" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="G54" s="16" t="s">
+      <c r="G54" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
       </c>
-      <c r="I54" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J54" s="15" t="s">
+      <c r="I54" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J54" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="18" t="s">
+      <c r="A55" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B55" s="17" t="s">
+      <c r="B55" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C55" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E55" s="14" t="s">
+      <c r="C55" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E55" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="F55" s="14" t="s">
+      <c r="F55" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="G55" s="16" t="s">
+      <c r="G55" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H55" t="s">
         <v>17</v>
       </c>
-      <c r="I55" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J55" s="15" t="s">
+      <c r="I55" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J55" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="18" t="s">
+      <c r="A56" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B56" s="17" t="s">
+      <c r="B56" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C56" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D56" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E56" s="14" t="s">
+      <c r="C56" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E56" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="F56" s="14" t="s">
+      <c r="F56" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="G56" s="16" t="s">
+      <c r="G56" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H56" t="s">
         <v>17</v>
       </c>
-      <c r="I56" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J56" s="15" t="s">
+      <c r="I56" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="18" t="s">
+      <c r="A57" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B57" s="17" t="s">
+      <c r="B57" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C57" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E57" s="14" t="s">
+      <c r="C57" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E57" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="F57" s="14" t="s">
+      <c r="F57" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="G57" s="16" t="s">
+      <c r="G57" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H57" t="s">
         <v>17</v>
       </c>
-      <c r="I57" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J57" s="15" t="s">
+      <c r="I57" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="18" t="s">
+      <c r="A58" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B58" s="17" t="s">
+      <c r="B58" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C58" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D58" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E58" s="14" t="s">
+      <c r="C58" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E58" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="F58" s="14" t="s">
+      <c r="F58" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="G58" s="16" t="s">
+      <c r="G58" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H58" t="s">
         <v>17</v>
       </c>
-      <c r="I58" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J58" s="15" t="s">
+      <c r="I58" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J58" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="18" t="s">
+      <c r="A59" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B59" s="17" t="s">
+      <c r="B59" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C59" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E59" s="14" t="s">
+      <c r="C59" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E59" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="F59" s="14" t="s">
+      <c r="F59" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="G59" s="16" t="s">
+      <c r="G59" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H59" t="s">
         <v>17</v>
       </c>
-      <c r="I59" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J59" s="15" t="s">
+      <c r="I59" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J59" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="18" t="s">
+      <c r="A60" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B60" s="17" t="s">
+      <c r="B60" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C60" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D60" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E60" s="14" t="s">
+      <c r="C60" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E60" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="F60" s="14" t="s">
+      <c r="F60" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="G60" s="16" t="s">
+      <c r="G60" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H60" t="s">
         <v>17</v>
       </c>
-      <c r="I60" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J60" s="15" t="s">
+      <c r="I60" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J60" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="18" t="s">
+      <c r="A61" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B61" s="17" t="s">
+      <c r="B61" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C61" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E61" s="14" t="s">
+      <c r="C61" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E61" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="F61" s="14" t="s">
+      <c r="F61" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G61" s="16" t="s">
+      <c r="G61" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H61" t="s">
         <v>17</v>
       </c>
-      <c r="I61" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J61" s="15" t="s">
+      <c r="I61" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J61" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="18" t="s">
+      <c r="A62" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B62" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C62" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D62" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E62" s="14" t="s">
+      <c r="C62" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E62" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="F62" s="14" t="s">
+      <c r="F62" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G62" s="16" t="s">
+      <c r="G62" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H62" t="s">
         <v>17</v>
       </c>
-      <c r="I62" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J62" s="15" t="s">
+      <c r="I62" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J62" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="18" t="s">
+      <c r="A63" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B63" s="17" t="s">
+      <c r="B63" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C63" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D63" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E63" s="14" t="s">
+      <c r="C63" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E63" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="F63" s="14" t="s">
+      <c r="F63" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G63" s="16" t="s">
+      <c r="G63" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H63" t="s">
         <v>17</v>
       </c>
-      <c r="I63" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J63" s="15" t="s">
+      <c r="I63" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J63" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="18" t="s">
+      <c r="A64" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B64" s="17" t="s">
+      <c r="B64" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C64" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D64" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E64" s="14" t="s">
+      <c r="C64" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E64" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="F64" s="14" t="s">
+      <c r="F64" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G64" s="16" t="s">
+      <c r="G64" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H64" t="s">
         <v>17</v>
       </c>
-      <c r="I64" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J64" s="15" t="s">
+      <c r="I64" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J64" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="18" t="s">
+      <c r="A65" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B65" s="17" t="s">
+      <c r="B65" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C65" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D65" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E65" s="14" t="s">
+      <c r="C65" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E65" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="F65" s="14" t="s">
+      <c r="F65" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G65" s="16" t="s">
+      <c r="G65" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H65" t="s">
         <v>17</v>
       </c>
-      <c r="I65" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J65" s="15" t="s">
+      <c r="I65" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J65" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="18" t="s">
+      <c r="A66" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="B66" s="17" t="s">
+      <c r="B66" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C66" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D66" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E66" s="14" t="s">
+      <c r="C66" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E66" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F66" s="14" t="s">
+      <c r="F66" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="G66" s="16" t="s">
+      <c r="G66" s="14" t="s">
         <v>114</v>
       </c>
       <c r="H66" t="s">
         <v>17</v>
       </c>
-      <c r="I66" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J66" s="15" t="s">
+      <c r="I66" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J66" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="18" t="s">
+      <c r="A67" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="B67" s="17" t="s">
+      <c r="B67" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C67" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D67" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E67" s="14" t="s">
+      <c r="C67" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E67" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F67" s="14" t="s">
+      <c r="F67" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="G67" s="16" t="s">
+      <c r="G67" s="14" t="s">
         <v>114</v>
       </c>
       <c r="H67" t="s">
         <v>17</v>
       </c>
-      <c r="I67" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J67" s="15" t="s">
+      <c r="I67" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J67" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="18" t="s">
+      <c r="A68" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="B68" s="17" t="s">
+      <c r="B68" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C68" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D68" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E68" s="14" t="s">
+      <c r="C68" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E68" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F68" s="14" t="s">
+      <c r="F68" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="G68" s="16" t="s">
+      <c r="G68" s="14" t="s">
         <v>114</v>
       </c>
       <c r="H68" t="s">
         <v>17</v>
       </c>
-      <c r="I68" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J68" s="15" t="s">
+      <c r="I68" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J68" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="18" t="s">
+      <c r="A69" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B69" s="17" t="s">
+      <c r="B69" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C69" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E69" s="14" t="s">
+      <c r="C69" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E69" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F69" s="14" t="s">
+      <c r="F69" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="G69" s="16" t="s">
+      <c r="G69" s="14" t="s">
         <v>114</v>
       </c>
       <c r="H69" t="s">
         <v>17</v>
       </c>
-      <c r="I69" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J69" s="15" t="s">
+      <c r="I69" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J69" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="18" t="s">
+      <c r="A70" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="B70" s="17" t="s">
+      <c r="B70" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C70" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D70" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E70" s="14" t="s">
+      <c r="C70" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E70" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="F70" s="14" t="s">
+      <c r="F70" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G70" s="16" t="s">
+      <c r="G70" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H70" t="s">
         <v>17</v>
       </c>
-      <c r="I70" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J70" s="15" t="s">
+      <c r="I70" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J70" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="18" t="s">
+      <c r="A71" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="B71" s="17" t="s">
+      <c r="B71" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C71" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D71" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E71" s="14" t="s">
+      <c r="C71" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E71" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="F71" s="14" t="s">
+      <c r="F71" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G71" s="16" t="s">
+      <c r="G71" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H71" t="s">
         <v>17</v>
       </c>
-      <c r="I71" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J71" s="15" t="s">
+      <c r="I71" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J71" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="18" t="s">
+      <c r="A72" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B72" s="17" t="s">
+      <c r="B72" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C72" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D72" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E72" s="14" t="s">
+      <c r="C72" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E72" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="F72" s="14" t="s">
+      <c r="F72" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G72" s="16" t="s">
+      <c r="G72" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H72" t="s">
         <v>17</v>
       </c>
-      <c r="I72" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J72" s="15" t="s">
+      <c r="I72" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="18" t="s">
+      <c r="A73" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B73" s="17" t="s">
+      <c r="B73" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C73" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D73" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E73" s="14" t="s">
+      <c r="C73" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E73" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="F73" s="14" t="s">
+      <c r="F73" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G73" s="16" t="s">
+      <c r="G73" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H73" t="s">
         <v>17</v>
       </c>
-      <c r="I73" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J73" s="15" t="s">
+      <c r="I73" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J73" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="18" t="s">
+      <c r="A74" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="B74" s="17" t="s">
+      <c r="B74" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C74" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D74" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E74" s="14" t="s">
+      <c r="C74" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E74" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F74" s="14" t="s">
+      <c r="F74" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="G74" s="16" t="s">
+      <c r="G74" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H74" t="s">
         <v>17</v>
       </c>
-      <c r="I74" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J74" s="15" t="s">
+      <c r="I74" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J74" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="18" t="s">
+      <c r="A75" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="B75" s="17" t="s">
+      <c r="B75" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C75" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D75" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E75" s="14" t="s">
+      <c r="C75" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E75" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F75" s="14" t="s">
+      <c r="F75" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="G75" s="16" t="s">
+      <c r="G75" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H75" t="s">
         <v>17</v>
       </c>
-      <c r="I75" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J75" s="15" t="s">
+      <c r="I75" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J75" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="18" t="s">
+      <c r="A76" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B76" s="17" t="s">
+      <c r="B76" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C76" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D76" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E76" s="14" t="s">
+      <c r="C76" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E76" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F76" s="14" t="s">
+      <c r="F76" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="G76" s="16" t="s">
+      <c r="G76" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H76" t="s">
         <v>17</v>
       </c>
-      <c r="I76" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J76" s="15" t="s">
+      <c r="I76" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J76" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="18" t="s">
+      <c r="A77" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B77" s="17" t="s">
+      <c r="B77" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C77" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D77" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E77" s="14" t="s">
+      <c r="C77" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E77" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F77" s="14" t="s">
+      <c r="F77" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="G77" s="16" t="s">
+      <c r="G77" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H77" t="s">
         <v>17</v>
       </c>
-      <c r="I77" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J77" s="15" t="s">
+      <c r="I77" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J77" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="18" t="s">
+      <c r="A78" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="B78" s="17" t="s">
+      <c r="B78" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C78" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D78" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E78" s="14" t="s">
+      <c r="C78" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E78" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="F78" s="14" t="s">
+      <c r="F78" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="G78" s="16" t="s">
+      <c r="G78" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H78" t="s">
         <v>17</v>
       </c>
-      <c r="I78" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J78" s="15" t="s">
+      <c r="I78" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J78" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="18" t="s">
+      <c r="A79" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="B79" s="17" t="s">
+      <c r="B79" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C79" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D79" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E79" s="14" t="s">
+      <c r="C79" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E79" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="F79" s="14" t="s">
+      <c r="F79" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="G79" s="16" t="s">
+      <c r="G79" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H79" t="s">
         <v>17</v>
       </c>
-      <c r="I79" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J79" s="15" t="s">
+      <c r="I79" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J79" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="18" t="s">
+      <c r="A80" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="B80" s="17" t="s">
+      <c r="B80" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C80" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D80" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E80" s="14" t="s">
+      <c r="C80" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E80" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="F80" s="14" t="s">
+      <c r="F80" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="G80" s="16" t="s">
+      <c r="G80" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H80" t="s">
         <v>17</v>
       </c>
-      <c r="I80" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J80" s="15" t="s">
+      <c r="I80" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J80" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="18" t="s">
+      <c r="A81" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B81" s="17" t="s">
+      <c r="B81" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C81" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D81" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E81" s="14" t="s">
+      <c r="C81" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E81" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="F81" s="14" t="s">
+      <c r="F81" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="G81" s="16" t="s">
+      <c r="G81" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H81" t="s">
         <v>17</v>
       </c>
-      <c r="I81" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J81" s="15" t="s">
+      <c r="I81" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J81" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="18" t="s">
+      <c r="A82" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="B82" s="17" t="s">
+      <c r="B82" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C82" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D82" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E82" s="14" t="s">
+      <c r="C82" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E82" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="F82" s="14" t="s">
+      <c r="F82" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="G82" s="16" t="s">
+      <c r="G82" s="14" t="s">
         <v>114</v>
       </c>
       <c r="H82" t="s">
         <v>17</v>
       </c>
-      <c r="I82" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J82" s="15" t="s">
+      <c r="I82" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J82" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="18" t="s">
+      <c r="A83" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B83" s="17" t="s">
+      <c r="B83" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C83" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D83" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E83" s="14" t="s">
+      <c r="C83" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E83" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="F83" s="14" t="s">
+      <c r="F83" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="G83" s="16" t="s">
+      <c r="G83" s="14" t="s">
         <v>114</v>
       </c>
       <c r="H83" t="s">
         <v>17</v>
       </c>
-      <c r="I83" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J83" s="15" t="s">
+      <c r="I83" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J83" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="18" t="s">
+      <c r="A84" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="B84" s="17" t="s">
+      <c r="B84" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C84" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D84" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E84" s="14" t="s">
+      <c r="C84" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E84" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="F84" s="14" t="s">
+      <c r="F84" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="G84" s="16" t="s">
+      <c r="G84" s="14" t="s">
         <v>114</v>
       </c>
       <c r="H84" t="s">
         <v>17</v>
       </c>
-      <c r="I84" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J84" s="15" t="s">
+      <c r="I84" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J84" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="18" t="s">
+      <c r="A85" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="B85" s="17" t="s">
+      <c r="B85" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C85" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D85" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E85" s="14" t="s">
+      <c r="C85" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E85" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="F85" s="14" t="s">
+      <c r="F85" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="G85" s="16" t="s">
+      <c r="G85" s="14" t="s">
         <v>114</v>
       </c>
       <c r="H85" t="s">
         <v>17</v>
       </c>
-      <c r="I85" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J85" s="15" t="s">
+      <c r="I85" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J85" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="18" t="s">
+      <c r="A86" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="B86" s="17" t="s">
+      <c r="B86" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C86" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D86" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E86" s="14" t="s">
+      <c r="C86" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E86" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="F86" s="14" t="s">
+      <c r="F86" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="G86" s="16" t="s">
+      <c r="G86" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H86" t="s">
         <v>17</v>
       </c>
-      <c r="I86" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J86" s="15" t="s">
+      <c r="I86" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J86" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="18" t="s">
+      <c r="A87" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="B87" s="17" t="s">
+      <c r="B87" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C87" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D87" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E87" s="14" t="s">
+      <c r="C87" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E87" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="F87" s="14" t="s">
+      <c r="F87" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="G87" s="16" t="s">
+      <c r="G87" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H87" t="s">
         <v>17</v>
       </c>
-      <c r="I87" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J87" s="15" t="s">
+      <c r="I87" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J87" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="18" t="s">
+      <c r="A88" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B88" s="17" t="s">
+      <c r="B88" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C88" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D88" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E88" s="14" t="s">
+      <c r="C88" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E88" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="F88" s="14" t="s">
+      <c r="F88" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="G88" s="16" t="s">
+      <c r="G88" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H88" t="s">
         <v>17</v>
       </c>
-      <c r="I88" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J88" s="15" t="s">
+      <c r="I88" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J88" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="18" t="s">
+      <c r="A89" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B89" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C89" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D89" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E89" s="14" t="s">
+      <c r="C89" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E89" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="F89" s="14" t="s">
+      <c r="F89" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="G89" s="16" t="s">
+      <c r="G89" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H89" t="s">
         <v>17</v>
       </c>
-      <c r="I89" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J89" s="15" t="s">
+      <c r="I89" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J89" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="18" t="s">
+      <c r="A90" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="B90" s="17" t="s">
+      <c r="B90" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C90" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D90" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E90" s="14" t="s">
+      <c r="C90" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E90" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="F90" s="14" t="s">
+      <c r="F90" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="G90" s="16" t="s">
+      <c r="G90" s="14" t="s">
         <v>114</v>
       </c>
       <c r="H90" t="s">
         <v>17</v>
       </c>
-      <c r="I90" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J90" s="15" t="s">
+      <c r="I90" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J90" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="18" t="s">
+      <c r="A91" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="B91" s="17" t="s">
+      <c r="B91" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C91" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D91" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E91" s="14" t="s">
+      <c r="C91" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E91" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="F91" s="14" t="s">
+      <c r="F91" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="G91" s="16" t="s">
+      <c r="G91" s="14" t="s">
         <v>114</v>
       </c>
       <c r="H91" t="s">
         <v>17</v>
       </c>
-      <c r="I91" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J91" s="15" t="s">
+      <c r="I91" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J91" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="18" t="s">
+      <c r="A92" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B92" s="17" t="s">
+      <c r="B92" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C92" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D92" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E92" s="14" t="s">
+      <c r="C92" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E92" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="F92" s="14" t="s">
+      <c r="F92" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="G92" s="16" t="s">
+      <c r="G92" s="14" t="s">
         <v>114</v>
       </c>
       <c r="H92" t="s">
         <v>17</v>
       </c>
-      <c r="I92" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J92" s="15" t="s">
+      <c r="I92" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J92" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="18" t="s">
+      <c r="A93" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="B93" s="17" t="s">
+      <c r="B93" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C93" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D93" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E93" s="14" t="s">
+      <c r="C93" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E93" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="F93" s="14" t="s">
+      <c r="F93" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="G93" s="16" t="s">
+      <c r="G93" s="14" t="s">
         <v>114</v>
       </c>
       <c r="H93" t="s">
         <v>17</v>
       </c>
-      <c r="I93" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J93" s="15" t="s">
+      <c r="I93" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J93" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="18" t="s">
+      <c r="A94" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="B94" s="17" t="s">
+      <c r="B94" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C94" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D94" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E94" s="14" t="s">
+      <c r="C94" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E94" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F94" s="14" t="s">
+      <c r="F94" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="G94" s="16" t="s">
+      <c r="G94" s="14" t="s">
         <v>85</v>
       </c>
       <c r="H94" t="s">
         <v>17</v>
       </c>
-      <c r="I94" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J94" s="15" t="s">
+      <c r="I94" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J94" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="18" t="s">
+      <c r="A95" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="B95" s="17" t="s">
+      <c r="B95" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C95" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D95" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E95" s="14" t="s">
+      <c r="C95" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E95" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F95" s="14" t="s">
+      <c r="F95" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="G95" s="16" t="s">
+      <c r="G95" s="14" t="s">
         <v>114</v>
       </c>
       <c r="H95" t="s">
         <v>17</v>
       </c>
-      <c r="I95" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J95" s="15" t="s">
+      <c r="I95" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J95" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="18" t="s">
+      <c r="A96" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B96" s="17" t="s">
+      <c r="B96" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C96" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D96" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E96" s="14" t="s">
+      <c r="C96" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E96" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="F96" s="14" t="s">
+      <c r="F96" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G96" s="16" t="s">
+      <c r="G96" s="14" t="s">
         <v>92</v>
       </c>
       <c r="H96" t="s">
         <v>17</v>
       </c>
-      <c r="I96" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J96" s="15" t="s">
+      <c r="I96" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J96" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="97" spans="1:10">
-      <c r="A97" s="18" t="s">
+      <c r="A97" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B97" s="17" t="s">
+      <c r="B97" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C97" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D97" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E97" s="14" t="s">
+      <c r="C97" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E97" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F97" s="14" t="s">
+      <c r="F97" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="G97" s="16" t="s">
+      <c r="G97" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H97" t="s">
         <v>17</v>
       </c>
-      <c r="I97" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J97" s="15" t="s">
+      <c r="I97" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J97" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="18" t="s">
+      <c r="A98" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="B98" s="17" t="s">
+      <c r="B98" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C98" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D98" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E98" s="14" t="s">
+      <c r="C98" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E98" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="F98" s="14" t="s">
+      <c r="F98" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="G98" s="16" t="s">
+      <c r="G98" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H98" t="s">
         <v>17</v>
       </c>
-      <c r="I98" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J98" s="15" t="s">
+      <c r="I98" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J98" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="18" t="s">
+      <c r="A99" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="B99" s="17" t="s">
+      <c r="B99" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C99" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D99" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E99" s="14" t="s">
+      <c r="C99" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E99" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="F99" s="14" t="s">
+      <c r="F99" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="G99" s="16" t="s">
+      <c r="G99" s="14" t="s">
         <v>114</v>
       </c>
       <c r="H99" t="s">
         <v>17</v>
       </c>
-      <c r="I99" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J99" s="15" t="s">
+      <c r="I99" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J99" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="18" t="s">
+      <c r="A100" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="B100" s="17" t="s">
+      <c r="B100" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C100" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D100" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E100" s="14" t="s">
+      <c r="C100" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E100" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="F100" s="14" t="s">
+      <c r="F100" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="G100" s="16" t="s">
+      <c r="G100" s="14" t="s">
         <v>108</v>
       </c>
       <c r="H100" t="s">
         <v>17</v>
       </c>
-      <c r="I100" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J100" s="15" t="s">
+      <c r="I100" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J100" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" s="18" t="s">
+      <c r="A101" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="B101" s="17" t="s">
+      <c r="B101" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C101" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D101" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E101" s="14" t="s">
+      <c r="C101" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E101" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="F101" s="14" t="s">
+      <c r="F101" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="G101" s="16" t="s">
+      <c r="G101" s="14" t="s">
         <v>114</v>
       </c>
       <c r="H101" t="s">
         <v>17</v>
       </c>
-      <c r="I101" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J101" s="15" t="s">
+      <c r="I101" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J101" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102" s="31">
+        <v>46182</v>
+      </c>
+      <c r="B102" s="35">
+        <v>0.47152777777777777</v>
+      </c>
+      <c r="C102" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="D102" s="43">
+        <v>81688</v>
+      </c>
+      <c r="E102" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="F102" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="G102" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="H102" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="I102" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="J102" s="52" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" s="32"/>
+      <c r="B103" s="36"/>
+      <c r="C103" s="40"/>
+      <c r="D103" s="44"/>
+      <c r="E103" s="48"/>
+      <c r="F103" s="48"/>
+      <c r="G103" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="H103" s="50"/>
+      <c r="I103" s="48"/>
+      <c r="J103" s="53"/>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104" s="32"/>
+      <c r="B104" s="36"/>
+      <c r="C104" s="40"/>
+      <c r="D104" s="44"/>
+      <c r="E104" s="48"/>
+      <c r="F104" s="48"/>
+      <c r="G104" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="H104" s="50"/>
+      <c r="I104" s="48"/>
+      <c r="J104" s="53"/>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" s="32"/>
+      <c r="B105" s="36"/>
+      <c r="C105" s="40"/>
+      <c r="D105" s="44"/>
+      <c r="E105" s="48"/>
+      <c r="F105" s="48"/>
+      <c r="G105" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="H105" s="50"/>
+      <c r="I105" s="48"/>
+      <c r="J105" s="53"/>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106" s="33"/>
+      <c r="B106" s="37"/>
+      <c r="C106" s="41"/>
+      <c r="D106" s="45"/>
+      <c r="E106" s="49"/>
+      <c r="F106" s="49"/>
+      <c r="G106" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="H106" s="50"/>
+      <c r="I106" s="49"/>
+      <c r="J106" s="54"/>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" s="30">
+        <v>46186</v>
+      </c>
+      <c r="B107" s="34">
+        <v>0.47152777777777777</v>
+      </c>
+      <c r="C107" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="D107" s="42">
+        <v>81685</v>
+      </c>
+      <c r="E107" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="F107" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="G107" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="H107" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="I107" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="J107" s="51" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" s="32"/>
+      <c r="B108" s="36"/>
+      <c r="C108" s="40"/>
+      <c r="D108" s="44"/>
+      <c r="E108" s="48"/>
+      <c r="F108" s="48"/>
+      <c r="G108" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="H108" s="50"/>
+      <c r="I108" s="48"/>
+      <c r="J108" s="53"/>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" s="32"/>
+      <c r="B109" s="36"/>
+      <c r="C109" s="40"/>
+      <c r="D109" s="44"/>
+      <c r="E109" s="48"/>
+      <c r="F109" s="48"/>
+      <c r="G109" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="H109" s="50"/>
+      <c r="I109" s="48"/>
+      <c r="J109" s="53"/>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110" s="32"/>
+      <c r="B110" s="36"/>
+      <c r="C110" s="40"/>
+      <c r="D110" s="44"/>
+      <c r="E110" s="48"/>
+      <c r="F110" s="48"/>
+      <c r="G110" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="H110" s="50"/>
+      <c r="I110" s="48"/>
+      <c r="J110" s="53"/>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111" s="33"/>
+      <c r="B111" s="37"/>
+      <c r="C111" s="41"/>
+      <c r="D111" s="45"/>
+      <c r="E111" s="49"/>
+      <c r="F111" s="49"/>
+      <c r="G111" s="22"/>
+      <c r="H111" s="50"/>
+      <c r="I111" s="49"/>
+      <c r="J111" s="54"/>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112" s="30">
+        <v>46190</v>
+      </c>
+      <c r="B112" s="34">
+        <v>0.77152777777777781</v>
+      </c>
+      <c r="C112" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="D112" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="E112" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="F112" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="G112" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="H112" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="I112" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="J112" s="51" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="A113" s="32"/>
+      <c r="B113" s="36"/>
+      <c r="C113" s="40"/>
+      <c r="D113" s="44"/>
+      <c r="E113" s="48"/>
+      <c r="F113" s="48"/>
+      <c r="G113" s="19"/>
+      <c r="H113" s="50"/>
+      <c r="I113" s="48"/>
+      <c r="J113" s="53"/>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114" s="32"/>
+      <c r="B114" s="36"/>
+      <c r="C114" s="40"/>
+      <c r="D114" s="44"/>
+      <c r="E114" s="48"/>
+      <c r="F114" s="48"/>
+      <c r="G114" s="19"/>
+      <c r="H114" s="50"/>
+      <c r="I114" s="48"/>
+      <c r="J114" s="53"/>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="A115" s="32"/>
+      <c r="B115" s="36"/>
+      <c r="C115" s="40"/>
+      <c r="D115" s="44"/>
+      <c r="E115" s="48"/>
+      <c r="F115" s="48"/>
+      <c r="G115" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="H115" s="50"/>
+      <c r="I115" s="48"/>
+      <c r="J115" s="53"/>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="A116" s="33"/>
+      <c r="B116" s="37"/>
+      <c r="C116" s="41"/>
+      <c r="D116" s="45"/>
+      <c r="E116" s="49"/>
+      <c r="F116" s="49"/>
+      <c r="G116" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="H116" s="50"/>
+      <c r="I116" s="49"/>
+      <c r="J116" s="54"/>
+    </row>
+    <row r="117" spans="1:10">
+      <c r="A117" s="30">
+        <v>46191</v>
+      </c>
+      <c r="B117" s="34">
+        <v>0.77152777777777781</v>
+      </c>
+      <c r="C117" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="D117" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="E117" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="F117" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="G117" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="H117" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="I117" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="J117" s="51" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10">
+      <c r="A118" s="32"/>
+      <c r="B118" s="36"/>
+      <c r="C118" s="40"/>
+      <c r="D118" s="44"/>
+      <c r="E118" s="48"/>
+      <c r="F118" s="48"/>
+      <c r="G118" s="19"/>
+      <c r="H118" s="50"/>
+      <c r="I118" s="48"/>
+      <c r="J118" s="53"/>
+    </row>
+    <row r="119" spans="1:10">
+      <c r="A119" s="32"/>
+      <c r="B119" s="36"/>
+      <c r="C119" s="40"/>
+      <c r="D119" s="44"/>
+      <c r="E119" s="48"/>
+      <c r="F119" s="48"/>
+      <c r="G119" s="19"/>
+      <c r="H119" s="50"/>
+      <c r="I119" s="48"/>
+      <c r="J119" s="53"/>
+    </row>
+    <row r="120" spans="1:10">
+      <c r="A120" s="32"/>
+      <c r="B120" s="36"/>
+      <c r="C120" s="40"/>
+      <c r="D120" s="44"/>
+      <c r="E120" s="48"/>
+      <c r="F120" s="48"/>
+      <c r="G120" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="H120" s="50"/>
+      <c r="I120" s="48"/>
+      <c r="J120" s="53"/>
+    </row>
+    <row r="121" spans="1:10">
+      <c r="A121" s="33"/>
+      <c r="B121" s="37"/>
+      <c r="C121" s="41"/>
+      <c r="D121" s="45"/>
+      <c r="E121" s="49"/>
+      <c r="F121" s="49"/>
+      <c r="G121" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="H121" s="50"/>
+      <c r="I121" s="49"/>
+      <c r="J121" s="54"/>
+    </row>
+    <row r="122" spans="1:10" ht="28.5">
+      <c r="A122" s="30">
+        <v>46183</v>
+      </c>
+      <c r="B122" s="34">
+        <v>0.77916666666666667</v>
+      </c>
+      <c r="C122" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="D122" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="E122" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="F122" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="G122" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="H122" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="I122" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="J122" s="51" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
+      <c r="A123" s="32"/>
+      <c r="B123" s="36"/>
+      <c r="C123" s="40"/>
+      <c r="D123" s="44"/>
+      <c r="E123" s="48"/>
+      <c r="F123" s="48"/>
+      <c r="G123" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="H123" s="50"/>
+      <c r="I123" s="48"/>
+      <c r="J123" s="53"/>
+    </row>
+    <row r="124" spans="1:10">
+      <c r="A124" s="32"/>
+      <c r="B124" s="36"/>
+      <c r="C124" s="40"/>
+      <c r="D124" s="44"/>
+      <c r="E124" s="48"/>
+      <c r="F124" s="48"/>
+      <c r="G124" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="H124" s="50"/>
+      <c r="I124" s="48"/>
+      <c r="J124" s="53"/>
+    </row>
+    <row r="125" spans="1:10">
+      <c r="A125" s="32"/>
+      <c r="B125" s="36"/>
+      <c r="C125" s="40"/>
+      <c r="D125" s="44"/>
+      <c r="E125" s="48"/>
+      <c r="F125" s="48"/>
+      <c r="G125" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="H125" s="50"/>
+      <c r="I125" s="48"/>
+      <c r="J125" s="53"/>
+    </row>
+    <row r="126" spans="1:10">
+      <c r="A126" s="33"/>
+      <c r="B126" s="37"/>
+      <c r="C126" s="41"/>
+      <c r="D126" s="45"/>
+      <c r="E126" s="49"/>
+      <c r="F126" s="49"/>
+      <c r="G126" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="H126" s="50"/>
+      <c r="I126" s="49"/>
+      <c r="J126" s="54"/>
+    </row>
+    <row r="127" spans="1:10" ht="57">
+      <c r="A127" s="24">
+        <v>46189</v>
+      </c>
+      <c r="B127" s="25">
+        <v>0.77916666666666667</v>
+      </c>
+      <c r="C127" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D127" s="27">
+        <v>9744</v>
+      </c>
+      <c r="E127" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="F127" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="G127" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="H127" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I127" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" s="29" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="45">
+    <mergeCell ref="H122:H126"/>
+    <mergeCell ref="I122:I126"/>
+    <mergeCell ref="J122:J126"/>
+    <mergeCell ref="A122:A126"/>
+    <mergeCell ref="B122:B126"/>
+    <mergeCell ref="C122:C126"/>
+    <mergeCell ref="D122:D126"/>
+    <mergeCell ref="E122:E126"/>
+    <mergeCell ref="F122:F126"/>
+    <mergeCell ref="J112:J116"/>
+    <mergeCell ref="A117:A121"/>
+    <mergeCell ref="B117:B121"/>
+    <mergeCell ref="C117:C121"/>
+    <mergeCell ref="D117:D121"/>
+    <mergeCell ref="E117:E121"/>
+    <mergeCell ref="F117:F121"/>
+    <mergeCell ref="H117:H121"/>
+    <mergeCell ref="I117:I121"/>
+    <mergeCell ref="J117:J121"/>
+    <mergeCell ref="I107:I111"/>
+    <mergeCell ref="J107:J111"/>
+    <mergeCell ref="A112:A116"/>
+    <mergeCell ref="B112:B116"/>
+    <mergeCell ref="C112:C116"/>
+    <mergeCell ref="D112:D116"/>
+    <mergeCell ref="E112:E116"/>
+    <mergeCell ref="F112:F116"/>
+    <mergeCell ref="H112:H116"/>
+    <mergeCell ref="I112:I116"/>
+    <mergeCell ref="H102:H106"/>
+    <mergeCell ref="I102:I106"/>
+    <mergeCell ref="J102:J106"/>
+    <mergeCell ref="A107:A111"/>
+    <mergeCell ref="B107:B111"/>
+    <mergeCell ref="C107:C111"/>
+    <mergeCell ref="D107:D111"/>
+    <mergeCell ref="E107:E111"/>
+    <mergeCell ref="F107:F111"/>
+    <mergeCell ref="H107:H111"/>
+    <mergeCell ref="A102:A106"/>
+    <mergeCell ref="B102:B106"/>
+    <mergeCell ref="C102:C106"/>
+    <mergeCell ref="D102:D106"/>
+    <mergeCell ref="E102:E106"/>
+    <mergeCell ref="F102:F106"/>
+  </mergeCells>
   <conditionalFormatting sqref="H2:H101">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>H2="Alta"</formula>
@@ -4288,14 +5160,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="5" t="s">

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A653DD-0324-43DE-9B6E-2CDDE8F6C02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC4FE56-6251-490D-86C4-65961274E93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="190">
   <si>
     <t>Fecha</t>
   </si>
@@ -609,6 +609,48 @@
   </si>
   <si>
     <t>solicitamos su apoyo para habilitar una mesa con mantel + dos sillas en el hall de pasillo del pabellón I. Para la socialización del aplicativo ApliJoven de MINEDU que se realizará el lunes16 de junio de 8:30 am a 2:00</t>
+  </si>
+  <si>
+    <t>Gaming Tournament</t>
+  </si>
+  <si>
+    <t>Auditorio O203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">solicitar el siguiente apoyo:                                                                      * 3 mesas con mantel.                                                                                                      Agradecemos mucho su apoyo y quedamos atentos a cualquier información adicional que necesiten para la coordinación.                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARRERA DE ENFERMERIA </t>
+  </si>
+  <si>
+    <t>Campaña por el día nacional de la prueba rápida del VIH</t>
+  </si>
+  <si>
+    <t>Jardín de pabellón N</t>
+  </si>
+  <si>
+    <t>Requerimiento :</t>
+  </si>
+  <si>
+    <t>Cinco toldos para la atención de los servicios.</t>
+  </si>
+  <si>
+    <t>Mesas (06) y sillas para los servicios (4 x cada mesa)</t>
+  </si>
+  <si>
+    <t>Manteles para todas las mesas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">los cables y puntos de conexión </t>
+  </si>
+  <si>
+    <t>AREA DE CCBB</t>
+  </si>
+  <si>
+    <t>Coloquio Internacional</t>
+  </si>
+  <si>
+    <t>Los insumos deberan estar el 12 y 13 de junio de 07:00 a 18:00 horas 5 sillones 2 mesitas mesa para registro vestida + 2 sillas 3 mesas para catering vestidas Recoger banner y totem de garita nueva (dice coloquio internacional de estudios generales 2026) 73 sillas Se requiere 2 mesas vestidas, palos de separación de ambiente.</t>
   </si>
 </sst>
 </file>
@@ -902,7 +944,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -948,10 +990,6 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -985,10 +1023,28 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1000,10 +1056,7 @@
     <xf numFmtId="20" fontId="6" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="6" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1012,10 +1065,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1024,40 +1074,47 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1300,7 +1357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J127"/>
+  <dimension ref="A1:J136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -3324,7 +3381,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" ht="14.25" customHeight="1">
       <c r="A64" s="16" t="s">
         <v>94</v>
       </c>
@@ -4541,16 +4598,16 @@
       </c>
     </row>
     <row r="102" spans="1:10">
-      <c r="A102" s="31">
+      <c r="A102" s="49">
         <v>46182</v>
       </c>
-      <c r="B102" s="35">
+      <c r="B102" s="50">
         <v>0.47152777777777777</v>
       </c>
-      <c r="C102" s="39" t="s">
+      <c r="C102" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="D102" s="43">
+      <c r="D102" s="52">
         <v>81688</v>
       </c>
       <c r="E102" s="47" t="s">
@@ -4559,480 +4616,676 @@
       <c r="F102" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="G102" s="21" t="s">
+      <c r="G102" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="H102" s="50" t="s">
+      <c r="H102" s="28" t="s">
         <v>17</v>
       </c>
       <c r="I102" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="J102" s="52" t="s">
+      <c r="J102" s="48" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="103" spans="1:10">
-      <c r="A103" s="32"/>
-      <c r="B103" s="36"/>
-      <c r="C103" s="40"/>
-      <c r="D103" s="44"/>
-      <c r="E103" s="48"/>
-      <c r="F103" s="48"/>
-      <c r="G103" s="20" t="s">
+      <c r="A103" s="36"/>
+      <c r="B103" s="39"/>
+      <c r="C103" s="42"/>
+      <c r="D103" s="45"/>
+      <c r="E103" s="30"/>
+      <c r="F103" s="30"/>
+      <c r="G103" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="H103" s="50"/>
-      <c r="I103" s="48"/>
-      <c r="J103" s="53"/>
+      <c r="H103" s="28"/>
+      <c r="I103" s="30"/>
+      <c r="J103" s="33"/>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" s="32"/>
-      <c r="B104" s="36"/>
-      <c r="C104" s="40"/>
-      <c r="D104" s="44"/>
-      <c r="E104" s="48"/>
-      <c r="F104" s="48"/>
-      <c r="G104" s="20" t="s">
+      <c r="A104" s="36"/>
+      <c r="B104" s="39"/>
+      <c r="C104" s="42"/>
+      <c r="D104" s="45"/>
+      <c r="E104" s="30"/>
+      <c r="F104" s="30"/>
+      <c r="G104" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="H104" s="50"/>
-      <c r="I104" s="48"/>
-      <c r="J104" s="53"/>
+      <c r="H104" s="28"/>
+      <c r="I104" s="30"/>
+      <c r="J104" s="33"/>
     </row>
     <row r="105" spans="1:10">
-      <c r="A105" s="32"/>
-      <c r="B105" s="36"/>
-      <c r="C105" s="40"/>
-      <c r="D105" s="44"/>
-      <c r="E105" s="48"/>
-      <c r="F105" s="48"/>
-      <c r="G105" s="20" t="s">
+      <c r="A105" s="36"/>
+      <c r="B105" s="39"/>
+      <c r="C105" s="42"/>
+      <c r="D105" s="45"/>
+      <c r="E105" s="30"/>
+      <c r="F105" s="30"/>
+      <c r="G105" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="H105" s="50"/>
-      <c r="I105" s="48"/>
-      <c r="J105" s="53"/>
+      <c r="H105" s="28"/>
+      <c r="I105" s="30"/>
+      <c r="J105" s="33"/>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" s="33"/>
-      <c r="B106" s="37"/>
-      <c r="C106" s="41"/>
-      <c r="D106" s="45"/>
-      <c r="E106" s="49"/>
-      <c r="F106" s="49"/>
-      <c r="G106" s="22" t="s">
+      <c r="A106" s="37"/>
+      <c r="B106" s="40"/>
+      <c r="C106" s="43"/>
+      <c r="D106" s="46"/>
+      <c r="E106" s="31"/>
+      <c r="F106" s="31"/>
+      <c r="G106" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="H106" s="50"/>
-      <c r="I106" s="49"/>
-      <c r="J106" s="54"/>
+      <c r="H106" s="28"/>
+      <c r="I106" s="31"/>
+      <c r="J106" s="34"/>
     </row>
     <row r="107" spans="1:10">
-      <c r="A107" s="30">
+      <c r="A107" s="35">
         <v>46186</v>
       </c>
-      <c r="B107" s="34">
+      <c r="B107" s="38">
         <v>0.47152777777777777</v>
       </c>
-      <c r="C107" s="38" t="s">
+      <c r="C107" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="D107" s="42">
+      <c r="D107" s="44">
         <v>81685</v>
       </c>
-      <c r="E107" s="46" t="s">
+      <c r="E107" s="29" t="s">
         <v>156</v>
       </c>
-      <c r="F107" s="46" t="s">
+      <c r="F107" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="G107" s="21" t="s">
+      <c r="G107" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="H107" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="I107" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="J107" s="51" t="s">
+      <c r="H107" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I107" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J107" s="32" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="108" spans="1:10">
-      <c r="A108" s="32"/>
-      <c r="B108" s="36"/>
-      <c r="C108" s="40"/>
-      <c r="D108" s="44"/>
-      <c r="E108" s="48"/>
-      <c r="F108" s="48"/>
-      <c r="G108" s="20" t="s">
+      <c r="A108" s="36"/>
+      <c r="B108" s="39"/>
+      <c r="C108" s="42"/>
+      <c r="D108" s="45"/>
+      <c r="E108" s="30"/>
+      <c r="F108" s="30"/>
+      <c r="G108" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="H108" s="50"/>
-      <c r="I108" s="48"/>
-      <c r="J108" s="53"/>
+      <c r="H108" s="28"/>
+      <c r="I108" s="30"/>
+      <c r="J108" s="33"/>
     </row>
     <row r="109" spans="1:10">
-      <c r="A109" s="32"/>
-      <c r="B109" s="36"/>
-      <c r="C109" s="40"/>
-      <c r="D109" s="44"/>
-      <c r="E109" s="48"/>
-      <c r="F109" s="48"/>
-      <c r="G109" s="20" t="s">
+      <c r="A109" s="36"/>
+      <c r="B109" s="39"/>
+      <c r="C109" s="42"/>
+      <c r="D109" s="45"/>
+      <c r="E109" s="30"/>
+      <c r="F109" s="30"/>
+      <c r="G109" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="H109" s="50"/>
-      <c r="I109" s="48"/>
-      <c r="J109" s="53"/>
+      <c r="H109" s="28"/>
+      <c r="I109" s="30"/>
+      <c r="J109" s="33"/>
     </row>
     <row r="110" spans="1:10">
-      <c r="A110" s="32"/>
-      <c r="B110" s="36"/>
-      <c r="C110" s="40"/>
-      <c r="D110" s="44"/>
-      <c r="E110" s="48"/>
-      <c r="F110" s="48"/>
-      <c r="G110" s="20" t="s">
+      <c r="A110" s="36"/>
+      <c r="B110" s="39"/>
+      <c r="C110" s="42"/>
+      <c r="D110" s="45"/>
+      <c r="E110" s="30"/>
+      <c r="F110" s="30"/>
+      <c r="G110" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="H110" s="50"/>
-      <c r="I110" s="48"/>
-      <c r="J110" s="53"/>
+      <c r="H110" s="28"/>
+      <c r="I110" s="30"/>
+      <c r="J110" s="33"/>
     </row>
     <row r="111" spans="1:10">
-      <c r="A111" s="33"/>
-      <c r="B111" s="37"/>
-      <c r="C111" s="41"/>
-      <c r="D111" s="45"/>
-      <c r="E111" s="49"/>
-      <c r="F111" s="49"/>
-      <c r="G111" s="22"/>
-      <c r="H111" s="50"/>
-      <c r="I111" s="49"/>
-      <c r="J111" s="54"/>
+      <c r="A111" s="37"/>
+      <c r="B111" s="40"/>
+      <c r="C111" s="43"/>
+      <c r="D111" s="46"/>
+      <c r="E111" s="31"/>
+      <c r="F111" s="31"/>
+      <c r="G111" s="20"/>
+      <c r="H111" s="28"/>
+      <c r="I111" s="31"/>
+      <c r="J111" s="34"/>
     </row>
     <row r="112" spans="1:10">
-      <c r="A112" s="30">
+      <c r="A112" s="35">
         <v>46190</v>
       </c>
-      <c r="B112" s="34">
+      <c r="B112" s="38">
         <v>0.77152777777777781</v>
       </c>
-      <c r="C112" s="38" t="s">
+      <c r="C112" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="D112" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="E112" s="46" t="s">
+      <c r="D112" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="E112" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="F112" s="46" t="s">
+      <c r="F112" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="G112" s="21" t="s">
+      <c r="G112" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="H112" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="I112" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="J112" s="51" t="s">
+      <c r="H112" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I112" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J112" s="32" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="113" spans="1:10">
-      <c r="A113" s="32"/>
-      <c r="B113" s="36"/>
-      <c r="C113" s="40"/>
-      <c r="D113" s="44"/>
-      <c r="E113" s="48"/>
-      <c r="F113" s="48"/>
-      <c r="G113" s="19"/>
-      <c r="H113" s="50"/>
-      <c r="I113" s="48"/>
-      <c r="J113" s="53"/>
+      <c r="A113" s="36"/>
+      <c r="B113" s="39"/>
+      <c r="C113" s="42"/>
+      <c r="D113" s="45"/>
+      <c r="E113" s="30"/>
+      <c r="F113" s="30"/>
+      <c r="G113" s="17"/>
+      <c r="H113" s="28"/>
+      <c r="I113" s="30"/>
+      <c r="J113" s="33"/>
     </row>
     <row r="114" spans="1:10">
-      <c r="A114" s="32"/>
-      <c r="B114" s="36"/>
-      <c r="C114" s="40"/>
-      <c r="D114" s="44"/>
-      <c r="E114" s="48"/>
-      <c r="F114" s="48"/>
-      <c r="G114" s="19"/>
-      <c r="H114" s="50"/>
-      <c r="I114" s="48"/>
-      <c r="J114" s="53"/>
+      <c r="A114" s="36"/>
+      <c r="B114" s="39"/>
+      <c r="C114" s="42"/>
+      <c r="D114" s="45"/>
+      <c r="E114" s="30"/>
+      <c r="F114" s="30"/>
+      <c r="G114" s="17"/>
+      <c r="H114" s="28"/>
+      <c r="I114" s="30"/>
+      <c r="J114" s="33"/>
     </row>
     <row r="115" spans="1:10">
-      <c r="A115" s="32"/>
-      <c r="B115" s="36"/>
-      <c r="C115" s="40"/>
-      <c r="D115" s="44"/>
-      <c r="E115" s="48"/>
-      <c r="F115" s="48"/>
-      <c r="G115" s="20" t="s">
+      <c r="A115" s="36"/>
+      <c r="B115" s="39"/>
+      <c r="C115" s="42"/>
+      <c r="D115" s="45"/>
+      <c r="E115" s="30"/>
+      <c r="F115" s="30"/>
+      <c r="G115" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="H115" s="50"/>
-      <c r="I115" s="48"/>
-      <c r="J115" s="53"/>
+      <c r="H115" s="28"/>
+      <c r="I115" s="30"/>
+      <c r="J115" s="33"/>
     </row>
     <row r="116" spans="1:10">
-      <c r="A116" s="33"/>
-      <c r="B116" s="37"/>
-      <c r="C116" s="41"/>
-      <c r="D116" s="45"/>
-      <c r="E116" s="49"/>
-      <c r="F116" s="49"/>
-      <c r="G116" s="22" t="s">
+      <c r="A116" s="37"/>
+      <c r="B116" s="40"/>
+      <c r="C116" s="43"/>
+      <c r="D116" s="46"/>
+      <c r="E116" s="31"/>
+      <c r="F116" s="31"/>
+      <c r="G116" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="H116" s="50"/>
-      <c r="I116" s="49"/>
-      <c r="J116" s="54"/>
+      <c r="H116" s="28"/>
+      <c r="I116" s="31"/>
+      <c r="J116" s="34"/>
     </row>
     <row r="117" spans="1:10">
-      <c r="A117" s="30">
+      <c r="A117" s="35">
         <v>46191</v>
       </c>
-      <c r="B117" s="34">
+      <c r="B117" s="38">
         <v>0.77152777777777781</v>
       </c>
-      <c r="C117" s="38" t="s">
+      <c r="C117" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="D117" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="E117" s="46" t="s">
+      <c r="D117" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="E117" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="F117" s="46" t="s">
+      <c r="F117" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="G117" s="21" t="s">
+      <c r="G117" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="H117" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="I117" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="J117" s="51" t="s">
+      <c r="H117" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I117" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J117" s="32" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="118" spans="1:10">
-      <c r="A118" s="32"/>
-      <c r="B118" s="36"/>
-      <c r="C118" s="40"/>
-      <c r="D118" s="44"/>
-      <c r="E118" s="48"/>
-      <c r="F118" s="48"/>
-      <c r="G118" s="19"/>
-      <c r="H118" s="50"/>
-      <c r="I118" s="48"/>
-      <c r="J118" s="53"/>
+      <c r="A118" s="36"/>
+      <c r="B118" s="39"/>
+      <c r="C118" s="42"/>
+      <c r="D118" s="45"/>
+      <c r="E118" s="30"/>
+      <c r="F118" s="30"/>
+      <c r="G118" s="17"/>
+      <c r="H118" s="28"/>
+      <c r="I118" s="30"/>
+      <c r="J118" s="33"/>
     </row>
     <row r="119" spans="1:10">
-      <c r="A119" s="32"/>
-      <c r="B119" s="36"/>
-      <c r="C119" s="40"/>
-      <c r="D119" s="44"/>
-      <c r="E119" s="48"/>
-      <c r="F119" s="48"/>
-      <c r="G119" s="19"/>
-      <c r="H119" s="50"/>
-      <c r="I119" s="48"/>
-      <c r="J119" s="53"/>
+      <c r="A119" s="36"/>
+      <c r="B119" s="39"/>
+      <c r="C119" s="42"/>
+      <c r="D119" s="45"/>
+      <c r="E119" s="30"/>
+      <c r="F119" s="30"/>
+      <c r="G119" s="17"/>
+      <c r="H119" s="28"/>
+      <c r="I119" s="30"/>
+      <c r="J119" s="33"/>
     </row>
     <row r="120" spans="1:10">
-      <c r="A120" s="32"/>
-      <c r="B120" s="36"/>
-      <c r="C120" s="40"/>
-      <c r="D120" s="44"/>
-      <c r="E120" s="48"/>
-      <c r="F120" s="48"/>
-      <c r="G120" s="20" t="s">
+      <c r="A120" s="36"/>
+      <c r="B120" s="39"/>
+      <c r="C120" s="42"/>
+      <c r="D120" s="45"/>
+      <c r="E120" s="30"/>
+      <c r="F120" s="30"/>
+      <c r="G120" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="H120" s="50"/>
-      <c r="I120" s="48"/>
-      <c r="J120" s="53"/>
+      <c r="H120" s="28"/>
+      <c r="I120" s="30"/>
+      <c r="J120" s="33"/>
     </row>
     <row r="121" spans="1:10">
-      <c r="A121" s="33"/>
-      <c r="B121" s="37"/>
-      <c r="C121" s="41"/>
-      <c r="D121" s="45"/>
-      <c r="E121" s="49"/>
-      <c r="F121" s="49"/>
-      <c r="G121" s="22" t="s">
+      <c r="A121" s="37"/>
+      <c r="B121" s="40"/>
+      <c r="C121" s="43"/>
+      <c r="D121" s="46"/>
+      <c r="E121" s="31"/>
+      <c r="F121" s="31"/>
+      <c r="G121" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="H121" s="50"/>
-      <c r="I121" s="49"/>
-      <c r="J121" s="54"/>
+      <c r="H121" s="28"/>
+      <c r="I121" s="31"/>
+      <c r="J121" s="34"/>
     </row>
     <row r="122" spans="1:10" ht="28.5">
-      <c r="A122" s="30">
+      <c r="A122" s="35">
         <v>46183</v>
       </c>
-      <c r="B122" s="34">
+      <c r="B122" s="38">
         <v>0.77916666666666667</v>
       </c>
-      <c r="C122" s="38" t="s">
+      <c r="C122" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="D122" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="E122" s="46" t="s">
+      <c r="D122" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="E122" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="F122" s="46" t="s">
+      <c r="F122" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="G122" s="21" t="s">
+      <c r="G122" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="H122" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="I122" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="J122" s="51" t="s">
+      <c r="H122" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I122" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J122" s="32" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="123" spans="1:10">
-      <c r="A123" s="32"/>
-      <c r="B123" s="36"/>
-      <c r="C123" s="40"/>
-      <c r="D123" s="44"/>
-      <c r="E123" s="48"/>
-      <c r="F123" s="48"/>
-      <c r="G123" s="20" t="s">
+      <c r="A123" s="36"/>
+      <c r="B123" s="39"/>
+      <c r="C123" s="42"/>
+      <c r="D123" s="45"/>
+      <c r="E123" s="30"/>
+      <c r="F123" s="30"/>
+      <c r="G123" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="H123" s="50"/>
-      <c r="I123" s="48"/>
-      <c r="J123" s="53"/>
+      <c r="H123" s="28"/>
+      <c r="I123" s="30"/>
+      <c r="J123" s="33"/>
     </row>
     <row r="124" spans="1:10">
-      <c r="A124" s="32"/>
-      <c r="B124" s="36"/>
-      <c r="C124" s="40"/>
-      <c r="D124" s="44"/>
-      <c r="E124" s="48"/>
-      <c r="F124" s="48"/>
-      <c r="G124" s="20" t="s">
+      <c r="A124" s="36"/>
+      <c r="B124" s="39"/>
+      <c r="C124" s="42"/>
+      <c r="D124" s="45"/>
+      <c r="E124" s="30"/>
+      <c r="F124" s="30"/>
+      <c r="G124" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="H124" s="50"/>
-      <c r="I124" s="48"/>
-      <c r="J124" s="53"/>
+      <c r="H124" s="28"/>
+      <c r="I124" s="30"/>
+      <c r="J124" s="33"/>
     </row>
     <row r="125" spans="1:10">
-      <c r="A125" s="32"/>
-      <c r="B125" s="36"/>
-      <c r="C125" s="40"/>
-      <c r="D125" s="44"/>
-      <c r="E125" s="48"/>
-      <c r="F125" s="48"/>
-      <c r="G125" s="20" t="s">
+      <c r="A125" s="36"/>
+      <c r="B125" s="39"/>
+      <c r="C125" s="42"/>
+      <c r="D125" s="45"/>
+      <c r="E125" s="30"/>
+      <c r="F125" s="30"/>
+      <c r="G125" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="H125" s="50"/>
-      <c r="I125" s="48"/>
-      <c r="J125" s="53"/>
+      <c r="H125" s="28"/>
+      <c r="I125" s="30"/>
+      <c r="J125" s="33"/>
     </row>
     <row r="126" spans="1:10">
-      <c r="A126" s="33"/>
-      <c r="B126" s="37"/>
-      <c r="C126" s="41"/>
-      <c r="D126" s="45"/>
-      <c r="E126" s="49"/>
-      <c r="F126" s="49"/>
-      <c r="G126" s="22" t="s">
+      <c r="A126" s="37"/>
+      <c r="B126" s="40"/>
+      <c r="C126" s="43"/>
+      <c r="D126" s="46"/>
+      <c r="E126" s="31"/>
+      <c r="F126" s="31"/>
+      <c r="G126" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="H126" s="50"/>
-      <c r="I126" s="49"/>
-      <c r="J126" s="54"/>
+      <c r="H126" s="28"/>
+      <c r="I126" s="31"/>
+      <c r="J126" s="34"/>
     </row>
     <row r="127" spans="1:10" ht="57">
-      <c r="A127" s="24">
+      <c r="A127" s="22">
         <v>46189</v>
       </c>
-      <c r="B127" s="25">
+      <c r="B127" s="23">
         <v>0.77916666666666667</v>
       </c>
-      <c r="C127" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="D127" s="27">
+      <c r="C127" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D127" s="25">
         <v>9744</v>
       </c>
-      <c r="E127" s="28" t="s">
+      <c r="E127" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="F127" s="28" t="s">
+      <c r="F127" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="G127" s="26" t="s">
+      <c r="G127" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="H127" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="I127" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J127" s="29" t="s">
+      <c r="H127" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I127" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" s="27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="71.25">
+      <c r="A128" s="22">
+        <v>46184</v>
+      </c>
+      <c r="B128" s="23">
+        <v>0.38055555555555554</v>
+      </c>
+      <c r="C128" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D128" s="25">
+        <v>9744</v>
+      </c>
+      <c r="E128" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="F128" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="G128" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="H128" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I128" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J128" s="27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10">
+      <c r="A129" s="35">
+        <v>46183</v>
+      </c>
+      <c r="B129" s="38">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C129" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="D129" s="44">
+        <v>9759</v>
+      </c>
+      <c r="E129" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="F129" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="G129" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="H129" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I129" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J129" s="32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" s="36"/>
+      <c r="B130" s="56"/>
+      <c r="C130" s="57"/>
+      <c r="D130" s="58"/>
+      <c r="E130" s="59"/>
+      <c r="F130" s="59"/>
+      <c r="G130" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="H130" s="28"/>
+      <c r="I130" s="59"/>
+      <c r="J130" s="33"/>
+    </row>
+    <row r="131" spans="1:10">
+      <c r="A131" s="36"/>
+      <c r="B131" s="56"/>
+      <c r="C131" s="57"/>
+      <c r="D131" s="58"/>
+      <c r="E131" s="59"/>
+      <c r="F131" s="59"/>
+      <c r="G131" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="H131" s="28"/>
+      <c r="I131" s="59"/>
+      <c r="J131" s="33"/>
+    </row>
+    <row r="132" spans="1:10">
+      <c r="A132" s="36"/>
+      <c r="B132" s="56"/>
+      <c r="C132" s="57"/>
+      <c r="D132" s="58"/>
+      <c r="E132" s="59"/>
+      <c r="F132" s="59"/>
+      <c r="G132" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="H132" s="28"/>
+      <c r="I132" s="59"/>
+      <c r="J132" s="33"/>
+    </row>
+    <row r="133" spans="1:10">
+      <c r="A133" s="37"/>
+      <c r="B133" s="40"/>
+      <c r="C133" s="43"/>
+      <c r="D133" s="46"/>
+      <c r="E133" s="31"/>
+      <c r="F133" s="31"/>
+      <c r="G133" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="H133" s="28"/>
+      <c r="I133" s="31"/>
+      <c r="J133" s="34"/>
+    </row>
+    <row r="134" spans="1:10" ht="99.75">
+      <c r="A134" s="22">
+        <v>46185</v>
+      </c>
+      <c r="B134" s="23">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C134" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="D134" s="25">
+        <v>9762</v>
+      </c>
+      <c r="E134" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="F134" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="G134" s="55" t="s">
+        <v>189</v>
+      </c>
+      <c r="H134" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I134" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J134" s="27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="99.75">
+      <c r="A135" s="22">
+        <v>46186</v>
+      </c>
+      <c r="B135" s="23">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C135" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="D135" s="25">
+        <v>9764</v>
+      </c>
+      <c r="E135" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="F135" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="G135" s="55" t="s">
+        <v>189</v>
+      </c>
+      <c r="H135" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I135" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J135" s="27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="99.75">
+      <c r="A136" s="22">
+        <v>46186</v>
+      </c>
+      <c r="B136" s="23">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C136" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="D136" s="25">
+        <v>9764</v>
+      </c>
+      <c r="E136" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="F136" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="G136" s="55" t="s">
+        <v>189</v>
+      </c>
+      <c r="H136" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I136" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J136" s="27" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="45">
-    <mergeCell ref="H122:H126"/>
-    <mergeCell ref="I122:I126"/>
-    <mergeCell ref="J122:J126"/>
-    <mergeCell ref="A122:A126"/>
-    <mergeCell ref="B122:B126"/>
-    <mergeCell ref="C122:C126"/>
-    <mergeCell ref="D122:D126"/>
-    <mergeCell ref="E122:E126"/>
-    <mergeCell ref="F122:F126"/>
-    <mergeCell ref="J112:J116"/>
-    <mergeCell ref="A117:A121"/>
-    <mergeCell ref="B117:B121"/>
-    <mergeCell ref="C117:C121"/>
-    <mergeCell ref="D117:D121"/>
-    <mergeCell ref="E117:E121"/>
-    <mergeCell ref="F117:F121"/>
-    <mergeCell ref="H117:H121"/>
-    <mergeCell ref="I117:I121"/>
-    <mergeCell ref="J117:J121"/>
-    <mergeCell ref="I107:I111"/>
-    <mergeCell ref="J107:J111"/>
-    <mergeCell ref="A112:A116"/>
-    <mergeCell ref="B112:B116"/>
-    <mergeCell ref="C112:C116"/>
-    <mergeCell ref="D112:D116"/>
-    <mergeCell ref="E112:E116"/>
-    <mergeCell ref="F112:F116"/>
-    <mergeCell ref="H112:H116"/>
-    <mergeCell ref="I112:I116"/>
+  <mergeCells count="54">
+    <mergeCell ref="F129:F133"/>
+    <mergeCell ref="H129:H133"/>
+    <mergeCell ref="I129:I133"/>
+    <mergeCell ref="J129:J133"/>
+    <mergeCell ref="A129:A133"/>
+    <mergeCell ref="B129:B133"/>
+    <mergeCell ref="C129:C133"/>
+    <mergeCell ref="D129:D133"/>
+    <mergeCell ref="E129:E133"/>
     <mergeCell ref="H102:H106"/>
     <mergeCell ref="I102:I106"/>
     <mergeCell ref="J102:J106"/>
@@ -5049,6 +5302,35 @@
     <mergeCell ref="D102:D106"/>
     <mergeCell ref="E102:E106"/>
     <mergeCell ref="F102:F106"/>
+    <mergeCell ref="I107:I111"/>
+    <mergeCell ref="J107:J111"/>
+    <mergeCell ref="A112:A116"/>
+    <mergeCell ref="B112:B116"/>
+    <mergeCell ref="C112:C116"/>
+    <mergeCell ref="D112:D116"/>
+    <mergeCell ref="E112:E116"/>
+    <mergeCell ref="F112:F116"/>
+    <mergeCell ref="H112:H116"/>
+    <mergeCell ref="I112:I116"/>
+    <mergeCell ref="J112:J116"/>
+    <mergeCell ref="A117:A121"/>
+    <mergeCell ref="B117:B121"/>
+    <mergeCell ref="C117:C121"/>
+    <mergeCell ref="D117:D121"/>
+    <mergeCell ref="E117:E121"/>
+    <mergeCell ref="F117:F121"/>
+    <mergeCell ref="H117:H121"/>
+    <mergeCell ref="I117:I121"/>
+    <mergeCell ref="J117:J121"/>
+    <mergeCell ref="H122:H126"/>
+    <mergeCell ref="I122:I126"/>
+    <mergeCell ref="J122:J126"/>
+    <mergeCell ref="A122:A126"/>
+    <mergeCell ref="B122:B126"/>
+    <mergeCell ref="C122:C126"/>
+    <mergeCell ref="D122:D126"/>
+    <mergeCell ref="E122:E126"/>
+    <mergeCell ref="F122:F126"/>
   </mergeCells>
   <conditionalFormatting sqref="H2:H101">
     <cfRule type="expression" dxfId="4" priority="1">
@@ -5160,14 +5442,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="5" t="s">

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FC4FE56-6251-490D-86C4-65961274E93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5171DC60-6849-4DEF-95F2-2F2DC9C3DDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVENTOS" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="186">
   <si>
     <t>Fecha</t>
   </si>
@@ -536,21 +536,6 @@
     <t>Sede Villa - Martes de la Semana de Ingeniería</t>
   </si>
   <si>
-    <t>Requerimientos :</t>
-  </si>
-  <si>
-    <t>• 3 toldos con 3 puntos de luz.</t>
-  </si>
-  <si>
-    <t>• 3 mesas con mantel.</t>
-  </si>
-  <si>
-    <t>• 6 sillas (2 por toldo).</t>
-  </si>
-  <si>
-    <t>• 1 televisor.</t>
-  </si>
-  <si>
     <t>Sede Villa - Feria Empresarial</t>
   </si>
   <si>
@@ -575,21 +560,12 @@
     <t>Clínica de Simulación</t>
   </si>
   <si>
-    <t>• 5 mesas</t>
-  </si>
-  <si>
-    <t>• 25 sillas</t>
-  </si>
-  <si>
     <t xml:space="preserve">no especifica </t>
   </si>
   <si>
     <t>Hall del Pabellón N</t>
   </si>
   <si>
-    <t>Por favor retirar muebles del hall y colocar: 9:30 am a 12:00 pm</t>
-  </si>
-  <si>
     <t>- 60 sillas en formato auditorio.</t>
   </si>
   <si>
@@ -605,21 +581,12 @@
     <t xml:space="preserve">Campaña Certijoven </t>
   </si>
   <si>
-    <t>Pabellon I</t>
-  </si>
-  <si>
-    <t>solicitamos su apoyo para habilitar una mesa con mantel + dos sillas en el hall de pasillo del pabellón I. Para la socialización del aplicativo ApliJoven de MINEDU que se realizará el lunes16 de junio de 8:30 am a 2:00</t>
-  </si>
-  <si>
     <t>Gaming Tournament</t>
   </si>
   <si>
     <t>Auditorio O203</t>
   </si>
   <si>
-    <t xml:space="preserve">solicitar el siguiente apoyo:                                                                      * 3 mesas con mantel.                                                                                                      Agradecemos mucho su apoyo y quedamos atentos a cualquier información adicional que necesiten para la coordinación.                          </t>
-  </si>
-  <si>
     <t xml:space="preserve">CARRERA DE ENFERMERIA </t>
   </si>
   <si>
@@ -629,9 +596,6 @@
     <t>Jardín de pabellón N</t>
   </si>
   <si>
-    <t>Requerimiento :</t>
-  </si>
-  <si>
     <t>Cinco toldos para la atención de los servicios.</t>
   </si>
   <si>
@@ -650,7 +614,31 @@
     <t>Coloquio Internacional</t>
   </si>
   <si>
-    <t>Los insumos deberan estar el 12 y 13 de junio de 07:00 a 18:00 horas 5 sillones 2 mesitas mesa para registro vestida + 2 sillas 3 mesas para catering vestidas Recoger banner y totem de garita nueva (dice coloquio internacional de estudios generales 2026) 73 sillas Se requiere 2 mesas vestidas, palos de separación de ambiente.</t>
+    <t xml:space="preserve">Requerimientos :3 toldos / 3 mesas  / 6 sillas / 1televisor </t>
+  </si>
+  <si>
+    <t>Requerimientos : 8 toldos / 8 mesas / 8 manteles / 16 sillas (2 por mesas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requerimientos : 5 mesas / 25 sillas </t>
+  </si>
+  <si>
+    <t>Por favor retirar muebles del hall y colocar: 9:30 am a 12:00 pm  /   60 sillas / tv con rack / banderas de cientifica y peru / podium</t>
+  </si>
+  <si>
+    <t>Requerimiento : 5 toldos / 6 mesas / 24 sillas / 6 manteles / puntos de energia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requerimientos: 5 sillones / 2 mesas de registro / 2 sillas / 3 mesas para catering / 3 manteles / totem colloquio / 73 sillas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pabellon I - pasillo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">mesa con mantel / 2 sillas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 mesas con mantel </t>
   </si>
 </sst>
 </file>
@@ -660,7 +648,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -696,6 +684,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -944,7 +938,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -990,11 +984,65 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1002,81 +1050,9 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1102,20 +1078,50 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1369,6 +1375,7 @@
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="5.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="26.1" customHeight="1">
@@ -4597,695 +4604,704 @@
         <v>86</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
-      <c r="A102" s="49">
+    <row r="102" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A102" s="43">
         <v>46182</v>
       </c>
-      <c r="B102" s="50">
+      <c r="B102" s="44">
         <v>0.47152777777777777</v>
       </c>
-      <c r="C102" s="51" t="s">
+      <c r="C102" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="D102" s="52">
+      <c r="D102" s="46">
         <v>81688</v>
       </c>
-      <c r="E102" s="47" t="s">
+      <c r="E102" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="F102" s="47" t="s">
+      <c r="F102" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="G102" s="19" t="s">
+      <c r="G102" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="H102" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I102" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="J102" s="42" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" s="33"/>
+      <c r="B103" s="52"/>
+      <c r="C103" s="51"/>
+      <c r="D103" s="50"/>
+      <c r="E103" s="49"/>
+      <c r="F103" s="49"/>
+      <c r="G103" s="54"/>
+      <c r="H103" s="28"/>
+      <c r="I103" s="26"/>
+      <c r="J103" s="30"/>
+    </row>
+    <row r="104" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A104" s="33"/>
+      <c r="B104" s="52"/>
+      <c r="C104" s="51"/>
+      <c r="D104" s="50"/>
+      <c r="E104" s="49"/>
+      <c r="F104" s="49"/>
+      <c r="G104" s="54"/>
+      <c r="H104" s="28"/>
+      <c r="I104" s="26"/>
+      <c r="J104" s="30"/>
+    </row>
+    <row r="105" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A105" s="33"/>
+      <c r="B105" s="52"/>
+      <c r="C105" s="51"/>
+      <c r="D105" s="50"/>
+      <c r="E105" s="49"/>
+      <c r="F105" s="49"/>
+      <c r="G105" s="54"/>
+      <c r="H105" s="28"/>
+      <c r="I105" s="26"/>
+      <c r="J105" s="30"/>
+    </row>
+    <row r="106" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A106" s="34"/>
+      <c r="B106" s="36"/>
+      <c r="C106" s="38"/>
+      <c r="D106" s="40"/>
+      <c r="E106" s="27"/>
+      <c r="F106" s="27"/>
+      <c r="G106" s="55"/>
+      <c r="H106" s="28"/>
+      <c r="I106" s="27"/>
+      <c r="J106" s="31"/>
+    </row>
+    <row r="107" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A107" s="32">
+        <v>46186</v>
+      </c>
+      <c r="B107" s="35">
+        <v>0.47152777777777777</v>
+      </c>
+      <c r="C107" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="D107" s="39">
+        <v>81685</v>
+      </c>
+      <c r="E107" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="H102" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="I102" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="J102" s="48" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10">
-      <c r="A103" s="36"/>
-      <c r="B103" s="39"/>
-      <c r="C103" s="42"/>
-      <c r="D103" s="45"/>
-      <c r="E103" s="30"/>
-      <c r="F103" s="30"/>
-      <c r="G103" s="18" t="s">
+      <c r="F107" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="H103" s="28"/>
-      <c r="I103" s="30"/>
-      <c r="J103" s="33"/>
-    </row>
-    <row r="104" spans="1:10">
-      <c r="A104" s="36"/>
-      <c r="B104" s="39"/>
-      <c r="C104" s="42"/>
-      <c r="D104" s="45"/>
-      <c r="E104" s="30"/>
-      <c r="F104" s="30"/>
-      <c r="G104" s="18" t="s">
+      <c r="G107" s="60" t="s">
+        <v>178</v>
+      </c>
+      <c r="H107" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I107" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J107" s="29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A108" s="33"/>
+      <c r="B108" s="52"/>
+      <c r="C108" s="51"/>
+      <c r="D108" s="50"/>
+      <c r="E108" s="49"/>
+      <c r="F108" s="49"/>
+      <c r="G108" s="61" t="s">
         <v>153</v>
       </c>
-      <c r="H104" s="28"/>
-      <c r="I104" s="30"/>
-      <c r="J104" s="33"/>
-    </row>
-    <row r="105" spans="1:10">
-      <c r="A105" s="36"/>
-      <c r="B105" s="39"/>
-      <c r="C105" s="42"/>
-      <c r="D105" s="45"/>
-      <c r="E105" s="30"/>
-      <c r="F105" s="30"/>
-      <c r="G105" s="18" t="s">
+      <c r="H108" s="28"/>
+      <c r="I108" s="26"/>
+      <c r="J108" s="30"/>
+    </row>
+    <row r="109" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A109" s="33"/>
+      <c r="B109" s="52"/>
+      <c r="C109" s="51"/>
+      <c r="D109" s="50"/>
+      <c r="E109" s="49"/>
+      <c r="F109" s="49"/>
+      <c r="G109" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="H105" s="28"/>
-      <c r="I105" s="30"/>
-      <c r="J105" s="33"/>
-    </row>
-    <row r="106" spans="1:10">
-      <c r="A106" s="37"/>
-      <c r="B106" s="40"/>
-      <c r="C106" s="43"/>
-      <c r="D106" s="46"/>
-      <c r="E106" s="31"/>
-      <c r="F106" s="31"/>
-      <c r="G106" s="20" t="s">
+      <c r="H109" s="28"/>
+      <c r="I109" s="26"/>
+      <c r="J109" s="30"/>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110" s="33"/>
+      <c r="B110" s="52"/>
+      <c r="C110" s="51"/>
+      <c r="D110" s="50"/>
+      <c r="E110" s="49"/>
+      <c r="F110" s="49"/>
+      <c r="G110" s="61" t="s">
         <v>155</v>
       </c>
-      <c r="H106" s="28"/>
-      <c r="I106" s="31"/>
-      <c r="J106" s="34"/>
-    </row>
-    <row r="107" spans="1:10">
-      <c r="A107" s="35">
+      <c r="H110" s="28"/>
+      <c r="I110" s="26"/>
+      <c r="J110" s="30"/>
+    </row>
+    <row r="111" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A111" s="34"/>
+      <c r="B111" s="36"/>
+      <c r="C111" s="38"/>
+      <c r="D111" s="40"/>
+      <c r="E111" s="27"/>
+      <c r="F111" s="27"/>
+      <c r="G111" s="62"/>
+      <c r="H111" s="28"/>
+      <c r="I111" s="27"/>
+      <c r="J111" s="31"/>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112" s="32">
+        <v>46190</v>
+      </c>
+      <c r="B112" s="35">
+        <v>0.77152777777777781</v>
+      </c>
+      <c r="C112" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="D112" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="E112" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="F112" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="G112" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H112" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I112" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J112" s="29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="A113" s="33"/>
+      <c r="B113" s="52"/>
+      <c r="C113" s="51"/>
+      <c r="D113" s="50"/>
+      <c r="E113" s="49"/>
+      <c r="F113" s="49"/>
+      <c r="G113" s="58"/>
+      <c r="H113" s="28"/>
+      <c r="I113" s="26"/>
+      <c r="J113" s="30"/>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114" s="33"/>
+      <c r="B114" s="52"/>
+      <c r="C114" s="51"/>
+      <c r="D114" s="50"/>
+      <c r="E114" s="49"/>
+      <c r="F114" s="49"/>
+      <c r="G114" s="58"/>
+      <c r="H114" s="28"/>
+      <c r="I114" s="26"/>
+      <c r="J114" s="30"/>
+    </row>
+    <row r="115" spans="1:10">
+      <c r="A115" s="33"/>
+      <c r="B115" s="52"/>
+      <c r="C115" s="51"/>
+      <c r="D115" s="50"/>
+      <c r="E115" s="49"/>
+      <c r="F115" s="49"/>
+      <c r="G115" s="58"/>
+      <c r="H115" s="28"/>
+      <c r="I115" s="26"/>
+      <c r="J115" s="30"/>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="A116" s="34"/>
+      <c r="B116" s="36"/>
+      <c r="C116" s="38"/>
+      <c r="D116" s="40"/>
+      <c r="E116" s="27"/>
+      <c r="F116" s="27"/>
+      <c r="G116" s="59"/>
+      <c r="H116" s="28"/>
+      <c r="I116" s="27"/>
+      <c r="J116" s="31"/>
+    </row>
+    <row r="117" spans="1:10">
+      <c r="A117" s="32">
+        <v>46191</v>
+      </c>
+      <c r="B117" s="35">
+        <v>0.77152777777777781</v>
+      </c>
+      <c r="C117" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="D117" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="E117" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="F117" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="G117" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="H117" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I117" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J117" s="29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10">
+      <c r="A118" s="33"/>
+      <c r="B118" s="52"/>
+      <c r="C118" s="51"/>
+      <c r="D118" s="50"/>
+      <c r="E118" s="49"/>
+      <c r="F118" s="49"/>
+      <c r="G118" s="58"/>
+      <c r="H118" s="28"/>
+      <c r="I118" s="26"/>
+      <c r="J118" s="30"/>
+    </row>
+    <row r="119" spans="1:10">
+      <c r="A119" s="33"/>
+      <c r="B119" s="52"/>
+      <c r="C119" s="51"/>
+      <c r="D119" s="50"/>
+      <c r="E119" s="49"/>
+      <c r="F119" s="49"/>
+      <c r="G119" s="58"/>
+      <c r="H119" s="28"/>
+      <c r="I119" s="26"/>
+      <c r="J119" s="30"/>
+    </row>
+    <row r="120" spans="1:10">
+      <c r="A120" s="33"/>
+      <c r="B120" s="52"/>
+      <c r="C120" s="51"/>
+      <c r="D120" s="50"/>
+      <c r="E120" s="49"/>
+      <c r="F120" s="49"/>
+      <c r="G120" s="58"/>
+      <c r="H120" s="28"/>
+      <c r="I120" s="26"/>
+      <c r="J120" s="30"/>
+    </row>
+    <row r="121" spans="1:10">
+      <c r="A121" s="34"/>
+      <c r="B121" s="36"/>
+      <c r="C121" s="38"/>
+      <c r="D121" s="40"/>
+      <c r="E121" s="27"/>
+      <c r="F121" s="27"/>
+      <c r="G121" s="59"/>
+      <c r="H121" s="28"/>
+      <c r="I121" s="27"/>
+      <c r="J121" s="31"/>
+    </row>
+    <row r="122" spans="1:10">
+      <c r="A122" s="32">
+        <v>46183</v>
+      </c>
+      <c r="B122" s="35">
+        <v>0.77916666666666667</v>
+      </c>
+      <c r="C122" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="D122" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="E122" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="F122" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="G122" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H122" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I122" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J122" s="29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
+      <c r="A123" s="33"/>
+      <c r="B123" s="52"/>
+      <c r="C123" s="51"/>
+      <c r="D123" s="50"/>
+      <c r="E123" s="49"/>
+      <c r="F123" s="49"/>
+      <c r="G123" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="H123" s="28"/>
+      <c r="I123" s="26"/>
+      <c r="J123" s="30"/>
+    </row>
+    <row r="124" spans="1:10">
+      <c r="A124" s="33"/>
+      <c r="B124" s="52"/>
+      <c r="C124" s="51"/>
+      <c r="D124" s="50"/>
+      <c r="E124" s="49"/>
+      <c r="F124" s="49"/>
+      <c r="G124" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="H124" s="28"/>
+      <c r="I124" s="26"/>
+      <c r="J124" s="30"/>
+    </row>
+    <row r="125" spans="1:10">
+      <c r="A125" s="33"/>
+      <c r="B125" s="52"/>
+      <c r="C125" s="51"/>
+      <c r="D125" s="50"/>
+      <c r="E125" s="49"/>
+      <c r="F125" s="49"/>
+      <c r="G125" s="63" t="s">
+        <v>163</v>
+      </c>
+      <c r="H125" s="28"/>
+      <c r="I125" s="26"/>
+      <c r="J125" s="30"/>
+    </row>
+    <row r="126" spans="1:10">
+      <c r="A126" s="34"/>
+      <c r="B126" s="36"/>
+      <c r="C126" s="38"/>
+      <c r="D126" s="40"/>
+      <c r="E126" s="27"/>
+      <c r="F126" s="27"/>
+      <c r="G126" s="63" t="s">
+        <v>164</v>
+      </c>
+      <c r="H126" s="28"/>
+      <c r="I126" s="27"/>
+      <c r="J126" s="31"/>
+    </row>
+    <row r="127" spans="1:10" ht="15">
+      <c r="A127" s="18">
+        <v>46189</v>
+      </c>
+      <c r="B127" s="19">
+        <v>0.77916666666666667</v>
+      </c>
+      <c r="C127" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D127" s="21">
+        <v>9744</v>
+      </c>
+      <c r="E127" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="F127" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="G127" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="H127" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I127" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" s="23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="15">
+      <c r="A128" s="18">
+        <v>46184</v>
+      </c>
+      <c r="B128" s="19">
+        <v>0.38055555555555554</v>
+      </c>
+      <c r="C128" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D128" s="21">
+        <v>9744</v>
+      </c>
+      <c r="E128" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="F128" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="G128" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="H128" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I128" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J128" s="23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A129" s="32">
+        <v>46183</v>
+      </c>
+      <c r="B129" s="35">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C129" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="D129" s="39">
+        <v>9759</v>
+      </c>
+      <c r="E129" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="F129" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="G129" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="H129" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="I129" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J129" s="29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" s="33"/>
+      <c r="B130" s="52"/>
+      <c r="C130" s="51"/>
+      <c r="D130" s="50"/>
+      <c r="E130" s="49"/>
+      <c r="F130" s="49"/>
+      <c r="G130" s="56" t="s">
+        <v>171</v>
+      </c>
+      <c r="H130" s="28"/>
+      <c r="I130" s="26"/>
+      <c r="J130" s="30"/>
+    </row>
+    <row r="131" spans="1:10">
+      <c r="A131" s="33"/>
+      <c r="B131" s="52"/>
+      <c r="C131" s="51"/>
+      <c r="D131" s="50"/>
+      <c r="E131" s="49"/>
+      <c r="F131" s="49"/>
+      <c r="G131" s="56" t="s">
+        <v>172</v>
+      </c>
+      <c r="H131" s="28"/>
+      <c r="I131" s="26"/>
+      <c r="J131" s="30"/>
+    </row>
+    <row r="132" spans="1:10">
+      <c r="A132" s="33"/>
+      <c r="B132" s="52"/>
+      <c r="C132" s="51"/>
+      <c r="D132" s="50"/>
+      <c r="E132" s="49"/>
+      <c r="F132" s="49"/>
+      <c r="G132" s="56" t="s">
+        <v>173</v>
+      </c>
+      <c r="H132" s="28"/>
+      <c r="I132" s="26"/>
+      <c r="J132" s="30"/>
+    </row>
+    <row r="133" spans="1:10">
+      <c r="A133" s="34"/>
+      <c r="B133" s="36"/>
+      <c r="C133" s="38"/>
+      <c r="D133" s="40"/>
+      <c r="E133" s="27"/>
+      <c r="F133" s="27"/>
+      <c r="G133" s="56" t="s">
+        <v>174</v>
+      </c>
+      <c r="H133" s="28"/>
+      <c r="I133" s="27"/>
+      <c r="J133" s="31"/>
+    </row>
+    <row r="134" spans="1:10" ht="42.75">
+      <c r="A134" s="18">
+        <v>46185</v>
+      </c>
+      <c r="B134" s="19">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C134" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="D134" s="21">
+        <v>9762</v>
+      </c>
+      <c r="E134" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="F134" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="G134" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="H134" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I134" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J134" s="23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="42.75">
+      <c r="A135" s="18">
         <v>46186</v>
       </c>
-      <c r="B107" s="38">
-        <v>0.47152777777777777</v>
-      </c>
-      <c r="C107" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="D107" s="44">
-        <v>81685</v>
-      </c>
-      <c r="E107" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="F107" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="G107" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="H107" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="I107" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J107" s="32" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10">
-      <c r="A108" s="36"/>
-      <c r="B108" s="39"/>
-      <c r="C108" s="42"/>
-      <c r="D108" s="45"/>
-      <c r="E108" s="30"/>
-      <c r="F108" s="30"/>
-      <c r="G108" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="H108" s="28"/>
-      <c r="I108" s="30"/>
-      <c r="J108" s="33"/>
-    </row>
-    <row r="109" spans="1:10">
-      <c r="A109" s="36"/>
-      <c r="B109" s="39"/>
-      <c r="C109" s="42"/>
-      <c r="D109" s="45"/>
-      <c r="E109" s="30"/>
-      <c r="F109" s="30"/>
-      <c r="G109" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H109" s="28"/>
-      <c r="I109" s="30"/>
-      <c r="J109" s="33"/>
-    </row>
-    <row r="110" spans="1:10">
-      <c r="A110" s="36"/>
-      <c r="B110" s="39"/>
-      <c r="C110" s="42"/>
-      <c r="D110" s="45"/>
-      <c r="E110" s="30"/>
-      <c r="F110" s="30"/>
-      <c r="G110" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="H110" s="28"/>
-      <c r="I110" s="30"/>
-      <c r="J110" s="33"/>
-    </row>
-    <row r="111" spans="1:10">
-      <c r="A111" s="37"/>
-      <c r="B111" s="40"/>
-      <c r="C111" s="43"/>
-      <c r="D111" s="46"/>
-      <c r="E111" s="31"/>
-      <c r="F111" s="31"/>
-      <c r="G111" s="20"/>
-      <c r="H111" s="28"/>
-      <c r="I111" s="31"/>
-      <c r="J111" s="34"/>
-    </row>
-    <row r="112" spans="1:10">
-      <c r="A112" s="35">
-        <v>46190</v>
-      </c>
-      <c r="B112" s="38">
-        <v>0.77152777777777781</v>
-      </c>
-      <c r="C112" s="41" t="s">
-        <v>161</v>
-      </c>
-      <c r="D112" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="E112" s="29" t="s">
-        <v>162</v>
-      </c>
-      <c r="F112" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="G112" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="H112" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="I112" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J112" s="32" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10">
-      <c r="A113" s="36"/>
-      <c r="B113" s="39"/>
-      <c r="C113" s="42"/>
-      <c r="D113" s="45"/>
-      <c r="E113" s="30"/>
-      <c r="F113" s="30"/>
-      <c r="G113" s="17"/>
-      <c r="H113" s="28"/>
-      <c r="I113" s="30"/>
-      <c r="J113" s="33"/>
-    </row>
-    <row r="114" spans="1:10">
-      <c r="A114" s="36"/>
-      <c r="B114" s="39"/>
-      <c r="C114" s="42"/>
-      <c r="D114" s="45"/>
-      <c r="E114" s="30"/>
-      <c r="F114" s="30"/>
-      <c r="G114" s="17"/>
-      <c r="H114" s="28"/>
-      <c r="I114" s="30"/>
-      <c r="J114" s="33"/>
-    </row>
-    <row r="115" spans="1:10">
-      <c r="A115" s="36"/>
-      <c r="B115" s="39"/>
-      <c r="C115" s="42"/>
-      <c r="D115" s="45"/>
-      <c r="E115" s="30"/>
-      <c r="F115" s="30"/>
-      <c r="G115" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="H115" s="28"/>
-      <c r="I115" s="30"/>
-      <c r="J115" s="33"/>
-    </row>
-    <row r="116" spans="1:10">
-      <c r="A116" s="37"/>
-      <c r="B116" s="40"/>
-      <c r="C116" s="43"/>
-      <c r="D116" s="46"/>
-      <c r="E116" s="31"/>
-      <c r="F116" s="31"/>
-      <c r="G116" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="H116" s="28"/>
-      <c r="I116" s="31"/>
-      <c r="J116" s="34"/>
-    </row>
-    <row r="117" spans="1:10">
-      <c r="A117" s="35">
-        <v>46191</v>
-      </c>
-      <c r="B117" s="38">
-        <v>0.77152777777777781</v>
-      </c>
-      <c r="C117" s="41" t="s">
-        <v>161</v>
-      </c>
-      <c r="D117" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="E117" s="29" t="s">
-        <v>162</v>
-      </c>
-      <c r="F117" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="G117" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="H117" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="I117" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J117" s="32" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10">
-      <c r="A118" s="36"/>
-      <c r="B118" s="39"/>
-      <c r="C118" s="42"/>
-      <c r="D118" s="45"/>
-      <c r="E118" s="30"/>
-      <c r="F118" s="30"/>
-      <c r="G118" s="17"/>
-      <c r="H118" s="28"/>
-      <c r="I118" s="30"/>
-      <c r="J118" s="33"/>
-    </row>
-    <row r="119" spans="1:10">
-      <c r="A119" s="36"/>
-      <c r="B119" s="39"/>
-      <c r="C119" s="42"/>
-      <c r="D119" s="45"/>
-      <c r="E119" s="30"/>
-      <c r="F119" s="30"/>
-      <c r="G119" s="17"/>
-      <c r="H119" s="28"/>
-      <c r="I119" s="30"/>
-      <c r="J119" s="33"/>
-    </row>
-    <row r="120" spans="1:10">
-      <c r="A120" s="36"/>
-      <c r="B120" s="39"/>
-      <c r="C120" s="42"/>
-      <c r="D120" s="45"/>
-      <c r="E120" s="30"/>
-      <c r="F120" s="30"/>
-      <c r="G120" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="H120" s="28"/>
-      <c r="I120" s="30"/>
-      <c r="J120" s="33"/>
-    </row>
-    <row r="121" spans="1:10">
-      <c r="A121" s="37"/>
-      <c r="B121" s="40"/>
-      <c r="C121" s="43"/>
-      <c r="D121" s="46"/>
-      <c r="E121" s="31"/>
-      <c r="F121" s="31"/>
-      <c r="G121" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="H121" s="28"/>
-      <c r="I121" s="31"/>
-      <c r="J121" s="34"/>
-    </row>
-    <row r="122" spans="1:10" ht="28.5">
-      <c r="A122" s="35">
-        <v>46183</v>
-      </c>
-      <c r="B122" s="38">
-        <v>0.77916666666666667</v>
-      </c>
-      <c r="C122" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="D122" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="E122" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="F122" s="29" t="s">
+      <c r="B135" s="19">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C135" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="D135" s="21">
+        <v>9764</v>
+      </c>
+      <c r="E135" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="F135" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="G122" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="H122" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="I122" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J122" s="32" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10">
-      <c r="A123" s="36"/>
-      <c r="B123" s="39"/>
-      <c r="C123" s="42"/>
-      <c r="D123" s="45"/>
-      <c r="E123" s="30"/>
-      <c r="F123" s="30"/>
-      <c r="G123" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="H123" s="28"/>
-      <c r="I123" s="30"/>
-      <c r="J123" s="33"/>
-    </row>
-    <row r="124" spans="1:10">
-      <c r="A124" s="36"/>
-      <c r="B124" s="39"/>
-      <c r="C124" s="42"/>
-      <c r="D124" s="45"/>
-      <c r="E124" s="30"/>
-      <c r="F124" s="30"/>
-      <c r="G124" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="H124" s="28"/>
-      <c r="I124" s="30"/>
-      <c r="J124" s="33"/>
-    </row>
-    <row r="125" spans="1:10">
-      <c r="A125" s="36"/>
-      <c r="B125" s="39"/>
-      <c r="C125" s="42"/>
-      <c r="D125" s="45"/>
-      <c r="E125" s="30"/>
-      <c r="F125" s="30"/>
-      <c r="G125" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="H125" s="28"/>
-      <c r="I125" s="30"/>
-      <c r="J125" s="33"/>
-    </row>
-    <row r="126" spans="1:10">
-      <c r="A126" s="37"/>
-      <c r="B126" s="40"/>
-      <c r="C126" s="43"/>
-      <c r="D126" s="46"/>
-      <c r="E126" s="31"/>
-      <c r="F126" s="31"/>
-      <c r="G126" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="H126" s="28"/>
-      <c r="I126" s="31"/>
-      <c r="J126" s="34"/>
-    </row>
-    <row r="127" spans="1:10" ht="57">
-      <c r="A127" s="22">
-        <v>46189</v>
-      </c>
-      <c r="B127" s="23">
-        <v>0.77916666666666667</v>
-      </c>
-      <c r="C127" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="D127" s="25">
-        <v>9744</v>
-      </c>
-      <c r="E127" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="F127" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="G127" s="24" t="s">
+      <c r="G135" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="H135" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I135" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J135" s="23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="42.75">
+      <c r="A136" s="18">
+        <v>46186</v>
+      </c>
+      <c r="B136" s="19">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C136" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="H127" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="I127" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J127" s="27" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="71.25">
-      <c r="A128" s="22">
-        <v>46184</v>
-      </c>
-      <c r="B128" s="23">
-        <v>0.38055555555555554</v>
-      </c>
-      <c r="C128" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D128" s="25">
-        <v>9744</v>
-      </c>
-      <c r="E128" s="26" t="s">
+      <c r="D136" s="21">
+        <v>9764</v>
+      </c>
+      <c r="E136" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="F128" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="G128" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="H128" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="I128" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J128" s="27" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10">
-      <c r="A129" s="35">
-        <v>46183</v>
-      </c>
-      <c r="B129" s="38">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="C129" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="D129" s="44">
-        <v>9759</v>
-      </c>
-      <c r="E129" s="29" t="s">
-        <v>180</v>
-      </c>
-      <c r="F129" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G129" s="19" t="s">
+      <c r="F136" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="G136" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="H129" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="I129" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J129" s="32" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10">
-      <c r="A130" s="36"/>
-      <c r="B130" s="56"/>
-      <c r="C130" s="57"/>
-      <c r="D130" s="58"/>
-      <c r="E130" s="59"/>
-      <c r="F130" s="59"/>
-      <c r="G130" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="H130" s="28"/>
-      <c r="I130" s="59"/>
-      <c r="J130" s="33"/>
-    </row>
-    <row r="131" spans="1:10">
-      <c r="A131" s="36"/>
-      <c r="B131" s="56"/>
-      <c r="C131" s="57"/>
-      <c r="D131" s="58"/>
-      <c r="E131" s="59"/>
-      <c r="F131" s="59"/>
-      <c r="G131" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="H131" s="28"/>
-      <c r="I131" s="59"/>
-      <c r="J131" s="33"/>
-    </row>
-    <row r="132" spans="1:10">
-      <c r="A132" s="36"/>
-      <c r="B132" s="56"/>
-      <c r="C132" s="57"/>
-      <c r="D132" s="58"/>
-      <c r="E132" s="59"/>
-      <c r="F132" s="59"/>
-      <c r="G132" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="H132" s="28"/>
-      <c r="I132" s="59"/>
-      <c r="J132" s="33"/>
-    </row>
-    <row r="133" spans="1:10">
-      <c r="A133" s="37"/>
-      <c r="B133" s="40"/>
-      <c r="C133" s="43"/>
-      <c r="D133" s="46"/>
-      <c r="E133" s="31"/>
-      <c r="F133" s="31"/>
-      <c r="G133" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="H133" s="28"/>
-      <c r="I133" s="31"/>
-      <c r="J133" s="34"/>
-    </row>
-    <row r="134" spans="1:10" ht="99.75">
-      <c r="A134" s="22">
-        <v>46185</v>
-      </c>
-      <c r="B134" s="23">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C134" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="D134" s="25">
-        <v>9762</v>
-      </c>
-      <c r="E134" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="F134" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="G134" s="55" t="s">
-        <v>189</v>
-      </c>
-      <c r="H134" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="I134" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J134" s="27" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" ht="99.75">
-      <c r="A135" s="22">
-        <v>46186</v>
-      </c>
-      <c r="B135" s="23">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C135" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="D135" s="25">
-        <v>9764</v>
-      </c>
-      <c r="E135" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="F135" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="G135" s="55" t="s">
-        <v>189</v>
-      </c>
-      <c r="H135" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="I135" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J135" s="27" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" ht="99.75">
-      <c r="A136" s="22">
-        <v>46186</v>
-      </c>
-      <c r="B136" s="23">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C136" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="D136" s="25">
-        <v>9764</v>
-      </c>
-      <c r="E136" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="F136" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="G136" s="55" t="s">
-        <v>189</v>
-      </c>
-      <c r="H136" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="I136" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="J136" s="27" t="s">
+      <c r="H136" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I136" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J136" s="23" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="54">
-    <mergeCell ref="F129:F133"/>
-    <mergeCell ref="H129:H133"/>
-    <mergeCell ref="I129:I133"/>
-    <mergeCell ref="J129:J133"/>
-    <mergeCell ref="A129:A133"/>
-    <mergeCell ref="B129:B133"/>
-    <mergeCell ref="C129:C133"/>
-    <mergeCell ref="D129:D133"/>
-    <mergeCell ref="E129:E133"/>
+  <mergeCells count="60">
+    <mergeCell ref="G102:G106"/>
+    <mergeCell ref="G107:G111"/>
+    <mergeCell ref="G112:G116"/>
+    <mergeCell ref="G117:G121"/>
+    <mergeCell ref="G122:G126"/>
+    <mergeCell ref="A122:A126"/>
+    <mergeCell ref="B122:B126"/>
+    <mergeCell ref="C122:C126"/>
+    <mergeCell ref="D122:D126"/>
+    <mergeCell ref="E122:E126"/>
+    <mergeCell ref="F117:F121"/>
+    <mergeCell ref="H117:H121"/>
+    <mergeCell ref="I117:I121"/>
+    <mergeCell ref="J117:J121"/>
+    <mergeCell ref="H122:H126"/>
+    <mergeCell ref="I122:I126"/>
+    <mergeCell ref="J122:J126"/>
+    <mergeCell ref="F122:F126"/>
+    <mergeCell ref="A117:A121"/>
+    <mergeCell ref="B117:B121"/>
+    <mergeCell ref="C117:C121"/>
+    <mergeCell ref="D117:D121"/>
+    <mergeCell ref="E117:E121"/>
+    <mergeCell ref="I107:I111"/>
+    <mergeCell ref="J107:J111"/>
+    <mergeCell ref="A112:A116"/>
+    <mergeCell ref="B112:B116"/>
+    <mergeCell ref="C112:C116"/>
+    <mergeCell ref="D112:D116"/>
+    <mergeCell ref="E112:E116"/>
+    <mergeCell ref="F112:F116"/>
+    <mergeCell ref="H112:H116"/>
+    <mergeCell ref="I112:I116"/>
+    <mergeCell ref="J112:J116"/>
     <mergeCell ref="H102:H106"/>
     <mergeCell ref="I102:I106"/>
     <mergeCell ref="J102:J106"/>
@@ -5302,35 +5318,16 @@
     <mergeCell ref="D102:D106"/>
     <mergeCell ref="E102:E106"/>
     <mergeCell ref="F102:F106"/>
-    <mergeCell ref="I107:I111"/>
-    <mergeCell ref="J107:J111"/>
-    <mergeCell ref="A112:A116"/>
-    <mergeCell ref="B112:B116"/>
-    <mergeCell ref="C112:C116"/>
-    <mergeCell ref="D112:D116"/>
-    <mergeCell ref="E112:E116"/>
-    <mergeCell ref="F112:F116"/>
-    <mergeCell ref="H112:H116"/>
-    <mergeCell ref="I112:I116"/>
-    <mergeCell ref="J112:J116"/>
-    <mergeCell ref="A117:A121"/>
-    <mergeCell ref="B117:B121"/>
-    <mergeCell ref="C117:C121"/>
-    <mergeCell ref="D117:D121"/>
-    <mergeCell ref="E117:E121"/>
-    <mergeCell ref="F117:F121"/>
-    <mergeCell ref="H117:H121"/>
-    <mergeCell ref="I117:I121"/>
-    <mergeCell ref="J117:J121"/>
-    <mergeCell ref="H122:H126"/>
-    <mergeCell ref="I122:I126"/>
-    <mergeCell ref="J122:J126"/>
-    <mergeCell ref="A122:A126"/>
-    <mergeCell ref="B122:B126"/>
-    <mergeCell ref="C122:C126"/>
-    <mergeCell ref="D122:D126"/>
-    <mergeCell ref="E122:E126"/>
-    <mergeCell ref="F122:F126"/>
+    <mergeCell ref="F129:F133"/>
+    <mergeCell ref="H129:H133"/>
+    <mergeCell ref="I129:I133"/>
+    <mergeCell ref="J129:J133"/>
+    <mergeCell ref="A129:A133"/>
+    <mergeCell ref="B129:B133"/>
+    <mergeCell ref="C129:C133"/>
+    <mergeCell ref="D129:D133"/>
+    <mergeCell ref="E129:E133"/>
+    <mergeCell ref="G129:G133"/>
   </mergeCells>
   <conditionalFormatting sqref="H2:H101">
     <cfRule type="expression" dxfId="4" priority="1">
@@ -5442,14 +5439,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="5" t="s">

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5171DC60-6849-4DEF-95F2-2F2DC9C3DDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AE5DC9-3298-40F7-A32D-BC333CB8A89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="175">
   <si>
     <t>Fecha</t>
   </si>
@@ -533,24 +533,9 @@
     <t>Ubicaciones registradas</t>
   </si>
   <si>
-    <t>Sede Villa - Martes de la Semana de Ingeniería</t>
-  </si>
-  <si>
-    <t>Sede Villa - Feria Empresarial</t>
-  </si>
-  <si>
     <t>Sede Villa – Jardin Lote 28</t>
   </si>
   <si>
-    <t>• 8 toldos.</t>
-  </si>
-  <si>
-    <t>• 8 mesas con mantel.</t>
-  </si>
-  <si>
-    <t>• 16 sillas (2 por mesa).</t>
-  </si>
-  <si>
     <t>MEDICINA HUMANA</t>
   </si>
   <si>
@@ -560,24 +545,9 @@
     <t>Clínica de Simulación</t>
   </si>
   <si>
-    <t xml:space="preserve">no especifica </t>
-  </si>
-  <si>
     <t>Hall del Pabellón N</t>
   </si>
   <si>
-    <t>- 60 sillas en formato auditorio.</t>
-  </si>
-  <si>
-    <t>-  TV en rack al fondo  - la del pabellón L.</t>
-  </si>
-  <si>
-    <t>- Bandera de Científica y del Perú</t>
-  </si>
-  <si>
-    <t>- Podio de Científica</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campaña Certijoven </t>
   </si>
   <si>
@@ -596,49 +566,46 @@
     <t>Jardín de pabellón N</t>
   </si>
   <si>
-    <t>Cinco toldos para la atención de los servicios.</t>
-  </si>
-  <si>
-    <t>Mesas (06) y sillas para los servicios (4 x cada mesa)</t>
-  </si>
-  <si>
-    <t>Manteles para todas las mesas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">los cables y puntos de conexión </t>
-  </si>
-  <si>
     <t>AREA DE CCBB</t>
   </si>
   <si>
     <t>Coloquio Internacional</t>
   </si>
   <si>
-    <t xml:space="preserve">Requerimientos :3 toldos / 3 mesas  / 6 sillas / 1televisor </t>
-  </si>
-  <si>
-    <t>Requerimientos : 8 toldos / 8 mesas / 8 manteles / 16 sillas (2 por mesas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requerimientos : 5 mesas / 25 sillas </t>
-  </si>
-  <si>
-    <t>Por favor retirar muebles del hall y colocar: 9:30 am a 12:00 pm  /   60 sillas / tv con rack / banderas de cientifica y peru / podium</t>
-  </si>
-  <si>
-    <t>Requerimiento : 5 toldos / 6 mesas / 24 sillas / 6 manteles / puntos de energia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requerimientos: 5 sillones / 2 mesas de registro / 2 sillas / 3 mesas para catering / 3 manteles / totem colloquio / 73 sillas </t>
-  </si>
-  <si>
     <t xml:space="preserve">Pabellon I - pasillo </t>
   </si>
   <si>
-    <t xml:space="preserve">mesa con mantel / 2 sillas </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 mesas con mantel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 mesas / 25 sillas </t>
+  </si>
+  <si>
+    <t>60 sillas / tv con rack / banderas de cientifica y peru / podium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 mesa con mantel / 2 sillas </t>
+  </si>
+  <si>
+    <t>5 toldos / 6 mesas / 24 sillas / 6 manteles / puntos de energia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 sillones / 2 mesas de registro / 2 sillas / 3 mesas para catering / 3 manteles / totem colloquio / 73 sillas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 toldos / 3 mesas  / 6 sillas / 1televisor </t>
+  </si>
+  <si>
+    <t>Semana de Ingeniería</t>
+  </si>
+  <si>
+    <t>Feria Empresarial</t>
+  </si>
+  <si>
+    <t>INGENIERA ACUICOLO</t>
+  </si>
+  <si>
+    <t>8 toldos / 8 mesas / 8 manteles / 16 sillas (2 por mesas)</t>
   </si>
 </sst>
 </file>
@@ -648,7 +615,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -675,25 +642,8 @@
       <color theme="1"/>
       <name val="Carlito"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF991B1B"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Carlito"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -722,26 +672,8 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E6F5"/>
-        <bgColor rgb="FFC0E6F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61CBF3"/>
-        <bgColor rgb="FFC0E6F5"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="18">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -786,159 +718,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF44B3E1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF44B3E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF44B3E1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF44B3E1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF44B3E1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF44B3E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF44B3E1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF44B3E1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF44B3E1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF44B3E1"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -984,150 +768,30 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1202,7 +866,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Área Solicitante"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="N° OT"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="N° OT" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Evento / Actividad"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ubicación"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Requerimientos"/>
@@ -1363,13 +1027,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J136"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="4" max="4" width="16" style="22" customWidth="1"/>
     <col min="5" max="6" width="34" customWidth="1"/>
     <col min="7" max="7" width="48" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
@@ -1420,7 +1084,7 @@
       <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="19" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -1452,7 +1116,7 @@
       <c r="C3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="19" t="s">
         <v>22</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -1484,7 +1148,7 @@
       <c r="C4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -1516,7 +1180,7 @@
       <c r="C5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -1548,7 +1212,7 @@
       <c r="C6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="19"/>
       <c r="E6" s="2" t="s">
         <v>37</v>
       </c>
@@ -1578,7 +1242,7 @@
       <c r="C7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="19"/>
       <c r="E7" s="2" t="s">
         <v>42</v>
       </c>
@@ -1606,7 +1270,7 @@
       <c r="C8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -1638,7 +1302,7 @@
       <c r="C9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -1670,7 +1334,7 @@
       <c r="C10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -1702,7 +1366,7 @@
       <c r="C11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="19" t="s">
         <v>60</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -1734,7 +1398,7 @@
       <c r="C12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="19" t="s">
         <v>65</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -1766,7 +1430,7 @@
       <c r="C13" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="19" t="s">
         <v>69</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -1798,7 +1462,7 @@
       <c r="C14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="19" t="s">
         <v>74</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -1830,7 +1494,7 @@
       <c r="C15" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="20" t="s">
         <v>78</v>
       </c>
       <c r="E15" s="8" t="s">
@@ -1862,7 +1526,7 @@
       <c r="C16" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="20" t="s">
         <v>78</v>
       </c>
       <c r="E16" s="8" t="s">
@@ -1894,7 +1558,7 @@
       <c r="C17" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E17" s="12" t="s">
@@ -1926,7 +1590,7 @@
       <c r="C18" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="12" t="s">
@@ -1958,7 +1622,7 @@
       <c r="C19" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="12" t="s">
@@ -1990,7 +1654,7 @@
       <c r="C20" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="12" t="s">
@@ -2022,7 +1686,7 @@
       <c r="C21" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E21" s="12" t="s">
@@ -2054,7 +1718,7 @@
       <c r="C22" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E22" s="12" t="s">
@@ -2086,7 +1750,7 @@
       <c r="C23" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="12" t="s">
@@ -2118,7 +1782,7 @@
       <c r="C24" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E24" s="12" t="s">
@@ -2150,7 +1814,7 @@
       <c r="C25" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="12" t="s">
@@ -2182,7 +1846,7 @@
       <c r="C26" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E26" s="12" t="s">
@@ -2214,7 +1878,7 @@
       <c r="C27" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E27" s="12" t="s">
@@ -2246,7 +1910,7 @@
       <c r="C28" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="12" t="s">
@@ -2278,7 +1942,7 @@
       <c r="C29" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="12" t="s">
@@ -2310,7 +1974,7 @@
       <c r="C30" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="12" t="s">
@@ -2342,7 +2006,7 @@
       <c r="C31" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="12" t="s">
@@ -2374,7 +2038,7 @@
       <c r="C32" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="12" t="s">
@@ -2406,7 +2070,7 @@
       <c r="C33" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="12" t="s">
@@ -2438,7 +2102,7 @@
       <c r="C34" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E34" s="12" t="s">
@@ -2470,7 +2134,7 @@
       <c r="C35" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E35" s="12" t="s">
@@ -2502,7 +2166,7 @@
       <c r="C36" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="12" t="s">
@@ -2534,7 +2198,7 @@
       <c r="C37" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E37" s="12" t="s">
@@ -2566,7 +2230,7 @@
       <c r="C38" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="12" t="s">
@@ -2598,7 +2262,7 @@
       <c r="C39" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="12" t="s">
@@ -2630,7 +2294,7 @@
       <c r="C40" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="12" t="s">
@@ -2662,7 +2326,7 @@
       <c r="C41" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="12" t="s">
@@ -2694,7 +2358,7 @@
       <c r="C42" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E42" s="12" t="s">
@@ -2726,7 +2390,7 @@
       <c r="C43" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="12" t="s">
@@ -2758,7 +2422,7 @@
       <c r="C44" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E44" s="12" t="s">
@@ -2790,7 +2454,7 @@
       <c r="C45" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E45" s="12" t="s">
@@ -2822,7 +2486,7 @@
       <c r="C46" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E46" s="12" t="s">
@@ -2854,7 +2518,7 @@
       <c r="C47" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E47" s="12" t="s">
@@ -2886,7 +2550,7 @@
       <c r="C48" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E48" s="12" t="s">
@@ -2918,7 +2582,7 @@
       <c r="C49" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="12" t="s">
@@ -2950,7 +2614,7 @@
       <c r="C50" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="12" t="s">
@@ -2982,7 +2646,7 @@
       <c r="C51" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E51" s="12" t="s">
@@ -3014,7 +2678,7 @@
       <c r="C52" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E52" s="12" t="s">
@@ -3046,7 +2710,7 @@
       <c r="C53" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="12" t="s">
@@ -3078,7 +2742,7 @@
       <c r="C54" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E54" s="12" t="s">
@@ -3110,7 +2774,7 @@
       <c r="C55" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="12" t="s">
@@ -3142,7 +2806,7 @@
       <c r="C56" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D56" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E56" s="12" t="s">
@@ -3174,7 +2838,7 @@
       <c r="C57" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="12" t="s">
@@ -3206,7 +2870,7 @@
       <c r="C58" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D58" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="12" t="s">
@@ -3238,7 +2902,7 @@
       <c r="C59" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="12" t="s">
@@ -3270,7 +2934,7 @@
       <c r="C60" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="D60" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="12" t="s">
@@ -3302,7 +2966,7 @@
       <c r="C61" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="12" t="s">
@@ -3334,7 +2998,7 @@
       <c r="C62" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="D62" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E62" s="12" t="s">
@@ -3366,7 +3030,7 @@
       <c r="C63" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D63" s="12" t="s">
+      <c r="D63" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="12" t="s">
@@ -3398,7 +3062,7 @@
       <c r="C64" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D64" s="12" t="s">
+      <c r="D64" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E64" s="12" t="s">
@@ -3430,7 +3094,7 @@
       <c r="C65" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D65" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E65" s="12" t="s">
@@ -3462,7 +3126,7 @@
       <c r="C66" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D66" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E66" s="12" t="s">
@@ -3494,7 +3158,7 @@
       <c r="C67" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D67" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E67" s="12" t="s">
@@ -3526,7 +3190,7 @@
       <c r="C68" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="D68" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E68" s="12" t="s">
@@ -3558,7 +3222,7 @@
       <c r="C69" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D69" s="12" t="s">
+      <c r="D69" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E69" s="12" t="s">
@@ -3590,7 +3254,7 @@
       <c r="C70" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D70" s="12" t="s">
+      <c r="D70" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="12" t="s">
@@ -3622,7 +3286,7 @@
       <c r="C71" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E71" s="12" t="s">
@@ -3654,7 +3318,7 @@
       <c r="C72" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D72" s="12" t="s">
+      <c r="D72" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="12" t="s">
@@ -3686,7 +3350,7 @@
       <c r="C73" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="D73" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="12" t="s">
@@ -3718,7 +3382,7 @@
       <c r="C74" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D74" s="12" t="s">
+      <c r="D74" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="12" t="s">
@@ -3750,7 +3414,7 @@
       <c r="C75" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="D75" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="12" t="s">
@@ -3782,7 +3446,7 @@
       <c r="C76" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D76" s="12" t="s">
+      <c r="D76" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="12" t="s">
@@ -3814,7 +3478,7 @@
       <c r="C77" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D77" s="12" t="s">
+      <c r="D77" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E77" s="12" t="s">
@@ -3846,7 +3510,7 @@
       <c r="C78" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D78" s="12" t="s">
+      <c r="D78" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="12" t="s">
@@ -3878,7 +3542,7 @@
       <c r="C79" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D79" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E79" s="12" t="s">
@@ -3910,7 +3574,7 @@
       <c r="C80" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="D80" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E80" s="12" t="s">
@@ -3942,7 +3606,7 @@
       <c r="C81" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D81" s="12" t="s">
+      <c r="D81" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="12" t="s">
@@ -3974,7 +3638,7 @@
       <c r="C82" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D82" s="12" t="s">
+      <c r="D82" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E82" s="12" t="s">
@@ -4006,7 +3670,7 @@
       <c r="C83" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D83" s="12" t="s">
+      <c r="D83" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E83" s="12" t="s">
@@ -4038,7 +3702,7 @@
       <c r="C84" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D84" s="12" t="s">
+      <c r="D84" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E84" s="12" t="s">
@@ -4070,7 +3734,7 @@
       <c r="C85" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D85" s="12" t="s">
+      <c r="D85" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E85" s="12" t="s">
@@ -4102,7 +3766,7 @@
       <c r="C86" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D86" s="12" t="s">
+      <c r="D86" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E86" s="12" t="s">
@@ -4134,7 +3798,7 @@
       <c r="C87" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D87" s="12" t="s">
+      <c r="D87" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E87" s="12" t="s">
@@ -4166,7 +3830,7 @@
       <c r="C88" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D88" s="12" t="s">
+      <c r="D88" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E88" s="12" t="s">
@@ -4198,7 +3862,7 @@
       <c r="C89" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D89" s="12" t="s">
+      <c r="D89" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E89" s="12" t="s">
@@ -4230,7 +3894,7 @@
       <c r="C90" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D90" s="12" t="s">
+      <c r="D90" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E90" s="12" t="s">
@@ -4262,7 +3926,7 @@
       <c r="C91" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D91" s="12" t="s">
+      <c r="D91" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E91" s="12" t="s">
@@ -4294,7 +3958,7 @@
       <c r="C92" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D92" s="12" t="s">
+      <c r="D92" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E92" s="12" t="s">
@@ -4326,7 +3990,7 @@
       <c r="C93" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D93" s="12" t="s">
+      <c r="D93" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E93" s="12" t="s">
@@ -4358,7 +4022,7 @@
       <c r="C94" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D94" s="12" t="s">
+      <c r="D94" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E94" s="12" t="s">
@@ -4390,7 +4054,7 @@
       <c r="C95" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D95" s="12" t="s">
+      <c r="D95" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E95" s="12" t="s">
@@ -4422,7 +4086,7 @@
       <c r="C96" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D96" s="12" t="s">
+      <c r="D96" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E96" s="12" t="s">
@@ -4454,7 +4118,7 @@
       <c r="C97" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D97" s="12" t="s">
+      <c r="D97" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E97" s="12" t="s">
@@ -4486,7 +4150,7 @@
       <c r="C98" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D98" s="12" t="s">
+      <c r="D98" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E98" s="12" t="s">
@@ -4518,7 +4182,7 @@
       <c r="C99" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D99" s="12" t="s">
+      <c r="D99" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E99" s="12" t="s">
@@ -4550,7 +4214,7 @@
       <c r="C100" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D100" s="12" t="s">
+      <c r="D100" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E100" s="12" t="s">
@@ -4582,7 +4246,7 @@
       <c r="C101" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D101" s="12" t="s">
+      <c r="D101" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E101" s="12" t="s">
@@ -4605,746 +4269,374 @@
       </c>
     </row>
     <row r="102" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A102" s="43">
+      <c r="A102" s="16">
         <v>46182</v>
       </c>
-      <c r="B102" s="44">
+      <c r="B102" s="15">
         <v>0.47152777777777777</v>
       </c>
-      <c r="C102" s="45" t="s">
+      <c r="C102" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D102" s="46">
+      <c r="D102" s="21">
         <v>81688</v>
       </c>
-      <c r="E102" s="41" t="s">
+      <c r="E102" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="F102" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G102" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H102" t="s">
+        <v>17</v>
+      </c>
+      <c r="I102" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J102" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A103" s="16">
+        <v>46186</v>
+      </c>
+      <c r="B103" s="15">
+        <v>0.47152777777777777</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D103" s="21">
+        <v>81685</v>
+      </c>
+      <c r="E103" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="F103" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="F102" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G102" s="53" t="s">
-        <v>177</v>
-      </c>
-      <c r="H102" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="I102" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="J102" s="42" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10">
-      <c r="A103" s="33"/>
-      <c r="B103" s="52"/>
-      <c r="C103" s="51"/>
-      <c r="D103" s="50"/>
-      <c r="E103" s="49"/>
-      <c r="F103" s="49"/>
-      <c r="G103" s="54"/>
-      <c r="H103" s="28"/>
-      <c r="I103" s="26"/>
-      <c r="J103" s="30"/>
+      <c r="G103" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="H103" t="s">
+        <v>17</v>
+      </c>
+      <c r="I103" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J103" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="104" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A104" s="33"/>
-      <c r="B104" s="52"/>
-      <c r="C104" s="51"/>
-      <c r="D104" s="50"/>
-      <c r="E104" s="49"/>
-      <c r="F104" s="49"/>
-      <c r="G104" s="54"/>
-      <c r="H104" s="28"/>
-      <c r="I104" s="26"/>
-      <c r="J104" s="30"/>
+      <c r="A104" s="16">
+        <v>46190</v>
+      </c>
+      <c r="B104" s="15">
+        <v>0.77152777777777781</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D104" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E104" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="F104" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="G104" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="H104" t="s">
+        <v>17</v>
+      </c>
+      <c r="I104" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J104" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="105" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A105" s="33"/>
-      <c r="B105" s="52"/>
-      <c r="C105" s="51"/>
-      <c r="D105" s="50"/>
-      <c r="E105" s="49"/>
-      <c r="F105" s="49"/>
-      <c r="G105" s="54"/>
-      <c r="H105" s="28"/>
-      <c r="I105" s="26"/>
-      <c r="J105" s="30"/>
+      <c r="A105" s="16">
+        <v>46191</v>
+      </c>
+      <c r="B105" s="15">
+        <v>0.77152777777777781</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D105" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E105" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="F105" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="G105" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="H105" t="s">
+        <v>17</v>
+      </c>
+      <c r="I105" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J105" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="106" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A106" s="34"/>
-      <c r="B106" s="36"/>
-      <c r="C106" s="38"/>
-      <c r="D106" s="40"/>
-      <c r="E106" s="27"/>
-      <c r="F106" s="27"/>
-      <c r="G106" s="55"/>
-      <c r="H106" s="28"/>
-      <c r="I106" s="27"/>
-      <c r="J106" s="31"/>
-    </row>
-    <row r="107" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A107" s="32">
+      <c r="A106" s="16">
+        <v>46183</v>
+      </c>
+      <c r="B106" s="15">
+        <v>0.77916666666666667</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D106" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E106" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="F106" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="G106" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="H106" t="s">
+        <v>17</v>
+      </c>
+      <c r="I106" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J106" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" s="16">
+        <v>46189</v>
+      </c>
+      <c r="B107" s="15">
+        <v>0.77916666666666667</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D107" s="21">
+        <v>9744</v>
+      </c>
+      <c r="E107" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="F107" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="G107" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="H107" t="s">
+        <v>17</v>
+      </c>
+      <c r="I107" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J107" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" s="16">
+        <v>46184</v>
+      </c>
+      <c r="B108" s="15">
+        <v>0.38055555555555554</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D108" s="21">
+        <v>9744</v>
+      </c>
+      <c r="E108" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="F108" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G108" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="H108" t="s">
+        <v>17</v>
+      </c>
+      <c r="I108" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J108" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A109" s="16">
+        <v>46183</v>
+      </c>
+      <c r="B109" s="15">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="D109" s="21">
+        <v>9759</v>
+      </c>
+      <c r="E109" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="F109" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="G109" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="H109" t="s">
+        <v>17</v>
+      </c>
+      <c r="I109" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J109" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="28.5">
+      <c r="A110" s="16">
+        <v>46185</v>
+      </c>
+      <c r="B110" s="15">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C110" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="D110" s="21">
+        <v>9762</v>
+      </c>
+      <c r="E110" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="F110" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="G110" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="H110" t="s">
+        <v>17</v>
+      </c>
+      <c r="I110" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J110" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="28.5">
+      <c r="A111" s="16">
         <v>46186</v>
       </c>
-      <c r="B107" s="35">
-        <v>0.47152777777777777</v>
-      </c>
-      <c r="C107" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="D107" s="39">
-        <v>81685</v>
-      </c>
-      <c r="E107" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="F107" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="G107" s="60" t="s">
-        <v>178</v>
-      </c>
-      <c r="H107" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="I107" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="J107" s="29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A108" s="33"/>
-      <c r="B108" s="52"/>
-      <c r="C108" s="51"/>
-      <c r="D108" s="50"/>
-      <c r="E108" s="49"/>
-      <c r="F108" s="49"/>
-      <c r="G108" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="H108" s="28"/>
-      <c r="I108" s="26"/>
-      <c r="J108" s="30"/>
-    </row>
-    <row r="109" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A109" s="33"/>
-      <c r="B109" s="52"/>
-      <c r="C109" s="51"/>
-      <c r="D109" s="50"/>
-      <c r="E109" s="49"/>
-      <c r="F109" s="49"/>
-      <c r="G109" s="61" t="s">
-        <v>154</v>
-      </c>
-      <c r="H109" s="28"/>
-      <c r="I109" s="26"/>
-      <c r="J109" s="30"/>
-    </row>
-    <row r="110" spans="1:10">
-      <c r="A110" s="33"/>
-      <c r="B110" s="52"/>
-      <c r="C110" s="51"/>
-      <c r="D110" s="50"/>
-      <c r="E110" s="49"/>
-      <c r="F110" s="49"/>
-      <c r="G110" s="61" t="s">
-        <v>155</v>
-      </c>
-      <c r="H110" s="28"/>
-      <c r="I110" s="26"/>
-      <c r="J110" s="30"/>
-    </row>
-    <row r="111" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A111" s="34"/>
-      <c r="B111" s="36"/>
-      <c r="C111" s="38"/>
-      <c r="D111" s="40"/>
-      <c r="E111" s="27"/>
-      <c r="F111" s="27"/>
-      <c r="G111" s="62"/>
-      <c r="H111" s="28"/>
-      <c r="I111" s="27"/>
-      <c r="J111" s="31"/>
-    </row>
-    <row r="112" spans="1:10">
-      <c r="A112" s="32">
-        <v>46190</v>
-      </c>
-      <c r="B112" s="35">
-        <v>0.77152777777777781</v>
-      </c>
-      <c r="C112" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="D112" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="E112" s="25" t="s">
+      <c r="B111" s="15">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="D111" s="21">
+        <v>9764</v>
+      </c>
+      <c r="E111" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="F111" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="F112" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="G112" s="57" t="s">
-        <v>179</v>
-      </c>
-      <c r="H112" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="I112" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="J112" s="29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10">
-      <c r="A113" s="33"/>
-      <c r="B113" s="52"/>
-      <c r="C113" s="51"/>
-      <c r="D113" s="50"/>
-      <c r="E113" s="49"/>
-      <c r="F113" s="49"/>
-      <c r="G113" s="58"/>
-      <c r="H113" s="28"/>
-      <c r="I113" s="26"/>
-      <c r="J113" s="30"/>
-    </row>
-    <row r="114" spans="1:10">
-      <c r="A114" s="33"/>
-      <c r="B114" s="52"/>
-      <c r="C114" s="51"/>
-      <c r="D114" s="50"/>
-      <c r="E114" s="49"/>
-      <c r="F114" s="49"/>
-      <c r="G114" s="58"/>
-      <c r="H114" s="28"/>
-      <c r="I114" s="26"/>
-      <c r="J114" s="30"/>
-    </row>
-    <row r="115" spans="1:10">
-      <c r="A115" s="33"/>
-      <c r="B115" s="52"/>
-      <c r="C115" s="51"/>
-      <c r="D115" s="50"/>
-      <c r="E115" s="49"/>
-      <c r="F115" s="49"/>
-      <c r="G115" s="58"/>
-      <c r="H115" s="28"/>
-      <c r="I115" s="26"/>
-      <c r="J115" s="30"/>
-    </row>
-    <row r="116" spans="1:10">
-      <c r="A116" s="34"/>
-      <c r="B116" s="36"/>
-      <c r="C116" s="38"/>
-      <c r="D116" s="40"/>
-      <c r="E116" s="27"/>
-      <c r="F116" s="27"/>
-      <c r="G116" s="59"/>
-      <c r="H116" s="28"/>
-      <c r="I116" s="27"/>
-      <c r="J116" s="31"/>
-    </row>
-    <row r="117" spans="1:10">
-      <c r="A117" s="32">
-        <v>46191</v>
-      </c>
-      <c r="B117" s="35">
-        <v>0.77152777777777781</v>
-      </c>
-      <c r="C117" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="D117" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="E117" s="25" t="s">
+      <c r="G111" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="H111" t="s">
+        <v>17</v>
+      </c>
+      <c r="I111" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J111" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="28.5">
+      <c r="A112" s="16">
+        <v>46186</v>
+      </c>
+      <c r="B112" s="15">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C112" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="D112" s="21">
+        <v>9764</v>
+      </c>
+      <c r="E112" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="F112" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="F117" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="G117" s="57" t="s">
-        <v>179</v>
-      </c>
-      <c r="H117" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="I117" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="J117" s="29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10">
-      <c r="A118" s="33"/>
-      <c r="B118" s="52"/>
-      <c r="C118" s="51"/>
-      <c r="D118" s="50"/>
-      <c r="E118" s="49"/>
-      <c r="F118" s="49"/>
-      <c r="G118" s="58"/>
-      <c r="H118" s="28"/>
-      <c r="I118" s="26"/>
-      <c r="J118" s="30"/>
-    </row>
-    <row r="119" spans="1:10">
-      <c r="A119" s="33"/>
-      <c r="B119" s="52"/>
-      <c r="C119" s="51"/>
-      <c r="D119" s="50"/>
-      <c r="E119" s="49"/>
-      <c r="F119" s="49"/>
-      <c r="G119" s="58"/>
-      <c r="H119" s="28"/>
-      <c r="I119" s="26"/>
-      <c r="J119" s="30"/>
-    </row>
-    <row r="120" spans="1:10">
-      <c r="A120" s="33"/>
-      <c r="B120" s="52"/>
-      <c r="C120" s="51"/>
-      <c r="D120" s="50"/>
-      <c r="E120" s="49"/>
-      <c r="F120" s="49"/>
-      <c r="G120" s="58"/>
-      <c r="H120" s="28"/>
-      <c r="I120" s="26"/>
-      <c r="J120" s="30"/>
-    </row>
-    <row r="121" spans="1:10">
-      <c r="A121" s="34"/>
-      <c r="B121" s="36"/>
-      <c r="C121" s="38"/>
-      <c r="D121" s="40"/>
-      <c r="E121" s="27"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="59"/>
-      <c r="H121" s="28"/>
-      <c r="I121" s="27"/>
-      <c r="J121" s="31"/>
-    </row>
-    <row r="122" spans="1:10">
-      <c r="A122" s="32">
-        <v>46183</v>
-      </c>
-      <c r="B122" s="35">
-        <v>0.77916666666666667</v>
-      </c>
-      <c r="C122" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="D122" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="E122" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="F122" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="G122" s="63" t="s">
-        <v>180</v>
-      </c>
-      <c r="H122" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="I122" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="J122" s="29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10">
-      <c r="A123" s="33"/>
-      <c r="B123" s="52"/>
-      <c r="C123" s="51"/>
-      <c r="D123" s="50"/>
-      <c r="E123" s="49"/>
-      <c r="F123" s="49"/>
-      <c r="G123" s="63" t="s">
-        <v>161</v>
-      </c>
-      <c r="H123" s="28"/>
-      <c r="I123" s="26"/>
-      <c r="J123" s="30"/>
-    </row>
-    <row r="124" spans="1:10">
-      <c r="A124" s="33"/>
-      <c r="B124" s="52"/>
-      <c r="C124" s="51"/>
-      <c r="D124" s="50"/>
-      <c r="E124" s="49"/>
-      <c r="F124" s="49"/>
-      <c r="G124" s="63" t="s">
-        <v>162</v>
-      </c>
-      <c r="H124" s="28"/>
-      <c r="I124" s="26"/>
-      <c r="J124" s="30"/>
-    </row>
-    <row r="125" spans="1:10">
-      <c r="A125" s="33"/>
-      <c r="B125" s="52"/>
-      <c r="C125" s="51"/>
-      <c r="D125" s="50"/>
-      <c r="E125" s="49"/>
-      <c r="F125" s="49"/>
-      <c r="G125" s="63" t="s">
-        <v>163</v>
-      </c>
-      <c r="H125" s="28"/>
-      <c r="I125" s="26"/>
-      <c r="J125" s="30"/>
-    </row>
-    <row r="126" spans="1:10">
-      <c r="A126" s="34"/>
-      <c r="B126" s="36"/>
-      <c r="C126" s="38"/>
-      <c r="D126" s="40"/>
-      <c r="E126" s="27"/>
-      <c r="F126" s="27"/>
-      <c r="G126" s="63" t="s">
-        <v>164</v>
-      </c>
-      <c r="H126" s="28"/>
-      <c r="I126" s="27"/>
-      <c r="J126" s="31"/>
-    </row>
-    <row r="127" spans="1:10" ht="15">
-      <c r="A127" s="18">
-        <v>46189</v>
-      </c>
-      <c r="B127" s="19">
-        <v>0.77916666666666667</v>
-      </c>
-      <c r="C127" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D127" s="21">
-        <v>9744</v>
-      </c>
-      <c r="E127" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="F127" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="G127" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="H127" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I127" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="J127" s="23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="15">
-      <c r="A128" s="18">
-        <v>46184</v>
-      </c>
-      <c r="B128" s="19">
-        <v>0.38055555555555554</v>
-      </c>
-      <c r="C128" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D128" s="21">
-        <v>9744</v>
-      </c>
-      <c r="E128" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="F128" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="G128" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="H128" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I128" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="J128" s="23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A129" s="32">
-        <v>46183</v>
-      </c>
-      <c r="B129" s="35">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="C129" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="D129" s="39">
-        <v>9759</v>
-      </c>
-      <c r="E129" s="25" t="s">
+      <c r="G112" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="F129" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="G129" s="63" t="s">
-        <v>181</v>
-      </c>
-      <c r="H129" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="I129" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="J129" s="29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10">
-      <c r="A130" s="33"/>
-      <c r="B130" s="52"/>
-      <c r="C130" s="51"/>
-      <c r="D130" s="50"/>
-      <c r="E130" s="49"/>
-      <c r="F130" s="49"/>
-      <c r="G130" s="56" t="s">
-        <v>171</v>
-      </c>
-      <c r="H130" s="28"/>
-      <c r="I130" s="26"/>
-      <c r="J130" s="30"/>
-    </row>
-    <row r="131" spans="1:10">
-      <c r="A131" s="33"/>
-      <c r="B131" s="52"/>
-      <c r="C131" s="51"/>
-      <c r="D131" s="50"/>
-      <c r="E131" s="49"/>
-      <c r="F131" s="49"/>
-      <c r="G131" s="56" t="s">
-        <v>172</v>
-      </c>
-      <c r="H131" s="28"/>
-      <c r="I131" s="26"/>
-      <c r="J131" s="30"/>
-    </row>
-    <row r="132" spans="1:10">
-      <c r="A132" s="33"/>
-      <c r="B132" s="52"/>
-      <c r="C132" s="51"/>
-      <c r="D132" s="50"/>
-      <c r="E132" s="49"/>
-      <c r="F132" s="49"/>
-      <c r="G132" s="56" t="s">
-        <v>173</v>
-      </c>
-      <c r="H132" s="28"/>
-      <c r="I132" s="26"/>
-      <c r="J132" s="30"/>
-    </row>
-    <row r="133" spans="1:10">
-      <c r="A133" s="34"/>
-      <c r="B133" s="36"/>
-      <c r="C133" s="38"/>
-      <c r="D133" s="40"/>
-      <c r="E133" s="27"/>
-      <c r="F133" s="27"/>
-      <c r="G133" s="56" t="s">
-        <v>174</v>
-      </c>
-      <c r="H133" s="28"/>
-      <c r="I133" s="27"/>
-      <c r="J133" s="31"/>
-    </row>
-    <row r="134" spans="1:10" ht="42.75">
-      <c r="A134" s="18">
-        <v>46185</v>
-      </c>
-      <c r="B134" s="19">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C134" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="D134" s="21">
-        <v>9762</v>
-      </c>
-      <c r="E134" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="F134" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="G134" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="H134" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I134" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="J134" s="23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" ht="42.75">
-      <c r="A135" s="18">
-        <v>46186</v>
-      </c>
-      <c r="B135" s="19">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C135" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="D135" s="21">
-        <v>9764</v>
-      </c>
-      <c r="E135" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="F135" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="G135" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="H135" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I135" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="J135" s="23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" ht="42.75">
-      <c r="A136" s="18">
-        <v>46186</v>
-      </c>
-      <c r="B136" s="19">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C136" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="D136" s="21">
-        <v>9764</v>
-      </c>
-      <c r="E136" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="F136" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="G136" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="H136" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I136" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="J136" s="23" t="s">
+      <c r="H112" t="s">
+        <v>17</v>
+      </c>
+      <c r="I112" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J112" s="13" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="60">
-    <mergeCell ref="G102:G106"/>
-    <mergeCell ref="G107:G111"/>
-    <mergeCell ref="G112:G116"/>
-    <mergeCell ref="G117:G121"/>
-    <mergeCell ref="G122:G126"/>
-    <mergeCell ref="A122:A126"/>
-    <mergeCell ref="B122:B126"/>
-    <mergeCell ref="C122:C126"/>
-    <mergeCell ref="D122:D126"/>
-    <mergeCell ref="E122:E126"/>
-    <mergeCell ref="F117:F121"/>
-    <mergeCell ref="H117:H121"/>
-    <mergeCell ref="I117:I121"/>
-    <mergeCell ref="J117:J121"/>
-    <mergeCell ref="H122:H126"/>
-    <mergeCell ref="I122:I126"/>
-    <mergeCell ref="J122:J126"/>
-    <mergeCell ref="F122:F126"/>
-    <mergeCell ref="A117:A121"/>
-    <mergeCell ref="B117:B121"/>
-    <mergeCell ref="C117:C121"/>
-    <mergeCell ref="D117:D121"/>
-    <mergeCell ref="E117:E121"/>
-    <mergeCell ref="I107:I111"/>
-    <mergeCell ref="J107:J111"/>
-    <mergeCell ref="A112:A116"/>
-    <mergeCell ref="B112:B116"/>
-    <mergeCell ref="C112:C116"/>
-    <mergeCell ref="D112:D116"/>
-    <mergeCell ref="E112:E116"/>
-    <mergeCell ref="F112:F116"/>
-    <mergeCell ref="H112:H116"/>
-    <mergeCell ref="I112:I116"/>
-    <mergeCell ref="J112:J116"/>
-    <mergeCell ref="H102:H106"/>
-    <mergeCell ref="I102:I106"/>
-    <mergeCell ref="J102:J106"/>
-    <mergeCell ref="A107:A111"/>
-    <mergeCell ref="B107:B111"/>
-    <mergeCell ref="C107:C111"/>
-    <mergeCell ref="D107:D111"/>
-    <mergeCell ref="E107:E111"/>
-    <mergeCell ref="F107:F111"/>
-    <mergeCell ref="H107:H111"/>
-    <mergeCell ref="A102:A106"/>
-    <mergeCell ref="B102:B106"/>
-    <mergeCell ref="C102:C106"/>
-    <mergeCell ref="D102:D106"/>
-    <mergeCell ref="E102:E106"/>
-    <mergeCell ref="F102:F106"/>
-    <mergeCell ref="F129:F133"/>
-    <mergeCell ref="H129:H133"/>
-    <mergeCell ref="I129:I133"/>
-    <mergeCell ref="J129:J133"/>
-    <mergeCell ref="A129:A133"/>
-    <mergeCell ref="B129:B133"/>
-    <mergeCell ref="C129:C133"/>
-    <mergeCell ref="D129:D133"/>
-    <mergeCell ref="E129:E133"/>
-    <mergeCell ref="G129:G133"/>
-  </mergeCells>
-  <conditionalFormatting sqref="H2:H101">
-    <cfRule type="expression" dxfId="4" priority="1">
+  <conditionalFormatting sqref="H2:H112">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>H2="Alta"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>H2="Media"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>H2="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J101">
-    <cfRule type="expression" dxfId="1" priority="4">
+  <conditionalFormatting sqref="J2:J112">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>J2="Ejecutado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>J2="Pendiente"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5439,14 +4731,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="5" t="s">

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AE5DC9-3298-40F7-A32D-BC333CB8A89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{002F63CC-6C9D-4F6F-806D-BFC37844DD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVENTOS" sheetId="1" r:id="rId1"/>
@@ -602,10 +602,10 @@
     <t>Feria Empresarial</t>
   </si>
   <si>
-    <t>INGENIERA ACUICOLO</t>
-  </si>
-  <si>
     <t>8 toldos / 8 mesas / 8 manteles / 16 sillas (2 por mesas)</t>
+  </si>
+  <si>
+    <t>INGENIERA ACUICOLA</t>
   </si>
 </sst>
 </file>
@@ -768,10 +768,6 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -784,14 +780,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -847,6 +844,9 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -866,7 +866,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Área Solicitante"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="N° OT" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="N° OT" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Evento / Actividad"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ubicación"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Requerimientos"/>
@@ -1033,7 +1033,7 @@
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="16" style="22" customWidth="1"/>
+    <col min="4" max="4" width="16" style="20" customWidth="1"/>
     <col min="5" max="6" width="34" customWidth="1"/>
     <col min="7" max="7" width="48" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
@@ -1084,7 +1084,7 @@
       <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -1116,7 +1116,7 @@
       <c r="C3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="17" t="s">
         <v>22</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -1148,7 +1148,7 @@
       <c r="C4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="17" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -1180,7 +1180,7 @@
       <c r="C5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="17" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -1212,7 +1212,7 @@
       <c r="C6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="19"/>
+      <c r="D6" s="17"/>
       <c r="E6" s="2" t="s">
         <v>37</v>
       </c>
@@ -1242,7 +1242,7 @@
       <c r="C7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="19"/>
+      <c r="D7" s="17"/>
       <c r="E7" s="2" t="s">
         <v>42</v>
       </c>
@@ -1270,7 +1270,7 @@
       <c r="C8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="17" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -1302,7 +1302,7 @@
       <c r="C9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="17" t="s">
         <v>28</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -1334,7 +1334,7 @@
       <c r="C10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="17" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -1366,7 +1366,7 @@
       <c r="C11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="17" t="s">
         <v>60</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -1398,7 +1398,7 @@
       <c r="C12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="17" t="s">
         <v>65</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -1430,7 +1430,7 @@
       <c r="C13" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="17" t="s">
         <v>69</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -1462,7 +1462,7 @@
       <c r="C14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="17" t="s">
         <v>74</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -1494,7 +1494,7 @@
       <c r="C15" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="18" t="s">
         <v>78</v>
       </c>
       <c r="E15" s="8" t="s">
@@ -1526,7 +1526,7 @@
       <c r="C16" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="18" t="s">
         <v>78</v>
       </c>
       <c r="E16" s="8" t="s">
@@ -1558,7 +1558,7 @@
       <c r="C17" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E17" s="12" t="s">
@@ -1590,7 +1590,7 @@
       <c r="C18" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E18" s="12" t="s">
@@ -1622,7 +1622,7 @@
       <c r="C19" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="12" t="s">
@@ -1654,7 +1654,7 @@
       <c r="C20" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="12" t="s">
@@ -1686,7 +1686,7 @@
       <c r="C21" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="D21" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E21" s="12" t="s">
@@ -1718,7 +1718,7 @@
       <c r="C22" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="D22" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E22" s="12" t="s">
@@ -1750,7 +1750,7 @@
       <c r="C23" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D23" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="12" t="s">
@@ -1782,7 +1782,7 @@
       <c r="C24" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="21" t="s">
+      <c r="D24" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E24" s="12" t="s">
@@ -1814,7 +1814,7 @@
       <c r="C25" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="21" t="s">
+      <c r="D25" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="12" t="s">
@@ -1846,7 +1846,7 @@
       <c r="C26" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="21" t="s">
+      <c r="D26" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E26" s="12" t="s">
@@ -1878,7 +1878,7 @@
       <c r="C27" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="D27" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E27" s="12" t="s">
@@ -1910,7 +1910,7 @@
       <c r="C28" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="D28" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E28" s="12" t="s">
@@ -1942,7 +1942,7 @@
       <c r="C29" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D29" s="21" t="s">
+      <c r="D29" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E29" s="12" t="s">
@@ -1974,7 +1974,7 @@
       <c r="C30" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="21" t="s">
+      <c r="D30" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E30" s="12" t="s">
@@ -2006,7 +2006,7 @@
       <c r="C31" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="D31" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="12" t="s">
@@ -2038,7 +2038,7 @@
       <c r="C32" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="12" t="s">
@@ -2070,7 +2070,7 @@
       <c r="C33" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="D33" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="12" t="s">
@@ -2102,7 +2102,7 @@
       <c r="C34" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="21" t="s">
+      <c r="D34" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E34" s="12" t="s">
@@ -2134,7 +2134,7 @@
       <c r="C35" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D35" s="21" t="s">
+      <c r="D35" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E35" s="12" t="s">
@@ -2166,7 +2166,7 @@
       <c r="C36" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D36" s="21" t="s">
+      <c r="D36" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E36" s="12" t="s">
@@ -2198,7 +2198,7 @@
       <c r="C37" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="D37" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E37" s="12" t="s">
@@ -2230,7 +2230,7 @@
       <c r="C38" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D38" s="21" t="s">
+      <c r="D38" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E38" s="12" t="s">
@@ -2262,7 +2262,7 @@
       <c r="C39" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D39" s="21" t="s">
+      <c r="D39" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E39" s="12" t="s">
@@ -2294,7 +2294,7 @@
       <c r="C40" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="21" t="s">
+      <c r="D40" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E40" s="12" t="s">
@@ -2326,7 +2326,7 @@
       <c r="C41" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D41" s="21" t="s">
+      <c r="D41" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="12" t="s">
@@ -2358,7 +2358,7 @@
       <c r="C42" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="21" t="s">
+      <c r="D42" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E42" s="12" t="s">
@@ -2390,7 +2390,7 @@
       <c r="C43" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D43" s="21" t="s">
+      <c r="D43" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="12" t="s">
@@ -2422,7 +2422,7 @@
       <c r="C44" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D44" s="21" t="s">
+      <c r="D44" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E44" s="12" t="s">
@@ -2454,7 +2454,7 @@
       <c r="C45" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D45" s="21" t="s">
+      <c r="D45" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E45" s="12" t="s">
@@ -2486,7 +2486,7 @@
       <c r="C46" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D46" s="21" t="s">
+      <c r="D46" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E46" s="12" t="s">
@@ -2518,7 +2518,7 @@
       <c r="C47" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D47" s="21" t="s">
+      <c r="D47" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E47" s="12" t="s">
@@ -2550,7 +2550,7 @@
       <c r="C48" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="21" t="s">
+      <c r="D48" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E48" s="12" t="s">
@@ -2582,7 +2582,7 @@
       <c r="C49" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="21" t="s">
+      <c r="D49" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="12" t="s">
@@ -2614,7 +2614,7 @@
       <c r="C50" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D50" s="21" t="s">
+      <c r="D50" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="12" t="s">
@@ -2646,7 +2646,7 @@
       <c r="C51" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D51" s="21" t="s">
+      <c r="D51" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E51" s="12" t="s">
@@ -2678,7 +2678,7 @@
       <c r="C52" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D52" s="21" t="s">
+      <c r="D52" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E52" s="12" t="s">
@@ -2710,7 +2710,7 @@
       <c r="C53" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D53" s="21" t="s">
+      <c r="D53" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E53" s="12" t="s">
@@ -2742,7 +2742,7 @@
       <c r="C54" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D54" s="21" t="s">
+      <c r="D54" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E54" s="12" t="s">
@@ -2774,7 +2774,7 @@
       <c r="C55" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D55" s="21" t="s">
+      <c r="D55" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E55" s="12" t="s">
@@ -2806,7 +2806,7 @@
       <c r="C56" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D56" s="21" t="s">
+      <c r="D56" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E56" s="12" t="s">
@@ -2838,7 +2838,7 @@
       <c r="C57" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D57" s="21" t="s">
+      <c r="D57" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E57" s="12" t="s">
@@ -2870,7 +2870,7 @@
       <c r="C58" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D58" s="21" t="s">
+      <c r="D58" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E58" s="12" t="s">
@@ -2902,7 +2902,7 @@
       <c r="C59" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D59" s="21" t="s">
+      <c r="D59" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E59" s="12" t="s">
@@ -2934,7 +2934,7 @@
       <c r="C60" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D60" s="21" t="s">
+      <c r="D60" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E60" s="12" t="s">
@@ -2966,7 +2966,7 @@
       <c r="C61" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D61" s="21" t="s">
+      <c r="D61" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E61" s="12" t="s">
@@ -2998,7 +2998,7 @@
       <c r="C62" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D62" s="21" t="s">
+      <c r="D62" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E62" s="12" t="s">
@@ -3030,7 +3030,7 @@
       <c r="C63" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D63" s="21" t="s">
+      <c r="D63" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E63" s="12" t="s">
@@ -3062,7 +3062,7 @@
       <c r="C64" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D64" s="21" t="s">
+      <c r="D64" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E64" s="12" t="s">
@@ -3094,7 +3094,7 @@
       <c r="C65" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D65" s="21" t="s">
+      <c r="D65" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E65" s="12" t="s">
@@ -3126,7 +3126,7 @@
       <c r="C66" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D66" s="21" t="s">
+      <c r="D66" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E66" s="12" t="s">
@@ -3158,7 +3158,7 @@
       <c r="C67" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D67" s="21" t="s">
+      <c r="D67" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E67" s="12" t="s">
@@ -3190,7 +3190,7 @@
       <c r="C68" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D68" s="21" t="s">
+      <c r="D68" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E68" s="12" t="s">
@@ -3222,7 +3222,7 @@
       <c r="C69" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D69" s="21" t="s">
+      <c r="D69" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E69" s="12" t="s">
@@ -3254,7 +3254,7 @@
       <c r="C70" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D70" s="21" t="s">
+      <c r="D70" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E70" s="12" t="s">
@@ -3286,7 +3286,7 @@
       <c r="C71" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D71" s="21" t="s">
+      <c r="D71" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E71" s="12" t="s">
@@ -3318,7 +3318,7 @@
       <c r="C72" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D72" s="21" t="s">
+      <c r="D72" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E72" s="12" t="s">
@@ -3350,7 +3350,7 @@
       <c r="C73" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D73" s="21" t="s">
+      <c r="D73" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E73" s="12" t="s">
@@ -3382,7 +3382,7 @@
       <c r="C74" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D74" s="21" t="s">
+      <c r="D74" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E74" s="12" t="s">
@@ -3414,7 +3414,7 @@
       <c r="C75" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D75" s="21" t="s">
+      <c r="D75" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E75" s="12" t="s">
@@ -3446,7 +3446,7 @@
       <c r="C76" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D76" s="21" t="s">
+      <c r="D76" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E76" s="12" t="s">
@@ -3478,7 +3478,7 @@
       <c r="C77" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D77" s="21" t="s">
+      <c r="D77" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E77" s="12" t="s">
@@ -3510,7 +3510,7 @@
       <c r="C78" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D78" s="21" t="s">
+      <c r="D78" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E78" s="12" t="s">
@@ -3542,7 +3542,7 @@
       <c r="C79" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D79" s="21" t="s">
+      <c r="D79" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E79" s="12" t="s">
@@ -3574,7 +3574,7 @@
       <c r="C80" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D80" s="21" t="s">
+      <c r="D80" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E80" s="12" t="s">
@@ -3606,7 +3606,7 @@
       <c r="C81" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D81" s="21" t="s">
+      <c r="D81" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E81" s="12" t="s">
@@ -3638,7 +3638,7 @@
       <c r="C82" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D82" s="21" t="s">
+      <c r="D82" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E82" s="12" t="s">
@@ -3670,7 +3670,7 @@
       <c r="C83" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D83" s="21" t="s">
+      <c r="D83" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E83" s="12" t="s">
@@ -3702,7 +3702,7 @@
       <c r="C84" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D84" s="21" t="s">
+      <c r="D84" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E84" s="12" t="s">
@@ -3734,7 +3734,7 @@
       <c r="C85" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D85" s="21" t="s">
+      <c r="D85" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E85" s="12" t="s">
@@ -3766,7 +3766,7 @@
       <c r="C86" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D86" s="21" t="s">
+      <c r="D86" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E86" s="12" t="s">
@@ -3798,7 +3798,7 @@
       <c r="C87" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D87" s="21" t="s">
+      <c r="D87" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E87" s="12" t="s">
@@ -3830,7 +3830,7 @@
       <c r="C88" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D88" s="21" t="s">
+      <c r="D88" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E88" s="12" t="s">
@@ -3862,7 +3862,7 @@
       <c r="C89" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D89" s="21" t="s">
+      <c r="D89" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E89" s="12" t="s">
@@ -3894,7 +3894,7 @@
       <c r="C90" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D90" s="21" t="s">
+      <c r="D90" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E90" s="12" t="s">
@@ -3926,7 +3926,7 @@
       <c r="C91" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D91" s="21" t="s">
+      <c r="D91" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E91" s="12" t="s">
@@ -3958,7 +3958,7 @@
       <c r="C92" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D92" s="21" t="s">
+      <c r="D92" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E92" s="12" t="s">
@@ -3990,7 +3990,7 @@
       <c r="C93" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D93" s="21" t="s">
+      <c r="D93" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E93" s="12" t="s">
@@ -4022,7 +4022,7 @@
       <c r="C94" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D94" s="21" t="s">
+      <c r="D94" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E94" s="12" t="s">
@@ -4054,7 +4054,7 @@
       <c r="C95" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D95" s="21" t="s">
+      <c r="D95" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E95" s="12" t="s">
@@ -4086,7 +4086,7 @@
       <c r="C96" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D96" s="21" t="s">
+      <c r="D96" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E96" s="12" t="s">
@@ -4118,7 +4118,7 @@
       <c r="C97" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D97" s="21" t="s">
+      <c r="D97" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E97" s="12" t="s">
@@ -4150,7 +4150,7 @@
       <c r="C98" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D98" s="21" t="s">
+      <c r="D98" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E98" s="12" t="s">
@@ -4182,7 +4182,7 @@
       <c r="C99" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D99" s="21" t="s">
+      <c r="D99" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E99" s="12" t="s">
@@ -4214,7 +4214,7 @@
       <c r="C100" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D100" s="21" t="s">
+      <c r="D100" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E100" s="12" t="s">
@@ -4246,7 +4246,7 @@
       <c r="C101" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D101" s="21" t="s">
+      <c r="D101" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E101" s="12" t="s">
@@ -4278,7 +4278,7 @@
       <c r="C102" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D102" s="21">
+      <c r="D102" s="19">
         <v>81688</v>
       </c>
       <c r="E102" s="12" t="s">
@@ -4310,7 +4310,7 @@
       <c r="C103" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D103" s="21">
+      <c r="D103" s="19">
         <v>81685</v>
       </c>
       <c r="E103" s="12" t="s">
@@ -4320,7 +4320,7 @@
         <v>150</v>
       </c>
       <c r="G103" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H103" t="s">
         <v>17</v>
@@ -4342,7 +4342,7 @@
       <c r="C104" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="D104" s="21" t="s">
+      <c r="D104" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E104" s="12" t="s">
@@ -4374,7 +4374,7 @@
       <c r="C105" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="D105" s="21" t="s">
+      <c r="D105" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E105" s="12" t="s">
@@ -4406,11 +4406,11 @@
       <c r="C106" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D106" s="21" t="s">
+      <c r="D106" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E106" s="12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F106" s="12" t="s">
         <v>154</v>
@@ -4438,7 +4438,7 @@
       <c r="C107" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D107" s="21">
+      <c r="D107" s="19">
         <v>9744</v>
       </c>
       <c r="E107" s="12" t="s">
@@ -4470,7 +4470,7 @@
       <c r="C108" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D108" s="21">
+      <c r="D108" s="19">
         <v>9744</v>
       </c>
       <c r="E108" s="12" t="s">
@@ -4494,7 +4494,7 @@
     </row>
     <row r="109" spans="1:10" ht="14.25" customHeight="1">
       <c r="A109" s="16">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B109" s="15">
         <v>0.64583333333333337</v>
@@ -4502,7 +4502,7 @@
       <c r="C109" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="D109" s="21">
+      <c r="D109" s="19">
         <v>9759</v>
       </c>
       <c r="E109" s="12" t="s">
@@ -4534,7 +4534,7 @@
       <c r="C110" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="D110" s="21">
+      <c r="D110" s="19">
         <v>9762</v>
       </c>
       <c r="E110" s="12" t="s">
@@ -4566,7 +4566,7 @@
       <c r="C111" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="D111" s="21">
+      <c r="D111" s="19">
         <v>9764</v>
       </c>
       <c r="E111" s="12" t="s">
@@ -4598,7 +4598,7 @@
       <c r="C112" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="D112" s="21">
+      <c r="D112" s="19">
         <v>9764</v>
       </c>
       <c r="E112" s="12" t="s">
@@ -4622,21 +4622,21 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H112">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>H2="Alta"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>H2="Media"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>H2="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J112">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>J2="Ejecutado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>J2="Pendiente"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4731,14 +4731,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="5" t="s">

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{002F63CC-6C9D-4F6F-806D-BFC37844DD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90EAB299-B8D2-4C55-8E76-2ECA0CF2801C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVENTOS" sheetId="1" r:id="rId1"/>
@@ -4497,7 +4497,7 @@
         <v>46184</v>
       </c>
       <c r="B109" s="15">
-        <v>0.64583333333333337</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="C109" s="12" t="s">
         <v>158</v>

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90EAB299-B8D2-4C55-8E76-2ECA0CF2801C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534D1F1D-1C79-45CB-BD3C-DD78E64B0A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVENTOS" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="189">
   <si>
     <t>Fecha</t>
   </si>
@@ -607,6 +607,48 @@
   <si>
     <t>INGENIERA ACUICOLA</t>
   </si>
+  <si>
+    <t>AREA VICERREPTORADO</t>
+  </si>
+  <si>
+    <t>Club de Emprendimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FACULTAD  DE INGENERIA </t>
+  </si>
+  <si>
+    <t>Semana de Ingeniería- Almuerzo Internacional</t>
+  </si>
+  <si>
+    <t>Terraza comedor / pabellon K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AREA CLINICA DE SIMULACION </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charla </t>
+  </si>
+  <si>
+    <t>Auditorio  pabellon L</t>
+  </si>
+  <si>
+    <t>Semana de Ingeniería Feria de Proyectos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anfiteatro del pabellón I </t>
+  </si>
+  <si>
+    <t>1 mesa para coffe / 1 mesa de registro / 1 2 mesas para ponentes / 5 mesas para estuadiantes / 40 sillas / 30 sillas estudiantes / 4 sillas ponentes / 6 sillas para registro y staff</t>
+  </si>
+  <si>
+    <t>Mesa para 7 personas / mantel institucional</t>
+  </si>
+  <si>
+    <t>5 toldos / 5 mesas / 15 sillas / 5 extensiones / 8 caballetes 6</t>
+  </si>
+  <si>
+    <t>2 mesas / 2 manteles / 2 sillas para coffe / 1 mesa de vidrio para colocar libros</t>
+  </si>
 </sst>
 </file>
 
@@ -615,7 +657,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -642,8 +684,19 @@
       <color theme="1"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF991B1B"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -672,8 +725,26 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E6F5"/>
+        <bgColor rgb="FFC0E6F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEE2E2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61CBF3"/>
+        <bgColor rgb="FFC0E6F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -718,11 +789,159 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF44B3E1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF44B3E1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF44B3E1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF44B3E1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF44B3E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF44B3E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF44B3E1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF44B3E1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF44B3E1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF44B3E1"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -784,6 +1003,111 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1027,7 +1351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J131"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4619,6 +4943,314 @@
       <c r="J112" s="13" t="s">
         <v>86</v>
       </c>
+    </row>
+    <row r="113" spans="1:10" ht="51" customHeight="1">
+      <c r="A113" s="41">
+        <v>46185</v>
+      </c>
+      <c r="B113" s="44">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C113" s="47" t="s">
+        <v>175</v>
+      </c>
+      <c r="D113" s="50">
+        <v>81767</v>
+      </c>
+      <c r="E113" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="F113" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="G113" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="H113" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I113" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="J113" s="54" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="28.5">
+      <c r="A114" s="33">
+        <v>46185</v>
+      </c>
+      <c r="B114" s="34">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C114" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="D114" s="36">
+        <v>81751</v>
+      </c>
+      <c r="E114" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="F114" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="G114" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="H114" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I114" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J114" s="39" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="28.5">
+      <c r="A115" s="23">
+        <v>46190</v>
+      </c>
+      <c r="B115" s="24">
+        <v>0.625</v>
+      </c>
+      <c r="C115" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="D115" s="26">
+        <v>81750</v>
+      </c>
+      <c r="E115" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="F115" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="G115" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="H115" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I115" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J115" s="32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A116" s="23">
+        <v>46185</v>
+      </c>
+      <c r="B116" s="24">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C116" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="D116" s="26">
+        <v>81729</v>
+      </c>
+      <c r="E116" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="F116" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="G116" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="H116" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I116" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J116" s="32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A117" s="42"/>
+      <c r="B117" s="45"/>
+      <c r="C117" s="48"/>
+      <c r="D117" s="52"/>
+      <c r="E117" s="52"/>
+      <c r="F117" s="52"/>
+      <c r="G117" s="57"/>
+      <c r="H117" s="31"/>
+      <c r="I117" s="52"/>
+      <c r="J117" s="55"/>
+    </row>
+    <row r="118" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A118" s="42"/>
+      <c r="B118" s="45"/>
+      <c r="C118" s="48"/>
+      <c r="D118" s="52"/>
+      <c r="E118" s="52"/>
+      <c r="F118" s="52"/>
+      <c r="G118" s="57"/>
+      <c r="H118" s="31"/>
+      <c r="I118" s="52"/>
+      <c r="J118" s="55"/>
+    </row>
+    <row r="119" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A119" s="42"/>
+      <c r="B119" s="45"/>
+      <c r="C119" s="48"/>
+      <c r="D119" s="52"/>
+      <c r="E119" s="52"/>
+      <c r="F119" s="52"/>
+      <c r="G119" s="57"/>
+      <c r="H119" s="31"/>
+      <c r="I119" s="52"/>
+      <c r="J119" s="55"/>
+    </row>
+    <row r="120" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A120" s="42"/>
+      <c r="B120" s="45"/>
+      <c r="C120" s="48"/>
+      <c r="D120" s="52"/>
+      <c r="E120" s="52"/>
+      <c r="F120" s="52"/>
+      <c r="G120" s="57"/>
+      <c r="H120" s="31"/>
+      <c r="I120" s="52"/>
+      <c r="J120" s="55"/>
+    </row>
+    <row r="121" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A121" s="42"/>
+      <c r="B121" s="45"/>
+      <c r="C121" s="48"/>
+      <c r="D121" s="52"/>
+      <c r="E121" s="52"/>
+      <c r="F121" s="52"/>
+      <c r="G121" s="57"/>
+      <c r="H121" s="31"/>
+      <c r="I121" s="52"/>
+      <c r="J121" s="55"/>
+    </row>
+    <row r="122" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A122" s="42"/>
+      <c r="B122" s="45"/>
+      <c r="C122" s="48"/>
+      <c r="D122" s="52"/>
+      <c r="E122" s="52"/>
+      <c r="F122" s="52"/>
+      <c r="G122" s="57"/>
+      <c r="H122" s="31"/>
+      <c r="I122" s="52"/>
+      <c r="J122" s="55"/>
+    </row>
+    <row r="123" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A123" s="42"/>
+      <c r="B123" s="45"/>
+      <c r="C123" s="48"/>
+      <c r="D123" s="52"/>
+      <c r="E123" s="52"/>
+      <c r="F123" s="52"/>
+      <c r="G123" s="57"/>
+      <c r="H123" s="31"/>
+      <c r="I123" s="52"/>
+      <c r="J123" s="55"/>
+    </row>
+    <row r="124" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A124" s="42"/>
+      <c r="B124" s="45"/>
+      <c r="C124" s="48"/>
+      <c r="D124" s="52"/>
+      <c r="E124" s="52"/>
+      <c r="F124" s="52"/>
+      <c r="G124" s="57"/>
+      <c r="H124" s="31"/>
+      <c r="I124" s="52"/>
+      <c r="J124" s="55"/>
+    </row>
+    <row r="125" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A125" s="42"/>
+      <c r="B125" s="45"/>
+      <c r="C125" s="48"/>
+      <c r="D125" s="52"/>
+      <c r="E125" s="52"/>
+      <c r="F125" s="52"/>
+      <c r="G125" s="28"/>
+      <c r="H125" s="31"/>
+      <c r="I125" s="52"/>
+      <c r="J125" s="55"/>
+    </row>
+    <row r="126" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A126" s="42"/>
+      <c r="B126" s="45"/>
+      <c r="C126" s="48"/>
+      <c r="D126" s="52"/>
+      <c r="E126" s="52"/>
+      <c r="F126" s="52"/>
+      <c r="G126" s="28"/>
+      <c r="H126" s="31"/>
+      <c r="I126" s="52"/>
+      <c r="J126" s="55"/>
+    </row>
+    <row r="127" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A127" s="42"/>
+      <c r="B127" s="45"/>
+      <c r="C127" s="48"/>
+      <c r="D127" s="52"/>
+      <c r="E127" s="52"/>
+      <c r="F127" s="52"/>
+      <c r="G127" s="28"/>
+      <c r="H127" s="31"/>
+      <c r="I127" s="52"/>
+      <c r="J127" s="55"/>
+    </row>
+    <row r="128" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A128" s="42"/>
+      <c r="B128" s="45"/>
+      <c r="C128" s="48"/>
+      <c r="D128" s="52"/>
+      <c r="E128" s="52"/>
+      <c r="F128" s="52"/>
+      <c r="G128" s="28"/>
+      <c r="H128" s="31"/>
+      <c r="I128" s="52"/>
+      <c r="J128" s="55"/>
+    </row>
+    <row r="129" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A129" s="42"/>
+      <c r="B129" s="45"/>
+      <c r="C129" s="48"/>
+      <c r="D129" s="52"/>
+      <c r="E129" s="52"/>
+      <c r="F129" s="52"/>
+      <c r="G129" s="28"/>
+      <c r="H129" s="31"/>
+      <c r="I129" s="52"/>
+      <c r="J129" s="55"/>
+    </row>
+    <row r="130" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A130" s="42"/>
+      <c r="B130" s="45"/>
+      <c r="C130" s="48"/>
+      <c r="D130" s="52"/>
+      <c r="E130" s="52"/>
+      <c r="F130" s="52"/>
+      <c r="G130" s="28"/>
+      <c r="H130" s="31"/>
+      <c r="I130" s="52"/>
+      <c r="J130" s="55"/>
+    </row>
+    <row r="131" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A131" s="43"/>
+      <c r="B131" s="46"/>
+      <c r="C131" s="49"/>
+      <c r="D131" s="53"/>
+      <c r="E131" s="53"/>
+      <c r="F131" s="53"/>
+      <c r="G131" s="30"/>
+      <c r="H131" s="31"/>
+      <c r="I131" s="53"/>
+      <c r="J131" s="56"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H112">

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534D1F1D-1C79-45CB-BD3C-DD78E64B0A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04604E57-7C77-4DBE-B3CA-12EF20AD3786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -608,9 +608,6 @@
     <t>INGENIERA ACUICOLA</t>
   </si>
   <si>
-    <t>AREA VICERREPTORADO</t>
-  </si>
-  <si>
     <t>Club de Emprendimiento</t>
   </si>
   <si>
@@ -648,6 +645,9 @@
   </si>
   <si>
     <t>2 mesas / 2 manteles / 2 sillas para coffe / 1 mesa de vidrio para colocar libros</t>
+  </si>
+  <si>
+    <t>AREA VICERRECTORADO</t>
   </si>
 </sst>
 </file>
@@ -999,10 +999,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1069,7 +1065,7 @@
     <xf numFmtId="20" fontId="6" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="6" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1078,7 +1074,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1090,7 +1086,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1105,9 +1101,13 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4945,312 +4945,312 @@
       </c>
     </row>
     <row r="113" spans="1:10" ht="51" customHeight="1">
-      <c r="A113" s="41">
+      <c r="A113" s="39">
         <v>46185</v>
       </c>
-      <c r="B113" s="44">
+      <c r="B113" s="42">
         <v>0.77083333333333337</v>
       </c>
-      <c r="C113" s="47" t="s">
+      <c r="C113" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="D113" s="48">
+        <v>81767</v>
+      </c>
+      <c r="E113" s="49" t="s">
         <v>175</v>
       </c>
-      <c r="D113" s="50">
-        <v>81767</v>
-      </c>
-      <c r="E113" s="51" t="s">
+      <c r="F113" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="G113" s="45" t="s">
+        <v>184</v>
+      </c>
+      <c r="H113" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="I113" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J113" s="52" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="28.5">
+      <c r="A114" s="31">
+        <v>46185</v>
+      </c>
+      <c r="B114" s="32">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C114" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="F113" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="G113" s="47" t="s">
+      <c r="D114" s="34">
+        <v>81751</v>
+      </c>
+      <c r="E114" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="F114" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="G114" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="H113" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="I113" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="J113" s="54" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" ht="28.5">
-      <c r="A114" s="33">
+      <c r="H114" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="I114" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J114" s="37" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="28.5">
+      <c r="A115" s="21">
+        <v>46190</v>
+      </c>
+      <c r="B115" s="22">
+        <v>0.625</v>
+      </c>
+      <c r="C115" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="D115" s="24">
+        <v>81750</v>
+      </c>
+      <c r="E115" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="F115" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="G115" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="H115" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="I115" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J115" s="30" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A116" s="21">
         <v>46185</v>
       </c>
-      <c r="B114" s="34">
+      <c r="B116" s="22">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C114" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="D114" s="36">
-        <v>81751</v>
-      </c>
-      <c r="E114" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="F114" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="G114" s="38" t="s">
+      <c r="C116" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="D116" s="24">
+        <v>81729</v>
+      </c>
+      <c r="E116" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="F116" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="G116" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="H114" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="I114" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J114" s="39" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="28.5">
-      <c r="A115" s="23">
-        <v>46190</v>
-      </c>
-      <c r="B115" s="24">
-        <v>0.625</v>
-      </c>
-      <c r="C115" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="D115" s="26">
-        <v>81750</v>
-      </c>
-      <c r="E115" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="F115" s="27" t="s">
-        <v>182</v>
-      </c>
-      <c r="G115" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="H115" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="I115" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="J115" s="32" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A116" s="23">
-        <v>46185</v>
-      </c>
-      <c r="B116" s="24">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="C116" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="D116" s="26">
-        <v>81729</v>
-      </c>
-      <c r="E116" s="27" t="s">
-        <v>183</v>
-      </c>
-      <c r="F116" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="G116" s="40" t="s">
-        <v>187</v>
-      </c>
-      <c r="H116" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="I116" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="J116" s="32" t="s">
+      <c r="H116" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="I116" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J116" s="30" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A117" s="42"/>
-      <c r="B117" s="45"/>
-      <c r="C117" s="48"/>
-      <c r="D117" s="52"/>
-      <c r="E117" s="52"/>
-      <c r="F117" s="52"/>
-      <c r="G117" s="57"/>
-      <c r="H117" s="31"/>
-      <c r="I117" s="52"/>
-      <c r="J117" s="55"/>
+      <c r="A117" s="40"/>
+      <c r="B117" s="43"/>
+      <c r="C117" s="46"/>
+      <c r="D117" s="50"/>
+      <c r="E117" s="50"/>
+      <c r="F117" s="50"/>
+      <c r="G117" s="55"/>
+      <c r="H117" s="29"/>
+      <c r="I117" s="50"/>
+      <c r="J117" s="53"/>
     </row>
     <row r="118" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A118" s="42"/>
-      <c r="B118" s="45"/>
-      <c r="C118" s="48"/>
-      <c r="D118" s="52"/>
-      <c r="E118" s="52"/>
-      <c r="F118" s="52"/>
-      <c r="G118" s="57"/>
-      <c r="H118" s="31"/>
-      <c r="I118" s="52"/>
-      <c r="J118" s="55"/>
+      <c r="A118" s="40"/>
+      <c r="B118" s="43"/>
+      <c r="C118" s="46"/>
+      <c r="D118" s="50"/>
+      <c r="E118" s="50"/>
+      <c r="F118" s="50"/>
+      <c r="G118" s="55"/>
+      <c r="H118" s="29"/>
+      <c r="I118" s="50"/>
+      <c r="J118" s="53"/>
     </row>
     <row r="119" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A119" s="42"/>
-      <c r="B119" s="45"/>
-      <c r="C119" s="48"/>
-      <c r="D119" s="52"/>
-      <c r="E119" s="52"/>
-      <c r="F119" s="52"/>
-      <c r="G119" s="57"/>
-      <c r="H119" s="31"/>
-      <c r="I119" s="52"/>
-      <c r="J119" s="55"/>
+      <c r="A119" s="40"/>
+      <c r="B119" s="43"/>
+      <c r="C119" s="46"/>
+      <c r="D119" s="50"/>
+      <c r="E119" s="50"/>
+      <c r="F119" s="50"/>
+      <c r="G119" s="55"/>
+      <c r="H119" s="29"/>
+      <c r="I119" s="50"/>
+      <c r="J119" s="53"/>
     </row>
     <row r="120" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A120" s="42"/>
-      <c r="B120" s="45"/>
-      <c r="C120" s="48"/>
-      <c r="D120" s="52"/>
-      <c r="E120" s="52"/>
-      <c r="F120" s="52"/>
-      <c r="G120" s="57"/>
-      <c r="H120" s="31"/>
-      <c r="I120" s="52"/>
-      <c r="J120" s="55"/>
+      <c r="A120" s="40"/>
+      <c r="B120" s="43"/>
+      <c r="C120" s="46"/>
+      <c r="D120" s="50"/>
+      <c r="E120" s="50"/>
+      <c r="F120" s="50"/>
+      <c r="G120" s="55"/>
+      <c r="H120" s="29"/>
+      <c r="I120" s="50"/>
+      <c r="J120" s="53"/>
     </row>
     <row r="121" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A121" s="42"/>
-      <c r="B121" s="45"/>
-      <c r="C121" s="48"/>
-      <c r="D121" s="52"/>
-      <c r="E121" s="52"/>
-      <c r="F121" s="52"/>
-      <c r="G121" s="57"/>
-      <c r="H121" s="31"/>
-      <c r="I121" s="52"/>
-      <c r="J121" s="55"/>
+      <c r="A121" s="40"/>
+      <c r="B121" s="43"/>
+      <c r="C121" s="46"/>
+      <c r="D121" s="50"/>
+      <c r="E121" s="50"/>
+      <c r="F121" s="50"/>
+      <c r="G121" s="55"/>
+      <c r="H121" s="29"/>
+      <c r="I121" s="50"/>
+      <c r="J121" s="53"/>
     </row>
     <row r="122" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A122" s="42"/>
-      <c r="B122" s="45"/>
-      <c r="C122" s="48"/>
-      <c r="D122" s="52"/>
-      <c r="E122" s="52"/>
-      <c r="F122" s="52"/>
-      <c r="G122" s="57"/>
-      <c r="H122" s="31"/>
-      <c r="I122" s="52"/>
-      <c r="J122" s="55"/>
+      <c r="A122" s="40"/>
+      <c r="B122" s="43"/>
+      <c r="C122" s="46"/>
+      <c r="D122" s="50"/>
+      <c r="E122" s="50"/>
+      <c r="F122" s="50"/>
+      <c r="G122" s="55"/>
+      <c r="H122" s="29"/>
+      <c r="I122" s="50"/>
+      <c r="J122" s="53"/>
     </row>
     <row r="123" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A123" s="42"/>
-      <c r="B123" s="45"/>
-      <c r="C123" s="48"/>
-      <c r="D123" s="52"/>
-      <c r="E123" s="52"/>
-      <c r="F123" s="52"/>
-      <c r="G123" s="57"/>
-      <c r="H123" s="31"/>
-      <c r="I123" s="52"/>
-      <c r="J123" s="55"/>
+      <c r="A123" s="40"/>
+      <c r="B123" s="43"/>
+      <c r="C123" s="46"/>
+      <c r="D123" s="50"/>
+      <c r="E123" s="50"/>
+      <c r="F123" s="50"/>
+      <c r="G123" s="55"/>
+      <c r="H123" s="29"/>
+      <c r="I123" s="50"/>
+      <c r="J123" s="53"/>
     </row>
     <row r="124" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A124" s="42"/>
-      <c r="B124" s="45"/>
-      <c r="C124" s="48"/>
-      <c r="D124" s="52"/>
-      <c r="E124" s="52"/>
-      <c r="F124" s="52"/>
-      <c r="G124" s="57"/>
-      <c r="H124" s="31"/>
-      <c r="I124" s="52"/>
-      <c r="J124" s="55"/>
+      <c r="A124" s="40"/>
+      <c r="B124" s="43"/>
+      <c r="C124" s="46"/>
+      <c r="D124" s="50"/>
+      <c r="E124" s="50"/>
+      <c r="F124" s="50"/>
+      <c r="G124" s="55"/>
+      <c r="H124" s="29"/>
+      <c r="I124" s="50"/>
+      <c r="J124" s="53"/>
     </row>
     <row r="125" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A125" s="42"/>
-      <c r="B125" s="45"/>
-      <c r="C125" s="48"/>
-      <c r="D125" s="52"/>
-      <c r="E125" s="52"/>
-      <c r="F125" s="52"/>
-      <c r="G125" s="28"/>
-      <c r="H125" s="31"/>
-      <c r="I125" s="52"/>
-      <c r="J125" s="55"/>
+      <c r="A125" s="40"/>
+      <c r="B125" s="43"/>
+      <c r="C125" s="46"/>
+      <c r="D125" s="50"/>
+      <c r="E125" s="50"/>
+      <c r="F125" s="50"/>
+      <c r="G125" s="26"/>
+      <c r="H125" s="29"/>
+      <c r="I125" s="50"/>
+      <c r="J125" s="53"/>
     </row>
     <row r="126" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A126" s="42"/>
-      <c r="B126" s="45"/>
-      <c r="C126" s="48"/>
-      <c r="D126" s="52"/>
-      <c r="E126" s="52"/>
-      <c r="F126" s="52"/>
-      <c r="G126" s="28"/>
-      <c r="H126" s="31"/>
-      <c r="I126" s="52"/>
-      <c r="J126" s="55"/>
+      <c r="A126" s="40"/>
+      <c r="B126" s="43"/>
+      <c r="C126" s="46"/>
+      <c r="D126" s="50"/>
+      <c r="E126" s="50"/>
+      <c r="F126" s="50"/>
+      <c r="G126" s="26"/>
+      <c r="H126" s="29"/>
+      <c r="I126" s="50"/>
+      <c r="J126" s="53"/>
     </row>
     <row r="127" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A127" s="42"/>
-      <c r="B127" s="45"/>
-      <c r="C127" s="48"/>
-      <c r="D127" s="52"/>
-      <c r="E127" s="52"/>
-      <c r="F127" s="52"/>
-      <c r="G127" s="28"/>
-      <c r="H127" s="31"/>
-      <c r="I127" s="52"/>
-      <c r="J127" s="55"/>
+      <c r="A127" s="40"/>
+      <c r="B127" s="43"/>
+      <c r="C127" s="46"/>
+      <c r="D127" s="50"/>
+      <c r="E127" s="50"/>
+      <c r="F127" s="50"/>
+      <c r="G127" s="26"/>
+      <c r="H127" s="29"/>
+      <c r="I127" s="50"/>
+      <c r="J127" s="53"/>
     </row>
     <row r="128" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A128" s="42"/>
-      <c r="B128" s="45"/>
-      <c r="C128" s="48"/>
-      <c r="D128" s="52"/>
-      <c r="E128" s="52"/>
-      <c r="F128" s="52"/>
-      <c r="G128" s="28"/>
-      <c r="H128" s="31"/>
-      <c r="I128" s="52"/>
-      <c r="J128" s="55"/>
+      <c r="A128" s="40"/>
+      <c r="B128" s="43"/>
+      <c r="C128" s="46"/>
+      <c r="D128" s="50"/>
+      <c r="E128" s="50"/>
+      <c r="F128" s="50"/>
+      <c r="G128" s="26"/>
+      <c r="H128" s="29"/>
+      <c r="I128" s="50"/>
+      <c r="J128" s="53"/>
     </row>
     <row r="129" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A129" s="42"/>
-      <c r="B129" s="45"/>
-      <c r="C129" s="48"/>
-      <c r="D129" s="52"/>
-      <c r="E129" s="52"/>
-      <c r="F129" s="52"/>
-      <c r="G129" s="28"/>
-      <c r="H129" s="31"/>
-      <c r="I129" s="52"/>
-      <c r="J129" s="55"/>
+      <c r="A129" s="40"/>
+      <c r="B129" s="43"/>
+      <c r="C129" s="46"/>
+      <c r="D129" s="50"/>
+      <c r="E129" s="50"/>
+      <c r="F129" s="50"/>
+      <c r="G129" s="26"/>
+      <c r="H129" s="29"/>
+      <c r="I129" s="50"/>
+      <c r="J129" s="53"/>
     </row>
     <row r="130" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A130" s="42"/>
-      <c r="B130" s="45"/>
-      <c r="C130" s="48"/>
-      <c r="D130" s="52"/>
-      <c r="E130" s="52"/>
-      <c r="F130" s="52"/>
-      <c r="G130" s="28"/>
-      <c r="H130" s="31"/>
-      <c r="I130" s="52"/>
-      <c r="J130" s="55"/>
+      <c r="A130" s="40"/>
+      <c r="B130" s="43"/>
+      <c r="C130" s="46"/>
+      <c r="D130" s="50"/>
+      <c r="E130" s="50"/>
+      <c r="F130" s="50"/>
+      <c r="G130" s="26"/>
+      <c r="H130" s="29"/>
+      <c r="I130" s="50"/>
+      <c r="J130" s="53"/>
     </row>
     <row r="131" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A131" s="43"/>
-      <c r="B131" s="46"/>
-      <c r="C131" s="49"/>
-      <c r="D131" s="53"/>
-      <c r="E131" s="53"/>
-      <c r="F131" s="53"/>
-      <c r="G131" s="30"/>
-      <c r="H131" s="31"/>
-      <c r="I131" s="53"/>
-      <c r="J131" s="56"/>
+      <c r="A131" s="41"/>
+      <c r="B131" s="44"/>
+      <c r="C131" s="47"/>
+      <c r="D131" s="51"/>
+      <c r="E131" s="51"/>
+      <c r="F131" s="51"/>
+      <c r="G131" s="28"/>
+      <c r="H131" s="29"/>
+      <c r="I131" s="51"/>
+      <c r="J131" s="54"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H112">
@@ -5363,14 +5363,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="5" t="s">

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04604E57-7C77-4DBE-B3CA-12EF20AD3786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FBCC2C1-2E5E-41D4-A333-56FC72C5A1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -744,7 +744,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -794,30 +794,6 @@
         <color rgb="FF44B3E1"/>
       </left>
       <right/>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF44B3E1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF44B3E1"/>
-      </left>
-      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -836,54 +812,10 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="thin">
         <color rgb="FF44B3E1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF44B3E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF44B3E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF44B3E1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -906,42 +838,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF44B3E1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF44B3E1"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -999,106 +900,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1351,7 +1189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4945,315 +4783,299 @@
       </c>
     </row>
     <row r="113" spans="1:10" ht="51" customHeight="1">
-      <c r="A113" s="39">
+      <c r="A113" s="16">
         <v>46185</v>
       </c>
-      <c r="B113" s="42">
+      <c r="B113" s="15">
         <v>0.77083333333333337</v>
       </c>
-      <c r="C113" s="45" t="s">
+      <c r="C113" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="D113" s="48">
+      <c r="D113" s="19">
         <v>81767</v>
       </c>
-      <c r="E113" s="49" t="s">
+      <c r="E113" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="F113" s="49" t="s">
+      <c r="F113" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="G113" s="45" t="s">
+      <c r="G113" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="H113" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="I113" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="J113" s="52" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" ht="28.5">
-      <c r="A114" s="31">
+      <c r="H113" t="s">
+        <v>17</v>
+      </c>
+      <c r="I113" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J113" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
+      <c r="A114" s="16">
         <v>46185</v>
       </c>
-      <c r="B114" s="32">
+      <c r="B114" s="15">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C114" s="33" t="s">
+      <c r="C114" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="D114" s="34">
+      <c r="D114" s="19">
         <v>81751</v>
       </c>
-      <c r="E114" s="35" t="s">
+      <c r="E114" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="F114" s="35" t="s">
+      <c r="F114" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="G114" s="36" t="s">
+      <c r="G114" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="H114" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="I114" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J114" s="37" t="s">
+      <c r="H114" t="s">
+        <v>17</v>
+      </c>
+      <c r="I114" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J114" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="28.5">
-      <c r="A115" s="21">
+      <c r="A115" s="16">
         <v>46190</v>
       </c>
-      <c r="B115" s="22">
+      <c r="B115" s="15">
         <v>0.625</v>
       </c>
-      <c r="C115" s="23" t="s">
+      <c r="C115" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="D115" s="24">
+      <c r="D115" s="19">
         <v>81750</v>
       </c>
-      <c r="E115" s="25" t="s">
+      <c r="E115" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="F115" s="25" t="s">
+      <c r="F115" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="G115" s="27" t="s">
+      <c r="G115" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="H115" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="I115" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="J115" s="30" t="s">
+      <c r="H115" t="s">
+        <v>17</v>
+      </c>
+      <c r="I115" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J115" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A116" s="21">
+      <c r="A116" s="16">
         <v>46185</v>
       </c>
-      <c r="B116" s="22">
+      <c r="B116" s="15">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C116" s="23" t="s">
+      <c r="C116" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="D116" s="24">
+      <c r="D116" s="19">
         <v>81729</v>
       </c>
-      <c r="E116" s="25" t="s">
+      <c r="E116" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="F116" s="25" t="s">
+      <c r="F116" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="G116" s="38" t="s">
+      <c r="G116" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="H116" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="I116" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="J116" s="30" t="s">
+      <c r="H116" t="s">
+        <v>17</v>
+      </c>
+      <c r="I116" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J116" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A117" s="40"/>
-      <c r="B117" s="43"/>
-      <c r="C117" s="46"/>
-      <c r="D117" s="50"/>
-      <c r="E117" s="50"/>
-      <c r="F117" s="50"/>
-      <c r="G117" s="55"/>
-      <c r="H117" s="29"/>
-      <c r="I117" s="50"/>
-      <c r="J117" s="53"/>
+      <c r="A117" s="16"/>
+      <c r="B117" s="15"/>
+      <c r="C117" s="12"/>
+      <c r="D117" s="19"/>
+      <c r="E117" s="12"/>
+      <c r="F117" s="12"/>
+      <c r="G117" s="14"/>
+      <c r="I117" s="12"/>
+      <c r="J117" s="13"/>
     </row>
     <row r="118" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A118" s="40"/>
-      <c r="B118" s="43"/>
-      <c r="C118" s="46"/>
-      <c r="D118" s="50"/>
-      <c r="E118" s="50"/>
-      <c r="F118" s="50"/>
-      <c r="G118" s="55"/>
-      <c r="H118" s="29"/>
-      <c r="I118" s="50"/>
-      <c r="J118" s="53"/>
+      <c r="A118" s="16"/>
+      <c r="B118" s="15"/>
+      <c r="C118" s="12"/>
+      <c r="D118" s="19"/>
+      <c r="E118" s="12"/>
+      <c r="F118" s="12"/>
+      <c r="G118" s="14"/>
+      <c r="I118" s="12"/>
+      <c r="J118" s="13"/>
     </row>
     <row r="119" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A119" s="40"/>
-      <c r="B119" s="43"/>
-      <c r="C119" s="46"/>
-      <c r="D119" s="50"/>
-      <c r="E119" s="50"/>
-      <c r="F119" s="50"/>
-      <c r="G119" s="55"/>
-      <c r="H119" s="29"/>
-      <c r="I119" s="50"/>
-      <c r="J119" s="53"/>
+      <c r="A119" s="16"/>
+      <c r="B119" s="15"/>
+      <c r="C119" s="12"/>
+      <c r="D119" s="19"/>
+      <c r="E119" s="12"/>
+      <c r="F119" s="12"/>
+      <c r="G119" s="14"/>
+      <c r="I119" s="12"/>
+      <c r="J119" s="13"/>
     </row>
     <row r="120" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A120" s="40"/>
-      <c r="B120" s="43"/>
-      <c r="C120" s="46"/>
-      <c r="D120" s="50"/>
-      <c r="E120" s="50"/>
-      <c r="F120" s="50"/>
-      <c r="G120" s="55"/>
-      <c r="H120" s="29"/>
-      <c r="I120" s="50"/>
-      <c r="J120" s="53"/>
+      <c r="A120" s="16"/>
+      <c r="B120" s="15"/>
+      <c r="C120" s="12"/>
+      <c r="D120" s="19"/>
+      <c r="E120" s="12"/>
+      <c r="F120" s="12"/>
+      <c r="G120" s="14"/>
+      <c r="I120" s="12"/>
+      <c r="J120" s="13"/>
     </row>
     <row r="121" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A121" s="40"/>
-      <c r="B121" s="43"/>
-      <c r="C121" s="46"/>
-      <c r="D121" s="50"/>
-      <c r="E121" s="50"/>
-      <c r="F121" s="50"/>
-      <c r="G121" s="55"/>
-      <c r="H121" s="29"/>
-      <c r="I121" s="50"/>
-      <c r="J121" s="53"/>
+      <c r="A121" s="24"/>
+      <c r="B121" s="26"/>
+      <c r="C121" s="28"/>
+      <c r="D121" s="30"/>
+      <c r="E121" s="30"/>
+      <c r="F121" s="30"/>
+      <c r="G121" s="34"/>
+      <c r="H121" s="23"/>
+      <c r="I121" s="30"/>
+      <c r="J121" s="32"/>
     </row>
     <row r="122" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A122" s="40"/>
-      <c r="B122" s="43"/>
-      <c r="C122" s="46"/>
-      <c r="D122" s="50"/>
-      <c r="E122" s="50"/>
-      <c r="F122" s="50"/>
-      <c r="G122" s="55"/>
-      <c r="H122" s="29"/>
-      <c r="I122" s="50"/>
-      <c r="J122" s="53"/>
+      <c r="A122" s="24"/>
+      <c r="B122" s="26"/>
+      <c r="C122" s="28"/>
+      <c r="D122" s="30"/>
+      <c r="E122" s="30"/>
+      <c r="F122" s="30"/>
+      <c r="G122" s="34"/>
+      <c r="H122" s="23"/>
+      <c r="I122" s="30"/>
+      <c r="J122" s="32"/>
     </row>
     <row r="123" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A123" s="40"/>
-      <c r="B123" s="43"/>
-      <c r="C123" s="46"/>
-      <c r="D123" s="50"/>
-      <c r="E123" s="50"/>
-      <c r="F123" s="50"/>
-      <c r="G123" s="55"/>
-      <c r="H123" s="29"/>
-      <c r="I123" s="50"/>
-      <c r="J123" s="53"/>
+      <c r="A123" s="24"/>
+      <c r="B123" s="26"/>
+      <c r="C123" s="28"/>
+      <c r="D123" s="30"/>
+      <c r="E123" s="30"/>
+      <c r="F123" s="30"/>
+      <c r="G123" s="34"/>
+      <c r="H123" s="23"/>
+      <c r="I123" s="30"/>
+      <c r="J123" s="32"/>
     </row>
     <row r="124" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A124" s="40"/>
-      <c r="B124" s="43"/>
-      <c r="C124" s="46"/>
-      <c r="D124" s="50"/>
-      <c r="E124" s="50"/>
-      <c r="F124" s="50"/>
-      <c r="G124" s="55"/>
-      <c r="H124" s="29"/>
-      <c r="I124" s="50"/>
-      <c r="J124" s="53"/>
+      <c r="A124" s="24"/>
+      <c r="B124" s="26"/>
+      <c r="C124" s="28"/>
+      <c r="D124" s="30"/>
+      <c r="E124" s="30"/>
+      <c r="F124" s="30"/>
+      <c r="G124" s="21"/>
+      <c r="H124" s="23"/>
+      <c r="I124" s="30"/>
+      <c r="J124" s="32"/>
     </row>
     <row r="125" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A125" s="40"/>
-      <c r="B125" s="43"/>
-      <c r="C125" s="46"/>
-      <c r="D125" s="50"/>
-      <c r="E125" s="50"/>
-      <c r="F125" s="50"/>
-      <c r="G125" s="26"/>
-      <c r="H125" s="29"/>
-      <c r="I125" s="50"/>
-      <c r="J125" s="53"/>
+      <c r="A125" s="24"/>
+      <c r="B125" s="26"/>
+      <c r="C125" s="28"/>
+      <c r="D125" s="30"/>
+      <c r="E125" s="30"/>
+      <c r="F125" s="30"/>
+      <c r="G125" s="21"/>
+      <c r="H125" s="23"/>
+      <c r="I125" s="30"/>
+      <c r="J125" s="32"/>
     </row>
     <row r="126" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A126" s="40"/>
-      <c r="B126" s="43"/>
-      <c r="C126" s="46"/>
-      <c r="D126" s="50"/>
-      <c r="E126" s="50"/>
-      <c r="F126" s="50"/>
-      <c r="G126" s="26"/>
-      <c r="H126" s="29"/>
-      <c r="I126" s="50"/>
-      <c r="J126" s="53"/>
+      <c r="A126" s="24"/>
+      <c r="B126" s="26"/>
+      <c r="C126" s="28"/>
+      <c r="D126" s="30"/>
+      <c r="E126" s="30"/>
+      <c r="F126" s="30"/>
+      <c r="G126" s="21"/>
+      <c r="H126" s="23"/>
+      <c r="I126" s="30"/>
+      <c r="J126" s="32"/>
     </row>
     <row r="127" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A127" s="40"/>
-      <c r="B127" s="43"/>
-      <c r="C127" s="46"/>
-      <c r="D127" s="50"/>
-      <c r="E127" s="50"/>
-      <c r="F127" s="50"/>
-      <c r="G127" s="26"/>
-      <c r="H127" s="29"/>
-      <c r="I127" s="50"/>
-      <c r="J127" s="53"/>
+      <c r="A127" s="24"/>
+      <c r="B127" s="26"/>
+      <c r="C127" s="28"/>
+      <c r="D127" s="30"/>
+      <c r="E127" s="30"/>
+      <c r="F127" s="30"/>
+      <c r="G127" s="21"/>
+      <c r="H127" s="23"/>
+      <c r="I127" s="30"/>
+      <c r="J127" s="32"/>
     </row>
     <row r="128" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A128" s="40"/>
-      <c r="B128" s="43"/>
-      <c r="C128" s="46"/>
-      <c r="D128" s="50"/>
-      <c r="E128" s="50"/>
-      <c r="F128" s="50"/>
-      <c r="G128" s="26"/>
-      <c r="H128" s="29"/>
-      <c r="I128" s="50"/>
-      <c r="J128" s="53"/>
+      <c r="A128" s="24"/>
+      <c r="B128" s="26"/>
+      <c r="C128" s="28"/>
+      <c r="D128" s="30"/>
+      <c r="E128" s="30"/>
+      <c r="F128" s="30"/>
+      <c r="G128" s="21"/>
+      <c r="H128" s="23"/>
+      <c r="I128" s="30"/>
+      <c r="J128" s="32"/>
     </row>
     <row r="129" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A129" s="40"/>
-      <c r="B129" s="43"/>
-      <c r="C129" s="46"/>
-      <c r="D129" s="50"/>
-      <c r="E129" s="50"/>
-      <c r="F129" s="50"/>
-      <c r="G129" s="26"/>
-      <c r="H129" s="29"/>
-      <c r="I129" s="50"/>
-      <c r="J129" s="53"/>
+      <c r="A129" s="24"/>
+      <c r="B129" s="26"/>
+      <c r="C129" s="28"/>
+      <c r="D129" s="30"/>
+      <c r="E129" s="30"/>
+      <c r="F129" s="30"/>
+      <c r="G129" s="21"/>
+      <c r="H129" s="23"/>
+      <c r="I129" s="30"/>
+      <c r="J129" s="32"/>
     </row>
     <row r="130" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A130" s="40"/>
-      <c r="B130" s="43"/>
-      <c r="C130" s="46"/>
-      <c r="D130" s="50"/>
-      <c r="E130" s="50"/>
-      <c r="F130" s="50"/>
-      <c r="G130" s="26"/>
-      <c r="H130" s="29"/>
-      <c r="I130" s="50"/>
-      <c r="J130" s="53"/>
-    </row>
-    <row r="131" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A131" s="41"/>
-      <c r="B131" s="44"/>
-      <c r="C131" s="47"/>
-      <c r="D131" s="51"/>
-      <c r="E131" s="51"/>
-      <c r="F131" s="51"/>
-      <c r="G131" s="28"/>
-      <c r="H131" s="29"/>
-      <c r="I131" s="51"/>
-      <c r="J131" s="54"/>
+      <c r="A130" s="25"/>
+      <c r="B130" s="27"/>
+      <c r="C130" s="29"/>
+      <c r="D130" s="31"/>
+      <c r="E130" s="31"/>
+      <c r="F130" s="31"/>
+      <c r="G130" s="22"/>
+      <c r="H130" s="23"/>
+      <c r="I130" s="31"/>
+      <c r="J130" s="33"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H112">
+  <conditionalFormatting sqref="H2:H120">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>H2="Alta"</formula>
     </cfRule>
@@ -5264,7 +5086,7 @@
       <formula>H2="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J112">
+  <conditionalFormatting sqref="J2:J120">
     <cfRule type="expression" dxfId="1" priority="4">
       <formula>J2="Ejecutado"</formula>
     </cfRule>
@@ -5363,14 +5185,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="5" t="s">

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FBCC2C1-2E5E-41D4-A333-56FC72C5A1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71DB78F-D966-4357-A405-3E500AA277F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVENTOS" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="264">
   <si>
     <t>Fecha</t>
   </si>
@@ -649,6 +649,231 @@
   <si>
     <t>AREA VICERRECTORADO</t>
   </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>Talleres Taekwondo</t>
+  </si>
+  <si>
+    <t>Espacio limpio</t>
+  </si>
+  <si>
+    <t>Selección Wushu Taolu</t>
+  </si>
+  <si>
+    <t>Talleres Wushu</t>
+  </si>
+  <si>
+    <t>Selección Tenis de Mesa</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>Selección Wushu Sanda</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>2026-06-06</t>
+  </si>
+  <si>
+    <t>Talleres Tenis de Mesa</t>
+  </si>
+  <si>
+    <t>Talleres Karate</t>
+  </si>
+  <si>
+    <t>Talleres Lucha Olímpica</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>2026-06-16</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>AREA DE MARKETING</t>
+  </si>
+  <si>
+    <t>Ceremonia Oficial de Reconocimiento de la carrera de Estomatología</t>
+  </si>
+  <si>
+    <t>Terraza, hall y sala de estudios 3er piso</t>
+  </si>
+  <si>
+    <t>Auditorio Pabellón O /Habilitar 90 sillas en auditorio. Prioridad sillas blancas, grises y verde claro adelante, alineadas./nstalar podio Bandera y tótem en escenario/Asegurar el funcionamiento del Aire acondicionado/</t>
+  </si>
+  <si>
+    <t>Colocar 1 mesa de registro vestida en ingreso con punto de luz y 3 sillas  /Pabellón O 3er piso/Liberar mobiliario total de hall, terraza y sala de estudios. Solo se mantendrán las mesas blancas empotradas de la Sala de estudios ya que ahí colocaremos el catering./Colocar enfiladores para cerrar el pase en sala de estudios y Terraza /Limpieza de ambos espacios.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AREA  TOPICO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campaña de vacunacion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jardin frente al N </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requererimientos : 2 toldos  / 3 mesas / 10 sillas </t>
+  </si>
+  <si>
+    <t>AREA GDT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evento dia del Padre </t>
+  </si>
+  <si>
+    <t>Auditorio Pabellón O</t>
+  </si>
+  <si>
+    <t>Requererimientos :Punto de luz. / Zona de trivia: Auditorio / 4 mesas. / unto de luz.</t>
+  </si>
 </sst>
 </file>
 
@@ -657,7 +882,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -684,19 +909,8 @@
       <color theme="1"/>
       <name val="Carlito"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF991B1B"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Carlito"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -725,26 +939,8 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E6F5"/>
-        <bgColor rgb="FFC0E6F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61CBF3"/>
-        <bgColor rgb="FFC0E6F5"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -789,60 +985,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF44B3E1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF44B3E1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF44B3E1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF44B3E1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF44B3E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -900,57 +1047,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF166534"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF166534"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF991B1B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1028,7 +1189,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Área Solicitante"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="N° OT" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="N° OT" dataDxfId="10"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Evento / Actividad"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ubicación"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Requerimientos"/>
@@ -1189,7 +1350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:L306"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1202,6 +1363,7 @@
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="5.75" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="26.1" customHeight="1">
@@ -4911,187 +5073,4580 @@
       </c>
     </row>
     <row r="117" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A117" s="16"/>
-      <c r="B117" s="15"/>
-      <c r="C117" s="12"/>
-      <c r="D117" s="19"/>
-      <c r="E117" s="12"/>
-      <c r="F117" s="12"/>
-      <c r="G117" s="14"/>
-      <c r="I117" s="12"/>
-      <c r="J117" s="13"/>
+      <c r="A117" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B117" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D117" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E117" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="F117" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G117" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H117" t="s">
+        <v>17</v>
+      </c>
+      <c r="I117" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J117" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="118" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A118" s="16"/>
-      <c r="B118" s="15"/>
-      <c r="C118" s="12"/>
-      <c r="D118" s="19"/>
-      <c r="E118" s="12"/>
-      <c r="F118" s="12"/>
-      <c r="G118" s="14"/>
-      <c r="I118" s="12"/>
-      <c r="J118" s="13"/>
+      <c r="A118" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B118" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D118" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E118" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F118" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G118" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H118" t="s">
+        <v>17</v>
+      </c>
+      <c r="I118" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J118" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="119" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A119" s="16"/>
-      <c r="B119" s="15"/>
-      <c r="C119" s="12"/>
-      <c r="D119" s="19"/>
-      <c r="E119" s="12"/>
-      <c r="F119" s="12"/>
-      <c r="G119" s="14"/>
-      <c r="I119" s="12"/>
-      <c r="J119" s="13"/>
+      <c r="A119" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B119" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D119" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E119" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F119" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G119" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H119" t="s">
+        <v>17</v>
+      </c>
+      <c r="I119" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J119" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="120" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A120" s="16"/>
-      <c r="B120" s="15"/>
-      <c r="C120" s="12"/>
-      <c r="D120" s="19"/>
-      <c r="E120" s="12"/>
-      <c r="F120" s="12"/>
-      <c r="G120" s="14"/>
-      <c r="I120" s="12"/>
-      <c r="J120" s="13"/>
+      <c r="A120" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B120" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D120" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E120" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F120" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G120" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H120" t="s">
+        <v>17</v>
+      </c>
+      <c r="I120" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J120" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="121" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A121" s="24"/>
-      <c r="B121" s="26"/>
-      <c r="C121" s="28"/>
-      <c r="D121" s="30"/>
-      <c r="E121" s="30"/>
-      <c r="F121" s="30"/>
-      <c r="G121" s="34"/>
-      <c r="H121" s="23"/>
-      <c r="I121" s="30"/>
-      <c r="J121" s="32"/>
+      <c r="A121" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B121" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D121" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E121" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F121" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G121" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H121" t="s">
+        <v>17</v>
+      </c>
+      <c r="I121" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J121" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="122" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A122" s="24"/>
-      <c r="B122" s="26"/>
-      <c r="C122" s="28"/>
-      <c r="D122" s="30"/>
-      <c r="E122" s="30"/>
-      <c r="F122" s="30"/>
-      <c r="G122" s="34"/>
-      <c r="H122" s="23"/>
-      <c r="I122" s="30"/>
-      <c r="J122" s="32"/>
+      <c r="A122" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="B122" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D122" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E122" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F122" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G122" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H122" t="s">
+        <v>17</v>
+      </c>
+      <c r="I122" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J122" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="123" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A123" s="24"/>
-      <c r="B123" s="26"/>
-      <c r="C123" s="28"/>
-      <c r="D123" s="30"/>
-      <c r="E123" s="30"/>
-      <c r="F123" s="30"/>
-      <c r="G123" s="34"/>
-      <c r="H123" s="23"/>
-      <c r="I123" s="30"/>
-      <c r="J123" s="32"/>
+      <c r="A123" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="B123" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C123" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D123" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E123" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F123" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G123" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H123" t="s">
+        <v>17</v>
+      </c>
+      <c r="I123" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J123" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="124" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A124" s="24"/>
-      <c r="B124" s="26"/>
-      <c r="C124" s="28"/>
-      <c r="D124" s="30"/>
-      <c r="E124" s="30"/>
-      <c r="F124" s="30"/>
-      <c r="G124" s="21"/>
-      <c r="H124" s="23"/>
-      <c r="I124" s="30"/>
-      <c r="J124" s="32"/>
+      <c r="A124" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B124" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C124" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D124" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E124" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F124" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G124" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H124" t="s">
+        <v>17</v>
+      </c>
+      <c r="I124" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J124" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="125" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A125" s="24"/>
-      <c r="B125" s="26"/>
-      <c r="C125" s="28"/>
-      <c r="D125" s="30"/>
-      <c r="E125" s="30"/>
-      <c r="F125" s="30"/>
-      <c r="G125" s="21"/>
-      <c r="H125" s="23"/>
-      <c r="I125" s="30"/>
-      <c r="J125" s="32"/>
+      <c r="A125" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="B125" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C125" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D125" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E125" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F125" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G125" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H125" t="s">
+        <v>17</v>
+      </c>
+      <c r="I125" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J125" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="126" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A126" s="24"/>
-      <c r="B126" s="26"/>
-      <c r="C126" s="28"/>
-      <c r="D126" s="30"/>
-      <c r="E126" s="30"/>
-      <c r="F126" s="30"/>
-      <c r="G126" s="21"/>
-      <c r="H126" s="23"/>
-      <c r="I126" s="30"/>
-      <c r="J126" s="32"/>
+      <c r="A126" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B126" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C126" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D126" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E126" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="F126" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G126" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H126" t="s">
+        <v>17</v>
+      </c>
+      <c r="I126" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J126" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="127" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A127" s="24"/>
-      <c r="B127" s="26"/>
-      <c r="C127" s="28"/>
-      <c r="D127" s="30"/>
-      <c r="E127" s="30"/>
-      <c r="F127" s="30"/>
-      <c r="G127" s="21"/>
-      <c r="H127" s="23"/>
-      <c r="I127" s="30"/>
-      <c r="J127" s="32"/>
+      <c r="A127" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B127" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C127" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D127" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E127" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F127" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G127" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H127" t="s">
+        <v>17</v>
+      </c>
+      <c r="I127" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="128" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A128" s="24"/>
-      <c r="B128" s="26"/>
-      <c r="C128" s="28"/>
-      <c r="D128" s="30"/>
-      <c r="E128" s="30"/>
-      <c r="F128" s="30"/>
-      <c r="G128" s="21"/>
-      <c r="H128" s="23"/>
-      <c r="I128" s="30"/>
-      <c r="J128" s="32"/>
+      <c r="A128" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B128" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C128" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D128" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E128" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F128" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G128" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H128" t="s">
+        <v>17</v>
+      </c>
+      <c r="I128" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J128" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="129" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A129" s="24"/>
-      <c r="B129" s="26"/>
-      <c r="C129" s="28"/>
-      <c r="D129" s="30"/>
-      <c r="E129" s="30"/>
-      <c r="F129" s="30"/>
-      <c r="G129" s="21"/>
-      <c r="H129" s="23"/>
-      <c r="I129" s="30"/>
-      <c r="J129" s="32"/>
+      <c r="A129" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B129" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D129" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E129" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="F129" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G129" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H129" t="s">
+        <v>17</v>
+      </c>
+      <c r="I129" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J129" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="130" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A130" s="25"/>
-      <c r="B130" s="27"/>
-      <c r="C130" s="29"/>
-      <c r="D130" s="31"/>
-      <c r="E130" s="31"/>
-      <c r="F130" s="31"/>
-      <c r="G130" s="22"/>
-      <c r="H130" s="23"/>
-      <c r="I130" s="31"/>
-      <c r="J130" s="33"/>
+      <c r="A130" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B130" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C130" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D130" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E130" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="F130" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G130" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H130" t="s">
+        <v>17</v>
+      </c>
+      <c r="I130" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J130" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10">
+      <c r="A131" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B131" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D131" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E131" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F131" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G131" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H131" t="s">
+        <v>17</v>
+      </c>
+      <c r="I131" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J131" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10">
+      <c r="A132" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B132" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D132" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E132" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F132" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G132" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H132" t="s">
+        <v>17</v>
+      </c>
+      <c r="I132" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J132" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10">
+      <c r="A133" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B133" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D133" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E133" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F133" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G133" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H133" t="s">
+        <v>17</v>
+      </c>
+      <c r="I133" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J133" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10">
+      <c r="A134" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="B134" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D134" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E134" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F134" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G134" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H134" t="s">
+        <v>17</v>
+      </c>
+      <c r="I134" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J134" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10">
+      <c r="A135" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B135" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D135" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E135" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F135" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G135" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H135" t="s">
+        <v>17</v>
+      </c>
+      <c r="I135" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J135" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10">
+      <c r="A136" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B136" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D136" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E136" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F136" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G136" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H136" t="s">
+        <v>17</v>
+      </c>
+      <c r="I136" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J136" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10">
+      <c r="A137" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="B137" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D137" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E137" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F137" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G137" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H137" t="s">
+        <v>17</v>
+      </c>
+      <c r="I137" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J137" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10">
+      <c r="A138" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="B138" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C138" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D138" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E138" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F138" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G138" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H138" t="s">
+        <v>17</v>
+      </c>
+      <c r="I138" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J138" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
+      <c r="A139" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B139" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C139" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D139" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E139" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="F139" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G139" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H139" t="s">
+        <v>17</v>
+      </c>
+      <c r="I139" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J139" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10">
+      <c r="A140" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B140" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C140" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D140" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E140" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F140" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G140" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H140" t="s">
+        <v>17</v>
+      </c>
+      <c r="I140" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J140" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10">
+      <c r="A141" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B141" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C141" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D141" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E141" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F141" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G141" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H141" t="s">
+        <v>17</v>
+      </c>
+      <c r="I141" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J141" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10">
+      <c r="A142" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="B142" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C142" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D142" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E142" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="F142" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G142" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H142" t="s">
+        <v>17</v>
+      </c>
+      <c r="I142" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J142" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10">
+      <c r="A143" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B143" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D143" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E143" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="F143" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G143" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H143" t="s">
+        <v>17</v>
+      </c>
+      <c r="I143" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J143" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
+      <c r="A144" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B144" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C144" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D144" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E144" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F144" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G144" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H144" t="s">
+        <v>17</v>
+      </c>
+      <c r="I144" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J144" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10">
+      <c r="A145" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B145" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C145" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D145" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E145" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F145" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G145" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H145" t="s">
+        <v>17</v>
+      </c>
+      <c r="I145" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J145" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10">
+      <c r="A146" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B146" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C146" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D146" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E146" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F146" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G146" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H146" t="s">
+        <v>17</v>
+      </c>
+      <c r="I146" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J146" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10">
+      <c r="A147" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="B147" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C147" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D147" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E147" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F147" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G147" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H147" t="s">
+        <v>17</v>
+      </c>
+      <c r="I147" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J147" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10">
+      <c r="A148" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B148" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C148" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D148" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E148" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F148" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G148" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H148" t="s">
+        <v>17</v>
+      </c>
+      <c r="I148" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J148" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10">
+      <c r="A149" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B149" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C149" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D149" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E149" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F149" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G149" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H149" t="s">
+        <v>17</v>
+      </c>
+      <c r="I149" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J149" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10">
+      <c r="A150" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="B150" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C150" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D150" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E150" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F150" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G150" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H150" t="s">
+        <v>17</v>
+      </c>
+      <c r="I150" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J150" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10">
+      <c r="A151" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="B151" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C151" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D151" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E151" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F151" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G151" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H151" t="s">
+        <v>17</v>
+      </c>
+      <c r="I151" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J151" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10">
+      <c r="A152" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B152" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C152" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D152" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E152" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="F152" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G152" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H152" t="s">
+        <v>17</v>
+      </c>
+      <c r="I152" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J152" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10">
+      <c r="A153" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B153" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C153" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D153" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E153" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F153" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G153" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H153" t="s">
+        <v>17</v>
+      </c>
+      <c r="I153" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J153" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10">
+      <c r="A154" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B154" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C154" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D154" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E154" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F154" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G154" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H154" t="s">
+        <v>17</v>
+      </c>
+      <c r="I154" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J154" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10">
+      <c r="A155" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="B155" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C155" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D155" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E155" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="F155" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G155" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H155" t="s">
+        <v>17</v>
+      </c>
+      <c r="I155" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J155" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10">
+      <c r="A156" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="B156" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C156" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D156" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E156" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="F156" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G156" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H156" t="s">
+        <v>17</v>
+      </c>
+      <c r="I156" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J156" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10">
+      <c r="A157" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="B157" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C157" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D157" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E157" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F157" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G157" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H157" t="s">
+        <v>17</v>
+      </c>
+      <c r="I157" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J157" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10">
+      <c r="A158" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="B158" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C158" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D158" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E158" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F158" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G158" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H158" t="s">
+        <v>17</v>
+      </c>
+      <c r="I158" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J158" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10">
+      <c r="A159" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="B159" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C159" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D159" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E159" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F159" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G159" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H159" t="s">
+        <v>17</v>
+      </c>
+      <c r="I159" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J159" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10">
+      <c r="A160" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="B160" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C160" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D160" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E160" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F160" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G160" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H160" t="s">
+        <v>17</v>
+      </c>
+      <c r="I160" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J160" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10">
+      <c r="A161" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="B161" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C161" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D161" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E161" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F161" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G161" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H161" t="s">
+        <v>17</v>
+      </c>
+      <c r="I161" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J161" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10">
+      <c r="A162" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="B162" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C162" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D162" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E162" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F162" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G162" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H162" t="s">
+        <v>17</v>
+      </c>
+      <c r="I162" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J162" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10">
+      <c r="A163" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="B163" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C163" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D163" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E163" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F163" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G163" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H163" t="s">
+        <v>17</v>
+      </c>
+      <c r="I163" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J163" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10">
+      <c r="A164" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="B164" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C164" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D164" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E164" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F164" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G164" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H164" t="s">
+        <v>17</v>
+      </c>
+      <c r="I164" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J164" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10">
+      <c r="A165" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="B165" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C165" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D165" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E165" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="F165" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G165" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H165" t="s">
+        <v>17</v>
+      </c>
+      <c r="I165" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J165" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10">
+      <c r="A166" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="B166" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C166" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D166" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E166" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F166" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G166" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H166" t="s">
+        <v>17</v>
+      </c>
+      <c r="I166" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J166" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10">
+      <c r="A167" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="B167" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C167" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D167" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E167" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F167" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G167" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H167" t="s">
+        <v>17</v>
+      </c>
+      <c r="I167" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J167" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10">
+      <c r="A168" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="B168" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C168" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D168" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E168" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="F168" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G168" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H168" t="s">
+        <v>17</v>
+      </c>
+      <c r="I168" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J168" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10">
+      <c r="A169" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="B169" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C169" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D169" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E169" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="F169" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G169" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H169" t="s">
+        <v>17</v>
+      </c>
+      <c r="I169" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J169" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10">
+      <c r="A170" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="B170" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C170" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D170" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E170" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F170" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G170" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H170" t="s">
+        <v>17</v>
+      </c>
+      <c r="I170" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J170" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10">
+      <c r="A171" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="B171" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C171" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D171" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E171" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F171" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G171" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H171" t="s">
+        <v>17</v>
+      </c>
+      <c r="I171" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J171" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10">
+      <c r="A172" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="B172" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C172" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D172" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E172" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F172" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G172" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H172" t="s">
+        <v>17</v>
+      </c>
+      <c r="I172" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J172" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10">
+      <c r="A173" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="B173" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C173" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D173" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E173" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F173" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G173" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H173" t="s">
+        <v>17</v>
+      </c>
+      <c r="I173" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J173" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10">
+      <c r="A174" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="B174" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C174" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D174" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E174" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F174" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G174" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H174" t="s">
+        <v>17</v>
+      </c>
+      <c r="I174" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J174" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10">
+      <c r="A175" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="B175" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C175" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D175" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E175" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F175" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G175" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H175" t="s">
+        <v>17</v>
+      </c>
+      <c r="I175" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J175" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10">
+      <c r="A176" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="B176" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D176" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E176" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F176" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G176" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H176" t="s">
+        <v>17</v>
+      </c>
+      <c r="I176" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J176" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10">
+      <c r="A177" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="B177" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C177" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D177" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E177" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F177" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G177" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H177" t="s">
+        <v>17</v>
+      </c>
+      <c r="I177" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J177" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10">
+      <c r="A178" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B178" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C178" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D178" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E178" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="F178" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G178" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H178" t="s">
+        <v>17</v>
+      </c>
+      <c r="I178" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J178" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10">
+      <c r="A179" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B179" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C179" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D179" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E179" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F179" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G179" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H179" t="s">
+        <v>17</v>
+      </c>
+      <c r="I179" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J179" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10">
+      <c r="A180" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B180" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C180" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D180" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E180" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F180" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G180" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H180" t="s">
+        <v>17</v>
+      </c>
+      <c r="I180" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J180" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10">
+      <c r="A181" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B181" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C181" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D181" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E181" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="F181" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G181" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H181" t="s">
+        <v>17</v>
+      </c>
+      <c r="I181" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J181" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10">
+      <c r="A182" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B182" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C182" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D182" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E182" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="F182" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G182" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H182" t="s">
+        <v>17</v>
+      </c>
+      <c r="I182" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J182" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10">
+      <c r="A183" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B183" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C183" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D183" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E183" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F183" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G183" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H183" t="s">
+        <v>17</v>
+      </c>
+      <c r="I183" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J183" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10">
+      <c r="A184" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B184" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C184" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D184" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E184" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F184" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G184" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H184" t="s">
+        <v>17</v>
+      </c>
+      <c r="I184" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J184" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10">
+      <c r="A185" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B185" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C185" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D185" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E185" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F185" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G185" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H185" t="s">
+        <v>17</v>
+      </c>
+      <c r="I185" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J185" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10">
+      <c r="A186" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B186" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C186" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D186" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E186" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F186" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G186" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H186" t="s">
+        <v>17</v>
+      </c>
+      <c r="I186" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J186" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10">
+      <c r="A187" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="B187" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C187" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D187" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E187" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F187" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G187" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H187" t="s">
+        <v>17</v>
+      </c>
+      <c r="I187" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J187" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10">
+      <c r="A188" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="B188" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C188" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D188" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E188" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F188" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G188" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H188" t="s">
+        <v>17</v>
+      </c>
+      <c r="I188" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J188" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10">
+      <c r="A189" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="B189" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C189" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D189" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E189" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F189" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G189" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H189" t="s">
+        <v>17</v>
+      </c>
+      <c r="I189" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J189" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10">
+      <c r="A190" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="B190" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C190" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D190" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E190" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F190" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G190" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H190" t="s">
+        <v>17</v>
+      </c>
+      <c r="I190" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J190" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10">
+      <c r="A191" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B191" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C191" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D191" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E191" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="F191" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G191" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H191" t="s">
+        <v>17</v>
+      </c>
+      <c r="I191" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J191" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10">
+      <c r="A192" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B192" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C192" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D192" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E192" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F192" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G192" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H192" t="s">
+        <v>17</v>
+      </c>
+      <c r="I192" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J192" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10">
+      <c r="A193" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B193" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C193" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D193" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E193" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F193" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G193" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H193" t="s">
+        <v>17</v>
+      </c>
+      <c r="I193" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J193" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10">
+      <c r="A194" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B194" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C194" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D194" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E194" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="F194" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G194" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H194" t="s">
+        <v>17</v>
+      </c>
+      <c r="I194" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J194" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10">
+      <c r="A195" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B195" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C195" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D195" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E195" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="F195" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G195" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H195" t="s">
+        <v>17</v>
+      </c>
+      <c r="I195" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J195" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10">
+      <c r="A196" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B196" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C196" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D196" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E196" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F196" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G196" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H196" t="s">
+        <v>17</v>
+      </c>
+      <c r="I196" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J196" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10">
+      <c r="A197" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B197" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C197" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D197" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E197" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F197" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G197" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H197" t="s">
+        <v>17</v>
+      </c>
+      <c r="I197" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J197" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10">
+      <c r="A198" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B198" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C198" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D198" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E198" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F198" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G198" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H198" t="s">
+        <v>17</v>
+      </c>
+      <c r="I198" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J198" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10">
+      <c r="A199" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B199" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C199" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D199" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E199" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F199" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G199" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H199" t="s">
+        <v>17</v>
+      </c>
+      <c r="I199" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J199" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10">
+      <c r="A200" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="B200" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C200" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D200" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E200" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F200" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G200" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H200" t="s">
+        <v>17</v>
+      </c>
+      <c r="I200" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J200" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10">
+      <c r="A201" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="B201" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C201" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D201" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E201" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F201" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G201" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H201" t="s">
+        <v>17</v>
+      </c>
+      <c r="I201" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J201" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10">
+      <c r="A202" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B202" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C202" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D202" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E202" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F202" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G202" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H202" t="s">
+        <v>17</v>
+      </c>
+      <c r="I202" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J202" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10">
+      <c r="A203" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="B203" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C203" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D203" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E203" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F203" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G203" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H203" t="s">
+        <v>17</v>
+      </c>
+      <c r="I203" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J203" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10">
+      <c r="A204" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B204" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C204" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D204" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E204" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="F204" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G204" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H204" t="s">
+        <v>17</v>
+      </c>
+      <c r="I204" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J204" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10">
+      <c r="A205" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B205" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C205" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D205" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E205" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F205" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G205" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H205" t="s">
+        <v>17</v>
+      </c>
+      <c r="I205" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J205" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10">
+      <c r="A206" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B206" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C206" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D206" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E206" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F206" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G206" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H206" t="s">
+        <v>17</v>
+      </c>
+      <c r="I206" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J206" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10">
+      <c r="A207" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B207" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C207" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D207" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E207" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="F207" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G207" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H207" t="s">
+        <v>17</v>
+      </c>
+      <c r="I207" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J207" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10">
+      <c r="A208" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="B208" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C208" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D208" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E208" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="F208" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G208" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H208" t="s">
+        <v>17</v>
+      </c>
+      <c r="I208" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J208" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10">
+      <c r="A209" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="B209" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C209" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D209" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E209" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F209" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G209" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H209" t="s">
+        <v>17</v>
+      </c>
+      <c r="I209" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J209" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10">
+      <c r="A210" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="B210" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C210" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D210" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E210" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F210" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G210" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H210" t="s">
+        <v>17</v>
+      </c>
+      <c r="I210" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J210" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10">
+      <c r="A211" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="B211" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C211" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D211" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E211" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F211" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G211" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H211" t="s">
+        <v>17</v>
+      </c>
+      <c r="I211" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J211" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10">
+      <c r="A212" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="B212" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C212" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D212" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E212" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F212" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G212" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H212" t="s">
+        <v>17</v>
+      </c>
+      <c r="I212" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J212" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10">
+      <c r="A213" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="B213" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C213" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D213" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E213" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F213" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G213" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H213" t="s">
+        <v>17</v>
+      </c>
+      <c r="I213" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J213" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10">
+      <c r="A214" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="B214" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C214" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D214" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E214" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F214" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G214" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H214" t="s">
+        <v>17</v>
+      </c>
+      <c r="I214" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J214" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10">
+      <c r="A215" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="B215" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C215" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D215" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E215" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F215" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G215" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H215" t="s">
+        <v>17</v>
+      </c>
+      <c r="I215" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J215" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10">
+      <c r="A216" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B216" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C216" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D216" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E216" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F216" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G216" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H216" t="s">
+        <v>17</v>
+      </c>
+      <c r="I216" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J216" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10">
+      <c r="A217" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="B217" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C217" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D217" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E217" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="F217" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G217" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H217" t="s">
+        <v>17</v>
+      </c>
+      <c r="I217" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J217" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10">
+      <c r="A218" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="B218" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C218" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D218" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E218" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F218" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G218" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H218" t="s">
+        <v>17</v>
+      </c>
+      <c r="I218" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J218" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10">
+      <c r="A219" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="B219" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C219" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D219" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E219" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="F219" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G219" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H219" t="s">
+        <v>17</v>
+      </c>
+      <c r="I219" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J219" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10">
+      <c r="A220" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="B220" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C220" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D220" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E220" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="F220" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G220" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H220" t="s">
+        <v>17</v>
+      </c>
+      <c r="I220" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J220" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10">
+      <c r="A221" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="B221" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C221" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D221" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E221" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="F221" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G221" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H221" t="s">
+        <v>17</v>
+      </c>
+      <c r="I221" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J221" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10">
+      <c r="A222" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="B222" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C222" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D222" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E222" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F222" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G222" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H222" t="s">
+        <v>17</v>
+      </c>
+      <c r="I222" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J222" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10">
+      <c r="A223" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="B223" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C223" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D223" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E223" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F223" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G223" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H223" t="s">
+        <v>17</v>
+      </c>
+      <c r="I223" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J223" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10">
+      <c r="A224" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="B224" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C224" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D224" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E224" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F224" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G224" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H224" t="s">
+        <v>17</v>
+      </c>
+      <c r="I224" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J224" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12">
+      <c r="A225" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="B225" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C225" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D225" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E225" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F225" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G225" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H225" t="s">
+        <v>17</v>
+      </c>
+      <c r="I225" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J225" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12">
+      <c r="A226" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="B226" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C226" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D226" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E226" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F226" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G226" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H226" t="s">
+        <v>17</v>
+      </c>
+      <c r="I226" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J226" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12">
+      <c r="A227" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="B227" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C227" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D227" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E227" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F227" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G227" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H227" t="s">
+        <v>17</v>
+      </c>
+      <c r="I227" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J227" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12">
+      <c r="A228" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="B228" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C228" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D228" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E228" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="F228" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G228" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H228" t="s">
+        <v>17</v>
+      </c>
+      <c r="I228" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J228" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12">
+      <c r="A229" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="B229" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C229" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D229" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E229" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="F229" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G229" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="H229" t="s">
+        <v>17</v>
+      </c>
+      <c r="I229" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J229" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" ht="71.25">
+      <c r="A230" s="16">
+        <v>46190</v>
+      </c>
+      <c r="B230" s="15">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C230" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="D230" s="19">
+        <v>9784</v>
+      </c>
+      <c r="E230" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="F230" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="G230" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="H230" t="s">
+        <v>17</v>
+      </c>
+      <c r="I230" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J230" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="L230" s="23"/>
+    </row>
+    <row r="231" spans="1:12" ht="99.75">
+      <c r="A231" s="16"/>
+      <c r="B231" s="15"/>
+      <c r="C231" s="12"/>
+      <c r="D231" s="19"/>
+      <c r="E231" s="12"/>
+      <c r="F231" s="12"/>
+      <c r="G231" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="H231" t="s">
+        <v>17</v>
+      </c>
+      <c r="I231" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J231" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12">
+      <c r="A232" s="16">
+        <v>46189</v>
+      </c>
+      <c r="B232" s="15">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C232" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="D232" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E232" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="F232" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="G232" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="H232" t="s">
+        <v>17</v>
+      </c>
+      <c r="I232" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J232" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" ht="28.5">
+      <c r="A233" s="16">
+        <v>46190</v>
+      </c>
+      <c r="B233" s="15">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C233" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="D233" s="19">
+        <v>81907</v>
+      </c>
+      <c r="E233" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="F233" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="G233" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="H233" t="s">
+        <v>17</v>
+      </c>
+      <c r="I233" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J233" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12">
+      <c r="A234" s="16"/>
+      <c r="B234" s="15"/>
+      <c r="C234" s="12"/>
+      <c r="D234" s="19"/>
+      <c r="E234" s="12"/>
+      <c r="F234" s="12"/>
+      <c r="G234" s="14"/>
+      <c r="I234" s="12"/>
+      <c r="J234" s="13"/>
+    </row>
+    <row r="235" spans="1:12">
+      <c r="A235" s="16"/>
+      <c r="B235" s="15"/>
+      <c r="C235" s="12"/>
+      <c r="D235" s="19"/>
+      <c r="E235" s="12"/>
+      <c r="F235" s="12"/>
+      <c r="G235" s="14"/>
+      <c r="I235" s="12"/>
+      <c r="J235" s="13"/>
+    </row>
+    <row r="236" spans="1:12">
+      <c r="A236" s="16"/>
+      <c r="B236" s="15"/>
+      <c r="C236" s="12"/>
+      <c r="D236" s="19"/>
+      <c r="E236" s="12"/>
+      <c r="F236" s="12"/>
+      <c r="G236" s="14"/>
+      <c r="I236" s="12"/>
+      <c r="J236" s="13"/>
+    </row>
+    <row r="237" spans="1:12">
+      <c r="A237" s="16"/>
+      <c r="B237" s="15"/>
+      <c r="C237" s="12"/>
+      <c r="D237" s="19"/>
+      <c r="E237" s="12"/>
+      <c r="F237" s="12"/>
+      <c r="G237" s="14"/>
+      <c r="I237" s="12"/>
+      <c r="J237" s="13"/>
+    </row>
+    <row r="238" spans="1:12">
+      <c r="A238" s="16"/>
+      <c r="B238" s="15"/>
+      <c r="C238" s="12"/>
+      <c r="D238" s="19"/>
+      <c r="E238" s="12"/>
+      <c r="F238" s="12"/>
+      <c r="G238" s="14"/>
+      <c r="I238" s="12"/>
+      <c r="J238" s="13"/>
+    </row>
+    <row r="239" spans="1:12">
+      <c r="A239" s="16"/>
+      <c r="B239" s="15"/>
+      <c r="C239" s="12"/>
+      <c r="D239" s="19"/>
+      <c r="E239" s="12"/>
+      <c r="F239" s="12"/>
+      <c r="G239" s="14"/>
+      <c r="I239" s="12"/>
+      <c r="J239" s="13"/>
+      <c r="L239" s="23"/>
+    </row>
+    <row r="240" spans="1:12">
+      <c r="A240" s="16"/>
+      <c r="B240" s="15"/>
+      <c r="C240" s="12"/>
+      <c r="D240" s="19"/>
+      <c r="E240" s="12"/>
+      <c r="F240" s="12"/>
+      <c r="G240" s="14"/>
+      <c r="I240" s="12"/>
+      <c r="J240" s="13"/>
+      <c r="L240" s="23"/>
+    </row>
+    <row r="241" spans="1:10">
+      <c r="A241" s="16"/>
+      <c r="B241" s="15"/>
+      <c r="C241" s="12"/>
+      <c r="D241" s="19"/>
+      <c r="E241" s="12"/>
+      <c r="F241" s="12"/>
+      <c r="G241" s="14"/>
+      <c r="I241" s="12"/>
+      <c r="J241" s="13"/>
+    </row>
+    <row r="242" spans="1:10">
+      <c r="A242" s="16"/>
+      <c r="B242" s="15"/>
+      <c r="C242" s="12"/>
+      <c r="D242" s="19"/>
+      <c r="E242" s="12"/>
+      <c r="F242" s="12"/>
+      <c r="G242" s="14"/>
+      <c r="I242" s="12"/>
+      <c r="J242" s="13"/>
+    </row>
+    <row r="243" spans="1:10">
+      <c r="A243" s="16"/>
+      <c r="B243" s="15"/>
+      <c r="C243" s="12"/>
+      <c r="D243" s="19"/>
+      <c r="E243" s="12"/>
+      <c r="F243" s="12"/>
+      <c r="G243" s="14"/>
+      <c r="I243" s="12"/>
+      <c r="J243" s="13"/>
+    </row>
+    <row r="244" spans="1:10">
+      <c r="A244" s="16"/>
+      <c r="B244" s="15"/>
+      <c r="C244" s="12"/>
+      <c r="D244" s="19"/>
+      <c r="E244" s="12"/>
+      <c r="F244" s="12"/>
+      <c r="G244" s="14"/>
+      <c r="I244" s="12"/>
+      <c r="J244" s="13"/>
+    </row>
+    <row r="245" spans="1:10">
+      <c r="A245" s="16"/>
+      <c r="B245" s="15"/>
+      <c r="C245" s="12"/>
+      <c r="D245" s="19"/>
+      <c r="E245" s="12"/>
+      <c r="F245" s="12"/>
+      <c r="G245" s="14"/>
+      <c r="I245" s="12"/>
+      <c r="J245" s="13"/>
+    </row>
+    <row r="246" spans="1:10">
+      <c r="A246" s="16"/>
+      <c r="B246" s="15"/>
+      <c r="C246" s="12"/>
+      <c r="D246" s="19"/>
+      <c r="E246" s="12"/>
+      <c r="F246" s="12"/>
+      <c r="G246" s="14"/>
+      <c r="I246" s="12"/>
+      <c r="J246" s="13"/>
+    </row>
+    <row r="247" spans="1:10">
+      <c r="A247" s="16"/>
+      <c r="B247" s="15"/>
+      <c r="C247" s="12"/>
+      <c r="D247" s="19"/>
+      <c r="E247" s="12"/>
+      <c r="F247" s="12"/>
+      <c r="G247" s="14"/>
+      <c r="I247" s="12"/>
+      <c r="J247" s="13"/>
+    </row>
+    <row r="248" spans="1:10">
+      <c r="A248" s="16"/>
+      <c r="B248" s="15"/>
+      <c r="C248" s="12"/>
+      <c r="D248" s="19"/>
+      <c r="E248" s="12"/>
+      <c r="F248" s="12"/>
+      <c r="G248" s="14"/>
+      <c r="I248" s="12"/>
+      <c r="J248" s="13"/>
+    </row>
+    <row r="249" spans="1:10">
+      <c r="A249" s="16"/>
+      <c r="B249" s="15"/>
+      <c r="C249" s="12"/>
+      <c r="D249" s="19"/>
+      <c r="E249" s="12"/>
+      <c r="F249" s="12"/>
+      <c r="G249" s="14"/>
+      <c r="I249" s="12"/>
+      <c r="J249" s="13"/>
+    </row>
+    <row r="250" spans="1:10">
+      <c r="A250" s="16"/>
+      <c r="B250" s="15"/>
+      <c r="C250" s="12"/>
+      <c r="D250" s="19"/>
+      <c r="E250" s="12"/>
+      <c r="F250" s="12"/>
+      <c r="G250" s="14"/>
+      <c r="I250" s="12"/>
+      <c r="J250" s="13"/>
+    </row>
+    <row r="251" spans="1:10">
+      <c r="A251" s="16"/>
+      <c r="B251" s="15"/>
+      <c r="C251" s="12"/>
+      <c r="D251" s="19"/>
+      <c r="E251" s="12"/>
+      <c r="F251" s="12"/>
+      <c r="G251" s="14"/>
+      <c r="I251" s="12"/>
+      <c r="J251" s="13"/>
+    </row>
+    <row r="252" spans="1:10">
+      <c r="A252" s="16"/>
+      <c r="B252" s="15"/>
+      <c r="C252" s="12"/>
+      <c r="D252" s="19"/>
+      <c r="E252" s="12"/>
+      <c r="F252" s="12"/>
+      <c r="G252" s="14"/>
+      <c r="I252" s="12"/>
+      <c r="J252" s="13"/>
+    </row>
+    <row r="253" spans="1:10">
+      <c r="A253" s="16"/>
+      <c r="B253" s="15"/>
+      <c r="C253" s="12"/>
+      <c r="D253" s="19"/>
+      <c r="E253" s="12"/>
+      <c r="F253" s="12"/>
+      <c r="G253" s="14"/>
+      <c r="I253" s="12"/>
+      <c r="J253" s="13"/>
+    </row>
+    <row r="254" spans="1:10">
+      <c r="A254" s="16"/>
+      <c r="B254" s="15"/>
+      <c r="C254" s="12"/>
+      <c r="D254" s="19"/>
+      <c r="E254" s="12"/>
+      <c r="F254" s="12"/>
+      <c r="G254" s="14"/>
+      <c r="I254" s="12"/>
+      <c r="J254" s="13"/>
+    </row>
+    <row r="255" spans="1:10">
+      <c r="A255" s="16"/>
+      <c r="B255" s="15"/>
+      <c r="C255" s="12"/>
+      <c r="D255" s="19"/>
+      <c r="E255" s="12"/>
+      <c r="F255" s="12"/>
+      <c r="G255" s="14"/>
+      <c r="I255" s="12"/>
+      <c r="J255" s="13"/>
+    </row>
+    <row r="256" spans="1:10">
+      <c r="A256" s="16"/>
+      <c r="B256" s="15"/>
+      <c r="C256" s="12"/>
+      <c r="D256" s="19"/>
+      <c r="E256" s="12"/>
+      <c r="F256" s="12"/>
+      <c r="G256" s="14"/>
+      <c r="I256" s="12"/>
+      <c r="J256" s="13"/>
+    </row>
+    <row r="257" spans="1:10">
+      <c r="A257" s="16"/>
+      <c r="B257" s="15"/>
+      <c r="C257" s="12"/>
+      <c r="D257" s="19"/>
+      <c r="E257" s="12"/>
+      <c r="F257" s="12"/>
+      <c r="G257" s="14"/>
+      <c r="I257" s="12"/>
+      <c r="J257" s="13"/>
+    </row>
+    <row r="258" spans="1:10">
+      <c r="A258" s="16"/>
+      <c r="B258" s="15"/>
+      <c r="C258" s="12"/>
+      <c r="D258" s="19"/>
+      <c r="E258" s="12"/>
+      <c r="F258" s="12"/>
+      <c r="G258" s="14"/>
+      <c r="I258" s="12"/>
+      <c r="J258" s="13"/>
+    </row>
+    <row r="259" spans="1:10">
+      <c r="A259" s="16"/>
+      <c r="B259" s="15"/>
+      <c r="C259" s="12"/>
+      <c r="D259" s="19"/>
+      <c r="E259" s="12"/>
+      <c r="F259" s="12"/>
+      <c r="G259" s="14"/>
+      <c r="I259" s="12"/>
+      <c r="J259" s="13"/>
+    </row>
+    <row r="260" spans="1:10">
+      <c r="A260" s="16"/>
+      <c r="B260" s="15"/>
+      <c r="C260" s="12"/>
+      <c r="D260" s="19"/>
+      <c r="E260" s="12"/>
+      <c r="F260" s="12"/>
+      <c r="G260" s="14"/>
+      <c r="I260" s="12"/>
+      <c r="J260" s="13"/>
+    </row>
+    <row r="261" spans="1:10">
+      <c r="A261" s="16"/>
+      <c r="B261" s="15"/>
+      <c r="C261" s="12"/>
+      <c r="D261" s="19"/>
+      <c r="E261" s="12"/>
+      <c r="F261" s="12"/>
+      <c r="G261" s="14"/>
+      <c r="I261" s="12"/>
+      <c r="J261" s="13"/>
+    </row>
+    <row r="262" spans="1:10">
+      <c r="A262" s="16"/>
+      <c r="B262" s="15"/>
+      <c r="C262" s="12"/>
+      <c r="D262" s="19"/>
+      <c r="E262" s="12"/>
+      <c r="F262" s="12"/>
+      <c r="G262" s="14"/>
+      <c r="I262" s="12"/>
+      <c r="J262" s="13"/>
+    </row>
+    <row r="263" spans="1:10">
+      <c r="A263" s="16"/>
+      <c r="B263" s="15"/>
+      <c r="C263" s="12"/>
+      <c r="D263" s="19"/>
+      <c r="E263" s="12"/>
+      <c r="F263" s="12"/>
+      <c r="G263" s="14"/>
+      <c r="I263" s="12"/>
+      <c r="J263" s="13"/>
+    </row>
+    <row r="264" spans="1:10">
+      <c r="A264" s="16"/>
+      <c r="B264" s="15"/>
+      <c r="C264" s="12"/>
+      <c r="D264" s="19"/>
+      <c r="E264" s="12"/>
+      <c r="F264" s="12"/>
+      <c r="G264" s="14"/>
+      <c r="I264" s="12"/>
+      <c r="J264" s="13"/>
+    </row>
+    <row r="265" spans="1:10">
+      <c r="A265" s="16"/>
+      <c r="B265" s="15"/>
+      <c r="C265" s="12"/>
+      <c r="D265" s="19"/>
+      <c r="E265" s="12"/>
+      <c r="F265" s="12"/>
+      <c r="G265" s="14"/>
+      <c r="I265" s="12"/>
+      <c r="J265" s="13"/>
+    </row>
+    <row r="266" spans="1:10">
+      <c r="A266" s="16"/>
+      <c r="B266" s="15"/>
+      <c r="C266" s="12"/>
+      <c r="D266" s="19"/>
+      <c r="E266" s="12"/>
+      <c r="F266" s="12"/>
+      <c r="G266" s="14"/>
+      <c r="I266" s="12"/>
+      <c r="J266" s="13"/>
+    </row>
+    <row r="267" spans="1:10">
+      <c r="A267" s="16"/>
+      <c r="B267" s="15"/>
+      <c r="C267" s="12"/>
+      <c r="D267" s="19"/>
+      <c r="E267" s="12"/>
+      <c r="F267" s="12"/>
+      <c r="G267" s="14"/>
+      <c r="I267" s="12"/>
+      <c r="J267" s="13"/>
+    </row>
+    <row r="268" spans="1:10">
+      <c r="A268" s="16"/>
+      <c r="B268" s="15"/>
+      <c r="C268" s="12"/>
+      <c r="D268" s="19"/>
+      <c r="E268" s="12"/>
+      <c r="F268" s="12"/>
+      <c r="G268" s="14"/>
+      <c r="I268" s="12"/>
+      <c r="J268" s="13"/>
+    </row>
+    <row r="269" spans="1:10">
+      <c r="A269" s="16"/>
+      <c r="B269" s="15"/>
+      <c r="C269" s="12"/>
+      <c r="D269" s="19"/>
+      <c r="E269" s="12"/>
+      <c r="F269" s="12"/>
+      <c r="G269" s="14"/>
+      <c r="I269" s="12"/>
+      <c r="J269" s="13"/>
+    </row>
+    <row r="270" spans="1:10">
+      <c r="A270" s="16"/>
+      <c r="B270" s="15"/>
+      <c r="C270" s="12"/>
+      <c r="D270" s="19"/>
+      <c r="E270" s="12"/>
+      <c r="F270" s="12"/>
+      <c r="G270" s="14"/>
+      <c r="I270" s="12"/>
+      <c r="J270" s="13"/>
+    </row>
+    <row r="271" spans="1:10">
+      <c r="A271" s="16"/>
+      <c r="B271" s="15"/>
+      <c r="C271" s="12"/>
+      <c r="D271" s="19"/>
+      <c r="E271" s="12"/>
+      <c r="F271" s="12"/>
+      <c r="G271" s="14"/>
+      <c r="I271" s="12"/>
+      <c r="J271" s="13"/>
+    </row>
+    <row r="272" spans="1:10">
+      <c r="A272" s="16"/>
+      <c r="B272" s="15"/>
+      <c r="C272" s="12"/>
+      <c r="D272" s="19"/>
+      <c r="E272" s="12"/>
+      <c r="F272" s="12"/>
+      <c r="G272" s="14"/>
+      <c r="I272" s="12"/>
+      <c r="J272" s="13"/>
+    </row>
+    <row r="273" spans="1:10">
+      <c r="A273" s="16"/>
+      <c r="B273" s="15"/>
+      <c r="C273" s="12"/>
+      <c r="D273" s="19"/>
+      <c r="E273" s="12"/>
+      <c r="F273" s="12"/>
+      <c r="G273" s="14"/>
+      <c r="I273" s="12"/>
+      <c r="J273" s="13"/>
+    </row>
+    <row r="274" spans="1:10">
+      <c r="A274" s="16"/>
+      <c r="B274" s="15"/>
+      <c r="C274" s="12"/>
+      <c r="D274" s="19"/>
+      <c r="E274" s="12"/>
+      <c r="F274" s="12"/>
+      <c r="G274" s="14"/>
+      <c r="I274" s="12"/>
+      <c r="J274" s="13"/>
+    </row>
+    <row r="275" spans="1:10">
+      <c r="A275" s="16"/>
+      <c r="B275" s="15"/>
+      <c r="C275" s="12"/>
+      <c r="D275" s="19"/>
+      <c r="E275" s="12"/>
+      <c r="F275" s="12"/>
+      <c r="G275" s="14"/>
+      <c r="I275" s="12"/>
+      <c r="J275" s="13"/>
+    </row>
+    <row r="276" spans="1:10">
+      <c r="A276" s="16"/>
+      <c r="B276" s="15"/>
+      <c r="C276" s="12"/>
+      <c r="D276" s="19"/>
+      <c r="E276" s="12"/>
+      <c r="F276" s="12"/>
+      <c r="G276" s="14"/>
+      <c r="I276" s="12"/>
+      <c r="J276" s="13"/>
+    </row>
+    <row r="277" spans="1:10">
+      <c r="A277" s="16"/>
+      <c r="B277" s="15"/>
+      <c r="C277" s="12"/>
+      <c r="D277" s="19"/>
+      <c r="E277" s="12"/>
+      <c r="F277" s="12"/>
+      <c r="G277" s="14"/>
+      <c r="I277" s="12"/>
+      <c r="J277" s="13"/>
+    </row>
+    <row r="278" spans="1:10">
+      <c r="A278" s="16"/>
+      <c r="B278" s="15"/>
+      <c r="C278" s="12"/>
+      <c r="D278" s="19"/>
+      <c r="E278" s="12"/>
+      <c r="F278" s="12"/>
+      <c r="G278" s="14"/>
+      <c r="I278" s="12"/>
+      <c r="J278" s="13"/>
+    </row>
+    <row r="279" spans="1:10">
+      <c r="A279" s="16"/>
+      <c r="B279" s="15"/>
+      <c r="C279" s="12"/>
+      <c r="D279" s="19"/>
+      <c r="E279" s="12"/>
+      <c r="F279" s="12"/>
+      <c r="G279" s="14"/>
+      <c r="I279" s="12"/>
+      <c r="J279" s="13"/>
+    </row>
+    <row r="280" spans="1:10">
+      <c r="A280" s="16"/>
+      <c r="B280" s="15"/>
+      <c r="C280" s="12"/>
+      <c r="D280" s="19"/>
+      <c r="E280" s="12"/>
+      <c r="F280" s="12"/>
+      <c r="G280" s="14"/>
+      <c r="I280" s="12"/>
+      <c r="J280" s="13"/>
+    </row>
+    <row r="281" spans="1:10">
+      <c r="A281" s="16"/>
+      <c r="B281" s="15"/>
+      <c r="C281" s="12"/>
+      <c r="D281" s="19"/>
+      <c r="E281" s="12"/>
+      <c r="F281" s="12"/>
+      <c r="G281" s="14"/>
+      <c r="I281" s="12"/>
+      <c r="J281" s="13"/>
+    </row>
+    <row r="282" spans="1:10">
+      <c r="A282" s="16"/>
+      <c r="B282" s="15"/>
+      <c r="C282" s="12"/>
+      <c r="D282" s="19"/>
+      <c r="E282" s="12"/>
+      <c r="F282" s="12"/>
+      <c r="G282" s="14"/>
+      <c r="I282" s="12"/>
+      <c r="J282" s="13"/>
+    </row>
+    <row r="283" spans="1:10">
+      <c r="A283" s="16"/>
+      <c r="B283" s="15"/>
+      <c r="C283" s="12"/>
+      <c r="D283" s="19"/>
+      <c r="E283" s="12"/>
+      <c r="F283" s="12"/>
+      <c r="G283" s="14"/>
+      <c r="I283" s="12"/>
+      <c r="J283" s="13"/>
+    </row>
+    <row r="284" spans="1:10">
+      <c r="A284" s="16"/>
+      <c r="B284" s="15"/>
+      <c r="C284" s="12"/>
+      <c r="D284" s="19"/>
+      <c r="E284" s="12"/>
+      <c r="F284" s="12"/>
+      <c r="G284" s="14"/>
+      <c r="I284" s="12"/>
+      <c r="J284" s="13"/>
+    </row>
+    <row r="285" spans="1:10">
+      <c r="A285" s="16"/>
+      <c r="B285" s="15"/>
+      <c r="C285" s="12"/>
+      <c r="D285" s="19"/>
+      <c r="E285" s="12"/>
+      <c r="F285" s="12"/>
+      <c r="G285" s="14"/>
+      <c r="I285" s="12"/>
+      <c r="J285" s="13"/>
+    </row>
+    <row r="286" spans="1:10">
+      <c r="A286" s="16"/>
+      <c r="B286" s="15"/>
+      <c r="C286" s="12"/>
+      <c r="D286" s="19"/>
+      <c r="E286" s="12"/>
+      <c r="F286" s="12"/>
+      <c r="G286" s="14"/>
+      <c r="I286" s="12"/>
+      <c r="J286" s="13"/>
+    </row>
+    <row r="287" spans="1:10">
+      <c r="A287" s="16"/>
+      <c r="B287" s="15"/>
+      <c r="C287" s="12"/>
+      <c r="D287" s="19"/>
+      <c r="E287" s="12"/>
+      <c r="F287" s="12"/>
+      <c r="G287" s="14"/>
+      <c r="I287" s="12"/>
+      <c r="J287" s="13"/>
+    </row>
+    <row r="288" spans="1:10">
+      <c r="A288" s="16"/>
+      <c r="B288" s="15"/>
+      <c r="C288" s="12"/>
+      <c r="D288" s="19"/>
+      <c r="E288" s="12"/>
+      <c r="F288" s="12"/>
+      <c r="G288" s="14"/>
+      <c r="I288" s="12"/>
+      <c r="J288" s="13"/>
+    </row>
+    <row r="289" spans="1:10">
+      <c r="A289" s="16"/>
+      <c r="B289" s="15"/>
+      <c r="C289" s="12"/>
+      <c r="D289" s="19"/>
+      <c r="E289" s="12"/>
+      <c r="F289" s="12"/>
+      <c r="G289" s="14"/>
+      <c r="I289" s="12"/>
+      <c r="J289" s="13"/>
+    </row>
+    <row r="290" spans="1:10">
+      <c r="A290" s="16"/>
+      <c r="B290" s="15"/>
+      <c r="C290" s="12"/>
+      <c r="D290" s="19"/>
+      <c r="E290" s="12"/>
+      <c r="F290" s="12"/>
+      <c r="G290" s="14"/>
+      <c r="I290" s="12"/>
+      <c r="J290" s="13"/>
+    </row>
+    <row r="291" spans="1:10">
+      <c r="A291" s="16"/>
+      <c r="B291" s="15"/>
+      <c r="C291" s="12"/>
+      <c r="D291" s="19"/>
+      <c r="E291" s="12"/>
+      <c r="F291" s="12"/>
+      <c r="G291" s="14"/>
+      <c r="I291" s="12"/>
+      <c r="J291" s="13"/>
+    </row>
+    <row r="292" spans="1:10">
+      <c r="A292" s="16"/>
+      <c r="B292" s="15"/>
+      <c r="C292" s="12"/>
+      <c r="D292" s="19"/>
+      <c r="E292" s="12"/>
+      <c r="F292" s="12"/>
+      <c r="G292" s="14"/>
+      <c r="I292" s="12"/>
+      <c r="J292" s="13"/>
+    </row>
+    <row r="293" spans="1:10">
+      <c r="A293" s="16"/>
+      <c r="B293" s="15"/>
+      <c r="C293" s="12"/>
+      <c r="D293" s="19"/>
+      <c r="E293" s="12"/>
+      <c r="F293" s="12"/>
+      <c r="G293" s="14"/>
+      <c r="I293" s="12"/>
+      <c r="J293" s="13"/>
+    </row>
+    <row r="294" spans="1:10">
+      <c r="A294" s="16"/>
+      <c r="B294" s="15"/>
+      <c r="C294" s="12"/>
+      <c r="D294" s="19"/>
+      <c r="E294" s="12"/>
+      <c r="F294" s="12"/>
+      <c r="G294" s="14"/>
+      <c r="I294" s="12"/>
+      <c r="J294" s="13"/>
+    </row>
+    <row r="295" spans="1:10">
+      <c r="A295" s="16"/>
+      <c r="B295" s="15"/>
+      <c r="C295" s="12"/>
+      <c r="D295" s="19"/>
+      <c r="E295" s="12"/>
+      <c r="F295" s="12"/>
+      <c r="G295" s="14"/>
+      <c r="I295" s="12"/>
+      <c r="J295" s="13"/>
+    </row>
+    <row r="296" spans="1:10">
+      <c r="A296" s="16"/>
+      <c r="B296" s="15"/>
+      <c r="C296" s="12"/>
+      <c r="D296" s="19"/>
+      <c r="E296" s="12"/>
+      <c r="F296" s="12"/>
+      <c r="G296" s="14"/>
+      <c r="I296" s="12"/>
+      <c r="J296" s="13"/>
+    </row>
+    <row r="297" spans="1:10">
+      <c r="A297" s="16"/>
+      <c r="B297" s="15"/>
+      <c r="C297" s="12"/>
+      <c r="D297" s="19"/>
+      <c r="E297" s="12"/>
+      <c r="F297" s="12"/>
+      <c r="G297" s="14"/>
+      <c r="I297" s="12"/>
+      <c r="J297" s="13"/>
+    </row>
+    <row r="298" spans="1:10">
+      <c r="A298" s="16"/>
+      <c r="B298" s="15"/>
+      <c r="C298" s="12"/>
+      <c r="D298" s="19"/>
+      <c r="E298" s="12"/>
+      <c r="F298" s="12"/>
+      <c r="G298" s="14"/>
+      <c r="I298" s="12"/>
+      <c r="J298" s="13"/>
+    </row>
+    <row r="299" spans="1:10">
+      <c r="A299" s="16"/>
+      <c r="B299" s="15"/>
+      <c r="C299" s="12"/>
+      <c r="D299" s="19"/>
+      <c r="E299" s="12"/>
+      <c r="F299" s="12"/>
+      <c r="G299" s="14"/>
+      <c r="I299" s="12"/>
+      <c r="J299" s="13"/>
+    </row>
+    <row r="300" spans="1:10">
+      <c r="A300" s="16"/>
+      <c r="B300" s="15"/>
+      <c r="C300" s="12"/>
+      <c r="D300" s="19"/>
+      <c r="E300" s="12"/>
+      <c r="F300" s="12"/>
+      <c r="G300" s="14"/>
+      <c r="I300" s="12"/>
+      <c r="J300" s="13"/>
+    </row>
+    <row r="301" spans="1:10">
+      <c r="A301" s="16"/>
+      <c r="B301" s="15"/>
+      <c r="C301" s="12"/>
+      <c r="D301" s="19"/>
+      <c r="E301" s="12"/>
+      <c r="F301" s="12"/>
+      <c r="G301" s="14"/>
+      <c r="I301" s="12"/>
+      <c r="J301" s="13"/>
+    </row>
+    <row r="302" spans="1:10">
+      <c r="A302" s="16"/>
+      <c r="B302" s="15"/>
+      <c r="C302" s="12"/>
+      <c r="D302" s="19"/>
+      <c r="E302" s="12"/>
+      <c r="F302" s="12"/>
+      <c r="G302" s="14"/>
+      <c r="I302" s="12"/>
+      <c r="J302" s="13"/>
+    </row>
+    <row r="303" spans="1:10">
+      <c r="A303" s="16"/>
+      <c r="B303" s="15"/>
+      <c r="C303" s="12"/>
+      <c r="D303" s="19"/>
+      <c r="E303" s="12"/>
+      <c r="F303" s="12"/>
+      <c r="G303" s="14"/>
+      <c r="I303" s="12"/>
+      <c r="J303" s="13"/>
+    </row>
+    <row r="304" spans="1:10">
+      <c r="A304" s="16"/>
+      <c r="B304" s="15"/>
+      <c r="C304" s="12"/>
+      <c r="D304" s="19"/>
+      <c r="E304" s="12"/>
+      <c r="F304" s="12"/>
+      <c r="G304" s="14"/>
+      <c r="I304" s="12"/>
+      <c r="J304" s="13"/>
+    </row>
+    <row r="305" spans="1:10">
+      <c r="A305" s="16"/>
+      <c r="B305" s="15"/>
+      <c r="C305" s="12"/>
+      <c r="D305" s="19"/>
+      <c r="E305" s="12"/>
+      <c r="F305" s="12"/>
+      <c r="G305" s="14"/>
+      <c r="I305" s="12"/>
+      <c r="J305" s="13"/>
+    </row>
+    <row r="306" spans="1:10">
+      <c r="A306" s="16"/>
+      <c r="B306" s="15"/>
+      <c r="C306" s="12"/>
+      <c r="D306" s="19"/>
+      <c r="E306" s="12"/>
+      <c r="F306" s="12"/>
+      <c r="G306" s="14"/>
+      <c r="I306" s="12"/>
+      <c r="J306" s="13"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H120">
-    <cfRule type="expression" dxfId="4" priority="1">
+  <conditionalFormatting sqref="H2:H229">
+    <cfRule type="expression" dxfId="9" priority="6">
       <formula>H2="Alta"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="8" priority="7">
       <formula>H2="Media"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>H2="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J120">
-    <cfRule type="expression" dxfId="1" priority="4">
+  <conditionalFormatting sqref="J2:J116">
+    <cfRule type="expression" dxfId="6" priority="9">
       <formula>J2="Ejecutado"</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="5" priority="10">
+      <formula>J2="Pendiente"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H230:H306">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>H230="Alta"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>H230="Media"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>H230="Baja"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J230:J306">
+    <cfRule type="expression" dxfId="1" priority="4">
+      <formula>J230="Ejecutado"</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="0" priority="5">
-      <formula>J2="Pendiente"</formula>
+      <formula>J230="Pendiente"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5185,14 +9740,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="5" t="s">

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71DB78F-D966-4357-A405-3E500AA277F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4124F7-07E4-4EEC-A451-069A894452AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVENTOS" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2334" uniqueCount="279">
   <si>
     <t>Fecha</t>
   </si>
@@ -873,6 +873,51 @@
   </si>
   <si>
     <t>Requererimientos :Punto de luz. / Zona de trivia: Auditorio / 4 mesas. / unto de luz.</t>
+  </si>
+  <si>
+    <t>Ensayo  elenco de danzas</t>
+  </si>
+  <si>
+    <t>Auditorio pabellon O</t>
+  </si>
+  <si>
+    <t>Retirar el mobiliario y que el espacio esté limpio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FACULTAD DE INGENERIA </t>
+  </si>
+  <si>
+    <t>Bienvenida de Cachimbos 2026-2</t>
+  </si>
+  <si>
+    <t>3 micrófonos inalámbricos con baterías/pilas cargadas / 2 sillones para el estrado / 1 mesa con mantel para la recepción de participantes /Asistencia técnica durante el evento.</t>
+  </si>
+  <si>
+    <t>Cinergia - Taller Innovación y diseño de soluciones</t>
+  </si>
+  <si>
+    <t>2 micrófonos inalámbricos con baterías/pilas cargadas / 2 sillones para el estrado / 1 mesa con mantel para la recepción de participantes /Asistencia técnica durante el evento.</t>
+  </si>
+  <si>
+    <t>Cinergia Bootcamp</t>
+  </si>
+  <si>
+    <t>Cinergia Talks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no indica hora </t>
+  </si>
+  <si>
+    <t>Administración de Empresas</t>
+  </si>
+  <si>
+    <t>4 micrófonos inalámbricos con baterías / pilas cargadas /  1 mesa con mantel para la recepción de participantes /  Asistencia técnica durante el evento.</t>
+  </si>
+  <si>
+    <t>2 micrófonos inalámbricos con baterías / pilas cargadas /  1 mesa con mantel para la recepción de participantes / Asistencia técnica durante el evento</t>
+  </si>
+  <si>
+    <t>50 sillas / Cuatro (4) mesas (2 en la parte externa del auditorio para recepción y coffee break y 2 a la interna para una dinámica) /  Cuatro (4) sillas de conversatorio para ponentes / Una (1) mesa de centro para poner las aguas de los ponentes.</t>
   </si>
 </sst>
 </file>
@@ -989,7 +1034,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1047,71 +1092,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF92400E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF166534"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDCFCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF166534"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDCFCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF92400E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF991B1B"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <b/>
@@ -1189,7 +1182,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Área Solicitante"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="N° OT" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="N° OT" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Evento / Actividad"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ubicación"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Requerimientos"/>
@@ -1350,7 +1343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L306"/>
+  <dimension ref="A1:L301"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1358,7 +1351,7 @@
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" style="20" customWidth="1"/>
     <col min="5" max="6" width="34" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
+    <col min="7" max="7" width="81.625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
@@ -2660,7 +2653,7 @@
         <v>105</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="H41" t="s">
         <v>17</v>
@@ -2692,7 +2685,7 @@
         <v>105</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
@@ -2724,7 +2717,7 @@
         <v>105</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
@@ -2756,7 +2749,7 @@
         <v>105</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
@@ -2788,7 +2781,7 @@
         <v>105</v>
       </c>
       <c r="G45" s="14" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="H45" t="s">
         <v>17</v>
@@ -8719,7 +8712,7 @@
       <c r="J230" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="L230" s="23"/>
+      <c r="L230" s="21"/>
     </row>
     <row r="231" spans="1:12" ht="99.75">
       <c r="A231" s="16"/>
@@ -8806,71 +8799,197 @@
       </c>
     </row>
     <row r="234" spans="1:12">
-      <c r="A234" s="16"/>
-      <c r="B234" s="15"/>
-      <c r="C234" s="12"/>
-      <c r="D234" s="19"/>
-      <c r="E234" s="12"/>
-      <c r="F234" s="12"/>
-      <c r="G234" s="14"/>
-      <c r="I234" s="12"/>
-      <c r="J234" s="13"/>
-    </row>
-    <row r="235" spans="1:12">
-      <c r="A235" s="16"/>
-      <c r="B235" s="15"/>
-      <c r="C235" s="12"/>
-      <c r="D235" s="19"/>
-      <c r="E235" s="12"/>
-      <c r="F235" s="12"/>
-      <c r="G235" s="14"/>
-      <c r="I235" s="12"/>
-      <c r="J235" s="13"/>
-    </row>
-    <row r="236" spans="1:12">
-      <c r="A236" s="16"/>
-      <c r="B236" s="15"/>
-      <c r="C236" s="12"/>
-      <c r="D236" s="19"/>
-      <c r="E236" s="12"/>
-      <c r="F236" s="12"/>
-      <c r="G236" s="14"/>
-      <c r="I236" s="12"/>
-      <c r="J236" s="13"/>
-    </row>
-    <row r="237" spans="1:12">
-      <c r="A237" s="16"/>
-      <c r="B237" s="15"/>
-      <c r="C237" s="12"/>
-      <c r="D237" s="19"/>
-      <c r="E237" s="12"/>
-      <c r="F237" s="12"/>
-      <c r="G237" s="14"/>
-      <c r="I237" s="12"/>
-      <c r="J237" s="13"/>
-    </row>
-    <row r="238" spans="1:12">
-      <c r="A238" s="16"/>
-      <c r="B238" s="15"/>
-      <c r="C238" s="12"/>
-      <c r="D238" s="19"/>
-      <c r="E238" s="12"/>
-      <c r="F238" s="12"/>
-      <c r="G238" s="14"/>
-      <c r="I238" s="12"/>
-      <c r="J238" s="13"/>
-    </row>
-    <row r="239" spans="1:12">
-      <c r="A239" s="16"/>
-      <c r="B239" s="15"/>
-      <c r="C239" s="12"/>
-      <c r="D239" s="19"/>
-      <c r="E239" s="12"/>
-      <c r="F239" s="12"/>
-      <c r="G239" s="14"/>
-      <c r="I239" s="12"/>
-      <c r="J239" s="13"/>
-      <c r="L239" s="23"/>
+      <c r="A234" s="16">
+        <v>46195</v>
+      </c>
+      <c r="B234" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C234" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D234" s="19">
+        <v>9846</v>
+      </c>
+      <c r="E234" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="F234" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="G234" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="H234" t="s">
+        <v>17</v>
+      </c>
+      <c r="I234" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J234" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" ht="57">
+      <c r="A235" s="16">
+        <v>46197</v>
+      </c>
+      <c r="B235" s="15">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C235" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D235" s="19">
+        <v>9850</v>
+      </c>
+      <c r="E235" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="F235" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="G235" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="H235" t="s">
+        <v>17</v>
+      </c>
+      <c r="I235" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J235" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" ht="57">
+      <c r="A236" s="16">
+        <v>46267</v>
+      </c>
+      <c r="B236" s="15">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C236" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D236" s="19">
+        <v>9847</v>
+      </c>
+      <c r="E236" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="F236" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="G236" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="H236" t="s">
+        <v>17</v>
+      </c>
+      <c r="I236" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J236" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" ht="28.5">
+      <c r="A237" s="16">
+        <v>46276</v>
+      </c>
+      <c r="B237" s="15">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C237" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D237" s="19">
+        <v>9849</v>
+      </c>
+      <c r="E237" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="F237" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="G237" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="H237" t="s">
+        <v>17</v>
+      </c>
+      <c r="I237" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J237" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" ht="28.5">
+      <c r="A238" s="16">
+        <v>46297</v>
+      </c>
+      <c r="B238" s="15">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C238" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D238" s="19">
+        <v>9848</v>
+      </c>
+      <c r="E238" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="F238" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="G238" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="H238" t="s">
+        <v>17</v>
+      </c>
+      <c r="I238" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J238" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="L238" s="21"/>
+    </row>
+    <row r="239" spans="1:12" s="8" customFormat="1" ht="42.75">
+      <c r="A239" s="24">
+        <v>46297</v>
+      </c>
+      <c r="B239" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="C239" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D239" s="19">
+        <v>9840</v>
+      </c>
+      <c r="E239" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="F239" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="G239" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="H239" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I239" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J239" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="240" spans="1:12">
       <c r="A240" s="16"/>
@@ -8882,7 +9001,6 @@
       <c r="G240" s="14"/>
       <c r="I240" s="12"/>
       <c r="J240" s="13"/>
-      <c r="L240" s="23"/>
     </row>
     <row r="241" spans="1:10">
       <c r="A241" s="16"/>
@@ -9555,98 +9673,24 @@
       <c r="I301" s="12"/>
       <c r="J301" s="13"/>
     </row>
-    <row r="302" spans="1:10">
-      <c r="A302" s="16"/>
-      <c r="B302" s="15"/>
-      <c r="C302" s="12"/>
-      <c r="D302" s="19"/>
-      <c r="E302" s="12"/>
-      <c r="F302" s="12"/>
-      <c r="G302" s="14"/>
-      <c r="I302" s="12"/>
-      <c r="J302" s="13"/>
-    </row>
-    <row r="303" spans="1:10">
-      <c r="A303" s="16"/>
-      <c r="B303" s="15"/>
-      <c r="C303" s="12"/>
-      <c r="D303" s="19"/>
-      <c r="E303" s="12"/>
-      <c r="F303" s="12"/>
-      <c r="G303" s="14"/>
-      <c r="I303" s="12"/>
-      <c r="J303" s="13"/>
-    </row>
-    <row r="304" spans="1:10">
-      <c r="A304" s="16"/>
-      <c r="B304" s="15"/>
-      <c r="C304" s="12"/>
-      <c r="D304" s="19"/>
-      <c r="E304" s="12"/>
-      <c r="F304" s="12"/>
-      <c r="G304" s="14"/>
-      <c r="I304" s="12"/>
-      <c r="J304" s="13"/>
-    </row>
-    <row r="305" spans="1:10">
-      <c r="A305" s="16"/>
-      <c r="B305" s="15"/>
-      <c r="C305" s="12"/>
-      <c r="D305" s="19"/>
-      <c r="E305" s="12"/>
-      <c r="F305" s="12"/>
-      <c r="G305" s="14"/>
-      <c r="I305" s="12"/>
-      <c r="J305" s="13"/>
-    </row>
-    <row r="306" spans="1:10">
-      <c r="A306" s="16"/>
-      <c r="B306" s="15"/>
-      <c r="C306" s="12"/>
-      <c r="D306" s="19"/>
-      <c r="E306" s="12"/>
-      <c r="F306" s="12"/>
-      <c r="G306" s="14"/>
-      <c r="I306" s="12"/>
-      <c r="J306" s="13"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H229">
-    <cfRule type="expression" dxfId="9" priority="6">
+  <conditionalFormatting sqref="H2:H301">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>H2="Alta"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="7">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>H2="Media"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>H2="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J116">
-    <cfRule type="expression" dxfId="6" priority="9">
+  <conditionalFormatting sqref="J2:J116 J230:J301">
+    <cfRule type="expression" dxfId="1" priority="9">
       <formula>J2="Ejecutado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="10">
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>J2="Pendiente"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H230:H306">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>H230="Alta"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="2">
-      <formula>H230="Media"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>H230="Baja"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J230:J306">
-    <cfRule type="expression" dxfId="1" priority="4">
-      <formula>J230="Ejecutado"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="5">
-      <formula>J230="Pendiente"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9740,14 +9784,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="5" t="s">

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4124F7-07E4-4EEC-A451-069A894452AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6602A6D5-7010-4823-B0DA-022B597DB61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1093,13 +1093,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4686,7 +4686,7 @@
         <v>46191</v>
       </c>
       <c r="B105" s="15">
-        <v>0.77152777777777781</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C105" s="12" t="s">
         <v>151</v>
@@ -5001,7 +5001,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="28.5">
+    <row r="115" spans="1:10">
       <c r="A115" s="16">
         <v>46190</v>
       </c>
@@ -8681,7 +8681,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="71.25">
+    <row r="230" spans="1:12" ht="42.75">
       <c r="A230" s="16">
         <v>46190</v>
       </c>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="L230" s="21"/>
     </row>
-    <row r="231" spans="1:12" ht="99.75">
+    <row r="231" spans="1:12" ht="57">
       <c r="A231" s="16"/>
       <c r="B231" s="15"/>
       <c r="C231" s="12"/>
@@ -8766,7 +8766,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="28.5">
+    <row r="233" spans="1:12">
       <c r="A233" s="16">
         <v>46190</v>
       </c>
@@ -8830,7 +8830,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="57">
+    <row r="235" spans="1:12" ht="28.5">
       <c r="A235" s="16">
         <v>46197</v>
       </c>
@@ -8862,7 +8862,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="236" spans="1:12" ht="57">
+    <row r="236" spans="1:12" ht="28.5">
       <c r="A236" s="16">
         <v>46267</v>
       </c>
@@ -8960,7 +8960,7 @@
       <c r="L238" s="21"/>
     </row>
     <row r="239" spans="1:12" s="8" customFormat="1" ht="42.75">
-      <c r="A239" s="24">
+      <c r="A239" s="22">
         <v>46297</v>
       </c>
       <c r="B239" s="15" t="s">
@@ -9784,14 +9784,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="5" t="s">

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6602A6D5-7010-4823-B0DA-022B597DB61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B1AD1E-E4DC-4433-B803-F7DFBE8CBFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2334" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2341" uniqueCount="282">
   <si>
     <t>Fecha</t>
   </si>
@@ -918,6 +918,15 @@
   </si>
   <si>
     <t>50 sillas / Cuatro (4) mesas (2 en la parte externa del auditorio para recepción y coffee break y 2 a la interna para una dinámica) /  Cuatro (4) sillas de conversatorio para ponentes / Una (1) mesa de centro para poner las aguas de los ponentes.</t>
+  </si>
+  <si>
+    <t>VICERRECTORADO DE GESTION ACADEMICA</t>
+  </si>
+  <si>
+    <t>reunión QS Latam 2026</t>
+  </si>
+  <si>
+    <t>45 sillas / 2 mesas con mantel afuera del auditorio para Coffee break / 1 Pizarra / Podio / Bandera de Científica / Aire acondicionado funcionando correctamente / 1 persona de apoyo por si hay algún requerimiento adicional</t>
   </si>
 </sst>
 </file>
@@ -8991,16 +9000,37 @@
         <v>86</v>
       </c>
     </row>
-    <row r="240" spans="1:12">
-      <c r="A240" s="16"/>
-      <c r="B240" s="15"/>
-      <c r="C240" s="12"/>
-      <c r="D240" s="19"/>
-      <c r="E240" s="12"/>
-      <c r="F240" s="12"/>
-      <c r="G240" s="14"/>
-      <c r="I240" s="12"/>
-      <c r="J240" s="13"/>
+    <row r="240" spans="1:12" s="8" customFormat="1" ht="42.75">
+      <c r="A240" s="22">
+        <v>46191</v>
+      </c>
+      <c r="B240" s="15">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C240" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="D240" s="19">
+        <v>9851</v>
+      </c>
+      <c r="E240" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="F240" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="G240" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="H240" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I240" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J240" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="241" spans="1:10">
       <c r="A241" s="16"/>

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B1AD1E-E4DC-4433-B803-F7DFBE8CBFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E475936-55A1-4196-8713-63D35EF77A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVENTOS" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2341" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2385" uniqueCount="301">
   <si>
     <t>Fecha</t>
   </si>
@@ -927,6 +927,63 @@
   </si>
   <si>
     <t>45 sillas / 2 mesas con mantel afuera del auditorio para Coffee break / 1 Pizarra / Podio / Bandera de Científica / Aire acondicionado funcionando correctamente / 1 persona de apoyo por si hay algún requerimiento adicional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AREA DE EMPLEABILIDAD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MENSAJE </t>
+  </si>
+  <si>
+    <t>Doble Grado Fest</t>
+  </si>
+  <si>
+    <t>Jardin Pabellon N</t>
+  </si>
+  <si>
+    <t>No indica</t>
+  </si>
+  <si>
+    <t>Evento Zofratacna</t>
+  </si>
+  <si>
+    <t>Auditorio pabellon L - 204</t>
+  </si>
+  <si>
+    <t>1 mesa / 2 sillas / mantel / 4 sillones / 2 mesas para el coffee break con mantel / 60 sillas</t>
+  </si>
+  <si>
+    <t>FACULTAD DE OBSTETRICIA</t>
+  </si>
+  <si>
+    <t>Jornada Cientifica Obstetricia</t>
+  </si>
+  <si>
+    <t>Atril / banderas /80 sillas/1 Mesa de Centro/4 butacas/1 Mesa de recepción/3 sillas/1 Mantel</t>
+  </si>
+  <si>
+    <t>AREA DE GDT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solicitud de soporte  Cumpleaños Villa 2 </t>
+  </si>
+  <si>
+    <t>50 sillas / 4 mesas / punto de luz</t>
+  </si>
+  <si>
+    <t>LEAD – Campeonato Deportivo</t>
+  </si>
+  <si>
+    <t>Campo Deportivo - pabellon I</t>
+  </si>
+  <si>
+    <t>2 mesas con mantel / 4 sillas / 2 toldos / 2 extensiones eléctricas / 1 pizarra acrílica móvil.</t>
+  </si>
+  <si>
+    <t>LEAD – Corporate Tech</t>
+  </si>
+  <si>
+    <t>1 mesa para recepción / 2 muebles para el estrado .</t>
   </si>
 </sst>
 </file>
@@ -1352,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L301"/>
+  <dimension ref="A1:L293"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -9033,70 +9090,196 @@
       </c>
     </row>
     <row r="241" spans="1:10">
-      <c r="A241" s="16"/>
-      <c r="B241" s="15"/>
-      <c r="C241" s="12"/>
-      <c r="D241" s="19"/>
-      <c r="E241" s="12"/>
-      <c r="F241" s="12"/>
-      <c r="G241" s="14"/>
-      <c r="I241" s="12"/>
-      <c r="J241" s="13"/>
+      <c r="A241" s="16">
+        <v>46198</v>
+      </c>
+      <c r="B241" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C241" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D241" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="E241" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="F241" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="G241" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="H241" t="s">
+        <v>17</v>
+      </c>
+      <c r="I241" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J241" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="242" spans="1:10">
-      <c r="A242" s="16"/>
-      <c r="B242" s="15"/>
-      <c r="C242" s="12"/>
-      <c r="D242" s="19"/>
-      <c r="E242" s="12"/>
-      <c r="F242" s="12"/>
-      <c r="G242" s="14"/>
-      <c r="I242" s="12"/>
-      <c r="J242" s="13"/>
+      <c r="A242" s="16">
+        <v>46192</v>
+      </c>
+      <c r="B242" s="15">
+        <v>0.625</v>
+      </c>
+      <c r="C242" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="D242" s="19">
+        <v>9861</v>
+      </c>
+      <c r="E242" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F242" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="G242" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="H242" t="s">
+        <v>17</v>
+      </c>
+      <c r="I242" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J242" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="243" spans="1:10">
-      <c r="A243" s="16"/>
-      <c r="B243" s="15"/>
-      <c r="C243" s="12"/>
-      <c r="D243" s="19"/>
-      <c r="E243" s="12"/>
-      <c r="F243" s="12"/>
-      <c r="G243" s="14"/>
-      <c r="I243" s="12"/>
-      <c r="J243" s="13"/>
+      <c r="A243" s="16">
+        <v>46199</v>
+      </c>
+      <c r="B243" s="15">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C243" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="D243" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E243" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="F243" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="G243" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="H243" t="s">
+        <v>17</v>
+      </c>
+      <c r="I243" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J243" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="244" spans="1:10">
-      <c r="A244" s="16"/>
-      <c r="B244" s="15"/>
-      <c r="C244" s="12"/>
-      <c r="D244" s="19"/>
-      <c r="E244" s="12"/>
-      <c r="F244" s="12"/>
-      <c r="G244" s="14"/>
-      <c r="I244" s="12"/>
-      <c r="J244" s="13"/>
+      <c r="A244" s="16">
+        <v>46199</v>
+      </c>
+      <c r="B244" s="15">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C244" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="D244" s="19">
+        <v>9884</v>
+      </c>
+      <c r="E244" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="F244" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="G244" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="H244" t="s">
+        <v>17</v>
+      </c>
+      <c r="I244" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J244" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="245" spans="1:10">
-      <c r="A245" s="16"/>
-      <c r="B245" s="15"/>
-      <c r="C245" s="12"/>
-      <c r="D245" s="19"/>
-      <c r="E245" s="12"/>
-      <c r="F245" s="12"/>
-      <c r="G245" s="14"/>
-      <c r="I245" s="12"/>
-      <c r="J245" s="13"/>
+      <c r="A245" s="16">
+        <v>46208</v>
+      </c>
+      <c r="B245" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="C245" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D245" s="19">
+        <v>9872</v>
+      </c>
+      <c r="E245" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="F245" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="G245" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="H245" t="s">
+        <v>17</v>
+      </c>
+      <c r="I245" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J245" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="246" spans="1:10">
-      <c r="A246" s="16"/>
-      <c r="B246" s="15"/>
-      <c r="C246" s="12"/>
-      <c r="D246" s="19"/>
-      <c r="E246" s="12"/>
-      <c r="F246" s="12"/>
-      <c r="G246" s="14"/>
-      <c r="I246" s="12"/>
-      <c r="J246" s="13"/>
+      <c r="A246" s="16">
+        <v>46308</v>
+      </c>
+      <c r="B246" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="C246" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D246" s="19">
+        <v>9870</v>
+      </c>
+      <c r="E246" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="F246" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="G246" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="H246" t="s">
+        <v>17</v>
+      </c>
+      <c r="I246" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J246" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="247" spans="1:10">
       <c r="A247" s="16"/>
@@ -9615,96 +9798,8 @@
       <c r="I293" s="12"/>
       <c r="J293" s="13"/>
     </row>
-    <row r="294" spans="1:10">
-      <c r="A294" s="16"/>
-      <c r="B294" s="15"/>
-      <c r="C294" s="12"/>
-      <c r="D294" s="19"/>
-      <c r="E294" s="12"/>
-      <c r="F294" s="12"/>
-      <c r="G294" s="14"/>
-      <c r="I294" s="12"/>
-      <c r="J294" s="13"/>
-    </row>
-    <row r="295" spans="1:10">
-      <c r="A295" s="16"/>
-      <c r="B295" s="15"/>
-      <c r="C295" s="12"/>
-      <c r="D295" s="19"/>
-      <c r="E295" s="12"/>
-      <c r="F295" s="12"/>
-      <c r="G295" s="14"/>
-      <c r="I295" s="12"/>
-      <c r="J295" s="13"/>
-    </row>
-    <row r="296" spans="1:10">
-      <c r="A296" s="16"/>
-      <c r="B296" s="15"/>
-      <c r="C296" s="12"/>
-      <c r="D296" s="19"/>
-      <c r="E296" s="12"/>
-      <c r="F296" s="12"/>
-      <c r="G296" s="14"/>
-      <c r="I296" s="12"/>
-      <c r="J296" s="13"/>
-    </row>
-    <row r="297" spans="1:10">
-      <c r="A297" s="16"/>
-      <c r="B297" s="15"/>
-      <c r="C297" s="12"/>
-      <c r="D297" s="19"/>
-      <c r="E297" s="12"/>
-      <c r="F297" s="12"/>
-      <c r="G297" s="14"/>
-      <c r="I297" s="12"/>
-      <c r="J297" s="13"/>
-    </row>
-    <row r="298" spans="1:10">
-      <c r="A298" s="16"/>
-      <c r="B298" s="15"/>
-      <c r="C298" s="12"/>
-      <c r="D298" s="19"/>
-      <c r="E298" s="12"/>
-      <c r="F298" s="12"/>
-      <c r="G298" s="14"/>
-      <c r="I298" s="12"/>
-      <c r="J298" s="13"/>
-    </row>
-    <row r="299" spans="1:10">
-      <c r="A299" s="16"/>
-      <c r="B299" s="15"/>
-      <c r="C299" s="12"/>
-      <c r="D299" s="19"/>
-      <c r="E299" s="12"/>
-      <c r="F299" s="12"/>
-      <c r="G299" s="14"/>
-      <c r="I299" s="12"/>
-      <c r="J299" s="13"/>
-    </row>
-    <row r="300" spans="1:10">
-      <c r="A300" s="16"/>
-      <c r="B300" s="15"/>
-      <c r="C300" s="12"/>
-      <c r="D300" s="19"/>
-      <c r="E300" s="12"/>
-      <c r="F300" s="12"/>
-      <c r="G300" s="14"/>
-      <c r="I300" s="12"/>
-      <c r="J300" s="13"/>
-    </row>
-    <row r="301" spans="1:10">
-      <c r="A301" s="16"/>
-      <c r="B301" s="15"/>
-      <c r="C301" s="12"/>
-      <c r="D301" s="19"/>
-      <c r="E301" s="12"/>
-      <c r="F301" s="12"/>
-      <c r="G301" s="14"/>
-      <c r="I301" s="12"/>
-      <c r="J301" s="13"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H301">
+  <conditionalFormatting sqref="H2:H293">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>H2="Alta"</formula>
     </cfRule>
@@ -9715,7 +9810,7 @@
       <formula>H2="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J116 J230:J301">
+  <conditionalFormatting sqref="J2:J116 J230:J293">
     <cfRule type="expression" dxfId="1" priority="9">
       <formula>J2="Ejecutado"</formula>
     </cfRule>

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E475936-55A1-4196-8713-63D35EF77A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0259CE00-E5E1-4ABC-A9DD-07383BAA3AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVENTOS" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2385" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2451" uniqueCount="339">
   <si>
     <t>Fecha</t>
   </si>
@@ -985,6 +985,197 @@
   <si>
     <t>1 mesa para recepción / 2 muebles para el estrado .</t>
   </si>
+  <si>
+    <t>AREA MARKETING</t>
+  </si>
+  <si>
+    <t>Pasantía Colegio COLEGIO FRIENDSHIP SCHOOL</t>
+  </si>
+  <si>
+    <t>zonas externa de mesas picnic  comedor pabellon K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Separacion de mesa picnic </t>
+  </si>
+  <si>
+    <t>Pasantía COLEGIO NUESTRA SEÑORA DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>Terraza comedor  - pabellon K</t>
+  </si>
+  <si>
+    <t>Separacion de espacio para  almuerzo</t>
+  </si>
+  <si>
+    <t>AREA  RSU</t>
+  </si>
+  <si>
+    <t>ACTIVACION EVENTO RSU</t>
+  </si>
+  <si>
+    <t>Zona de sombrillas del comedor (frente al pabellón K)</t>
+  </si>
+  <si>
+    <t>01 toldo Científica / 01 mesa con mantel Científica /02 sillas</t>
+  </si>
+  <si>
+    <t>AREA DE ING. AMBIENTAL</t>
+  </si>
+  <si>
+    <t>Vuela CIENTÍFICA: I festival universitario de aves</t>
+  </si>
+  <si>
+    <t>Jardin Lote 28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  4 toldos /  8 mesas con mantel / 16 sillas / Podio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AREA VGU - DEPORTES </t>
+  </si>
+  <si>
+    <r>
+      <t>festival</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF242424"/>
+        <rFont val="Segoe UI"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> de Woodball 5</t>
+    </r>
+  </si>
+  <si>
+    <t>Zona Multideportiva - lote 28</t>
+  </si>
+  <si>
+    <t>40 sillas / pies de campo  / 4 Cubos /  1 toldo /  2 mesas /  1 punto de energía  / 3 puntos de energía eléctrica para los carritos de food trucks.</t>
+  </si>
+  <si>
+    <t>Tour VIP Centro de Cirugía Robótica 26  de junio | Sede Villa</t>
+  </si>
+  <si>
+    <r>
+      <t>Auditorio O</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> / Liberación de mobiliario de auditorio desde las 4:00 p.m., Dejarlo sin sillas / Traslado de Letra C a ingreso a auditorio y durante tour llevarlo al jardín del Pabellón N / Colocar mesa de registro vestidas con 2 sillas en ingreso de Auditorio.                                                                                                                                               </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">Jardín Pabellón N / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Suspender regado de jardín del Pabellón N desde 24 de junio (habrá show de caballos) / Personal disponible para brindar accesos de corriente a productora desde las 4:00 p.m. Se colocará luminaria con reflectores. / Colocación de 8 pies de cancha en perímetro de jardín</t>
+    </r>
+  </si>
+  <si>
+    <t>Tour VIP Centro de Cirugía Robótica 27  de junio | Sede Villa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TERRAZA COMEDOR </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">Pabellón O </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Habilitar mobiliario de auditorio / Traslado de Letra C a ingreso a auditorio / mesa de registro vestidas con 2 sillas</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Jardín Pabellón N </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Suspender regado de jardín del Pabellón N desde 24 de junio (habrá show de caballos) / Personal disponible para brindar accesos de corriente a productora desde las 4:00 p.m. Se colocará luminaria con reflectores / Colocación de 8 pies de cancha</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Terraza Cafetería </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>Liberación de sillones de 2do nivel de terraza ya que se colocará toldo para Kitchen desde 26 de junio / Limpieza de terraza de cafetería / Colocación de separadores para reserva de espacios / Mantenimiento de jardín, luces de techo, espacios y toldo de terraza (adjunto fotografías de espacios tomadas ayer).</t>
+    </r>
+  </si>
+  <si>
+    <t>AREA DE RSU</t>
+  </si>
+  <si>
+    <t>Xplora tu Futuro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANFITEATRO </t>
+  </si>
+  <si>
+    <t>4 toldos / 4 mesas con mantel / 12 sillas / 4 conexiones eléctricas /2 extensiones</t>
+  </si>
+  <si>
+    <t>AREA DE VGU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feria del Bienestar Mental </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JARDIN DEL PABELLON  N </t>
+  </si>
+  <si>
+    <t>Puntos de luz para proveedor Parlantes 2500 voltios (2 puntos) para Escenario / Puntos de luz para proveedor Puestos de comida 220 voltios (2 puntos) 1 por cada puesto  / 50 Sillas  / 4 mesas sin mantel / 3 mesas vestidas  6 sillas adicionales / 3 puntos de luz, una para cada mesa vestida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FACULTAD DE OBSTETRICIA </t>
+  </si>
+  <si>
+    <t>actividad académica de Obstetricia</t>
+  </si>
+  <si>
+    <t>04 toldos / 06 mesas / 06 sillas / mantel para las mesas</t>
+  </si>
 </sst>
 </file>
 
@@ -993,7 +1184,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1020,8 +1211,31 @@
       <color theme="1"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF991B1B"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF242424"/>
+      <name val="Segoe UI"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1050,8 +1264,20 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E6F5"/>
+        <bgColor rgb="FFC0E6F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEE2E2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1096,11 +1322,115 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF44B3E1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF44B3E1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF44B3E1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF44B3E1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF44B3E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF44B3E1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF44B3E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF44B3E1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1166,6 +1496,122 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="6" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9281,202 +9727,402 @@
         <v>86</v>
       </c>
     </row>
-    <row r="247" spans="1:10">
-      <c r="A247" s="16"/>
-      <c r="B247" s="15"/>
-      <c r="C247" s="12"/>
-      <c r="D247" s="19"/>
-      <c r="E247" s="12"/>
-      <c r="F247" s="12"/>
-      <c r="G247" s="14"/>
-      <c r="I247" s="12"/>
+    <row r="247" spans="1:10" ht="15">
+      <c r="A247" s="25">
+        <v>46198</v>
+      </c>
+      <c r="B247" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="C247" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="D247" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="E247" s="29" t="s">
+        <v>302</v>
+      </c>
+      <c r="F247" s="29" t="s">
+        <v>303</v>
+      </c>
+      <c r="G247" s="30" t="s">
+        <v>304</v>
+      </c>
+      <c r="H247" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I247" s="32" t="s">
+        <v>18</v>
+      </c>
       <c r="J247" s="13"/>
     </row>
-    <row r="248" spans="1:10">
-      <c r="A248" s="16"/>
-      <c r="B248" s="15"/>
-      <c r="C248" s="12"/>
-      <c r="D248" s="19"/>
-      <c r="E248" s="12"/>
-      <c r="F248" s="12"/>
-      <c r="G248" s="14"/>
-      <c r="I248" s="12"/>
+    <row r="248" spans="1:10" ht="15">
+      <c r="A248" s="25">
+        <v>46199</v>
+      </c>
+      <c r="B248" s="26">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C248" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="D248" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="E248" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="F248" s="29" t="s">
+        <v>306</v>
+      </c>
+      <c r="G248" s="30" t="s">
+        <v>307</v>
+      </c>
+      <c r="H248" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I248" s="32" t="s">
+        <v>18</v>
+      </c>
       <c r="J248" s="13"/>
     </row>
-    <row r="249" spans="1:10">
-      <c r="A249" s="16"/>
-      <c r="B249" s="15"/>
-      <c r="C249" s="12"/>
-      <c r="D249" s="19"/>
-      <c r="E249" s="12"/>
-      <c r="F249" s="12"/>
-      <c r="G249" s="14"/>
-      <c r="I249" s="12"/>
+    <row r="249" spans="1:10" ht="15">
+      <c r="A249" s="25">
+        <v>46199</v>
+      </c>
+      <c r="B249" s="26">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C249" s="27" t="s">
+        <v>308</v>
+      </c>
+      <c r="D249" s="28">
+        <v>9910</v>
+      </c>
+      <c r="E249" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="F249" s="29" t="s">
+        <v>310</v>
+      </c>
+      <c r="G249" s="30" t="s">
+        <v>311</v>
+      </c>
+      <c r="H249" s="31"/>
+      <c r="I249" s="32"/>
       <c r="J249" s="13"/>
     </row>
-    <row r="250" spans="1:10">
-      <c r="A250" s="16"/>
-      <c r="B250" s="15"/>
-      <c r="C250" s="12"/>
-      <c r="D250" s="19"/>
-      <c r="E250" s="12"/>
-      <c r="F250" s="12"/>
-      <c r="G250" s="14"/>
-      <c r="I250" s="12"/>
+    <row r="250" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A250" s="41">
+        <v>46206</v>
+      </c>
+      <c r="B250" s="43">
+        <v>0.375</v>
+      </c>
+      <c r="C250" s="45" t="s">
+        <v>312</v>
+      </c>
+      <c r="D250" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="E250" s="49" t="s">
+        <v>313</v>
+      </c>
+      <c r="F250" s="51" t="s">
+        <v>314</v>
+      </c>
+      <c r="G250" s="33"/>
+      <c r="H250" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="I250" s="54" t="s">
+        <v>18</v>
+      </c>
       <c r="J250" s="13"/>
     </row>
     <row r="251" spans="1:10">
-      <c r="A251" s="16"/>
-      <c r="B251" s="15"/>
-      <c r="C251" s="12"/>
-      <c r="D251" s="19"/>
-      <c r="E251" s="12"/>
-      <c r="F251" s="12"/>
-      <c r="G251" s="14"/>
-      <c r="I251" s="12"/>
+      <c r="A251" s="42"/>
+      <c r="B251" s="44"/>
+      <c r="C251" s="46"/>
+      <c r="D251" s="48"/>
+      <c r="E251" s="50"/>
+      <c r="F251" s="52"/>
+      <c r="G251" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="H251" s="53"/>
+      <c r="I251" s="55"/>
       <c r="J251" s="13"/>
     </row>
-    <row r="252" spans="1:10">
-      <c r="A252" s="16"/>
-      <c r="B252" s="15"/>
-      <c r="C252" s="12"/>
-      <c r="D252" s="19"/>
-      <c r="E252" s="12"/>
-      <c r="F252" s="12"/>
-      <c r="G252" s="14"/>
-      <c r="I252" s="12"/>
+    <row r="252" spans="1:10" ht="28.5">
+      <c r="A252" s="25">
+        <v>46208</v>
+      </c>
+      <c r="B252" s="26">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C252" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="D252" s="28">
+        <v>9912</v>
+      </c>
+      <c r="E252" s="29" t="s">
+        <v>317</v>
+      </c>
+      <c r="F252" s="29" t="s">
+        <v>318</v>
+      </c>
+      <c r="G252" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="H252" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="I252" s="32" t="s">
+        <v>18</v>
+      </c>
       <c r="J252" s="13"/>
     </row>
-    <row r="253" spans="1:10">
-      <c r="A253" s="16"/>
-      <c r="B253" s="15"/>
-      <c r="C253" s="12"/>
-      <c r="D253" s="19"/>
-      <c r="E253" s="12"/>
-      <c r="F253" s="12"/>
-      <c r="G253" s="14"/>
-      <c r="I253" s="12"/>
+    <row r="253" spans="1:10" ht="60.75" customHeight="1">
+      <c r="A253" s="41">
+        <v>46199</v>
+      </c>
+      <c r="B253" s="43">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C253" s="45" t="s">
+        <v>251</v>
+      </c>
+      <c r="D253" s="47">
+        <v>9901</v>
+      </c>
+      <c r="E253" s="49" t="s">
+        <v>320</v>
+      </c>
+      <c r="F253" s="51" t="s">
+        <v>265</v>
+      </c>
+      <c r="G253" s="62" t="s">
+        <v>321</v>
+      </c>
+      <c r="H253" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="I253" s="49" t="s">
+        <v>18</v>
+      </c>
       <c r="J253" s="13"/>
     </row>
-    <row r="254" spans="1:10">
-      <c r="A254" s="16"/>
-      <c r="B254" s="15"/>
-      <c r="C254" s="12"/>
-      <c r="D254" s="19"/>
-      <c r="E254" s="12"/>
-      <c r="F254" s="12"/>
-      <c r="G254" s="14"/>
-      <c r="I254" s="12"/>
+    <row r="254" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A254" s="56"/>
+      <c r="B254" s="57"/>
+      <c r="C254" s="58"/>
+      <c r="D254" s="59"/>
+      <c r="E254" s="60"/>
+      <c r="F254" s="61"/>
+      <c r="G254" s="63"/>
+      <c r="H254" s="65"/>
+      <c r="I254" s="66"/>
       <c r="J254" s="13"/>
     </row>
-    <row r="255" spans="1:10">
-      <c r="A255" s="16"/>
-      <c r="B255" s="15"/>
-      <c r="C255" s="12"/>
-      <c r="D255" s="19"/>
-      <c r="E255" s="12"/>
-      <c r="F255" s="12"/>
-      <c r="G255" s="14"/>
-      <c r="I255" s="12"/>
+    <row r="255" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A255" s="56"/>
+      <c r="B255" s="57"/>
+      <c r="C255" s="58"/>
+      <c r="D255" s="59"/>
+      <c r="E255" s="60"/>
+      <c r="F255" s="61"/>
+      <c r="G255" s="63"/>
+      <c r="H255" s="65"/>
+      <c r="I255" s="66"/>
       <c r="J255" s="13"/>
     </row>
-    <row r="256" spans="1:10">
-      <c r="A256" s="16"/>
-      <c r="B256" s="15"/>
-      <c r="C256" s="12"/>
-      <c r="D256" s="19"/>
-      <c r="E256" s="12"/>
-      <c r="F256" s="12"/>
-      <c r="G256" s="14"/>
-      <c r="I256" s="12"/>
+    <row r="256" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A256" s="42"/>
+      <c r="B256" s="44"/>
+      <c r="C256" s="46"/>
+      <c r="D256" s="48"/>
+      <c r="E256" s="50"/>
+      <c r="F256" s="52"/>
+      <c r="G256" s="64"/>
+      <c r="H256" s="65"/>
+      <c r="I256" s="50"/>
       <c r="J256" s="13"/>
     </row>
-    <row r="257" spans="1:10">
-      <c r="A257" s="16"/>
-      <c r="B257" s="15"/>
-      <c r="C257" s="12"/>
-      <c r="D257" s="19"/>
-      <c r="E257" s="12"/>
-      <c r="F257" s="12"/>
-      <c r="G257" s="14"/>
-      <c r="I257" s="12"/>
+    <row r="257" spans="1:10" ht="29.25">
+      <c r="A257" s="41">
+        <v>46200</v>
+      </c>
+      <c r="B257" s="43">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C257" s="45" t="s">
+        <v>251</v>
+      </c>
+      <c r="D257" s="47">
+        <v>9902</v>
+      </c>
+      <c r="E257" s="49" t="s">
+        <v>322</v>
+      </c>
+      <c r="F257" s="51" t="s">
+        <v>323</v>
+      </c>
+      <c r="G257" s="37" t="s">
+        <v>324</v>
+      </c>
+      <c r="H257" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="I257" s="49" t="s">
+        <v>18</v>
+      </c>
       <c r="J257" s="13"/>
     </row>
     <row r="258" spans="1:10">
-      <c r="A258" s="16"/>
-      <c r="B258" s="15"/>
-      <c r="C258" s="12"/>
-      <c r="D258" s="19"/>
-      <c r="E258" s="12"/>
-      <c r="F258" s="12"/>
-      <c r="G258" s="14"/>
-      <c r="I258" s="12"/>
+      <c r="A258" s="56"/>
+      <c r="B258" s="57"/>
+      <c r="C258" s="58"/>
+      <c r="D258" s="59"/>
+      <c r="E258" s="60"/>
+      <c r="F258" s="61"/>
+      <c r="G258" s="35" t="s">
+        <v>325</v>
+      </c>
+      <c r="H258" s="65"/>
+      <c r="I258" s="66"/>
       <c r="J258" s="13"/>
     </row>
-    <row r="259" spans="1:10">
-      <c r="A259" s="16"/>
-      <c r="B259" s="15"/>
-      <c r="C259" s="12"/>
-      <c r="D259" s="19"/>
-      <c r="E259" s="12"/>
-      <c r="F259" s="12"/>
-      <c r="G259" s="14"/>
-      <c r="I259" s="12"/>
+    <row r="259" spans="1:10" ht="43.5">
+      <c r="A259" s="56"/>
+      <c r="B259" s="57"/>
+      <c r="C259" s="58"/>
+      <c r="D259" s="59"/>
+      <c r="E259" s="60"/>
+      <c r="F259" s="61"/>
+      <c r="G259" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="H259" s="65"/>
+      <c r="I259" s="66"/>
       <c r="J259" s="13"/>
     </row>
     <row r="260" spans="1:10">
-      <c r="A260" s="16"/>
-      <c r="B260" s="15"/>
-      <c r="C260" s="12"/>
-      <c r="D260" s="19"/>
-      <c r="E260" s="12"/>
-      <c r="F260" s="12"/>
-      <c r="G260" s="14"/>
-      <c r="I260" s="12"/>
+      <c r="A260" s="56"/>
+      <c r="B260" s="57"/>
+      <c r="C260" s="58"/>
+      <c r="D260" s="59"/>
+      <c r="E260" s="60"/>
+      <c r="F260" s="61"/>
+      <c r="G260" s="35" t="s">
+        <v>325</v>
+      </c>
+      <c r="H260" s="65"/>
+      <c r="I260" s="66"/>
       <c r="J260" s="13"/>
     </row>
-    <row r="261" spans="1:10">
-      <c r="A261" s="16"/>
-      <c r="B261" s="15"/>
-      <c r="C261" s="12"/>
-      <c r="D261" s="19"/>
-      <c r="E261" s="12"/>
-      <c r="F261" s="12"/>
-      <c r="G261" s="14"/>
-      <c r="I261" s="12"/>
+    <row r="261" spans="1:10" ht="57.75">
+      <c r="A261" s="42"/>
+      <c r="B261" s="44"/>
+      <c r="C261" s="46"/>
+      <c r="D261" s="48"/>
+      <c r="E261" s="50"/>
+      <c r="F261" s="52"/>
+      <c r="G261" s="39" t="s">
+        <v>327</v>
+      </c>
+      <c r="H261" s="65"/>
+      <c r="I261" s="50"/>
       <c r="J261" s="13"/>
     </row>
-    <row r="262" spans="1:10">
-      <c r="A262" s="16"/>
-      <c r="B262" s="15"/>
-      <c r="C262" s="12"/>
-      <c r="D262" s="19"/>
-      <c r="E262" s="12"/>
-      <c r="F262" s="12"/>
-      <c r="G262" s="14"/>
-      <c r="I262" s="12"/>
+    <row r="262" spans="1:10" ht="15">
+      <c r="A262" s="25">
+        <v>46205</v>
+      </c>
+      <c r="B262" s="26">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C262" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="D262" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="E262" s="29" t="s">
+        <v>329</v>
+      </c>
+      <c r="F262" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="G262" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="H262" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="I262" s="40" t="s">
+        <v>18</v>
+      </c>
       <c r="J262" s="13"/>
     </row>
-    <row r="263" spans="1:10">
-      <c r="A263" s="16"/>
-      <c r="B263" s="15"/>
-      <c r="C263" s="12"/>
-      <c r="D263" s="19"/>
-      <c r="E263" s="12"/>
-      <c r="F263" s="12"/>
-      <c r="G263" s="14"/>
-      <c r="I263" s="12"/>
+    <row r="263" spans="1:10" ht="42.75">
+      <c r="A263" s="25">
+        <v>46205</v>
+      </c>
+      <c r="B263" s="26">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C263" s="27" t="s">
+        <v>332</v>
+      </c>
+      <c r="D263" s="28">
+        <v>9916</v>
+      </c>
+      <c r="E263" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="F263" s="29" t="s">
+        <v>334</v>
+      </c>
+      <c r="G263" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="H263" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="I263" s="40" t="s">
+        <v>18</v>
+      </c>
       <c r="J263" s="13"/>
     </row>
-    <row r="264" spans="1:10">
-      <c r="A264" s="16"/>
-      <c r="B264" s="15"/>
-      <c r="C264" s="12"/>
-      <c r="D264" s="19"/>
-      <c r="E264" s="12"/>
-      <c r="F264" s="12"/>
-      <c r="G264" s="14"/>
-      <c r="I264" s="12"/>
+    <row r="264" spans="1:10" ht="28.5">
+      <c r="A264" s="25">
+        <v>46207</v>
+      </c>
+      <c r="B264" s="26">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C264" s="27" t="s">
+        <v>336</v>
+      </c>
+      <c r="D264" s="28"/>
+      <c r="E264" s="29" t="s">
+        <v>337</v>
+      </c>
+      <c r="F264" s="29" t="s">
+        <v>334</v>
+      </c>
+      <c r="G264" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="H264" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="I264" s="40" t="s">
+        <v>18</v>
+      </c>
       <c r="J264" s="13"/>
     </row>
     <row r="265" spans="1:10">
@@ -9799,7 +10445,34 @@
       <c r="J293" s="13"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H293">
+  <mergeCells count="25">
+    <mergeCell ref="I253:I256"/>
+    <mergeCell ref="A257:A261"/>
+    <mergeCell ref="B257:B261"/>
+    <mergeCell ref="C257:C261"/>
+    <mergeCell ref="D257:D261"/>
+    <mergeCell ref="E257:E261"/>
+    <mergeCell ref="F257:F261"/>
+    <mergeCell ref="H257:H261"/>
+    <mergeCell ref="I257:I261"/>
+    <mergeCell ref="H250:H251"/>
+    <mergeCell ref="I250:I251"/>
+    <mergeCell ref="A253:A256"/>
+    <mergeCell ref="B253:B256"/>
+    <mergeCell ref="C253:C256"/>
+    <mergeCell ref="D253:D256"/>
+    <mergeCell ref="E253:E256"/>
+    <mergeCell ref="F253:F256"/>
+    <mergeCell ref="G253:G256"/>
+    <mergeCell ref="H253:H256"/>
+    <mergeCell ref="A250:A251"/>
+    <mergeCell ref="B250:B251"/>
+    <mergeCell ref="C250:C251"/>
+    <mergeCell ref="D250:D251"/>
+    <mergeCell ref="E250:E251"/>
+    <mergeCell ref="F250:F251"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H2:H246 H265:H293">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>H2="Alta"</formula>
     </cfRule>

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C7F733-33D4-4BE2-8197-4C1B9CE60238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7567E5-A714-4D92-B67D-CDAA5A3D9826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVENTOS" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2460" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2475" uniqueCount="339">
   <si>
     <t>Fecha</t>
   </si>
@@ -1100,6 +1100,15 @@
   </si>
   <si>
     <t>Pabellón O Habilitar mobiliario de auditorio / Traslado de Letra C a ingreso a auditorio / mesa de registro vestidas con 2 sillas /Jardín Pabellón N Suspender regado de jardín del Pabellón N desde 24 de junio (habrá show de caballos) / Personal disponible para brindar accesos de corriente a productora desde las 4:00 p.m. Se colocará luminaria con reflectores / Colocación de 8 pies de cancha. Terraza Cafetería Liberación de sillones de 2do nivel de terraza ya que se colocará toldo para Kitchen desde 26 de junio / Limpieza de terraza de cafetería / Colocación de separadores para reserva de espacios / Mantenimiento de jardín, luces de techo, espacios y toldo de terraza (adjunto fotografías de espacios tomadas ayer).</t>
+  </si>
+  <si>
+    <t>ACTIVIDAD VISITA DE COLEGIOS</t>
+  </si>
+  <si>
+    <t>COSTADO DE VENTAS PABELLON I</t>
+  </si>
+  <si>
+    <t>01 TOLDO / 01 MESA / 02 SILLAS / 01 PUNTO DE ENERGIA</t>
   </si>
 </sst>
 </file>
@@ -1272,27 +1281,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="7">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1351,6 +1357,9 @@
     <dxf>
       <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1367,10 +1376,10 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaEventosV4" displayName="TablaEventosV4" ref="A1:J16">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Área Solicitante"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="N° OT" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="N° OT" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Evento / Actividad"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ubicación"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Requerimientos"/>
@@ -1580,7 +1589,7 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="19" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -1612,7 +1621,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="19" t="s">
         <v>20</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1644,7 +1653,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="19" t="s">
         <v>20</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -1676,7 +1685,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="19" t="s">
         <v>20</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1708,7 +1717,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="19" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -1738,7 +1747,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="19" t="s">
         <v>40</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1766,7 +1775,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="19" t="s">
         <v>45</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -1798,7 +1807,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="19" t="s">
         <v>51</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1830,7 +1839,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="19" t="s">
         <v>51</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -1862,7 +1871,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="143.25" customHeight="1">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="19" t="s">
         <v>58</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -1894,7 +1903,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="228.75" customHeight="1">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="19" t="s">
         <v>64</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -1926,7 +1935,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="200.25" customHeight="1">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="19" t="s">
         <v>64</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -1958,7 +1967,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="129" customHeight="1">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="19" t="s">
         <v>72</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -1990,7 +1999,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="270.75" customHeight="1">
-      <c r="A15" s="21">
+      <c r="A15" s="19">
         <v>46177</v>
       </c>
       <c r="B15" s="9">
@@ -2022,7 +2031,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="270.75" customHeight="1">
-      <c r="A16" s="21">
+      <c r="A16" s="19">
         <v>46178</v>
       </c>
       <c r="B16" s="9">
@@ -2054,7 +2063,7 @@
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="20" t="s">
         <v>45</v>
       </c>
       <c r="B17" s="13" t="s">
@@ -2086,7 +2095,7 @@
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="20" t="s">
         <v>87</v>
       </c>
       <c r="B18" s="13" t="s">
@@ -2118,7 +2127,7 @@
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="20" t="s">
         <v>88</v>
       </c>
       <c r="B19" s="13" t="s">
@@ -2150,7 +2159,7 @@
       </c>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="20" t="s">
         <v>72</v>
       </c>
       <c r="B20" s="13" t="s">
@@ -2182,7 +2191,7 @@
       </c>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="20" t="s">
         <v>89</v>
       </c>
       <c r="B21" s="13" t="s">
@@ -2214,7 +2223,7 @@
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B22" s="13" t="s">
@@ -2246,7 +2255,7 @@
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="20" t="s">
         <v>93</v>
       </c>
       <c r="B23" s="13" t="s">
@@ -2278,7 +2287,7 @@
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="20" t="s">
         <v>94</v>
       </c>
       <c r="B24" s="13" t="s">
@@ -2310,7 +2319,7 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="20" t="s">
         <v>95</v>
       </c>
       <c r="B25" s="13" t="s">
@@ -2342,7 +2351,7 @@
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="20" t="s">
         <v>89</v>
       </c>
       <c r="B26" s="13" t="s">
@@ -2374,7 +2383,7 @@
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B27" s="13" t="s">
@@ -2406,7 +2415,7 @@
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="20" t="s">
         <v>93</v>
       </c>
       <c r="B28" s="13" t="s">
@@ -2438,7 +2447,7 @@
       </c>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="20" t="s">
         <v>94</v>
       </c>
       <c r="B29" s="13" t="s">
@@ -2470,7 +2479,7 @@
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="20" t="s">
         <v>95</v>
       </c>
       <c r="B30" s="13" t="s">
@@ -2502,7 +2511,7 @@
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="20" t="s">
         <v>89</v>
       </c>
       <c r="B31" s="13" t="s">
@@ -2534,7 +2543,7 @@
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B32" s="13" t="s">
@@ -2566,7 +2575,7 @@
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="22" t="s">
+      <c r="A33" s="20" t="s">
         <v>93</v>
       </c>
       <c r="B33" s="13" t="s">
@@ -2598,7 +2607,7 @@
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="20" t="s">
         <v>94</v>
       </c>
       <c r="B34" s="13" t="s">
@@ -2630,7 +2639,7 @@
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="20" t="s">
         <v>95</v>
       </c>
       <c r="B35" s="13" t="s">
@@ -2662,7 +2671,7 @@
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="20" t="s">
         <v>89</v>
       </c>
       <c r="B36" s="13" t="s">
@@ -2694,7 +2703,7 @@
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B37" s="13" t="s">
@@ -2726,7 +2735,7 @@
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="22" t="s">
+      <c r="A38" s="20" t="s">
         <v>93</v>
       </c>
       <c r="B38" s="13" t="s">
@@ -2758,7 +2767,7 @@
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="20" t="s">
         <v>94</v>
       </c>
       <c r="B39" s="13" t="s">
@@ -2790,7 +2799,7 @@
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="22" t="s">
+      <c r="A40" s="20" t="s">
         <v>95</v>
       </c>
       <c r="B40" s="13" t="s">
@@ -2822,7 +2831,7 @@
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="22" t="s">
+      <c r="A41" s="20" t="s">
         <v>89</v>
       </c>
       <c r="B41" s="13" t="s">
@@ -2854,7 +2863,7 @@
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B42" s="13" t="s">
@@ -2886,7 +2895,7 @@
       </c>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="22" t="s">
+      <c r="A43" s="20" t="s">
         <v>93</v>
       </c>
       <c r="B43" s="13" t="s">
@@ -2918,7 +2927,7 @@
       </c>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="22" t="s">
+      <c r="A44" s="20" t="s">
         <v>94</v>
       </c>
       <c r="B44" s="13" t="s">
@@ -2950,7 +2959,7 @@
       </c>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="22" t="s">
+      <c r="A45" s="20" t="s">
         <v>95</v>
       </c>
       <c r="B45" s="13" t="s">
@@ -2982,7 +2991,7 @@
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="22" t="s">
+      <c r="A46" s="20" t="s">
         <v>89</v>
       </c>
       <c r="B46" s="13" t="s">
@@ -3014,7 +3023,7 @@
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="22" t="s">
+      <c r="A47" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B47" s="13" t="s">
@@ -3046,7 +3055,7 @@
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="22" t="s">
+      <c r="A48" s="20" t="s">
         <v>93</v>
       </c>
       <c r="B48" s="13" t="s">
@@ -3078,7 +3087,7 @@
       </c>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="22" t="s">
+      <c r="A49" s="20" t="s">
         <v>94</v>
       </c>
       <c r="B49" s="13" t="s">
@@ -3110,7 +3119,7 @@
       </c>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="22" t="s">
+      <c r="A50" s="20" t="s">
         <v>95</v>
       </c>
       <c r="B50" s="13" t="s">
@@ -3142,7 +3151,7 @@
       </c>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="22" t="s">
+      <c r="A51" s="20" t="s">
         <v>89</v>
       </c>
       <c r="B51" s="13" t="s">
@@ -3174,7 +3183,7 @@
       </c>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="22" t="s">
+      <c r="A52" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B52" s="13" t="s">
@@ -3206,7 +3215,7 @@
       </c>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="22" t="s">
+      <c r="A53" s="20" t="s">
         <v>93</v>
       </c>
       <c r="B53" s="13" t="s">
@@ -3238,7 +3247,7 @@
       </c>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="22" t="s">
+      <c r="A54" s="20" t="s">
         <v>94</v>
       </c>
       <c r="B54" s="13" t="s">
@@ -3270,7 +3279,7 @@
       </c>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="22" t="s">
+      <c r="A55" s="20" t="s">
         <v>95</v>
       </c>
       <c r="B55" s="13" t="s">
@@ -3302,7 +3311,7 @@
       </c>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="22" t="s">
+      <c r="A56" s="20" t="s">
         <v>89</v>
       </c>
       <c r="B56" s="13" t="s">
@@ -3334,7 +3343,7 @@
       </c>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="22" t="s">
+      <c r="A57" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B57" s="13" t="s">
@@ -3366,7 +3375,7 @@
       </c>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="22" t="s">
+      <c r="A58" s="20" t="s">
         <v>93</v>
       </c>
       <c r="B58" s="13" t="s">
@@ -3398,7 +3407,7 @@
       </c>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="22" t="s">
+      <c r="A59" s="20" t="s">
         <v>94</v>
       </c>
       <c r="B59" s="13" t="s">
@@ -3430,7 +3439,7 @@
       </c>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="22" t="s">
+      <c r="A60" s="20" t="s">
         <v>95</v>
       </c>
       <c r="B60" s="13" t="s">
@@ -3462,7 +3471,7 @@
       </c>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="22" t="s">
+      <c r="A61" s="20" t="s">
         <v>89</v>
       </c>
       <c r="B61" s="13" t="s">
@@ -3494,7 +3503,7 @@
       </c>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="22" t="s">
+      <c r="A62" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B62" s="13" t="s">
@@ -3526,7 +3535,7 @@
       </c>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="22" t="s">
+      <c r="A63" s="20" t="s">
         <v>93</v>
       </c>
       <c r="B63" s="13" t="s">
@@ -3558,7 +3567,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A64" s="22" t="s">
+      <c r="A64" s="20" t="s">
         <v>94</v>
       </c>
       <c r="B64" s="13" t="s">
@@ -3590,7 +3599,7 @@
       </c>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="22" t="s">
+      <c r="A65" s="20" t="s">
         <v>95</v>
       </c>
       <c r="B65" s="13" t="s">
@@ -3622,7 +3631,7 @@
       </c>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="22" t="s">
+      <c r="A66" s="20" t="s">
         <v>112</v>
       </c>
       <c r="B66" s="13" t="s">
@@ -3654,7 +3663,7 @@
       </c>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="22" t="s">
+      <c r="A67" s="20" t="s">
         <v>115</v>
       </c>
       <c r="B67" s="13" t="s">
@@ -3686,7 +3695,7 @@
       </c>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="22" t="s">
+      <c r="A68" s="20" t="s">
         <v>116</v>
       </c>
       <c r="B68" s="13" t="s">
@@ -3718,7 +3727,7 @@
       </c>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="22" t="s">
+      <c r="A69" s="20" t="s">
         <v>58</v>
       </c>
       <c r="B69" s="13" t="s">
@@ -3750,7 +3759,7 @@
       </c>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="22" t="s">
+      <c r="A70" s="20" t="s">
         <v>117</v>
       </c>
       <c r="B70" s="13" t="s">
@@ -3782,7 +3791,7 @@
       </c>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="22" t="s">
+      <c r="A71" s="20" t="s">
         <v>119</v>
       </c>
       <c r="B71" s="13" t="s">
@@ -3814,7 +3823,7 @@
       </c>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="22" t="s">
+      <c r="A72" s="20" t="s">
         <v>120</v>
       </c>
       <c r="B72" s="13" t="s">
@@ -3846,7 +3855,7 @@
       </c>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="22" t="s">
+      <c r="A73" s="20" t="s">
         <v>64</v>
       </c>
       <c r="B73" s="13" t="s">
@@ -3878,7 +3887,7 @@
       </c>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="22" t="s">
+      <c r="A74" s="20" t="s">
         <v>117</v>
       </c>
       <c r="B74" s="13" t="s">
@@ -3910,7 +3919,7 @@
       </c>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="22" t="s">
+      <c r="A75" s="20" t="s">
         <v>119</v>
       </c>
       <c r="B75" s="13" t="s">
@@ -3942,7 +3951,7 @@
       </c>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="22" t="s">
+      <c r="A76" s="20" t="s">
         <v>120</v>
       </c>
       <c r="B76" s="13" t="s">
@@ -3974,7 +3983,7 @@
       </c>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="22" t="s">
+      <c r="A77" s="20" t="s">
         <v>64</v>
       </c>
       <c r="B77" s="13" t="s">
@@ -4006,7 +4015,7 @@
       </c>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="22" t="s">
+      <c r="A78" s="20" t="s">
         <v>117</v>
       </c>
       <c r="B78" s="13" t="s">
@@ -4038,7 +4047,7 @@
       </c>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="22" t="s">
+      <c r="A79" s="20" t="s">
         <v>119</v>
       </c>
       <c r="B79" s="13" t="s">
@@ -4070,7 +4079,7 @@
       </c>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="22" t="s">
+      <c r="A80" s="20" t="s">
         <v>120</v>
       </c>
       <c r="B80" s="13" t="s">
@@ -4102,7 +4111,7 @@
       </c>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="22" t="s">
+      <c r="A81" s="20" t="s">
         <v>64</v>
       </c>
       <c r="B81" s="13" t="s">
@@ -4134,7 +4143,7 @@
       </c>
     </row>
     <row r="82" spans="1:10">
-      <c r="A82" s="22" t="s">
+      <c r="A82" s="20" t="s">
         <v>123</v>
       </c>
       <c r="B82" s="13" t="s">
@@ -4166,7 +4175,7 @@
       </c>
     </row>
     <row r="83" spans="1:10">
-      <c r="A83" s="22" t="s">
+      <c r="A83" s="20" t="s">
         <v>125</v>
       </c>
       <c r="B83" s="13" t="s">
@@ -4198,7 +4207,7 @@
       </c>
     </row>
     <row r="84" spans="1:10">
-      <c r="A84" s="22" t="s">
+      <c r="A84" s="20" t="s">
         <v>126</v>
       </c>
       <c r="B84" s="13" t="s">
@@ -4230,7 +4239,7 @@
       </c>
     </row>
     <row r="85" spans="1:10">
-      <c r="A85" s="22" t="s">
+      <c r="A85" s="20" t="s">
         <v>127</v>
       </c>
       <c r="B85" s="13" t="s">
@@ -4262,7 +4271,7 @@
       </c>
     </row>
     <row r="86" spans="1:10">
-      <c r="A86" s="22" t="s">
+      <c r="A86" s="20" t="s">
         <v>123</v>
       </c>
       <c r="B86" s="13" t="s">
@@ -4294,7 +4303,7 @@
       </c>
     </row>
     <row r="87" spans="1:10">
-      <c r="A87" s="22" t="s">
+      <c r="A87" s="20" t="s">
         <v>127</v>
       </c>
       <c r="B87" s="13" t="s">
@@ -4326,7 +4335,7 @@
       </c>
     </row>
     <row r="88" spans="1:10">
-      <c r="A88" s="22" t="s">
+      <c r="A88" s="20" t="s">
         <v>125</v>
       </c>
       <c r="B88" s="13" t="s">
@@ -4358,7 +4367,7 @@
       </c>
     </row>
     <row r="89" spans="1:10">
-      <c r="A89" s="22" t="s">
+      <c r="A89" s="20" t="s">
         <v>126</v>
       </c>
       <c r="B89" s="13" t="s">
@@ -4390,7 +4399,7 @@
       </c>
     </row>
     <row r="90" spans="1:10">
-      <c r="A90" s="22" t="s">
+      <c r="A90" s="20" t="s">
         <v>123</v>
       </c>
       <c r="B90" s="13" t="s">
@@ -4422,7 +4431,7 @@
       </c>
     </row>
     <row r="91" spans="1:10">
-      <c r="A91" s="22" t="s">
+      <c r="A91" s="20" t="s">
         <v>127</v>
       </c>
       <c r="B91" s="13" t="s">
@@ -4454,7 +4463,7 @@
       </c>
     </row>
     <row r="92" spans="1:10">
-      <c r="A92" s="22" t="s">
+      <c r="A92" s="20" t="s">
         <v>125</v>
       </c>
       <c r="B92" s="13" t="s">
@@ -4486,7 +4495,7 @@
       </c>
     </row>
     <row r="93" spans="1:10">
-      <c r="A93" s="22" t="s">
+      <c r="A93" s="20" t="s">
         <v>126</v>
       </c>
       <c r="B93" s="13" t="s">
@@ -4518,7 +4527,7 @@
       </c>
     </row>
     <row r="94" spans="1:10">
-      <c r="A94" s="22" t="s">
+      <c r="A94" s="20" t="s">
         <v>133</v>
       </c>
       <c r="B94" s="13" t="s">
@@ -4550,7 +4559,7 @@
       </c>
     </row>
     <row r="95" spans="1:10">
-      <c r="A95" s="22" t="s">
+      <c r="A95" s="20" t="s">
         <v>134</v>
       </c>
       <c r="B95" s="13" t="s">
@@ -4582,7 +4591,7 @@
       </c>
     </row>
     <row r="96" spans="1:10">
-      <c r="A96" s="22" t="s">
+      <c r="A96" s="20" t="s">
         <v>135</v>
       </c>
       <c r="B96" s="13" t="s">
@@ -4614,7 +4623,7 @@
       </c>
     </row>
     <row r="97" spans="1:10">
-      <c r="A97" s="22" t="s">
+      <c r="A97" s="20" t="s">
         <v>135</v>
       </c>
       <c r="B97" s="13" t="s">
@@ -4646,7 +4655,7 @@
       </c>
     </row>
     <row r="98" spans="1:10">
-      <c r="A98" s="22" t="s">
+      <c r="A98" s="20" t="s">
         <v>135</v>
       </c>
       <c r="B98" s="13" t="s">
@@ -4678,7 +4687,7 @@
       </c>
     </row>
     <row r="99" spans="1:10">
-      <c r="A99" s="22" t="s">
+      <c r="A99" s="20" t="s">
         <v>136</v>
       </c>
       <c r="B99" s="13" t="s">
@@ -4710,7 +4719,7 @@
       </c>
     </row>
     <row r="100" spans="1:10">
-      <c r="A100" s="22" t="s">
+      <c r="A100" s="20" t="s">
         <v>136</v>
       </c>
       <c r="B100" s="13" t="s">
@@ -4742,7 +4751,7 @@
       </c>
     </row>
     <row r="101" spans="1:10">
-      <c r="A101" s="22" t="s">
+      <c r="A101" s="20" t="s">
         <v>136</v>
       </c>
       <c r="B101" s="13" t="s">
@@ -4774,7 +4783,7 @@
       </c>
     </row>
     <row r="102" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A102" s="22">
+      <c r="A102" s="20">
         <v>46182</v>
       </c>
       <c r="B102" s="13">
@@ -4806,7 +4815,7 @@
       </c>
     </row>
     <row r="103" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A103" s="22">
+      <c r="A103" s="20">
         <v>46186</v>
       </c>
       <c r="B103" s="13">
@@ -4838,7 +4847,7 @@
       </c>
     </row>
     <row r="104" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A104" s="22">
+      <c r="A104" s="20">
         <v>46190</v>
       </c>
       <c r="B104" s="13">
@@ -4870,7 +4879,7 @@
       </c>
     </row>
     <row r="105" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A105" s="22">
+      <c r="A105" s="20">
         <v>46191</v>
       </c>
       <c r="B105" s="13">
@@ -4902,7 +4911,7 @@
       </c>
     </row>
     <row r="106" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A106" s="22">
+      <c r="A106" s="20">
         <v>46183</v>
       </c>
       <c r="B106" s="13">
@@ -4934,7 +4943,7 @@
       </c>
     </row>
     <row r="107" spans="1:10">
-      <c r="A107" s="22">
+      <c r="A107" s="20">
         <v>46189</v>
       </c>
       <c r="B107" s="13">
@@ -4966,7 +4975,7 @@
       </c>
     </row>
     <row r="108" spans="1:10">
-      <c r="A108" s="22">
+      <c r="A108" s="20">
         <v>46184</v>
       </c>
       <c r="B108" s="13">
@@ -4998,7 +5007,7 @@
       </c>
     </row>
     <row r="109" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A109" s="22">
+      <c r="A109" s="20">
         <v>46184</v>
       </c>
       <c r="B109" s="13">
@@ -5030,7 +5039,7 @@
       </c>
     </row>
     <row r="110" spans="1:10" ht="28.5">
-      <c r="A110" s="22">
+      <c r="A110" s="20">
         <v>46185</v>
       </c>
       <c r="B110" s="13">
@@ -5062,7 +5071,7 @@
       </c>
     </row>
     <row r="111" spans="1:10" ht="28.5">
-      <c r="A111" s="22">
+      <c r="A111" s="20">
         <v>46186</v>
       </c>
       <c r="B111" s="13">
@@ -5094,7 +5103,7 @@
       </c>
     </row>
     <row r="112" spans="1:10" ht="28.5">
-      <c r="A112" s="22">
+      <c r="A112" s="20">
         <v>46186</v>
       </c>
       <c r="B112" s="13">
@@ -5126,7 +5135,7 @@
       </c>
     </row>
     <row r="113" spans="1:10" ht="51" customHeight="1">
-      <c r="A113" s="22">
+      <c r="A113" s="20">
         <v>46185</v>
       </c>
       <c r="B113" s="13">
@@ -5158,7 +5167,7 @@
       </c>
     </row>
     <row r="114" spans="1:10">
-      <c r="A114" s="22">
+      <c r="A114" s="20">
         <v>46185</v>
       </c>
       <c r="B114" s="13">
@@ -5190,7 +5199,7 @@
       </c>
     </row>
     <row r="115" spans="1:10">
-      <c r="A115" s="22">
+      <c r="A115" s="20">
         <v>46190</v>
       </c>
       <c r="B115" s="13">
@@ -5222,7 +5231,7 @@
       </c>
     </row>
     <row r="116" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A116" s="22">
+      <c r="A116" s="20">
         <v>46185</v>
       </c>
       <c r="B116" s="13">
@@ -5254,7 +5263,7 @@
       </c>
     </row>
     <row r="117" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A117" s="22" t="s">
+      <c r="A117" s="20" t="s">
         <v>189</v>
       </c>
       <c r="B117" s="13" t="s">
@@ -5286,7 +5295,7 @@
       </c>
     </row>
     <row r="118" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A118" s="22" t="s">
+      <c r="A118" s="20" t="s">
         <v>189</v>
       </c>
       <c r="B118" s="13" t="s">
@@ -5318,7 +5327,7 @@
       </c>
     </row>
     <row r="119" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A119" s="22" t="s">
+      <c r="A119" s="20" t="s">
         <v>189</v>
       </c>
       <c r="B119" s="13" t="s">
@@ -5350,7 +5359,7 @@
       </c>
     </row>
     <row r="120" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A120" s="22" t="s">
+      <c r="A120" s="20" t="s">
         <v>189</v>
       </c>
       <c r="B120" s="13" t="s">
@@ -5382,7 +5391,7 @@
       </c>
     </row>
     <row r="121" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A121" s="22" t="s">
+      <c r="A121" s="20" t="s">
         <v>195</v>
       </c>
       <c r="B121" s="13" t="s">
@@ -5414,7 +5423,7 @@
       </c>
     </row>
     <row r="122" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A122" s="22" t="s">
+      <c r="A122" s="20" t="s">
         <v>197</v>
       </c>
       <c r="B122" s="13" t="s">
@@ -5446,7 +5455,7 @@
       </c>
     </row>
     <row r="123" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A123" s="22" t="s">
+      <c r="A123" s="20" t="s">
         <v>197</v>
       </c>
       <c r="B123" s="13" t="s">
@@ -5478,7 +5487,7 @@
       </c>
     </row>
     <row r="124" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A124" s="22" t="s">
+      <c r="A124" s="20" t="s">
         <v>198</v>
       </c>
       <c r="B124" s="13" t="s">
@@ -5510,7 +5519,7 @@
       </c>
     </row>
     <row r="125" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A125" s="22" t="s">
+      <c r="A125" s="20" t="s">
         <v>199</v>
       </c>
       <c r="B125" s="13" t="s">
@@ -5542,7 +5551,7 @@
       </c>
     </row>
     <row r="126" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A126" s="22" t="s">
+      <c r="A126" s="20" t="s">
         <v>200</v>
       </c>
       <c r="B126" s="13" t="s">
@@ -5574,7 +5583,7 @@
       </c>
     </row>
     <row r="127" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A127" s="22" t="s">
+      <c r="A127" s="20" t="s">
         <v>200</v>
       </c>
       <c r="B127" s="13" t="s">
@@ -5606,7 +5615,7 @@
       </c>
     </row>
     <row r="128" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A128" s="22" t="s">
+      <c r="A128" s="20" t="s">
         <v>200</v>
       </c>
       <c r="B128" s="13" t="s">
@@ -5638,7 +5647,7 @@
       </c>
     </row>
     <row r="129" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A129" s="22" t="s">
+      <c r="A129" s="20" t="s">
         <v>200</v>
       </c>
       <c r="B129" s="13" t="s">
@@ -5670,7 +5679,7 @@
       </c>
     </row>
     <row r="130" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A130" s="22" t="s">
+      <c r="A130" s="20" t="s">
         <v>204</v>
       </c>
       <c r="B130" s="13" t="s">
@@ -5702,7 +5711,7 @@
       </c>
     </row>
     <row r="131" spans="1:10">
-      <c r="A131" s="22" t="s">
+      <c r="A131" s="20" t="s">
         <v>204</v>
       </c>
       <c r="B131" s="13" t="s">
@@ -5734,7 +5743,7 @@
       </c>
     </row>
     <row r="132" spans="1:10">
-      <c r="A132" s="22" t="s">
+      <c r="A132" s="20" t="s">
         <v>204</v>
       </c>
       <c r="B132" s="13" t="s">
@@ -5766,7 +5775,7 @@
       </c>
     </row>
     <row r="133" spans="1:10">
-      <c r="A133" s="22" t="s">
+      <c r="A133" s="20" t="s">
         <v>204</v>
       </c>
       <c r="B133" s="13" t="s">
@@ -5798,7 +5807,7 @@
       </c>
     </row>
     <row r="134" spans="1:10">
-      <c r="A134" s="22" t="s">
+      <c r="A134" s="20" t="s">
         <v>205</v>
       </c>
       <c r="B134" s="13" t="s">
@@ -5830,7 +5839,7 @@
       </c>
     </row>
     <row r="135" spans="1:10">
-      <c r="A135" s="22" t="s">
+      <c r="A135" s="20" t="s">
         <v>206</v>
       </c>
       <c r="B135" s="13" t="s">
@@ -5862,7 +5871,7 @@
       </c>
     </row>
     <row r="136" spans="1:10">
-      <c r="A136" s="22" t="s">
+      <c r="A136" s="20" t="s">
         <v>206</v>
       </c>
       <c r="B136" s="13" t="s">
@@ -5894,7 +5903,7 @@
       </c>
     </row>
     <row r="137" spans="1:10">
-      <c r="A137" s="22" t="s">
+      <c r="A137" s="20" t="s">
         <v>207</v>
       </c>
       <c r="B137" s="13" t="s">
@@ -5926,7 +5935,7 @@
       </c>
     </row>
     <row r="138" spans="1:10">
-      <c r="A138" s="22" t="s">
+      <c r="A138" s="20" t="s">
         <v>208</v>
       </c>
       <c r="B138" s="13" t="s">
@@ -5958,7 +5967,7 @@
       </c>
     </row>
     <row r="139" spans="1:10">
-      <c r="A139" s="22" t="s">
+      <c r="A139" s="20" t="s">
         <v>209</v>
       </c>
       <c r="B139" s="13" t="s">
@@ -5990,7 +5999,7 @@
       </c>
     </row>
     <row r="140" spans="1:10">
-      <c r="A140" s="22" t="s">
+      <c r="A140" s="20" t="s">
         <v>209</v>
       </c>
       <c r="B140" s="13" t="s">
@@ -6022,7 +6031,7 @@
       </c>
     </row>
     <row r="141" spans="1:10">
-      <c r="A141" s="22" t="s">
+      <c r="A141" s="20" t="s">
         <v>209</v>
       </c>
       <c r="B141" s="13" t="s">
@@ -6054,7 +6063,7 @@
       </c>
     </row>
     <row r="142" spans="1:10">
-      <c r="A142" s="22" t="s">
+      <c r="A142" s="20" t="s">
         <v>209</v>
       </c>
       <c r="B142" s="13" t="s">
@@ -6086,7 +6095,7 @@
       </c>
     </row>
     <row r="143" spans="1:10">
-      <c r="A143" s="22" t="s">
+      <c r="A143" s="20" t="s">
         <v>210</v>
       </c>
       <c r="B143" s="13" t="s">
@@ -6118,7 +6127,7 @@
       </c>
     </row>
     <row r="144" spans="1:10">
-      <c r="A144" s="22" t="s">
+      <c r="A144" s="20" t="s">
         <v>210</v>
       </c>
       <c r="B144" s="13" t="s">
@@ -6150,7 +6159,7 @@
       </c>
     </row>
     <row r="145" spans="1:10">
-      <c r="A145" s="22" t="s">
+      <c r="A145" s="20" t="s">
         <v>210</v>
       </c>
       <c r="B145" s="13" t="s">
@@ -6182,7 +6191,7 @@
       </c>
     </row>
     <row r="146" spans="1:10">
-      <c r="A146" s="22" t="s">
+      <c r="A146" s="20" t="s">
         <v>210</v>
       </c>
       <c r="B146" s="13" t="s">
@@ -6214,7 +6223,7 @@
       </c>
     </row>
     <row r="147" spans="1:10">
-      <c r="A147" s="22" t="s">
+      <c r="A147" s="20" t="s">
         <v>211</v>
       </c>
       <c r="B147" s="13" t="s">
@@ -6246,7 +6255,7 @@
       </c>
     </row>
     <row r="148" spans="1:10">
-      <c r="A148" s="22" t="s">
+      <c r="A148" s="20" t="s">
         <v>212</v>
       </c>
       <c r="B148" s="13" t="s">
@@ -6278,7 +6287,7 @@
       </c>
     </row>
     <row r="149" spans="1:10">
-      <c r="A149" s="22" t="s">
+      <c r="A149" s="20" t="s">
         <v>212</v>
       </c>
       <c r="B149" s="13" t="s">
@@ -6310,7 +6319,7 @@
       </c>
     </row>
     <row r="150" spans="1:10">
-      <c r="A150" s="22" t="s">
+      <c r="A150" s="20" t="s">
         <v>213</v>
       </c>
       <c r="B150" s="13" t="s">
@@ -6342,7 +6351,7 @@
       </c>
     </row>
     <row r="151" spans="1:10">
-      <c r="A151" s="22" t="s">
+      <c r="A151" s="20" t="s">
         <v>214</v>
       </c>
       <c r="B151" s="13" t="s">
@@ -6374,7 +6383,7 @@
       </c>
     </row>
     <row r="152" spans="1:10">
-      <c r="A152" s="22" t="s">
+      <c r="A152" s="20" t="s">
         <v>215</v>
       </c>
       <c r="B152" s="13" t="s">
@@ -6406,7 +6415,7 @@
       </c>
     </row>
     <row r="153" spans="1:10">
-      <c r="A153" s="22" t="s">
+      <c r="A153" s="20" t="s">
         <v>215</v>
       </c>
       <c r="B153" s="13" t="s">
@@ -6438,7 +6447,7 @@
       </c>
     </row>
     <row r="154" spans="1:10">
-      <c r="A154" s="22" t="s">
+      <c r="A154" s="20" t="s">
         <v>215</v>
       </c>
       <c r="B154" s="13" t="s">
@@ -6470,7 +6479,7 @@
       </c>
     </row>
     <row r="155" spans="1:10">
-      <c r="A155" s="22" t="s">
+      <c r="A155" s="20" t="s">
         <v>215</v>
       </c>
       <c r="B155" s="13" t="s">
@@ -6502,7 +6511,7 @@
       </c>
     </row>
     <row r="156" spans="1:10">
-      <c r="A156" s="22" t="s">
+      <c r="A156" s="20" t="s">
         <v>216</v>
       </c>
       <c r="B156" s="13" t="s">
@@ -6534,7 +6543,7 @@
       </c>
     </row>
     <row r="157" spans="1:10">
-      <c r="A157" s="22" t="s">
+      <c r="A157" s="20" t="s">
         <v>216</v>
       </c>
       <c r="B157" s="13" t="s">
@@ -6566,7 +6575,7 @@
       </c>
     </row>
     <row r="158" spans="1:10">
-      <c r="A158" s="22" t="s">
+      <c r="A158" s="20" t="s">
         <v>216</v>
       </c>
       <c r="B158" s="13" t="s">
@@ -6598,7 +6607,7 @@
       </c>
     </row>
     <row r="159" spans="1:10">
-      <c r="A159" s="22" t="s">
+      <c r="A159" s="20" t="s">
         <v>216</v>
       </c>
       <c r="B159" s="13" t="s">
@@ -6630,7 +6639,7 @@
       </c>
     </row>
     <row r="160" spans="1:10">
-      <c r="A160" s="22" t="s">
+      <c r="A160" s="20" t="s">
         <v>217</v>
       </c>
       <c r="B160" s="13" t="s">
@@ -6662,7 +6671,7 @@
       </c>
     </row>
     <row r="161" spans="1:10">
-      <c r="A161" s="22" t="s">
+      <c r="A161" s="20" t="s">
         <v>218</v>
       </c>
       <c r="B161" s="13" t="s">
@@ -6694,7 +6703,7 @@
       </c>
     </row>
     <row r="162" spans="1:10">
-      <c r="A162" s="22" t="s">
+      <c r="A162" s="20" t="s">
         <v>218</v>
       </c>
       <c r="B162" s="13" t="s">
@@ -6726,7 +6735,7 @@
       </c>
     </row>
     <row r="163" spans="1:10">
-      <c r="A163" s="22" t="s">
+      <c r="A163" s="20" t="s">
         <v>219</v>
       </c>
       <c r="B163" s="13" t="s">
@@ -6758,7 +6767,7 @@
       </c>
     </row>
     <row r="164" spans="1:10">
-      <c r="A164" s="22" t="s">
+      <c r="A164" s="20" t="s">
         <v>220</v>
       </c>
       <c r="B164" s="13" t="s">
@@ -6790,7 +6799,7 @@
       </c>
     </row>
     <row r="165" spans="1:10">
-      <c r="A165" s="22" t="s">
+      <c r="A165" s="20" t="s">
         <v>221</v>
       </c>
       <c r="B165" s="13" t="s">
@@ -6822,7 +6831,7 @@
       </c>
     </row>
     <row r="166" spans="1:10">
-      <c r="A166" s="22" t="s">
+      <c r="A166" s="20" t="s">
         <v>221</v>
       </c>
       <c r="B166" s="13" t="s">
@@ -6854,7 +6863,7 @@
       </c>
     </row>
     <row r="167" spans="1:10">
-      <c r="A167" s="22" t="s">
+      <c r="A167" s="20" t="s">
         <v>221</v>
       </c>
       <c r="B167" s="13" t="s">
@@ -6886,7 +6895,7 @@
       </c>
     </row>
     <row r="168" spans="1:10">
-      <c r="A168" s="22" t="s">
+      <c r="A168" s="20" t="s">
         <v>221</v>
       </c>
       <c r="B168" s="13" t="s">
@@ -6918,7 +6927,7 @@
       </c>
     </row>
     <row r="169" spans="1:10">
-      <c r="A169" s="22" t="s">
+      <c r="A169" s="20" t="s">
         <v>222</v>
       </c>
       <c r="B169" s="13" t="s">
@@ -6950,7 +6959,7 @@
       </c>
     </row>
     <row r="170" spans="1:10">
-      <c r="A170" s="22" t="s">
+      <c r="A170" s="20" t="s">
         <v>222</v>
       </c>
       <c r="B170" s="13" t="s">
@@ -6982,7 +6991,7 @@
       </c>
     </row>
     <row r="171" spans="1:10">
-      <c r="A171" s="22" t="s">
+      <c r="A171" s="20" t="s">
         <v>222</v>
       </c>
       <c r="B171" s="13" t="s">
@@ -7014,7 +7023,7 @@
       </c>
     </row>
     <row r="172" spans="1:10">
-      <c r="A172" s="22" t="s">
+      <c r="A172" s="20" t="s">
         <v>222</v>
       </c>
       <c r="B172" s="13" t="s">
@@ -7046,7 +7055,7 @@
       </c>
     </row>
     <row r="173" spans="1:10">
-      <c r="A173" s="22" t="s">
+      <c r="A173" s="20" t="s">
         <v>223</v>
       </c>
       <c r="B173" s="13" t="s">
@@ -7078,7 +7087,7 @@
       </c>
     </row>
     <row r="174" spans="1:10">
-      <c r="A174" s="22" t="s">
+      <c r="A174" s="20" t="s">
         <v>224</v>
       </c>
       <c r="B174" s="13" t="s">
@@ -7110,7 +7119,7 @@
       </c>
     </row>
     <row r="175" spans="1:10">
-      <c r="A175" s="22" t="s">
+      <c r="A175" s="20" t="s">
         <v>224</v>
       </c>
       <c r="B175" s="13" t="s">
@@ -7142,7 +7151,7 @@
       </c>
     </row>
     <row r="176" spans="1:10">
-      <c r="A176" s="22" t="s">
+      <c r="A176" s="20" t="s">
         <v>225</v>
       </c>
       <c r="B176" s="13" t="s">
@@ -7174,7 +7183,7 @@
       </c>
     </row>
     <row r="177" spans="1:10">
-      <c r="A177" s="22" t="s">
+      <c r="A177" s="20" t="s">
         <v>226</v>
       </c>
       <c r="B177" s="13" t="s">
@@ -7206,7 +7215,7 @@
       </c>
     </row>
     <row r="178" spans="1:10">
-      <c r="A178" s="22" t="s">
+      <c r="A178" s="20" t="s">
         <v>227</v>
       </c>
       <c r="B178" s="13" t="s">
@@ -7238,7 +7247,7 @@
       </c>
     </row>
     <row r="179" spans="1:10">
-      <c r="A179" s="22" t="s">
+      <c r="A179" s="20" t="s">
         <v>227</v>
       </c>
       <c r="B179" s="13" t="s">
@@ -7270,7 +7279,7 @@
       </c>
     </row>
     <row r="180" spans="1:10">
-      <c r="A180" s="22" t="s">
+      <c r="A180" s="20" t="s">
         <v>227</v>
       </c>
       <c r="B180" s="13" t="s">
@@ -7302,7 +7311,7 @@
       </c>
     </row>
     <row r="181" spans="1:10">
-      <c r="A181" s="22" t="s">
+      <c r="A181" s="20" t="s">
         <v>227</v>
       </c>
       <c r="B181" s="13" t="s">
@@ -7334,7 +7343,7 @@
       </c>
     </row>
     <row r="182" spans="1:10">
-      <c r="A182" s="22" t="s">
+      <c r="A182" s="20" t="s">
         <v>228</v>
       </c>
       <c r="B182" s="13" t="s">
@@ -7366,7 +7375,7 @@
       </c>
     </row>
     <row r="183" spans="1:10">
-      <c r="A183" s="22" t="s">
+      <c r="A183" s="20" t="s">
         <v>228</v>
       </c>
       <c r="B183" s="13" t="s">
@@ -7398,7 +7407,7 @@
       </c>
     </row>
     <row r="184" spans="1:10">
-      <c r="A184" s="22" t="s">
+      <c r="A184" s="20" t="s">
         <v>228</v>
       </c>
       <c r="B184" s="13" t="s">
@@ -7430,7 +7439,7 @@
       </c>
     </row>
     <row r="185" spans="1:10">
-      <c r="A185" s="22" t="s">
+      <c r="A185" s="20" t="s">
         <v>228</v>
       </c>
       <c r="B185" s="13" t="s">
@@ -7462,7 +7471,7 @@
       </c>
     </row>
     <row r="186" spans="1:10">
-      <c r="A186" s="22" t="s">
+      <c r="A186" s="20" t="s">
         <v>229</v>
       </c>
       <c r="B186" s="13" t="s">
@@ -7494,7 +7503,7 @@
       </c>
     </row>
     <row r="187" spans="1:10">
-      <c r="A187" s="22" t="s">
+      <c r="A187" s="20" t="s">
         <v>230</v>
       </c>
       <c r="B187" s="13" t="s">
@@ -7526,7 +7535,7 @@
       </c>
     </row>
     <row r="188" spans="1:10">
-      <c r="A188" s="22" t="s">
+      <c r="A188" s="20" t="s">
         <v>230</v>
       </c>
       <c r="B188" s="13" t="s">
@@ -7558,7 +7567,7 @@
       </c>
     </row>
     <row r="189" spans="1:10">
-      <c r="A189" s="22" t="s">
+      <c r="A189" s="20" t="s">
         <v>231</v>
       </c>
       <c r="B189" s="13" t="s">
@@ -7590,7 +7599,7 @@
       </c>
     </row>
     <row r="190" spans="1:10">
-      <c r="A190" s="22" t="s">
+      <c r="A190" s="20" t="s">
         <v>232</v>
       </c>
       <c r="B190" s="13" t="s">
@@ -7622,7 +7631,7 @@
       </c>
     </row>
     <row r="191" spans="1:10">
-      <c r="A191" s="22" t="s">
+      <c r="A191" s="20" t="s">
         <v>233</v>
       </c>
       <c r="B191" s="13" t="s">
@@ -7654,7 +7663,7 @@
       </c>
     </row>
     <row r="192" spans="1:10">
-      <c r="A192" s="22" t="s">
+      <c r="A192" s="20" t="s">
         <v>233</v>
       </c>
       <c r="B192" s="13" t="s">
@@ -7686,7 +7695,7 @@
       </c>
     </row>
     <row r="193" spans="1:10">
-      <c r="A193" s="22" t="s">
+      <c r="A193" s="20" t="s">
         <v>233</v>
       </c>
       <c r="B193" s="13" t="s">
@@ -7718,7 +7727,7 @@
       </c>
     </row>
     <row r="194" spans="1:10">
-      <c r="A194" s="22" t="s">
+      <c r="A194" s="20" t="s">
         <v>233</v>
       </c>
       <c r="B194" s="13" t="s">
@@ -7750,7 +7759,7 @@
       </c>
     </row>
     <row r="195" spans="1:10">
-      <c r="A195" s="22" t="s">
+      <c r="A195" s="20" t="s">
         <v>234</v>
       </c>
       <c r="B195" s="13" t="s">
@@ -7782,7 +7791,7 @@
       </c>
     </row>
     <row r="196" spans="1:10">
-      <c r="A196" s="22" t="s">
+      <c r="A196" s="20" t="s">
         <v>234</v>
       </c>
       <c r="B196" s="13" t="s">
@@ -7814,7 +7823,7 @@
       </c>
     </row>
     <row r="197" spans="1:10">
-      <c r="A197" s="22" t="s">
+      <c r="A197" s="20" t="s">
         <v>234</v>
       </c>
       <c r="B197" s="13" t="s">
@@ -7846,7 +7855,7 @@
       </c>
     </row>
     <row r="198" spans="1:10">
-      <c r="A198" s="22" t="s">
+      <c r="A198" s="20" t="s">
         <v>234</v>
       </c>
       <c r="B198" s="13" t="s">
@@ -7878,7 +7887,7 @@
       </c>
     </row>
     <row r="199" spans="1:10">
-      <c r="A199" s="22" t="s">
+      <c r="A199" s="20" t="s">
         <v>235</v>
       </c>
       <c r="B199" s="13" t="s">
@@ -7910,7 +7919,7 @@
       </c>
     </row>
     <row r="200" spans="1:10">
-      <c r="A200" s="22" t="s">
+      <c r="A200" s="20" t="s">
         <v>236</v>
       </c>
       <c r="B200" s="13" t="s">
@@ -7942,7 +7951,7 @@
       </c>
     </row>
     <row r="201" spans="1:10">
-      <c r="A201" s="22" t="s">
+      <c r="A201" s="20" t="s">
         <v>236</v>
       </c>
       <c r="B201" s="13" t="s">
@@ -7974,7 +7983,7 @@
       </c>
     </row>
     <row r="202" spans="1:10">
-      <c r="A202" s="22" t="s">
+      <c r="A202" s="20" t="s">
         <v>237</v>
       </c>
       <c r="B202" s="13" t="s">
@@ -8006,7 +8015,7 @@
       </c>
     </row>
     <row r="203" spans="1:10">
-      <c r="A203" s="22" t="s">
+      <c r="A203" s="20" t="s">
         <v>238</v>
       </c>
       <c r="B203" s="13" t="s">
@@ -8038,7 +8047,7 @@
       </c>
     </row>
     <row r="204" spans="1:10">
-      <c r="A204" s="22" t="s">
+      <c r="A204" s="20" t="s">
         <v>239</v>
       </c>
       <c r="B204" s="13" t="s">
@@ -8070,7 +8079,7 @@
       </c>
     </row>
     <row r="205" spans="1:10">
-      <c r="A205" s="22" t="s">
+      <c r="A205" s="20" t="s">
         <v>239</v>
       </c>
       <c r="B205" s="13" t="s">
@@ -8102,7 +8111,7 @@
       </c>
     </row>
     <row r="206" spans="1:10">
-      <c r="A206" s="22" t="s">
+      <c r="A206" s="20" t="s">
         <v>239</v>
       </c>
       <c r="B206" s="13" t="s">
@@ -8134,7 +8143,7 @@
       </c>
     </row>
     <row r="207" spans="1:10">
-      <c r="A207" s="22" t="s">
+      <c r="A207" s="20" t="s">
         <v>239</v>
       </c>
       <c r="B207" s="13" t="s">
@@ -8166,7 +8175,7 @@
       </c>
     </row>
     <row r="208" spans="1:10">
-      <c r="A208" s="22" t="s">
+      <c r="A208" s="20" t="s">
         <v>240</v>
       </c>
       <c r="B208" s="13" t="s">
@@ -8198,7 +8207,7 @@
       </c>
     </row>
     <row r="209" spans="1:10">
-      <c r="A209" s="22" t="s">
+      <c r="A209" s="20" t="s">
         <v>240</v>
       </c>
       <c r="B209" s="13" t="s">
@@ -8230,7 +8239,7 @@
       </c>
     </row>
     <row r="210" spans="1:10">
-      <c r="A210" s="22" t="s">
+      <c r="A210" s="20" t="s">
         <v>240</v>
       </c>
       <c r="B210" s="13" t="s">
@@ -8262,7 +8271,7 @@
       </c>
     </row>
     <row r="211" spans="1:10">
-      <c r="A211" s="22" t="s">
+      <c r="A211" s="20" t="s">
         <v>240</v>
       </c>
       <c r="B211" s="13" t="s">
@@ -8294,7 +8303,7 @@
       </c>
     </row>
     <row r="212" spans="1:10">
-      <c r="A212" s="22" t="s">
+      <c r="A212" s="20" t="s">
         <v>241</v>
       </c>
       <c r="B212" s="13" t="s">
@@ -8326,7 +8335,7 @@
       </c>
     </row>
     <row r="213" spans="1:10">
-      <c r="A213" s="22" t="s">
+      <c r="A213" s="20" t="s">
         <v>242</v>
       </c>
       <c r="B213" s="13" t="s">
@@ -8358,7 +8367,7 @@
       </c>
     </row>
     <row r="214" spans="1:10">
-      <c r="A214" s="22" t="s">
+      <c r="A214" s="20" t="s">
         <v>242</v>
       </c>
       <c r="B214" s="13" t="s">
@@ -8390,7 +8399,7 @@
       </c>
     </row>
     <row r="215" spans="1:10">
-      <c r="A215" s="22" t="s">
+      <c r="A215" s="20" t="s">
         <v>243</v>
       </c>
       <c r="B215" s="13" t="s">
@@ -8422,7 +8431,7 @@
       </c>
     </row>
     <row r="216" spans="1:10">
-      <c r="A216" s="22" t="s">
+      <c r="A216" s="20" t="s">
         <v>244</v>
       </c>
       <c r="B216" s="13" t="s">
@@ -8454,7 +8463,7 @@
       </c>
     </row>
     <row r="217" spans="1:10">
-      <c r="A217" s="22" t="s">
+      <c r="A217" s="20" t="s">
         <v>245</v>
       </c>
       <c r="B217" s="13" t="s">
@@ -8486,7 +8495,7 @@
       </c>
     </row>
     <row r="218" spans="1:10">
-      <c r="A218" s="22" t="s">
+      <c r="A218" s="20" t="s">
         <v>245</v>
       </c>
       <c r="B218" s="13" t="s">
@@ -8518,7 +8527,7 @@
       </c>
     </row>
     <row r="219" spans="1:10">
-      <c r="A219" s="22" t="s">
+      <c r="A219" s="20" t="s">
         <v>245</v>
       </c>
       <c r="B219" s="13" t="s">
@@ -8550,7 +8559,7 @@
       </c>
     </row>
     <row r="220" spans="1:10">
-      <c r="A220" s="22" t="s">
+      <c r="A220" s="20" t="s">
         <v>245</v>
       </c>
       <c r="B220" s="13" t="s">
@@ -8582,7 +8591,7 @@
       </c>
     </row>
     <row r="221" spans="1:10">
-      <c r="A221" s="22" t="s">
+      <c r="A221" s="20" t="s">
         <v>246</v>
       </c>
       <c r="B221" s="13" t="s">
@@ -8614,7 +8623,7 @@
       </c>
     </row>
     <row r="222" spans="1:10">
-      <c r="A222" s="22" t="s">
+      <c r="A222" s="20" t="s">
         <v>246</v>
       </c>
       <c r="B222" s="13" t="s">
@@ -8646,7 +8655,7 @@
       </c>
     </row>
     <row r="223" spans="1:10">
-      <c r="A223" s="22" t="s">
+      <c r="A223" s="20" t="s">
         <v>246</v>
       </c>
       <c r="B223" s="13" t="s">
@@ -8678,7 +8687,7 @@
       </c>
     </row>
     <row r="224" spans="1:10">
-      <c r="A224" s="22" t="s">
+      <c r="A224" s="20" t="s">
         <v>246</v>
       </c>
       <c r="B224" s="13" t="s">
@@ -8710,7 +8719,7 @@
       </c>
     </row>
     <row r="225" spans="1:12">
-      <c r="A225" s="22" t="s">
+      <c r="A225" s="20" t="s">
         <v>247</v>
       </c>
       <c r="B225" s="13" t="s">
@@ -8742,7 +8751,7 @@
       </c>
     </row>
     <row r="226" spans="1:12">
-      <c r="A226" s="22" t="s">
+      <c r="A226" s="20" t="s">
         <v>248</v>
       </c>
       <c r="B226" s="13" t="s">
@@ -8774,7 +8783,7 @@
       </c>
     </row>
     <row r="227" spans="1:12">
-      <c r="A227" s="22" t="s">
+      <c r="A227" s="20" t="s">
         <v>248</v>
       </c>
       <c r="B227" s="13" t="s">
@@ -8806,7 +8815,7 @@
       </c>
     </row>
     <row r="228" spans="1:12">
-      <c r="A228" s="22" t="s">
+      <c r="A228" s="20" t="s">
         <v>249</v>
       </c>
       <c r="B228" s="13" t="s">
@@ -8838,7 +8847,7 @@
       </c>
     </row>
     <row r="229" spans="1:12">
-      <c r="A229" s="22" t="s">
+      <c r="A229" s="20" t="s">
         <v>250</v>
       </c>
       <c r="B229" s="13" t="s">
@@ -8870,7 +8879,7 @@
       </c>
     </row>
     <row r="230" spans="1:12" ht="42.75">
-      <c r="A230" s="22">
+      <c r="A230" s="20">
         <v>46190</v>
       </c>
       <c r="B230" s="13">
@@ -8903,7 +8912,7 @@
       <c r="L230" s="18"/>
     </row>
     <row r="231" spans="1:12" ht="57">
-      <c r="A231" s="22"/>
+      <c r="A231" s="20"/>
       <c r="B231" s="13"/>
       <c r="C231" s="10"/>
       <c r="D231" s="16"/>
@@ -8923,7 +8932,7 @@
       </c>
     </row>
     <row r="232" spans="1:12">
-      <c r="A232" s="22">
+      <c r="A232" s="20">
         <v>46189</v>
       </c>
       <c r="B232" s="13">
@@ -8955,7 +8964,7 @@
       </c>
     </row>
     <row r="233" spans="1:12">
-      <c r="A233" s="22">
+      <c r="A233" s="20">
         <v>46190</v>
       </c>
       <c r="B233" s="13">
@@ -8987,7 +8996,7 @@
       </c>
     </row>
     <row r="234" spans="1:12">
-      <c r="A234" s="22">
+      <c r="A234" s="20">
         <v>46195</v>
       </c>
       <c r="B234" s="13">
@@ -9019,7 +9028,7 @@
       </c>
     </row>
     <row r="235" spans="1:12" ht="28.5">
-      <c r="A235" s="22">
+      <c r="A235" s="20">
         <v>46197</v>
       </c>
       <c r="B235" s="13">
@@ -9051,7 +9060,7 @@
       </c>
     </row>
     <row r="236" spans="1:12" ht="28.5">
-      <c r="A236" s="22">
+      <c r="A236" s="20">
         <v>46267</v>
       </c>
       <c r="B236" s="13">
@@ -9083,7 +9092,7 @@
       </c>
     </row>
     <row r="237" spans="1:12" ht="28.5">
-      <c r="A237" s="22">
+      <c r="A237" s="20">
         <v>46276</v>
       </c>
       <c r="B237" s="13">
@@ -9115,7 +9124,7 @@
       </c>
     </row>
     <row r="238" spans="1:12" ht="28.5">
-      <c r="A238" s="22">
+      <c r="A238" s="20">
         <v>46297</v>
       </c>
       <c r="B238" s="13">
@@ -9148,7 +9157,7 @@
       <c r="L238" s="18"/>
     </row>
     <row r="239" spans="1:12" s="7" customFormat="1" ht="42.75">
-      <c r="A239" s="22">
+      <c r="A239" s="20">
         <v>46297</v>
       </c>
       <c r="B239" s="13" t="s">
@@ -9180,7 +9189,7 @@
       </c>
     </row>
     <row r="240" spans="1:12" s="7" customFormat="1" ht="42.75">
-      <c r="A240" s="22">
+      <c r="A240" s="20">
         <v>46191</v>
       </c>
       <c r="B240" s="13">
@@ -9212,7 +9221,7 @@
       </c>
     </row>
     <row r="241" spans="1:10">
-      <c r="A241" s="22">
+      <c r="A241" s="20">
         <v>46198</v>
       </c>
       <c r="B241" s="13">
@@ -9244,7 +9253,7 @@
       </c>
     </row>
     <row r="242" spans="1:10">
-      <c r="A242" s="22">
+      <c r="A242" s="20">
         <v>46192</v>
       </c>
       <c r="B242" s="13">
@@ -9276,7 +9285,7 @@
       </c>
     </row>
     <row r="243" spans="1:10">
-      <c r="A243" s="22">
+      <c r="A243" s="20">
         <v>46199</v>
       </c>
       <c r="B243" s="13">
@@ -9308,7 +9317,7 @@
       </c>
     </row>
     <row r="244" spans="1:10">
-      <c r="A244" s="22">
+      <c r="A244" s="20">
         <v>46199</v>
       </c>
       <c r="B244" s="13">
@@ -9340,7 +9349,7 @@
       </c>
     </row>
     <row r="245" spans="1:10">
-      <c r="A245" s="22">
+      <c r="A245" s="20">
         <v>46208</v>
       </c>
       <c r="B245" s="13">
@@ -9372,7 +9381,7 @@
       </c>
     </row>
     <row r="246" spans="1:10">
-      <c r="A246" s="22">
+      <c r="A246" s="20">
         <v>46308</v>
       </c>
       <c r="B246" s="13">
@@ -9404,7 +9413,7 @@
       </c>
     </row>
     <row r="247" spans="1:10">
-      <c r="A247" s="22">
+      <c r="A247" s="20">
         <v>46198</v>
       </c>
       <c r="B247" s="13">
@@ -9436,7 +9445,7 @@
       </c>
     </row>
     <row r="248" spans="1:10">
-      <c r="A248" s="22">
+      <c r="A248" s="20">
         <v>46199</v>
       </c>
       <c r="B248" s="13">
@@ -9468,7 +9477,7 @@
       </c>
     </row>
     <row r="249" spans="1:10">
-      <c r="A249" s="22">
+      <c r="A249" s="20">
         <v>46199</v>
       </c>
       <c r="B249" s="13">
@@ -9489,7 +9498,7 @@
       <c r="G249" s="12" t="s">
         <v>311</v>
       </c>
-      <c r="H249" s="23" t="s">
+      <c r="H249" s="21" t="s">
         <v>17</v>
       </c>
       <c r="I249" s="10"/>
@@ -9498,7 +9507,7 @@
       </c>
     </row>
     <row r="250" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A250" s="22">
+      <c r="A250" s="20">
         <v>46206</v>
       </c>
       <c r="B250" s="13">
@@ -9528,7 +9537,7 @@
       </c>
     </row>
     <row r="251" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A251" s="22"/>
+      <c r="A251" s="20"/>
       <c r="B251" s="13"/>
       <c r="C251" s="10"/>
       <c r="D251" s="16"/>
@@ -9546,7 +9555,7 @@
       </c>
     </row>
     <row r="252" spans="1:10" ht="28.5">
-      <c r="A252" s="22">
+      <c r="A252" s="20">
         <v>46208</v>
       </c>
       <c r="B252" s="13">
@@ -9578,7 +9587,7 @@
       </c>
     </row>
     <row r="253" spans="1:10" ht="93.75" customHeight="1">
-      <c r="A253" s="22">
+      <c r="A253" s="20">
         <v>46199</v>
       </c>
       <c r="B253" s="13">
@@ -9610,7 +9619,7 @@
       </c>
     </row>
     <row r="254" spans="1:10" ht="129.75" customHeight="1">
-      <c r="A254" s="22">
+      <c r="A254" s="20">
         <v>46200</v>
       </c>
       <c r="B254" s="13">
@@ -9642,7 +9651,7 @@
       </c>
     </row>
     <row r="255" spans="1:10">
-      <c r="A255" s="22">
+      <c r="A255" s="20">
         <v>46205</v>
       </c>
       <c r="B255" s="13">
@@ -9674,7 +9683,7 @@
       </c>
     </row>
     <row r="256" spans="1:10" ht="51.75" customHeight="1">
-      <c r="A256" s="22">
+      <c r="A256" s="20">
         <v>46205</v>
       </c>
       <c r="B256" s="13">
@@ -9706,7 +9715,7 @@
       </c>
     </row>
     <row r="257" spans="1:10" ht="46.5" customHeight="1">
-      <c r="A257" s="22">
+      <c r="A257" s="20">
         <v>46207</v>
       </c>
       <c r="B257" s="13">
@@ -9715,7 +9724,9 @@
       <c r="C257" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="D257" s="16"/>
+      <c r="D257" s="16" t="s">
+        <v>28</v>
+      </c>
       <c r="E257" s="10" t="s">
         <v>332</v>
       </c>
@@ -9736,29 +9747,71 @@
       </c>
     </row>
     <row r="258" spans="1:10">
-      <c r="A258" s="22"/>
-      <c r="B258" s="13"/>
-      <c r="C258" s="10"/>
-      <c r="D258" s="16"/>
-      <c r="E258" s="10"/>
-      <c r="F258" s="10"/>
-      <c r="G258" s="12"/>
-      <c r="I258" s="10"/>
-      <c r="J258" s="11"/>
+      <c r="A258" s="20">
+        <v>46198</v>
+      </c>
+      <c r="B258" s="13">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C258" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="D258" s="16">
+        <v>9905</v>
+      </c>
+      <c r="E258" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="F258" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="G258" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="H258" t="s">
+        <v>17</v>
+      </c>
+      <c r="I258" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J258" s="11" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="259" spans="1:10">
-      <c r="A259" s="22"/>
-      <c r="B259" s="13"/>
-      <c r="C259" s="10"/>
-      <c r="D259" s="16"/>
-      <c r="E259" s="10"/>
-      <c r="F259" s="10"/>
-      <c r="G259" s="12"/>
-      <c r="I259" s="10"/>
-      <c r="J259" s="11"/>
+      <c r="A259" s="20">
+        <v>46199</v>
+      </c>
+      <c r="B259" s="13">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C259" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="D259" s="16">
+        <v>9905</v>
+      </c>
+      <c r="E259" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="F259" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="G259" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="H259" t="s">
+        <v>17</v>
+      </c>
+      <c r="I259" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J259" s="11" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="260" spans="1:10">
-      <c r="A260" s="22"/>
+      <c r="A260" s="20"/>
       <c r="B260" s="13"/>
       <c r="C260" s="10"/>
       <c r="D260" s="16"/>
@@ -9769,7 +9822,7 @@
       <c r="J260" s="11"/>
     </row>
     <row r="261" spans="1:10">
-      <c r="A261" s="22"/>
+      <c r="A261" s="20"/>
       <c r="B261" s="13"/>
       <c r="C261" s="10"/>
       <c r="D261" s="16"/>
@@ -9780,7 +9833,7 @@
       <c r="J261" s="11"/>
     </row>
     <row r="262" spans="1:10">
-      <c r="A262" s="22"/>
+      <c r="A262" s="20"/>
       <c r="B262" s="13"/>
       <c r="C262" s="10"/>
       <c r="D262" s="16"/>
@@ -9791,7 +9844,7 @@
       <c r="J262" s="11"/>
     </row>
     <row r="263" spans="1:10">
-      <c r="A263" s="22"/>
+      <c r="A263" s="20"/>
       <c r="B263" s="13"/>
       <c r="C263" s="10"/>
       <c r="D263" s="16"/>
@@ -9802,7 +9855,7 @@
       <c r="J263" s="11"/>
     </row>
     <row r="264" spans="1:10">
-      <c r="A264" s="22"/>
+      <c r="A264" s="20"/>
       <c r="B264" s="13"/>
       <c r="C264" s="10"/>
       <c r="D264" s="16"/>
@@ -9813,7 +9866,7 @@
       <c r="J264" s="11"/>
     </row>
     <row r="265" spans="1:10">
-      <c r="A265" s="22"/>
+      <c r="A265" s="20"/>
       <c r="B265" s="13"/>
       <c r="C265" s="10"/>
       <c r="D265" s="16"/>
@@ -9824,7 +9877,7 @@
       <c r="J265" s="11"/>
     </row>
     <row r="266" spans="1:10">
-      <c r="A266" s="22"/>
+      <c r="A266" s="20"/>
       <c r="B266" s="13"/>
       <c r="C266" s="10"/>
       <c r="D266" s="16"/>
@@ -9835,7 +9888,7 @@
       <c r="J266" s="11"/>
     </row>
     <row r="267" spans="1:10">
-      <c r="A267" s="22"/>
+      <c r="A267" s="20"/>
       <c r="B267" s="13"/>
       <c r="C267" s="10"/>
       <c r="D267" s="16"/>
@@ -9846,7 +9899,7 @@
       <c r="J267" s="11"/>
     </row>
     <row r="268" spans="1:10">
-      <c r="A268" s="22"/>
+      <c r="A268" s="20"/>
       <c r="B268" s="13"/>
       <c r="C268" s="10"/>
       <c r="D268" s="16"/>
@@ -9857,7 +9910,7 @@
       <c r="J268" s="11"/>
     </row>
     <row r="269" spans="1:10">
-      <c r="A269" s="22"/>
+      <c r="A269" s="20"/>
       <c r="B269" s="13"/>
       <c r="C269" s="10"/>
       <c r="D269" s="16"/>
@@ -9868,7 +9921,7 @@
       <c r="J269" s="11"/>
     </row>
     <row r="270" spans="1:10">
-      <c r="A270" s="22"/>
+      <c r="A270" s="20"/>
       <c r="B270" s="13"/>
       <c r="C270" s="10"/>
       <c r="D270" s="16"/>
@@ -9879,7 +9932,7 @@
       <c r="J270" s="11"/>
     </row>
     <row r="271" spans="1:10">
-      <c r="A271" s="22"/>
+      <c r="A271" s="20"/>
       <c r="B271" s="13"/>
       <c r="C271" s="10"/>
       <c r="D271" s="16"/>
@@ -9890,7 +9943,7 @@
       <c r="J271" s="11"/>
     </row>
     <row r="272" spans="1:10">
-      <c r="A272" s="22"/>
+      <c r="A272" s="20"/>
       <c r="B272" s="13"/>
       <c r="C272" s="10"/>
       <c r="D272" s="16"/>
@@ -9901,7 +9954,7 @@
       <c r="J272" s="11"/>
     </row>
     <row r="273" spans="1:10">
-      <c r="A273" s="22"/>
+      <c r="A273" s="20"/>
       <c r="B273" s="13"/>
       <c r="C273" s="10"/>
       <c r="D273" s="16"/>
@@ -9912,7 +9965,7 @@
       <c r="J273" s="11"/>
     </row>
     <row r="274" spans="1:10">
-      <c r="A274" s="22"/>
+      <c r="A274" s="20"/>
       <c r="B274" s="13"/>
       <c r="C274" s="10"/>
       <c r="D274" s="16"/>
@@ -9923,7 +9976,7 @@
       <c r="J274" s="11"/>
     </row>
     <row r="275" spans="1:10">
-      <c r="A275" s="22"/>
+      <c r="A275" s="20"/>
       <c r="B275" s="13"/>
       <c r="C275" s="10"/>
       <c r="D275" s="16"/>
@@ -9934,7 +9987,7 @@
       <c r="J275" s="11"/>
     </row>
     <row r="276" spans="1:10">
-      <c r="A276" s="22"/>
+      <c r="A276" s="20"/>
       <c r="B276" s="13"/>
       <c r="C276" s="10"/>
       <c r="D276" s="16"/>
@@ -9945,7 +9998,7 @@
       <c r="J276" s="11"/>
     </row>
     <row r="277" spans="1:10">
-      <c r="A277" s="22"/>
+      <c r="A277" s="20"/>
       <c r="B277" s="13"/>
       <c r="C277" s="10"/>
       <c r="D277" s="16"/>
@@ -9956,7 +10009,7 @@
       <c r="J277" s="11"/>
     </row>
     <row r="278" spans="1:10">
-      <c r="A278" s="22"/>
+      <c r="A278" s="20"/>
       <c r="B278" s="13"/>
       <c r="C278" s="10"/>
       <c r="D278" s="16"/>
@@ -9967,7 +10020,7 @@
       <c r="J278" s="11"/>
     </row>
     <row r="279" spans="1:10">
-      <c r="A279" s="22"/>
+      <c r="A279" s="20"/>
       <c r="B279" s="13"/>
       <c r="C279" s="10"/>
       <c r="D279" s="16"/>
@@ -9978,7 +10031,7 @@
       <c r="J279" s="11"/>
     </row>
     <row r="280" spans="1:10">
-      <c r="A280" s="22"/>
+      <c r="A280" s="20"/>
       <c r="B280" s="13"/>
       <c r="C280" s="10"/>
       <c r="D280" s="16"/>
@@ -9989,7 +10042,7 @@
       <c r="J280" s="11"/>
     </row>
     <row r="281" spans="1:10">
-      <c r="A281" s="22"/>
+      <c r="A281" s="20"/>
       <c r="B281" s="13"/>
       <c r="C281" s="10"/>
       <c r="D281" s="16"/>
@@ -10000,7 +10053,7 @@
       <c r="J281" s="11"/>
     </row>
     <row r="282" spans="1:10">
-      <c r="A282" s="22"/>
+      <c r="A282" s="20"/>
       <c r="B282" s="13"/>
       <c r="C282" s="10"/>
       <c r="D282" s="16"/>
@@ -10011,7 +10064,7 @@
       <c r="J282" s="11"/>
     </row>
     <row r="283" spans="1:10">
-      <c r="A283" s="22"/>
+      <c r="A283" s="20"/>
       <c r="B283" s="13"/>
       <c r="C283" s="10"/>
       <c r="D283" s="16"/>
@@ -10022,7 +10075,7 @@
       <c r="J283" s="11"/>
     </row>
     <row r="284" spans="1:10">
-      <c r="A284" s="22"/>
+      <c r="A284" s="20"/>
       <c r="B284" s="13"/>
       <c r="C284" s="10"/>
       <c r="D284" s="16"/>
@@ -10033,7 +10086,7 @@
       <c r="J284" s="11"/>
     </row>
     <row r="285" spans="1:10">
-      <c r="A285" s="22"/>
+      <c r="A285" s="20"/>
       <c r="B285" s="13"/>
       <c r="C285" s="10"/>
       <c r="D285" s="16"/>
@@ -10044,7 +10097,7 @@
       <c r="J285" s="11"/>
     </row>
     <row r="286" spans="1:10">
-      <c r="A286" s="22"/>
+      <c r="A286" s="20"/>
       <c r="B286" s="13"/>
       <c r="C286" s="10"/>
       <c r="D286" s="16"/>
@@ -10056,21 +10109,21 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H286">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>H2="Alta"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>H2="Media"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>H2="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J116 J230:J286">
-    <cfRule type="expression" dxfId="2" priority="9">
+    <cfRule type="expression" dxfId="1" priority="9">
       <formula>J2="Ejecutado"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="10">
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>J2="Pendiente"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10166,14 +10219,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="4" t="s">

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7567E5-A714-4D92-B67D-CDAA5A3D9826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B807F2F8-EA00-4873-A293-EFC8A8913E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1093,9 +1093,6 @@
     <t>actividad académica de Obstetricia</t>
   </si>
   <si>
-    <t>04 toldos / 06 mesas / 06 sillas / mantel para las mesas</t>
-  </si>
-  <si>
     <t>Liberación de mobiliario de auditorio desde las 4:00 p.m., Dejarlo sin sillas / Traslado de Letra C a ingreso a auditorio y durante tour llevarlo al jardín del Pabellón N / Colocar mesa de registro vestidas con 2 sillas en ingreso de Auditorio.                                                                                                                                               Jardín Pabellón N / Suspender regado de jardín del Pabellón N desde 24 de junio (habrá show de caballos) / Personal disponible para brindar accesos de corriente a productora desde las 4:00 p.m. Se colocará luminaria con reflectores. / Colocación de 8 pies de cancha en perímetro de jardín</t>
   </si>
   <si>
@@ -1109,6 +1106,9 @@
   </si>
   <si>
     <t>01 TOLDO / 01 MESA / 02 SILLAS / 01 PUNTO DE ENERGIA</t>
+  </si>
+  <si>
+    <t>04 toldos / 06 mesas / 06 sillas / 01 mantel por cada mesa</t>
   </si>
 </sst>
 </file>
@@ -1231,7 +1231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1294,6 +1294,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9606,7 +9609,7 @@
         <v>265</v>
       </c>
       <c r="G253" s="12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H253" t="s">
         <v>17</v>
@@ -9638,7 +9641,7 @@
         <v>322</v>
       </c>
       <c r="G254" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H254" t="s">
         <v>17</v>
@@ -9714,8 +9717,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="257" spans="1:10" ht="46.5" customHeight="1">
-      <c r="A257" s="20">
+    <row r="257" spans="1:10" ht="30.75" customHeight="1">
+      <c r="A257" s="24">
         <v>46207</v>
       </c>
       <c r="B257" s="13">
@@ -9733,8 +9736,8 @@
       <c r="F257" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="G257" s="12" t="s">
-        <v>333</v>
+      <c r="G257" s="10" t="s">
+        <v>338</v>
       </c>
       <c r="H257" t="s">
         <v>17</v>
@@ -9760,13 +9763,13 @@
         <v>9905</v>
       </c>
       <c r="E258" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="F258" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="F258" s="10" t="s">
+      <c r="G258" s="12" t="s">
         <v>337</v>
-      </c>
-      <c r="G258" s="12" t="s">
-        <v>338</v>
       </c>
       <c r="H258" t="s">
         <v>17</v>
@@ -9792,13 +9795,13 @@
         <v>9905</v>
       </c>
       <c r="E259" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="F259" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="F259" s="10" t="s">
+      <c r="G259" s="12" t="s">
         <v>337</v>
-      </c>
-      <c r="G259" s="12" t="s">
-        <v>338</v>
       </c>
       <c r="H259" t="s">
         <v>17</v>
@@ -9861,7 +9864,7 @@
       <c r="D264" s="16"/>
       <c r="E264" s="10"/>
       <c r="F264" s="10"/>
-      <c r="G264" s="12"/>
+      <c r="G264" s="10"/>
       <c r="I264" s="10"/>
       <c r="J264" s="11"/>
     </row>

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B807F2F8-EA00-4873-A293-EFC8A8913E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5154D2DA-3321-49E0-B41B-2AFED8065213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1090,9 +1090,6 @@
     <t xml:space="preserve">FACULTAD DE OBSTETRICIA </t>
   </si>
   <si>
-    <t>actividad académica de Obstetricia</t>
-  </si>
-  <si>
     <t>Liberación de mobiliario de auditorio desde las 4:00 p.m., Dejarlo sin sillas / Traslado de Letra C a ingreso a auditorio y durante tour llevarlo al jardín del Pabellón N / Colocar mesa de registro vestidas con 2 sillas en ingreso de Auditorio.                                                                                                                                               Jardín Pabellón N / Suspender regado de jardín del Pabellón N desde 24 de junio (habrá show de caballos) / Personal disponible para brindar accesos de corriente a productora desde las 4:00 p.m. Se colocará luminaria con reflectores. / Colocación de 8 pies de cancha en perímetro de jardín</t>
   </si>
   <si>
@@ -1109,6 +1106,9 @@
   </si>
   <si>
     <t>04 toldos / 06 mesas / 06 sillas / 01 mantel por cada mesa</t>
+  </si>
+  <si>
+    <t>Carrera Obstetricia</t>
   </si>
 </sst>
 </file>
@@ -1231,7 +1231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1290,12 +1290,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9609,7 +9612,7 @@
         <v>265</v>
       </c>
       <c r="G253" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H253" t="s">
         <v>17</v>
@@ -9641,7 +9644,7 @@
         <v>322</v>
       </c>
       <c r="G254" s="12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H254" t="s">
         <v>17</v>
@@ -9718,7 +9721,7 @@
       </c>
     </row>
     <row r="257" spans="1:10" ht="30.75" customHeight="1">
-      <c r="A257" s="24">
+      <c r="A257" s="22">
         <v>46207</v>
       </c>
       <c r="B257" s="13">
@@ -9731,13 +9734,13 @@
         <v>28</v>
       </c>
       <c r="E257" s="10" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="F257" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="G257" s="10" t="s">
-        <v>338</v>
+      <c r="G257" s="25" t="s">
+        <v>337</v>
       </c>
       <c r="H257" t="s">
         <v>17</v>
@@ -9763,13 +9766,13 @@
         <v>9905</v>
       </c>
       <c r="E258" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="F258" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="F258" s="10" t="s">
+      <c r="G258" s="12" t="s">
         <v>336</v>
-      </c>
-      <c r="G258" s="12" t="s">
-        <v>337</v>
       </c>
       <c r="H258" t="s">
         <v>17</v>
@@ -9795,13 +9798,13 @@
         <v>9905</v>
       </c>
       <c r="E259" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="F259" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="F259" s="10" t="s">
+      <c r="G259" s="12" t="s">
         <v>336</v>
-      </c>
-      <c r="G259" s="12" t="s">
-        <v>337</v>
       </c>
       <c r="H259" t="s">
         <v>17</v>
@@ -9831,7 +9834,6 @@
       <c r="D261" s="16"/>
       <c r="E261" s="10"/>
       <c r="F261" s="10"/>
-      <c r="G261" s="12"/>
       <c r="I261" s="10"/>
       <c r="J261" s="11"/>
     </row>
@@ -10222,14 +10224,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="4" t="s">

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5154D2DA-3321-49E0-B41B-2AFED8065213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3970AA40-3FBE-4AE2-A713-3A7B4F18E3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVENTOS" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2475" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2489" uniqueCount="342">
   <si>
     <t>Fecha</t>
   </si>
@@ -1109,6 +1109,15 @@
   </si>
   <si>
     <t>Carrera Obstetricia</t>
+  </si>
+  <si>
+    <t>COMPETENCIA FEDUP</t>
+  </si>
+  <si>
+    <t>CANCHA DE BASQUET</t>
+  </si>
+  <si>
+    <t>04 PIES DE CANCHA / DEJAR TRAPOS DE LIMPIEZA / DEJAR ESCOBA 7 01 PUNTO DE ENERGIA</t>
   </si>
 </sst>
 </file>
@@ -1293,13 +1302,13 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9739,7 +9748,7 @@
       <c r="F257" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="G257" s="25" t="s">
+      <c r="G257" s="23" t="s">
         <v>337</v>
       </c>
       <c r="H257" t="s">
@@ -9816,26 +9825,69 @@
         <v>86</v>
       </c>
     </row>
-    <row r="260" spans="1:10">
-      <c r="A260" s="20"/>
-      <c r="B260" s="13"/>
-      <c r="C260" s="10"/>
-      <c r="D260" s="16"/>
-      <c r="E260" s="10"/>
-      <c r="F260" s="10"/>
-      <c r="G260" s="12"/>
-      <c r="I260" s="10"/>
-      <c r="J260" s="11"/>
-    </row>
-    <row r="261" spans="1:10">
-      <c r="A261" s="20"/>
-      <c r="B261" s="13"/>
-      <c r="C261" s="10"/>
-      <c r="D261" s="16"/>
-      <c r="E261" s="10"/>
-      <c r="F261" s="10"/>
-      <c r="I261" s="10"/>
-      <c r="J261" s="11"/>
+    <row r="260" spans="1:10" ht="28.5">
+      <c r="A260" s="20">
+        <v>46200</v>
+      </c>
+      <c r="B260" s="13">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C260" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D260" s="16">
+        <v>9930</v>
+      </c>
+      <c r="E260" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="F260" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="G260" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="H260" t="s">
+        <v>17</v>
+      </c>
+      <c r="I260" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J260" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" ht="28.5">
+      <c r="A261" s="20">
+        <v>46201</v>
+      </c>
+      <c r="B261" s="13">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C261" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D261" s="16">
+        <v>9930</v>
+      </c>
+      <c r="E261" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="F261" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="G261" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="H261" t="s">
+        <v>17</v>
+      </c>
+      <c r="I261" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J261" s="11" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="262" spans="1:10">
       <c r="A262" s="20"/>
@@ -10224,14 +10276,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="4" t="s">

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3970AA40-3FBE-4AE2-A713-3A7B4F18E3E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0847ACD2-BE34-4BB5-AF54-010EAAB3A016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVENTOS" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2489" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2545" uniqueCount="364">
   <si>
     <t>Fecha</t>
   </si>
@@ -1022,15 +1022,6 @@
     <t>AREA DE ING. AMBIENTAL</t>
   </si>
   <si>
-    <t>Vuela CIENTÍFICA: I festival universitario de aves</t>
-  </si>
-  <si>
-    <t>Jardin Lote 28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  4 toldos /  8 mesas con mantel / 16 sillas / Podio</t>
-  </si>
-  <si>
     <t xml:space="preserve">AREA VGU - DEPORTES </t>
   </si>
   <si>
@@ -1069,9 +1060,6 @@
     <t>Xplora tu Futuro</t>
   </si>
   <si>
-    <t xml:space="preserve">ANFITEATRO </t>
-  </si>
-  <si>
     <t>4 toldos / 4 mesas con mantel / 12 sillas / 4 conexiones eléctricas /2 extensiones</t>
   </si>
   <si>
@@ -1118,6 +1106,84 @@
   </si>
   <si>
     <t>04 PIES DE CANCHA / DEJAR TRAPOS DE LIMPIEZA / DEJAR ESCOBA 7 01 PUNTO DE ENERGIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASADIZO DEL N </t>
+  </si>
+  <si>
+    <t>05 MESAS / 10 SILLAS</t>
+  </si>
+  <si>
+    <t>FERIA EMPRESARIAL</t>
+  </si>
+  <si>
+    <t>INGRESO DEL PABELLON N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 MESAS / 15 SILLAS </t>
+  </si>
+  <si>
+    <t>No programado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANFITEATRO PABELLON I </t>
+  </si>
+  <si>
+    <t>Vuela CIENTÍFICA</t>
+  </si>
+  <si>
+    <t>LOTE 28</t>
+  </si>
+  <si>
+    <t>04 TOLDOS / 08 MESAS / 16 SILLAS / 01 PODIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVESTIGACION </t>
+  </si>
+  <si>
+    <t>EVENTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUDITORIO - PABELLON O </t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 PODIUM / 1 MESA PARA LAPTOP / 03 MESAS COFFE BREAK </t>
+  </si>
+  <si>
+    <t>UZIT</t>
+  </si>
+  <si>
+    <t>VETERINARIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/ TOLDOS / 06 MESAS / 18 SILLAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMPLEABILIDAD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELLER MINDSET EMPRENDEDOR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">08 MESAS / 60 SILLAS / 02 MESAS COFFE / 01 MESA REGISTRO </t>
+  </si>
+  <si>
+    <t>CLUB DE MINERIA Y CONSTRUCCION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 MESAS / 70 SILLAS / 3 SILLONES / 01 PODIUM </t>
+  </si>
+  <si>
+    <t>Habilitación ambientes-Talleres Culturales-Julio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMBIENTES VARIOS </t>
+  </si>
+  <si>
+    <t>Habilitación ambientes-Talleres Deportivos-Julio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espacio deportiva cultural / Lote 28 </t>
   </si>
 </sst>
 </file>
@@ -1240,7 +1306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1309,6 +1375,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1555,7 +1624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L286"/>
+  <dimension ref="A1:L283"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" style="15" customWidth="1"/>
@@ -9535,61 +9604,77 @@
         <v>28</v>
       </c>
       <c r="E250" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="F250" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="G250" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="H250" t="s">
+        <v>17</v>
+      </c>
+      <c r="I250" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J250" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" ht="28.5">
+      <c r="A251" s="20">
+        <v>46208</v>
+      </c>
+      <c r="B251" s="13">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C251" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="F250" s="10" t="s">
+      <c r="D251" s="16">
+        <v>9912</v>
+      </c>
+      <c r="E251" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="G250" s="12"/>
-      <c r="H250" t="s">
-        <v>17</v>
-      </c>
-      <c r="I250" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J250" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="251" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A251" s="20"/>
-      <c r="B251" s="13"/>
-      <c r="C251" s="10"/>
-      <c r="D251" s="16"/>
-      <c r="E251" s="10"/>
-      <c r="F251" s="10"/>
+      <c r="F251" s="10" t="s">
+        <v>315</v>
+      </c>
       <c r="G251" s="12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H251" t="s">
         <v>17</v>
       </c>
-      <c r="I251" s="10"/>
+      <c r="I251" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="J251" s="11" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="252" spans="1:10" ht="28.5">
+    <row r="252" spans="1:10" ht="93.75" customHeight="1">
       <c r="A252" s="20">
-        <v>46208</v>
+        <v>46199</v>
       </c>
       <c r="B252" s="13">
-        <v>0.29166666666666669</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="C252" s="10" t="s">
-        <v>316</v>
+        <v>251</v>
       </c>
       <c r="D252" s="16">
-        <v>9912</v>
+        <v>9901</v>
       </c>
       <c r="E252" s="10" t="s">
         <v>317</v>
       </c>
       <c r="F252" s="10" t="s">
-        <v>318</v>
+        <v>265</v>
       </c>
       <c r="G252" s="12" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="H252" t="s">
         <v>17</v>
@@ -9601,60 +9686,60 @@
         <v>86</v>
       </c>
     </row>
-    <row r="253" spans="1:10" ht="93.75" customHeight="1">
+    <row r="253" spans="1:10" ht="129.75" customHeight="1">
       <c r="A253" s="20">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B253" s="13">
-        <v>0.83333333333333337</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="C253" s="10" t="s">
         <v>251</v>
       </c>
       <c r="D253" s="16">
-        <v>9901</v>
+        <v>9902</v>
       </c>
       <c r="E253" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="F253" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="G253" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="H253" t="s">
+        <v>17</v>
+      </c>
+      <c r="I253" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J253" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10">
+      <c r="A254" s="20">
+        <v>46205</v>
+      </c>
+      <c r="B254" s="13">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C254" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="F253" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="G253" s="12" t="s">
-        <v>332</v>
-      </c>
-      <c r="H253" t="s">
-        <v>17</v>
-      </c>
-      <c r="I253" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J253" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="254" spans="1:10" ht="129.75" customHeight="1">
-      <c r="A254" s="20">
-        <v>46200</v>
-      </c>
-      <c r="B254" s="13">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="C254" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="D254" s="16">
-        <v>9902</v>
+      <c r="D254" s="16" t="s">
+        <v>28</v>
       </c>
       <c r="E254" s="10" t="s">
         <v>321</v>
       </c>
       <c r="F254" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="G254" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="G254" s="12" t="s">
-        <v>333</v>
-      </c>
       <c r="H254" t="s">
         <v>17</v>
       </c>
@@ -9665,18 +9750,18 @@
         <v>86</v>
       </c>
     </row>
-    <row r="255" spans="1:10">
+    <row r="255" spans="1:10" ht="51.75" customHeight="1">
       <c r="A255" s="20">
         <v>46205</v>
       </c>
       <c r="B255" s="13">
-        <v>0.29166666666666669</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="C255" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="D255" s="16" t="s">
-        <v>28</v>
+      <c r="D255" s="16">
+        <v>9916</v>
       </c>
       <c r="E255" s="10" t="s">
         <v>324</v>
@@ -9697,59 +9782,59 @@
         <v>86</v>
       </c>
     </row>
-    <row r="256" spans="1:10" ht="51.75" customHeight="1">
-      <c r="A256" s="20">
-        <v>46205</v>
+    <row r="256" spans="1:10" ht="30.75" customHeight="1">
+      <c r="A256" s="22">
+        <v>46207</v>
       </c>
       <c r="B256" s="13">
-        <v>0.41666666666666669</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="C256" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="D256" s="16">
-        <v>9916</v>
+      <c r="D256" s="16" t="s">
+        <v>28</v>
       </c>
       <c r="E256" s="10" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="F256" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="G256" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="G256" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="H256" t="s">
+        <v>17</v>
+      </c>
+      <c r="I256" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J256" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10">
+      <c r="A257" s="20">
+        <v>46198</v>
+      </c>
+      <c r="B257" s="13">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C257" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="D257" s="16">
+        <v>9905</v>
+      </c>
+      <c r="E257" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="H256" t="s">
-        <v>17</v>
-      </c>
-      <c r="I256" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J256" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="257" spans="1:10" ht="30.75" customHeight="1">
-      <c r="A257" s="22">
-        <v>46207</v>
-      </c>
-      <c r="B257" s="13">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="C257" s="10" t="s">
+      <c r="F257" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="D257" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E257" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="F257" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="G257" s="23" t="s">
-        <v>337</v>
+      <c r="G257" s="12" t="s">
+        <v>332</v>
       </c>
       <c r="H257" t="s">
         <v>17</v>
@@ -9763,7 +9848,7 @@
     </row>
     <row r="258" spans="1:10">
       <c r="A258" s="20">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B258" s="13">
         <v>0.33333333333333331</v>
@@ -9775,13 +9860,13 @@
         <v>9905</v>
       </c>
       <c r="E258" s="10" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="F258" s="10" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="G258" s="12" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="H258" t="s">
         <v>17</v>
@@ -9793,27 +9878,27 @@
         <v>86</v>
       </c>
     </row>
-    <row r="259" spans="1:10">
+    <row r="259" spans="1:10" ht="28.5">
       <c r="A259" s="20">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B259" s="13">
         <v>0.33333333333333331</v>
       </c>
       <c r="C259" s="10" t="s">
-        <v>251</v>
+        <v>21</v>
       </c>
       <c r="D259" s="16">
-        <v>9905</v>
+        <v>9930</v>
       </c>
       <c r="E259" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F259" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G259" s="12" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H259" t="s">
         <v>17</v>
@@ -9827,7 +9912,7 @@
     </row>
     <row r="260" spans="1:10" ht="28.5">
       <c r="A260" s="20">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="B260" s="13">
         <v>0.33333333333333331</v>
@@ -9839,13 +9924,13 @@
         <v>9930</v>
       </c>
       <c r="E260" s="10" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F260" s="10" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G260" s="12" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="H260" t="s">
         <v>17</v>
@@ -9857,114 +9942,261 @@
         <v>86</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="28.5">
+    <row r="261" spans="1:10">
       <c r="A261" s="20">
-        <v>46201</v>
+        <v>46205</v>
       </c>
       <c r="B261" s="13">
         <v>0.33333333333333331</v>
       </c>
       <c r="C261" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D261" s="16">
-        <v>9930</v>
+        <v>77</v>
+      </c>
+      <c r="D261" s="16" t="s">
+        <v>28</v>
       </c>
       <c r="E261" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="F261" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="G261" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="F261" s="10" t="s">
+      <c r="H261" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="I261" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J261" s="11" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10">
+      <c r="A262" s="20">
+        <v>46205</v>
+      </c>
+      <c r="B262" s="13">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C262" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D262" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E262" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="G261" s="12" t="s">
+      <c r="F262" s="10" t="s">
         <v>341</v>
       </c>
-      <c r="H261" t="s">
-        <v>17</v>
-      </c>
-      <c r="I261" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J261" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="262" spans="1:10">
-      <c r="A262" s="20"/>
-      <c r="B262" s="13"/>
-      <c r="C262" s="10"/>
-      <c r="D262" s="16"/>
-      <c r="E262" s="10"/>
-      <c r="F262" s="10"/>
-      <c r="G262" s="12"/>
-      <c r="I262" s="10"/>
-      <c r="J262" s="11"/>
+      <c r="G262" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="H262" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="I262" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J262" s="11" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="263" spans="1:10">
-      <c r="A263" s="20"/>
-      <c r="B263" s="13"/>
-      <c r="C263" s="10"/>
-      <c r="D263" s="16"/>
-      <c r="E263" s="10"/>
-      <c r="F263" s="10"/>
-      <c r="G263" s="12"/>
-      <c r="I263" s="10"/>
-      <c r="J263" s="11"/>
+      <c r="A263" s="20">
+        <v>46209</v>
+      </c>
+      <c r="B263" s="13">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C263" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="D263" s="16">
+        <v>82461</v>
+      </c>
+      <c r="E263" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="F263" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="G263" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="H263" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="I263" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J263" s="11" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="264" spans="1:10">
-      <c r="A264" s="20"/>
-      <c r="B264" s="13"/>
-      <c r="C264" s="10"/>
-      <c r="D264" s="16"/>
-      <c r="E264" s="10"/>
-      <c r="F264" s="10"/>
-      <c r="G264" s="10"/>
-      <c r="I264" s="10"/>
-      <c r="J264" s="11"/>
+      <c r="A264" s="20">
+        <v>46211</v>
+      </c>
+      <c r="B264" s="13">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C264" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="D264" s="16">
+        <v>82447</v>
+      </c>
+      <c r="E264" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="F264" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="G264" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="H264" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="I264" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J264" s="11" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="265" spans="1:10">
-      <c r="A265" s="20"/>
-      <c r="B265" s="13"/>
-      <c r="C265" s="10"/>
-      <c r="D265" s="16"/>
-      <c r="E265" s="10"/>
-      <c r="F265" s="10"/>
-      <c r="G265" s="12"/>
-      <c r="I265" s="10"/>
-      <c r="J265" s="11"/>
+      <c r="A265" s="20">
+        <v>46206</v>
+      </c>
+      <c r="B265" s="13">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C265" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="D265" s="16">
+        <v>82383</v>
+      </c>
+      <c r="E265" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="F265" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="G265" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="H265" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="I265" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J265" s="11" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="266" spans="1:10">
-      <c r="A266" s="20"/>
-      <c r="B266" s="13"/>
-      <c r="C266" s="10"/>
-      <c r="D266" s="16"/>
-      <c r="E266" s="10"/>
-      <c r="F266" s="10"/>
-      <c r="G266" s="12"/>
-      <c r="I266" s="10"/>
-      <c r="J266" s="11"/>
+      <c r="A266" s="20">
+        <v>46203</v>
+      </c>
+      <c r="B266" s="13">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C266" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D266" s="16">
+        <v>82338</v>
+      </c>
+      <c r="E266" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="F266" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="G266" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="H266" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="I266" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J266" s="11" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="267" spans="1:10">
-      <c r="A267" s="20"/>
-      <c r="B267" s="13"/>
-      <c r="C267" s="10"/>
-      <c r="D267" s="16"/>
-      <c r="E267" s="10"/>
-      <c r="F267" s="10"/>
-      <c r="G267" s="12"/>
-      <c r="I267" s="10"/>
-      <c r="J267" s="11"/>
+      <c r="A267" s="20">
+        <v>46204</v>
+      </c>
+      <c r="B267" s="13">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C267" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D267" s="16">
+        <v>9963</v>
+      </c>
+      <c r="E267" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="F267" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="G267" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="H267" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="I267" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J267" s="11" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="268" spans="1:10">
-      <c r="A268" s="20"/>
-      <c r="B268" s="13"/>
-      <c r="C268" s="10"/>
-      <c r="D268" s="16"/>
-      <c r="E268" s="10"/>
-      <c r="F268" s="10"/>
-      <c r="G268" s="12"/>
-      <c r="I268" s="10"/>
-      <c r="J268" s="11"/>
+      <c r="A268" s="20">
+        <v>46205</v>
+      </c>
+      <c r="B268" s="13">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="C268" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D268" s="16">
+        <v>9962</v>
+      </c>
+      <c r="E268" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="F268" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="G268" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="H268" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="I268" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J268" s="11" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="269" spans="1:10">
       <c r="A269" s="20"/>
@@ -10131,41 +10363,8 @@
       <c r="I283" s="10"/>
       <c r="J283" s="11"/>
     </row>
-    <row r="284" spans="1:10">
-      <c r="A284" s="20"/>
-      <c r="B284" s="13"/>
-      <c r="C284" s="10"/>
-      <c r="D284" s="16"/>
-      <c r="E284" s="10"/>
-      <c r="F284" s="10"/>
-      <c r="G284" s="12"/>
-      <c r="I284" s="10"/>
-      <c r="J284" s="11"/>
-    </row>
-    <row r="285" spans="1:10">
-      <c r="A285" s="20"/>
-      <c r="B285" s="13"/>
-      <c r="C285" s="10"/>
-      <c r="D285" s="16"/>
-      <c r="E285" s="10"/>
-      <c r="F285" s="10"/>
-      <c r="G285" s="12"/>
-      <c r="I285" s="10"/>
-      <c r="J285" s="11"/>
-    </row>
-    <row r="286" spans="1:10">
-      <c r="A286" s="20"/>
-      <c r="B286" s="13"/>
-      <c r="C286" s="10"/>
-      <c r="D286" s="16"/>
-      <c r="E286" s="10"/>
-      <c r="F286" s="10"/>
-      <c r="G286" s="12"/>
-      <c r="I286" s="10"/>
-      <c r="J286" s="11"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H286">
+  <conditionalFormatting sqref="H2:H283">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>H2="Alta"</formula>
     </cfRule>
@@ -10176,7 +10375,7 @@
       <formula>H2="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J116 J230:J286">
+  <conditionalFormatting sqref="J2:J116 J230:J283">
     <cfRule type="expression" dxfId="1" priority="9">
       <formula>J2="Ejecutado"</formula>
     </cfRule>

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3CABD6-FF20-4301-8BDB-BB64F332C879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D459EB0-7015-4FE1-96D5-0E62A9B2BD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2901" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2892" uniqueCount="411">
   <si>
     <t>Prioridad</t>
   </si>
@@ -1300,15 +1300,9 @@
     <t>2026-07-18</t>
   </si>
   <si>
-    <t>evento</t>
-  </si>
-  <si>
     <t>Clausura del Programa de Mentoría Beca 18</t>
   </si>
   <si>
-    <t>solicitus de mobiliarios</t>
-  </si>
-  <si>
     <t>2 MESAS CON MANTEL Y 4 SILLAS + 1 TOLDO</t>
   </si>
   <si>
@@ -1318,10 +1312,10 @@
     <t>Instalar el tatami a las 12:30 p.m. / desinstalar a las 5:00 p.m.</t>
   </si>
   <si>
-    <t>instalar 6 toldos de cientifica / 6 mesas / 18 sillas.</t>
-  </si>
-  <si>
     <t>70 sillas / 2 mesas con mantel, bandera cientific.</t>
+  </si>
+  <si>
+    <t>Solicitud de Mobiliario</t>
   </si>
 </sst>
 </file>
@@ -1753,7 +1747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L291"/>
+  <dimension ref="A1:L290"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13" style="9" customWidth="1"/>
@@ -9253,8 +9247,8 @@
       </c>
     </row>
     <row r="235" spans="1:12" ht="15">
-      <c r="A235" s="22" t="s">
-        <v>364</v>
+      <c r="A235" s="22">
+        <v>46211</v>
       </c>
       <c r="B235" s="14" t="s">
         <v>106</v>
@@ -10809,7 +10803,7 @@
         <v>388</v>
       </c>
       <c r="G283" s="7" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H283" s="1" t="s">
         <v>3</v>
@@ -10841,7 +10835,7 @@
         <v>388</v>
       </c>
       <c r="G284" s="7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H284" s="1" t="s">
         <v>3</v>
@@ -10855,25 +10849,25 @@
     </row>
     <row r="285" spans="1:10" ht="15">
       <c r="A285" s="22">
-        <v>46211</v>
-      </c>
-      <c r="B285" s="14" t="s">
-        <v>51</v>
+        <v>46214</v>
+      </c>
+      <c r="B285" s="14">
+        <v>0.375</v>
       </c>
       <c r="C285" s="7" t="s">
         <v>58</v>
       </c>
       <c r="D285" s="15">
-        <v>9935</v>
+        <v>9994</v>
       </c>
       <c r="E285" s="7" t="s">
         <v>405</v>
       </c>
       <c r="F285" s="7" t="s">
-        <v>321</v>
+        <v>254</v>
       </c>
       <c r="G285" s="7" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H285" s="1" t="s">
         <v>3</v>
@@ -10887,7 +10881,7 @@
     </row>
     <row r="286" spans="1:10" ht="15">
       <c r="A286" s="22">
-        <v>46214</v>
+        <v>46211</v>
       </c>
       <c r="B286" s="14">
         <v>0.375</v>
@@ -10896,17 +10890,17 @@
         <v>58</v>
       </c>
       <c r="D286" s="15">
-        <v>9994</v>
+        <v>10002</v>
       </c>
       <c r="E286" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="F286" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G286" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="F286" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="G286" s="7" t="s">
-        <v>412</v>
-      </c>
       <c r="H286" s="1" t="s">
         <v>3</v>
       </c>
@@ -10917,37 +10911,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="1:10" ht="15">
-      <c r="A287" s="22">
-        <v>46211</v>
-      </c>
-      <c r="B287" s="14">
-        <v>0.375</v>
-      </c>
-      <c r="C287" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D287" s="15">
-        <v>10002</v>
-      </c>
-      <c r="E287" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="F287" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="G287" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="H287" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I287" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J287" s="16" t="s">
-        <v>4</v>
-      </c>
+    <row r="287" spans="1:10">
+      <c r="A287" s="22"/>
+      <c r="B287" s="14"/>
+      <c r="C287" s="7"/>
+      <c r="D287" s="15"/>
+      <c r="E287" s="7"/>
+      <c r="F287" s="7"/>
+      <c r="G287" s="7"/>
+      <c r="H287" s="1"/>
+      <c r="I287" s="7"/>
+      <c r="J287" s="16"/>
     </row>
     <row r="288" spans="1:10">
       <c r="A288" s="22"/>
@@ -10985,20 +10959,8 @@
       <c r="I290" s="7"/>
       <c r="J290" s="16"/>
     </row>
-    <row r="291" spans="1:10">
-      <c r="A291" s="22"/>
-      <c r="B291" s="14"/>
-      <c r="C291" s="7"/>
-      <c r="D291" s="15"/>
-      <c r="E291" s="7"/>
-      <c r="F291" s="7"/>
-      <c r="G291" s="7"/>
-      <c r="H291" s="1"/>
-      <c r="I291" s="7"/>
-      <c r="J291" s="16"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H291">
+  <conditionalFormatting sqref="H2:H290">
     <cfRule type="expression" dxfId="4" priority="1">
       <formula>H2="Alta"</formula>
     </cfRule>
@@ -11009,7 +10971,7 @@
       <formula>H2="Baja"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J116 J230:J291">
+  <conditionalFormatting sqref="J2:J116 J230:J290">
     <cfRule type="expression" dxfId="1" priority="9">
       <formula>J2="Ejecutado"</formula>
     </cfRule>

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D459EB0-7015-4FE1-96D5-0E62A9B2BD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E62BC93-3710-410B-83C5-38D3EFED9228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVENTOS" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2892" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2864" uniqueCount="411">
   <si>
     <t>Prioridad</t>
   </si>
@@ -1582,6 +1582,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaEventosV4" displayName="TablaEventosV4" ref="A1:J16">
+  <autoFilter ref="A1:J16" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hora"/>
@@ -9664,9 +9665,7 @@
       </c>
     </row>
     <row r="248" spans="1:10" ht="15">
-      <c r="A248" s="22" t="s">
-        <v>399</v>
-      </c>
+      <c r="A248" s="22"/>
       <c r="B248" s="14" t="s">
         <v>237</v>
       </c>
@@ -9696,9 +9695,7 @@
       </c>
     </row>
     <row r="249" spans="1:10" ht="28.5">
-      <c r="A249" s="22" t="s">
-        <v>399</v>
-      </c>
+      <c r="A249" s="22"/>
       <c r="B249" s="14" t="s">
         <v>51</v>
       </c>
@@ -9728,9 +9725,7 @@
       </c>
     </row>
     <row r="250" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A250" s="22" t="s">
-        <v>399</v>
-      </c>
+      <c r="A250" s="22"/>
       <c r="B250" s="14" t="s">
         <v>51</v>
       </c>
@@ -9760,9 +9755,7 @@
       </c>
     </row>
     <row r="251" spans="1:10" ht="15">
-      <c r="A251" s="22" t="s">
-        <v>399</v>
-      </c>
+      <c r="A251" s="22"/>
       <c r="B251" s="14" t="s">
         <v>51</v>
       </c>
@@ -9856,9 +9849,7 @@
       </c>
     </row>
     <row r="254" spans="1:10" ht="28.5">
-      <c r="A254" s="22" t="s">
-        <v>399</v>
-      </c>
+      <c r="A254" s="22"/>
       <c r="B254" s="14" t="s">
         <v>151</v>
       </c>
@@ -9888,9 +9879,7 @@
       </c>
     </row>
     <row r="255" spans="1:10" ht="51.75" customHeight="1">
-      <c r="A255" s="22" t="s">
-        <v>399</v>
-      </c>
+      <c r="A255" s="22"/>
       <c r="B255" s="14" t="s">
         <v>137</v>
       </c>
@@ -9920,9 +9909,7 @@
       </c>
     </row>
     <row r="256" spans="1:10" ht="30.75" customHeight="1">
-      <c r="A256" s="22" t="s">
-        <v>234</v>
-      </c>
+      <c r="A256" s="22"/>
       <c r="B256" s="14" t="s">
         <v>106</v>
       </c>
@@ -9952,9 +9939,7 @@
       </c>
     </row>
     <row r="257" spans="1:10" ht="15">
-      <c r="A257" s="22" t="s">
-        <v>234</v>
-      </c>
+      <c r="A257" s="22"/>
       <c r="B257" s="14" t="s">
         <v>132</v>
       </c>
@@ -10016,9 +10001,7 @@
       </c>
     </row>
     <row r="259" spans="1:10" ht="28.5">
-      <c r="A259" s="22" t="s">
-        <v>234</v>
-      </c>
+      <c r="A259" s="22"/>
       <c r="B259" s="14" t="s">
         <v>117</v>
       </c>
@@ -10080,9 +10063,7 @@
       </c>
     </row>
     <row r="261" spans="1:10" ht="15">
-      <c r="A261" s="22" t="s">
-        <v>400</v>
-      </c>
+      <c r="A261" s="22"/>
       <c r="B261" s="14" t="s">
         <v>132</v>
       </c>
@@ -10112,9 +10093,7 @@
       </c>
     </row>
     <row r="262" spans="1:10" ht="15">
-      <c r="A262" s="22" t="s">
-        <v>400</v>
-      </c>
+      <c r="A262" s="22"/>
       <c r="B262" s="14" t="s">
         <v>137</v>
       </c>
@@ -10144,9 +10123,7 @@
       </c>
     </row>
     <row r="263" spans="1:10" ht="15">
-      <c r="A263" s="22" t="s">
-        <v>400</v>
-      </c>
+      <c r="A263" s="22"/>
       <c r="B263" s="14" t="s">
         <v>143</v>
       </c>
@@ -10240,9 +10217,7 @@
       </c>
     </row>
     <row r="266" spans="1:10" ht="28.5">
-      <c r="A266" s="22" t="s">
-        <v>401</v>
-      </c>
+      <c r="A266" s="22"/>
       <c r="B266" s="14" t="s">
         <v>117</v>
       </c>
@@ -10304,9 +10279,7 @@
       </c>
     </row>
     <row r="268" spans="1:10" ht="15">
-      <c r="A268" s="22" t="s">
-        <v>402</v>
-      </c>
+      <c r="A268" s="22"/>
       <c r="B268" s="14" t="s">
         <v>151</v>
       </c>
@@ -10336,9 +10309,7 @@
       </c>
     </row>
     <row r="269" spans="1:10" ht="28.5">
-      <c r="A269" s="22" t="s">
-        <v>402</v>
-      </c>
+      <c r="A269" s="22"/>
       <c r="B269" s="14" t="s">
         <v>137</v>
       </c>
@@ -10368,9 +10339,7 @@
       </c>
     </row>
     <row r="270" spans="1:10" ht="15">
-      <c r="A270" s="22" t="s">
-        <v>402</v>
-      </c>
+      <c r="A270" s="22"/>
       <c r="B270" s="14" t="s">
         <v>137</v>
       </c>
@@ -10400,9 +10369,7 @@
       </c>
     </row>
     <row r="271" spans="1:10" ht="28.5">
-      <c r="A271" s="22" t="s">
-        <v>402</v>
-      </c>
+      <c r="A271" s="22"/>
       <c r="B271" s="14" t="s">
         <v>143</v>
       </c>
@@ -10432,9 +10399,7 @@
       </c>
     </row>
     <row r="272" spans="1:10" ht="15">
-      <c r="A272" s="22" t="s">
-        <v>403</v>
-      </c>
+      <c r="A272" s="22"/>
       <c r="B272" s="14" t="s">
         <v>106</v>
       </c>
@@ -10496,9 +10461,7 @@
       </c>
     </row>
     <row r="274" spans="1:10" ht="28.5">
-      <c r="A274" s="22" t="s">
-        <v>403</v>
-      </c>
+      <c r="A274" s="22"/>
       <c r="B274" s="14" t="s">
         <v>161</v>
       </c>
@@ -10528,9 +10491,7 @@
       </c>
     </row>
     <row r="275" spans="1:10" ht="15">
-      <c r="A275" s="22" t="s">
-        <v>403</v>
-      </c>
+      <c r="A275" s="22"/>
       <c r="B275" s="14" t="s">
         <v>130</v>
       </c>
@@ -10560,9 +10521,7 @@
       </c>
     </row>
     <row r="276" spans="1:10" ht="28.5">
-      <c r="A276" s="22" t="s">
-        <v>403</v>
-      </c>
+      <c r="A276" s="22"/>
       <c r="B276" s="14" t="s">
         <v>132</v>
       </c>
@@ -10592,9 +10551,7 @@
       </c>
     </row>
     <row r="277" spans="1:10" ht="15">
-      <c r="A277" s="22" t="s">
-        <v>404</v>
-      </c>
+      <c r="A277" s="22"/>
       <c r="B277" s="14" t="s">
         <v>237</v>
       </c>
@@ -10624,9 +10581,7 @@
       </c>
     </row>
     <row r="278" spans="1:10" ht="28.5">
-      <c r="A278" s="22" t="s">
-        <v>404</v>
-      </c>
+      <c r="A278" s="22"/>
       <c r="B278" s="14" t="s">
         <v>51</v>
       </c>
@@ -10656,9 +10611,7 @@
       </c>
     </row>
     <row r="279" spans="1:10" ht="42.75">
-      <c r="A279" s="22" t="s">
-        <v>404</v>
-      </c>
+      <c r="A279" s="22"/>
       <c r="B279" s="14" t="s">
         <v>51</v>
       </c>
@@ -10688,9 +10641,7 @@
       </c>
     </row>
     <row r="280" spans="1:10" ht="15">
-      <c r="A280" s="22" t="s">
-        <v>404</v>
-      </c>
+      <c r="A280" s="22"/>
       <c r="B280" s="14" t="s">
         <v>51</v>
       </c>
@@ -10752,9 +10703,7 @@
       </c>
     </row>
     <row r="282" spans="1:10" ht="42.75">
-      <c r="A282" s="22" t="s">
-        <v>404</v>
-      </c>
+      <c r="A282" s="22"/>
       <c r="B282" s="14" t="s">
         <v>106</v>
       </c>
@@ -10784,9 +10733,7 @@
       </c>
     </row>
     <row r="283" spans="1:10" ht="28.5">
-      <c r="A283" s="22" t="s">
-        <v>404</v>
-      </c>
+      <c r="A283" s="22"/>
       <c r="B283" s="14" t="s">
         <v>151</v>
       </c>
@@ -10816,9 +10763,7 @@
       </c>
     </row>
     <row r="284" spans="1:10" ht="28.5">
-      <c r="A284" s="22" t="s">
-        <v>404</v>
-      </c>
+      <c r="A284" s="22"/>
       <c r="B284" s="14" t="s">
         <v>137</v>
       </c>

--- a/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
+++ b/PLANTILLA CONTROL EVENTOS CAMPUS VILLA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FCHAVEZC\Desktop\DASBOARD_EVENTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E62BC93-3710-410B-83C5-38D3EFED9228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75233EFC-E9FD-404B-A544-434EA229DE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EVENTOS" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2864" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2860" uniqueCount="409">
   <si>
     <t>Prioridad</t>
   </si>
@@ -787,12 +787,6 @@
   </si>
   <si>
     <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>2026-07-20</t>
-  </si>
-  <si>
-    <t>2026-07-27</t>
   </si>
   <si>
     <t>07:00</t>
@@ -7071,9 +7065,7 @@
       </c>
     </row>
     <row r="167" spans="1:10" ht="15">
-      <c r="A167" s="22" t="s">
-        <v>234</v>
-      </c>
+      <c r="A167" s="22"/>
       <c r="B167" s="14" t="s">
         <v>51</v>
       </c>
@@ -7103,9 +7095,7 @@
       </c>
     </row>
     <row r="168" spans="1:10" ht="15">
-      <c r="A168" s="22" t="s">
-        <v>235</v>
-      </c>
+      <c r="A168" s="22"/>
       <c r="B168" s="14" t="s">
         <v>51</v>
       </c>
@@ -7135,9 +7125,7 @@
       </c>
     </row>
     <row r="169" spans="1:10" ht="15">
-      <c r="A169" s="22" t="s">
-        <v>236</v>
-      </c>
+      <c r="A169" s="22"/>
       <c r="B169" s="14" t="s">
         <v>51</v>
       </c>
@@ -7171,22 +7159,22 @@
         <v>150</v>
       </c>
       <c r="B170" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="D170" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="C170" s="7" t="s">
+      <c r="E170" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="D170" s="15" t="s">
+      <c r="F170" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="E170" s="7" t="s">
+      <c r="G170" s="7" t="s">
         <v>240</v>
-      </c>
-      <c r="F170" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="G170" s="7" t="s">
-        <v>242</v>
       </c>
       <c r="H170" s="1" t="s">
         <v>3</v>
@@ -7206,19 +7194,19 @@
         <v>51</v>
       </c>
       <c r="C171" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D171" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E171" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="F171" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="D171" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E171" s="7" t="s">
+      <c r="G171" s="7" t="s">
         <v>244</v>
-      </c>
-      <c r="F171" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="G171" s="7" t="s">
-        <v>246</v>
       </c>
       <c r="H171" s="1" t="s">
         <v>3</v>
@@ -7235,22 +7223,22 @@
         <v>150</v>
       </c>
       <c r="B172" s="14" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C172" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="D172" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="E172" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="D172" s="15" t="s">
+      <c r="F172" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="E172" s="7" t="s">
+      <c r="G172" s="7" t="s">
         <v>249</v>
-      </c>
-      <c r="F172" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="G172" s="7" t="s">
-        <v>251</v>
       </c>
       <c r="H172" s="1" t="s">
         <v>3</v>
@@ -7273,16 +7261,16 @@
         <v>58</v>
       </c>
       <c r="D173" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="E173" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F173" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="E173" s="7" t="s">
+      <c r="G173" s="7" t="s">
         <v>253</v>
-      </c>
-      <c r="F173" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="G173" s="7" t="s">
-        <v>255</v>
       </c>
       <c r="H173" s="1" t="s">
         <v>3</v>
@@ -7302,19 +7290,19 @@
         <v>161</v>
       </c>
       <c r="C174" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D174" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="E174" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="D174" s="15" t="s">
+      <c r="F174" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G174" s="7" t="s">
         <v>257</v>
-      </c>
-      <c r="E174" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="F174" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="G174" s="7" t="s">
-        <v>259</v>
       </c>
       <c r="H174" s="1" t="s">
         <v>3</v>
@@ -7328,25 +7316,25 @@
     </row>
     <row r="175" spans="1:10" ht="57">
       <c r="A175" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="B175" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D175" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="B175" s="14" t="s">
+      <c r="E175" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="C175" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="D175" s="15" t="s">
+      <c r="F175" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G175" s="7" t="s">
         <v>262</v>
-      </c>
-      <c r="E175" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="F175" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="G175" s="7" t="s">
-        <v>264</v>
       </c>
       <c r="H175" s="1" t="s">
         <v>3</v>
@@ -7360,25 +7348,25 @@
     </row>
     <row r="176" spans="1:10" ht="42.75">
       <c r="A176" s="22" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B176" s="14" t="s">
         <v>132</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D176" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="E176" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="F176" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G176" s="7" t="s">
         <v>266</v>
-      </c>
-      <c r="E176" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="F176" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="G176" s="7" t="s">
-        <v>268</v>
       </c>
       <c r="H176" s="1" t="s">
         <v>3</v>
@@ -7392,25 +7380,25 @@
     </row>
     <row r="177" spans="1:10" ht="42.75">
       <c r="A177" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="B177" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D177" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="E177" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="B177" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="C177" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="D177" s="15" t="s">
+      <c r="F177" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G177" s="7" t="s">
         <v>270</v>
-      </c>
-      <c r="E177" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="F177" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="G177" s="7" t="s">
-        <v>272</v>
       </c>
       <c r="H177" s="1" t="s">
         <v>3</v>
@@ -7424,25 +7412,25 @@
     </row>
     <row r="178" spans="1:10" ht="71.25">
       <c r="A178" s="22" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B178" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D178" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="E178" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="C178" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="D178" s="15" t="s">
+      <c r="F178" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G178" s="7" t="s">
         <v>274</v>
-      </c>
-      <c r="E178" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="F178" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="G178" s="7" t="s">
-        <v>276</v>
       </c>
       <c r="H178" s="1" t="s">
         <v>3</v>
@@ -7462,19 +7450,19 @@
         <v>51</v>
       </c>
       <c r="C179" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D179" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="E179" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="D179" s="15" t="s">
+      <c r="F179" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G179" s="7" t="s">
         <v>278</v>
-      </c>
-      <c r="E179" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="F179" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="G179" s="7" t="s">
-        <v>280</v>
       </c>
       <c r="H179" s="1" t="s">
         <v>3</v>
@@ -7494,19 +7482,19 @@
         <v>106</v>
       </c>
       <c r="C180" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="D180" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="E180" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="D180" s="15" t="s">
+      <c r="F180" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="E180" s="7" t="s">
+      <c r="G180" s="7" t="s">
         <v>283</v>
-      </c>
-      <c r="F180" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="G180" s="7" t="s">
-        <v>285</v>
       </c>
       <c r="H180" s="1" t="s">
         <v>3</v>
@@ -7526,19 +7514,19 @@
         <v>137</v>
       </c>
       <c r="C181" s="7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D181" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="E181" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="F181" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E181" s="7" t="s">
+      <c r="G181" s="7" t="s">
         <v>287</v>
-      </c>
-      <c r="F181" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="G181" s="7" t="s">
-        <v>289</v>
       </c>
       <c r="H181" s="1" t="s">
         <v>3</v>
@@ -7555,22 +7543,22 @@
         <v>158</v>
       </c>
       <c r="B182" s="14" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C182" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="D182" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E182" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="F182" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="G182" s="7" t="s">
         <v>290</v>
-      </c>
-      <c r="D182" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E182" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="F182" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="G182" s="7" t="s">
-        <v>292</v>
       </c>
       <c r="H182" s="1" t="s">
         <v>3</v>
@@ -7587,22 +7575,22 @@
         <v>158</v>
       </c>
       <c r="B183" s="14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C183" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="D183" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="E183" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="D183" s="15" t="s">
+      <c r="F183" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G183" s="7" t="s">
         <v>294</v>
-      </c>
-      <c r="E183" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="F183" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="G183" s="7" t="s">
-        <v>296</v>
       </c>
       <c r="H183" s="1" t="s">
         <v>3</v>
@@ -7616,25 +7604,25 @@
     </row>
     <row r="184" spans="1:10" ht="28.5">
       <c r="A184" s="22" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B184" s="14" t="s">
         <v>130</v>
       </c>
       <c r="C184" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D184" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="E184" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="F184" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E184" s="7" t="s">
+      <c r="G184" s="7" t="s">
         <v>299</v>
-      </c>
-      <c r="F184" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="G184" s="7" t="s">
-        <v>301</v>
       </c>
       <c r="H184" s="1" t="s">
         <v>3</v>
@@ -7648,25 +7636,25 @@
     </row>
     <row r="185" spans="1:10" ht="28.5">
       <c r="A185" s="22" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B185" s="14" t="s">
         <v>130</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D185" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="E185" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="F185" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G185" s="7" t="s">
         <v>303</v>
-      </c>
-      <c r="E185" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="F185" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="G185" s="7" t="s">
-        <v>305</v>
       </c>
       <c r="H185" s="1" t="s">
         <v>3</v>
@@ -7686,19 +7674,19 @@
         <v>130</v>
       </c>
       <c r="C186" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D186" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E186" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="F186" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="D186" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E186" s="7" t="s">
+      <c r="G186" s="7" t="s">
         <v>307</v>
-      </c>
-      <c r="F186" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="G186" s="7" t="s">
-        <v>309</v>
       </c>
       <c r="H186" s="1" t="s">
         <v>3</v>
@@ -7718,19 +7706,19 @@
         <v>106</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D187" s="15" t="s">
         <v>64</v>
       </c>
       <c r="E187" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="F187" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="G187" s="7" t="s">
         <v>310</v>
-      </c>
-      <c r="F187" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="G187" s="7" t="s">
-        <v>312</v>
       </c>
       <c r="H187" s="1" t="s">
         <v>3</v>
@@ -7750,19 +7738,19 @@
         <v>106</v>
       </c>
       <c r="C188" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D188" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="E188" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="D188" s="15" t="s">
+      <c r="F188" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="E188" s="7" t="s">
+      <c r="G188" s="7" t="s">
         <v>315</v>
-      </c>
-      <c r="F188" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="G188" s="7" t="s">
-        <v>317</v>
       </c>
       <c r="H188" s="1" t="s">
         <v>3</v>
@@ -7776,25 +7764,25 @@
     </row>
     <row r="189" spans="1:10" ht="28.5">
       <c r="A189" s="22" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B189" s="14" t="s">
         <v>67</v>
       </c>
       <c r="C189" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D189" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E189" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="F189" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="D189" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E189" s="7" t="s">
+      <c r="G189" s="7" t="s">
         <v>320</v>
-      </c>
-      <c r="F189" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="G189" s="7" t="s">
-        <v>322</v>
       </c>
       <c r="H189" s="1" t="s">
         <v>3</v>
@@ -7811,22 +7799,22 @@
         <v>158</v>
       </c>
       <c r="B190" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="D190" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="E190" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="C190" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="D190" s="15" t="s">
+      <c r="F190" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G190" s="7" t="s">
         <v>324</v>
-      </c>
-      <c r="E190" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="F190" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="G190" s="7" t="s">
-        <v>326</v>
       </c>
       <c r="H190" s="1" t="s">
         <v>3</v>
@@ -7846,19 +7834,19 @@
         <v>106</v>
       </c>
       <c r="C191" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D191" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="E191" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="F191" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="E191" s="7" t="s">
+      <c r="G191" s="7" t="s">
         <v>328</v>
-      </c>
-      <c r="F191" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="G191" s="7" t="s">
-        <v>330</v>
       </c>
       <c r="H191" s="1" t="s">
         <v>3</v>
@@ -7872,25 +7860,25 @@
     </row>
     <row r="192" spans="1:10" ht="28.5">
       <c r="A192" s="22" t="s">
+        <v>329</v>
+      </c>
+      <c r="B192" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="D192" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E192" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="B192" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="C192" s="7" t="s">
+      <c r="F192" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="D192" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E192" s="7" t="s">
+      <c r="G192" s="7" t="s">
         <v>333</v>
-      </c>
-      <c r="F192" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="G192" s="7" t="s">
-        <v>335</v>
       </c>
       <c r="H192" s="1" t="s">
         <v>3</v>
@@ -7904,25 +7892,25 @@
     </row>
     <row r="193" spans="1:10" ht="85.5">
       <c r="A193" s="22" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B193" s="14" t="s">
         <v>106</v>
       </c>
       <c r="C193" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="D193" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="E193" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="D193" s="15" t="s">
+      <c r="F193" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="E193" s="7" t="s">
+      <c r="G193" s="7" t="s">
         <v>338</v>
-      </c>
-      <c r="F193" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="G193" s="7" t="s">
-        <v>340</v>
       </c>
       <c r="H193" s="1" t="s">
         <v>3</v>
@@ -7936,25 +7924,25 @@
     </row>
     <row r="194" spans="1:10" ht="28.5">
       <c r="A194" s="22" t="s">
+        <v>339</v>
+      </c>
+      <c r="B194" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="C194" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="D194" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E194" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="F194" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="G194" s="7" t="s">
         <v>341</v>
-      </c>
-      <c r="B194" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="C194" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="D194" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E194" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="F194" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="G194" s="7" t="s">
-        <v>343</v>
       </c>
       <c r="H194" s="1" t="s">
         <v>3</v>
@@ -7974,19 +7962,19 @@
         <v>51</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D195" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="E195" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="F195" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="E195" s="7" t="s">
+      <c r="G195" s="7" t="s">
         <v>345</v>
-      </c>
-      <c r="F195" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="G195" s="7" t="s">
-        <v>347</v>
       </c>
       <c r="H195" s="1" t="s">
         <v>3</v>
@@ -8006,19 +7994,19 @@
         <v>51</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D196" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="E196" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="F196" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="E196" s="7" t="s">
+      <c r="G196" s="7" t="s">
         <v>345</v>
-      </c>
-      <c r="F196" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="G196" s="7" t="s">
-        <v>347</v>
       </c>
       <c r="H196" s="1" t="s">
         <v>3</v>
@@ -8041,16 +8029,16 @@
         <v>58</v>
       </c>
       <c r="D197" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="E197" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="F197" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="E197" s="7" t="s">
+      <c r="G197" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="F197" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="G197" s="7" t="s">
-        <v>351</v>
       </c>
       <c r="H197" s="1" t="s">
         <v>3</v>
@@ -8064,7 +8052,7 @@
     </row>
     <row r="198" spans="1:10" ht="42.75">
       <c r="A198" s="22" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B198" s="14" t="s">
         <v>51</v>
@@ -8073,16 +8061,16 @@
         <v>58</v>
       </c>
       <c r="D198" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="E198" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="F198" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="E198" s="7" t="s">
+      <c r="G198" s="7" t="s">
         <v>349</v>
-      </c>
-      <c r="F198" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="G198" s="7" t="s">
-        <v>351</v>
       </c>
       <c r="H198" s="1" t="s">
         <v>3</v>
@@ -8096,7 +8084,7 @@
     </row>
     <row r="199" spans="1:10" ht="15">
       <c r="A199" s="22" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B199" s="14" t="s">
         <v>51</v>
@@ -8108,27 +8096,27 @@
         <v>64</v>
       </c>
       <c r="E199" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="F199" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="G199" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="F199" s="7" t="s">
+      <c r="H199" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I199" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J199" s="16" t="s">
         <v>354</v>
-      </c>
-      <c r="G199" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="H199" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I199" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J199" s="16" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="200" spans="1:10" ht="15">
       <c r="A200" s="22" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B200" s="14" t="s">
         <v>51</v>
@@ -8140,13 +8128,13 @@
         <v>64</v>
       </c>
       <c r="E200" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G200" s="7" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H200" s="1" t="s">
         <v>3</v>
@@ -8155,7 +8143,7 @@
         <v>5</v>
       </c>
       <c r="J200" s="16" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="201" spans="1:10" ht="28.5">
@@ -8166,19 +8154,19 @@
         <v>132</v>
       </c>
       <c r="C201" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="D201" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="E201" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="D201" s="15" t="s">
+      <c r="F201" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="E201" s="7" t="s">
+      <c r="G201" s="7" t="s">
         <v>361</v>
-      </c>
-      <c r="F201" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="G201" s="7" t="s">
-        <v>363</v>
       </c>
       <c r="H201" s="1" t="s">
         <v>3</v>
@@ -8192,25 +8180,25 @@
     </row>
     <row r="202" spans="1:10" ht="15">
       <c r="A202" s="22" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B202" s="14" t="s">
         <v>51</v>
       </c>
       <c r="C202" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="D202" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="E202" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="D202" s="15" t="s">
+      <c r="F202" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="G202" s="7" t="s">
         <v>366</v>
-      </c>
-      <c r="E202" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="F202" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="G202" s="7" t="s">
-        <v>368</v>
       </c>
       <c r="H202" s="1" t="s">
         <v>3</v>
@@ -8224,7 +8212,7 @@
     </row>
     <row r="203" spans="1:10" ht="28.5">
       <c r="A203" s="22" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B203" s="14" t="s">
         <v>161</v>
@@ -8233,16 +8221,16 @@
         <v>111</v>
       </c>
       <c r="D203" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="E203" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="F203" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="G203" s="7" t="s">
         <v>369</v>
-      </c>
-      <c r="E203" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="F203" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="G203" s="7" t="s">
-        <v>371</v>
       </c>
       <c r="H203" s="1" t="s">
         <v>3</v>
@@ -8265,16 +8253,16 @@
         <v>111</v>
       </c>
       <c r="D204" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="E204" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="F204" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="G204" s="7" t="s">
         <v>372</v>
-      </c>
-      <c r="E204" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="F204" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="G204" s="7" t="s">
-        <v>374</v>
       </c>
       <c r="H204" s="1" t="s">
         <v>3</v>
@@ -8288,7 +8276,7 @@
     </row>
     <row r="205" spans="1:10" ht="15">
       <c r="A205" s="22" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B205" s="14" t="s">
         <v>141</v>
@@ -8300,14 +8288,14 @@
         <v>82622</v>
       </c>
       <c r="E205" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="F205" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="G205" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="F205" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="G205" s="7" t="s">
-        <v>377</v>
-      </c>
       <c r="H205" s="1" t="s">
         <v>3</v>
       </c>
@@ -8315,12 +8303,12 @@
         <v>5</v>
       </c>
       <c r="J205" s="16" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="206" spans="1:10" ht="15">
       <c r="A206" s="22" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B206" s="14" t="s">
         <v>106</v>
@@ -8329,7 +8317,7 @@
         <v>58</v>
       </c>
       <c r="D206" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E206" s="7" t="s">
         <v>222</v>
@@ -8352,7 +8340,7 @@
     </row>
     <row r="207" spans="1:10" ht="15">
       <c r="A207" s="22" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B207" s="14" t="s">
         <v>143</v>
@@ -8361,7 +8349,7 @@
         <v>58</v>
       </c>
       <c r="D207" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E207" s="7" t="s">
         <v>224</v>
@@ -8384,7 +8372,7 @@
     </row>
     <row r="208" spans="1:10" ht="28.5">
       <c r="A208" s="22" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B208" s="14" t="s">
         <v>117</v>
@@ -8393,7 +8381,7 @@
         <v>58</v>
       </c>
       <c r="D208" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E208" s="7" t="s">
         <v>118</v>
@@ -8402,7 +8390,7 @@
         <v>147</v>
       </c>
       <c r="G208" s="7" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="H208" s="1" t="s">
         <v>3</v>
@@ -8416,7 +8404,7 @@
     </row>
     <row r="209" spans="1:10" ht="15">
       <c r="A209" s="22" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B209" s="14" t="s">
         <v>106</v>
@@ -8425,7 +8413,7 @@
         <v>58</v>
       </c>
       <c r="D209" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E209" s="7" t="s">
         <v>225</v>
@@ -8448,7 +8436,7 @@
     </row>
     <row r="210" spans="1:10" ht="15">
       <c r="A210" s="22" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B210" s="14" t="s">
         <v>151</v>
@@ -8457,7 +8445,7 @@
         <v>58</v>
       </c>
       <c r="D210" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E210" s="7" t="s">
         <v>133</v>
@@ -8480,7 +8468,7 @@
     </row>
     <row r="211" spans="1:10" ht="28.5">
       <c r="A211" s="22" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B211" s="14" t="s">
         <v>137</v>
@@ -8489,7 +8477,7 @@
         <v>58</v>
       </c>
       <c r="D211" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E211" s="7" t="s">
         <v>138</v>
@@ -8512,7 +8500,7 @@
     </row>
     <row r="212" spans="1:10" ht="15">
       <c r="A212" s="22" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B212" s="14" t="s">
         <v>137</v>
@@ -8521,13 +8509,13 @@
         <v>58</v>
       </c>
       <c r="D212" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="E212" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="E212" s="7" t="s">
-        <v>382</v>
-      </c>
       <c r="F212" s="7" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G212" s="7" t="s">
         <v>221</v>
@@ -8544,7 +8532,7 @@
     </row>
     <row r="213" spans="1:10" ht="28.5">
       <c r="A213" s="22" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B213" s="14" t="s">
         <v>143</v>
@@ -8553,7 +8541,7 @@
         <v>58</v>
       </c>
       <c r="D213" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>144</v>
@@ -8576,7 +8564,7 @@
     </row>
     <row r="214" spans="1:10" ht="15">
       <c r="A214" s="22" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B214" s="14" t="s">
         <v>106</v>
@@ -8585,7 +8573,7 @@
         <v>58</v>
       </c>
       <c r="D214" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E214" s="7" t="s">
         <v>156</v>
@@ -8608,7 +8596,7 @@
     </row>
     <row r="215" spans="1:10" ht="15">
       <c r="A215" s="22" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B215" s="14" t="s">
         <v>106</v>
@@ -8617,7 +8605,7 @@
         <v>58</v>
       </c>
       <c r="D215" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E215" s="7" t="s">
         <v>222</v>
@@ -8640,7 +8628,7 @@
     </row>
     <row r="216" spans="1:10" ht="28.5">
       <c r="A216" s="22" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B216" s="14" t="s">
         <v>161</v>
@@ -8649,7 +8637,7 @@
         <v>58</v>
       </c>
       <c r="D216" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E216" s="7" t="s">
         <v>162</v>
@@ -8672,7 +8660,7 @@
     </row>
     <row r="217" spans="1:10" ht="15">
       <c r="A217" s="22" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B217" s="14" t="s">
         <v>130</v>
@@ -8681,7 +8669,7 @@
         <v>58</v>
       </c>
       <c r="D217" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E217" s="7" t="s">
         <v>156</v>
@@ -8704,7 +8692,7 @@
     </row>
     <row r="218" spans="1:10" ht="28.5">
       <c r="A218" s="22" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B218" s="14" t="s">
         <v>132</v>
@@ -8713,13 +8701,13 @@
         <v>58</v>
       </c>
       <c r="D218" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E218" s="7" t="s">
         <v>162</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G218" s="7" t="s">
         <v>140</v>
@@ -8736,25 +8724,25 @@
     </row>
     <row r="219" spans="1:10" ht="15">
       <c r="A219" s="22" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B219" s="14" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C219" s="7" t="s">
         <v>58</v>
       </c>
       <c r="D219" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E219" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="F219" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G219" s="7" t="s">
         <v>385</v>
-      </c>
-      <c r="F219" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="G219" s="7" t="s">
-        <v>387</v>
       </c>
       <c r="H219" s="1" t="s">
         <v>3</v>
@@ -8768,7 +8756,7 @@
     </row>
     <row r="220" spans="1:10" ht="28.5">
       <c r="A220" s="22" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B220" s="14" t="s">
         <v>51</v>
@@ -8777,16 +8765,16 @@
         <v>58</v>
       </c>
       <c r="D220" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E220" s="7" t="s">
         <v>227</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G220" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H220" s="1" t="s">
         <v>3</v>
@@ -8800,7 +8788,7 @@
     </row>
     <row r="221" spans="1:10" ht="42.75">
       <c r="A221" s="22" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B221" s="14" t="s">
         <v>51</v>
@@ -8809,16 +8797,16 @@
         <v>58</v>
       </c>
       <c r="D221" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F221" s="7" t="s">
         <v>61</v>
       </c>
       <c r="G221" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H221" s="1" t="s">
         <v>3</v>
@@ -8832,7 +8820,7 @@
     </row>
     <row r="222" spans="1:10" ht="15">
       <c r="A222" s="22" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B222" s="14" t="s">
         <v>51</v>
@@ -8841,16 +8829,16 @@
         <v>58</v>
       </c>
       <c r="D222" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F222" s="7" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G222" s="7" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H222" s="1" t="s">
         <v>3</v>
@@ -8864,7 +8852,7 @@
     </row>
     <row r="223" spans="1:10" ht="15">
       <c r="A223" s="22" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B223" s="14" t="s">
         <v>106</v>
@@ -8873,7 +8861,7 @@
         <v>58</v>
       </c>
       <c r="D223" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E223" s="7" t="s">
         <v>225</v>
@@ -8896,7 +8884,7 @@
     </row>
     <row r="224" spans="1:10" ht="42.75">
       <c r="A224" s="22" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B224" s="14" t="s">
         <v>106</v>
@@ -8905,16 +8893,16 @@
         <v>58</v>
       </c>
       <c r="D224" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E224" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F224" s="7" t="s">
         <v>61</v>
       </c>
       <c r="G224" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H224" s="1" t="s">
         <v>3</v>
@@ -8928,7 +8916,7 @@
     </row>
     <row r="225" spans="1:12" ht="28.5">
       <c r="A225" s="22" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B225" s="14" t="s">
         <v>151</v>
@@ -8937,16 +8925,16 @@
         <v>58</v>
       </c>
       <c r="D225" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E225" s="7" t="s">
         <v>228</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G225" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H225" s="1" t="s">
         <v>3</v>
@@ -8960,7 +8948,7 @@
     </row>
     <row r="226" spans="1:12" ht="28.5">
       <c r="A226" s="22" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B226" s="14" t="s">
         <v>137</v>
@@ -8969,16 +8957,16 @@
         <v>58</v>
       </c>
       <c r="D226" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E226" s="7" t="s">
         <v>229</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G226" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H226" s="1" t="s">
         <v>3</v>
@@ -9001,7 +8989,7 @@
         <v>58</v>
       </c>
       <c r="D227" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E227" s="7" t="s">
         <v>222</v>
@@ -9033,7 +9021,7 @@
         <v>58</v>
       </c>
       <c r="D228" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E228" s="7" t="s">
         <v>223</v>
@@ -9065,7 +9053,7 @@
         <v>58</v>
       </c>
       <c r="D229" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E229" s="7" t="s">
         <v>224</v>
@@ -9097,7 +9085,7 @@
         <v>58</v>
       </c>
       <c r="D230" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E230" s="7" t="s">
         <v>118</v>
@@ -9106,7 +9094,7 @@
         <v>119</v>
       </c>
       <c r="G230" s="7" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H230" s="1" t="s">
         <v>3</v>
@@ -9121,7 +9109,7 @@
     </row>
     <row r="231" spans="1:12" ht="15">
       <c r="A231" s="22" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B231" s="14" t="s">
         <v>106</v>
@@ -9130,7 +9118,7 @@
         <v>58</v>
       </c>
       <c r="D231" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E231" s="7" t="s">
         <v>225</v>
@@ -9153,7 +9141,7 @@
     </row>
     <row r="232" spans="1:12" ht="15">
       <c r="A232" s="22" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B232" s="14" t="s">
         <v>132</v>
@@ -9162,7 +9150,7 @@
         <v>58</v>
       </c>
       <c r="D232" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E232" s="7" t="s">
         <v>133</v>
@@ -9185,7 +9173,7 @@
     </row>
     <row r="233" spans="1:12" ht="15">
       <c r="A233" s="22" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B233" s="14" t="s">
         <v>137</v>
@@ -9194,7 +9182,7 @@
         <v>58</v>
       </c>
       <c r="D233" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E233" s="7" t="s">
         <v>124</v>
@@ -9203,7 +9191,7 @@
         <v>125</v>
       </c>
       <c r="G233" s="7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H233" s="1" t="s">
         <v>3</v>
@@ -9217,7 +9205,7 @@
     </row>
     <row r="234" spans="1:12" ht="15">
       <c r="A234" s="22" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B234" s="14" t="s">
         <v>143</v>
@@ -9226,7 +9214,7 @@
         <v>58</v>
       </c>
       <c r="D234" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E234" s="7" t="s">
         <v>131</v>
@@ -9235,7 +9223,7 @@
         <v>125</v>
       </c>
       <c r="G234" s="7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H234" s="1" t="s">
         <v>3</v>
@@ -9258,7 +9246,7 @@
         <v>58</v>
       </c>
       <c r="D235" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E235" s="7" t="s">
         <v>222</v>
@@ -9281,7 +9269,7 @@
     </row>
     <row r="236" spans="1:12" ht="15">
       <c r="A236" s="22" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B236" s="14" t="s">
         <v>143</v>
@@ -9290,7 +9278,7 @@
         <v>58</v>
       </c>
       <c r="D236" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E236" s="7" t="s">
         <v>224</v>
@@ -9313,7 +9301,7 @@
     </row>
     <row r="237" spans="1:12" ht="28.5">
       <c r="A237" s="22" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B237" s="14" t="s">
         <v>117</v>
@@ -9322,7 +9310,7 @@
         <v>58</v>
       </c>
       <c r="D237" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E237" s="7" t="s">
         <v>118</v>
@@ -9331,7 +9319,7 @@
         <v>147</v>
       </c>
       <c r="G237" s="7" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="H237" s="1" t="s">
         <v>3</v>
@@ -9345,7 +9333,7 @@
     </row>
     <row r="238" spans="1:12" ht="15">
       <c r="A238" s="22" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B238" s="14" t="s">
         <v>106</v>
@@ -9354,7 +9342,7 @@
         <v>58</v>
       </c>
       <c r="D238" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E238" s="7" t="s">
         <v>225</v>
@@ -9378,7 +9366,7 @@
     </row>
     <row r="239" spans="1:12" s="5" customFormat="1" ht="15">
       <c r="A239" s="22" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B239" s="14" t="s">
         <v>151</v>
@@ -9387,7 +9375,7 @@
         <v>58</v>
       </c>
       <c r="D239" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E239" s="7" t="s">
         <v>133</v>
@@ -9410,7 +9398,7 @@
     </row>
     <row r="240" spans="1:12" s="5" customFormat="1" ht="28.5">
       <c r="A240" s="22" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B240" s="14" t="s">
         <v>137</v>
@@ -9419,7 +9407,7 @@
         <v>58</v>
       </c>
       <c r="D240" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E240" s="7" t="s">
         <v>138</v>
@@ -9442,7 +9430,7 @@
     </row>
     <row r="241" spans="1:10" ht="15">
       <c r="A241" s="22" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B241" s="14" t="s">
         <v>137</v>
@@ -9451,13 +9439,13 @@
         <v>58</v>
       </c>
       <c r="D241" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="E241" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="E241" s="7" t="s">
-        <v>382</v>
-      </c>
       <c r="F241" s="7" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G241" s="7" t="s">
         <v>221</v>
@@ -9474,7 +9462,7 @@
     </row>
     <row r="242" spans="1:10" ht="28.5">
       <c r="A242" s="22" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B242" s="14" t="s">
         <v>143</v>
@@ -9483,7 +9471,7 @@
         <v>58</v>
       </c>
       <c r="D242" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E242" s="7" t="s">
         <v>144</v>
@@ -9506,7 +9494,7 @@
     </row>
     <row r="243" spans="1:10" ht="15">
       <c r="A243" s="22" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B243" s="14" t="s">
         <v>106</v>
@@ -9515,7 +9503,7 @@
         <v>58</v>
       </c>
       <c r="D243" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E243" s="7" t="s">
         <v>156</v>
@@ -9538,7 +9526,7 @@
     </row>
     <row r="244" spans="1:10" ht="15">
       <c r="A244" s="22" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B244" s="14" t="s">
         <v>106</v>
@@ -9547,7 +9535,7 @@
         <v>58</v>
       </c>
       <c r="D244" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E244" s="7" t="s">
         <v>222</v>
@@ -9570,7 +9558,7 @@
     </row>
     <row r="245" spans="1:10" ht="28.5">
       <c r="A245" s="22" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B245" s="14" t="s">
         <v>161</v>
@@ -9579,7 +9567,7 @@
         <v>58</v>
       </c>
       <c r="D245" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E245" s="7" t="s">
         <v>162</v>
@@ -9602,7 +9590,7 @@
     </row>
     <row r="246" spans="1:10" ht="15">
       <c r="A246" s="22" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B246" s="14" t="s">
         <v>130</v>
@@ -9611,7 +9599,7 @@
         <v>58</v>
       </c>
       <c r="D246" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E246" s="7" t="s">
         <v>156</v>
@@ -9634,7 +9622,7 @@
     </row>
     <row r="247" spans="1:10" ht="28.5">
       <c r="A247" s="22" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B247" s="14" t="s">
         <v>132</v>
@@ -9643,13 +9631,13 @@
         <v>58</v>
       </c>
       <c r="D247" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E247" s="7" t="s">
         <v>162</v>
       </c>
       <c r="F247" s="7" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G247" s="7" t="s">
         <v>140</v>
@@ -9667,22 +9655,22 @@
     <row r="248" spans="1:10" ht="15">
       <c r="A248" s="22"/>
       <c r="B248" s="14" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C248" s="7" t="s">
         <v>58</v>
       </c>
       <c r="D248" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E248" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="F248" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G248" s="7" t="s">
         <v>385</v>
-      </c>
-      <c r="F248" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="G248" s="7" t="s">
-        <v>387</v>
       </c>
       <c r="H248" s="1" t="s">
         <v>3</v>
@@ -9703,16 +9691,16 @@
         <v>58</v>
       </c>
       <c r="D249" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E249" s="7" t="s">
         <v>227</v>
       </c>
       <c r="F249" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G249" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H249" s="17" t="s">
         <v>3</v>
@@ -9733,16 +9721,16 @@
         <v>58</v>
       </c>
       <c r="D250" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E250" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F250" s="7" t="s">
         <v>61</v>
       </c>
       <c r="G250" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H250" s="1" t="s">
         <v>3</v>
@@ -9763,16 +9751,16 @@
         <v>58</v>
       </c>
       <c r="D251" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E251" s="7" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F251" s="7" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G251" s="7" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H251" s="1" t="s">
         <v>3</v>
@@ -9786,7 +9774,7 @@
     </row>
     <row r="252" spans="1:10" ht="93.75" customHeight="1">
       <c r="A252" s="22" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B252" s="14" t="s">
         <v>106</v>
@@ -9795,7 +9783,7 @@
         <v>58</v>
       </c>
       <c r="D252" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E252" s="7" t="s">
         <v>225</v>
@@ -9817,9 +9805,7 @@
       </c>
     </row>
     <row r="253" spans="1:10" ht="129.75" customHeight="1">
-      <c r="A253" s="22" t="s">
-        <v>399</v>
-      </c>
+      <c r="A253" s="22"/>
       <c r="B253" s="14" t="s">
         <v>106</v>
       </c>
@@ -9827,16 +9813,16 @@
         <v>58</v>
       </c>
       <c r="D253" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E253" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F253" s="7" t="s">
         <v>61</v>
       </c>
       <c r="G253" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H253" s="1" t="s">
         <v>3</v>
@@ -9857,16 +9843,16 @@
         <v>58</v>
       </c>
       <c r="D254" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E254" s="7" t="s">
         <v>228</v>
       </c>
       <c r="F254" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G254" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H254" s="1" t="s">
         <v>3</v>
@@ -9887,16 +9873,16 @@
         <v>58</v>
       </c>
       <c r="D255" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E255" s="7" t="s">
         <v>229</v>
       </c>
       <c r="F255" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G255" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H255" s="1" t="s">
         <v>3</v>
@@ -9917,7 +9903,7 @@
         <v>58</v>
       </c>
       <c r="D256" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E256" s="7" t="s">
         <v>222</v>
@@ -9947,7 +9933,7 @@
         <v>58</v>
       </c>
       <c r="D257" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E257" s="7" t="s">
         <v>223</v>
@@ -9979,7 +9965,7 @@
         <v>58</v>
       </c>
       <c r="D258" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E258" s="7" t="s">
         <v>224</v>
@@ -10009,7 +9995,7 @@
         <v>58</v>
       </c>
       <c r="D259" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E259" s="7" t="s">
         <v>118</v>
@@ -10018,7 +10004,7 @@
         <v>119</v>
       </c>
       <c r="G259" s="7" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H259" s="1" t="s">
         <v>3</v>
@@ -10032,7 +10018,7 @@
     </row>
     <row r="260" spans="1:10" ht="15">
       <c r="A260" s="22" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B260" s="14" t="s">
         <v>106</v>
@@ -10041,7 +10027,7 @@
         <v>58</v>
       </c>
       <c r="D260" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E260" s="7" t="s">
         <v>225</v>
@@ -10071,7 +10057,7 @@
         <v>58</v>
       </c>
       <c r="D261" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E261" s="7" t="s">
         <v>133</v>
@@ -10101,7 +10087,7 @@
         <v>58</v>
       </c>
       <c r="D262" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E262" s="7" t="s">
         <v>124</v>
@@ -10110,7 +10096,7 @@
         <v>125</v>
       </c>
       <c r="G262" s="7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H262" s="17" t="s">
         <v>3</v>
@@ -10131,7 +10117,7 @@
         <v>58</v>
       </c>
       <c r="D263" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E263" s="7" t="s">
         <v>131</v>
@@ -10140,7 +10126,7 @@
         <v>125</v>
       </c>
       <c r="G263" s="7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H263" s="17" t="s">
         <v>3</v>
@@ -10154,7 +10140,7 @@
     </row>
     <row r="264" spans="1:10" ht="15">
       <c r="A264" s="22" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B264" s="14" t="s">
         <v>106</v>
@@ -10163,7 +10149,7 @@
         <v>58</v>
       </c>
       <c r="D264" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E264" s="7" t="s">
         <v>222</v>
@@ -10186,7 +10172,7 @@
     </row>
     <row r="265" spans="1:10" ht="15">
       <c r="A265" s="22" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B265" s="14" t="s">
         <v>143</v>
@@ -10195,7 +10181,7 @@
         <v>58</v>
       </c>
       <c r="D265" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E265" s="7" t="s">
         <v>224</v>
@@ -10225,7 +10211,7 @@
         <v>58</v>
       </c>
       <c r="D266" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E266" s="7" t="s">
         <v>118</v>
@@ -10234,7 +10220,7 @@
         <v>147</v>
       </c>
       <c r="G266" s="7" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="H266" s="17" t="s">
         <v>3</v>
@@ -10248,7 +10234,7 @@
     </row>
     <row r="267" spans="1:10" ht="15">
       <c r="A267" s="22" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B267" s="14" t="s">
         <v>106</v>
@@ -10257,7 +10243,7 @@
         <v>58</v>
       </c>
       <c r="D267" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E267" s="7" t="s">
         <v>225</v>
@@ -10287,7 +10273,7 @@
         <v>58</v>
       </c>
       <c r="D268" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E268" s="7" t="s">
         <v>133</v>
@@ -10317,7 +10303,7 @@
         <v>58</v>
       </c>
       <c r="D269" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E269" s="7" t="s">
         <v>138</v>
@@ -10347,13 +10333,13 @@
         <v>58</v>
       </c>
       <c r="D270" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="E270" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="E270" s="7" t="s">
-        <v>382</v>
-      </c>
       <c r="F270" s="7" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G270" s="7" t="s">
         <v>221</v>
@@ -10377,7 +10363,7 @@
         <v>58</v>
       </c>
       <c r="D271" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E271" s="7" t="s">
         <v>144</v>
@@ -10407,7 +10393,7 @@
         <v>58</v>
       </c>
       <c r="D272" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E272" s="7" t="s">
         <v>156</v>
@@ -10430,7 +10416,7 @@
     </row>
     <row r="273" spans="1:10" ht="15">
       <c r="A273" s="22" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B273" s="14" t="s">
         <v>106</v>
@@ -10439,7 +10425,7 @@
         <v>58</v>
       </c>
       <c r="D273" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E273" s="7" t="s">
         <v>222</v>
@@ -10469,7 +10455,7 @@
         <v>58</v>
       </c>
       <c r="D274" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E274" s="7" t="s">
         <v>162</v>
@@ -10499,7 +10485,7 @@
         <v>58</v>
       </c>
       <c r="D275" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E275" s="7" t="s">
         <v>156</v>
@@ -10529,13 +10515,13 @@
         <v>58</v>
       </c>
       <c r="D276" s="15" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E276" s="7" t="s">
         <v>162</v>
       </c>
       <c r="F276" s="7" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G276" s="7" t="s">
         <v>140</v>
@@ -10553,22 +10539,22 @@
     <row r="277" spans="1:10" ht="15">
       <c r="A277" s="22"/>
       <c r="B277" s="14" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C277" s="7" t="s">
         <v>58</v>
       </c>
       <c r="D277" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E277" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="F277" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G277" s="7" t="s">
         <v>385</v>
-      </c>
-      <c r="F277" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="G277" s="7" t="s">
-        <v>387</v>
       </c>
       <c r="H277" s="1" t="s">
         <v>3</v>
@@ -10589,16 +10575,16 @@
         <v>58</v>
       </c>
       <c r="D278" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E278" s="7" t="s">
         <v>227</v>
       </c>
       <c r="F278" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G278" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H278" s="1" t="s">
         <v>3</v>
@@ -10619,16 +10605,16 @@
         <v>58</v>
       </c>
       <c r="D279" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E279" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F279" s="7" t="s">
         <v>61</v>
       </c>
       <c r="G279" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H279" s="1" t="s">
         <v>3</v>
@@ -10649,16 +10635,16 @@
         <v>58</v>
       </c>
       <c r="D280" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E280" s="7" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F280" s="7" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G280" s="7" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H280" s="1" t="s">
         <v>3</v>
@@ -10672,7 +10658,7 @@
     </row>
     <row r="281" spans="1:10" ht="15">
       <c r="A281" s="22" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B281" s="14" t="s">
         <v>106</v>
@@ -10681,7 +10667,7 @@
         <v>58</v>
       </c>
       <c r="D281" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E281" s="7" t="s">
         <v>225</v>
@@ -10711,16 +10697,16 @@
         <v>58</v>
       </c>
       <c r="D282" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E282" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F282" s="7" t="s">
         <v>61</v>
       </c>
       <c r="G282" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H282" s="1" t="s">
         <v>3</v>
@@ -10741,16 +10727,16 @@
         <v>58</v>
       </c>
       <c r="D283" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E283" s="7" t="s">
         <v>228</v>
       </c>
       <c r="F283" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G283" s="7" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H283" s="1" t="s">
         <v>3</v>
@@ -10771,16 +10757,16 @@
         <v>58</v>
       </c>
       <c r="D284" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E284" s="7" t="s">
         <v>229</v>
       </c>
       <c r="F284" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G284" s="7" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H284" s="1" t="s">
         <v>3</v>
@@ -10806,13 +10792,13 @@
         <v>9994</v>
       </c>
       <c r="E285" s="7" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F285" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G285" s="7" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H285" s="1" t="s">
         <v>3</v>
@@ -10838,13 +10824,13 @@
         <v>10002</v>
       </c>
       <c r="E286" s="7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F286" s="7" t="s">
         <v>186</v>
       </c>
       <c r="G286" s="7" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H286" s="1" t="s">
         <v>3</v>
